--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Pirate Rat</t>
+          <t>Pirat</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -46926,7 +46926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -46986,682 +46986,719 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>찍!찍!!찍!!!</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Squeak! Squeak!! Squeak!!!</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>게임 제목 (사용자 2026-10-13)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>찍 / 찍찍 / 찍?!</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Squeak / Squeak squeak / Squeak?!</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>쥐 소리. 짧은 소리는 Eep · Squee 도 섞어 말맛 살림</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>찍찍!! (무리 힘 수치)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>SQUEAK!!</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>HUD 'SQUEAK!! 1,234 / Rec. 2,000'. 적정 찍찍 = Rec. SQUEAK!!</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>적정</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Rec.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>recommended 줄임</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>훈장</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>훈장 승급/달기 = Rank Up · n훈장 = Rank n · 찍찍!! 훈장(탭) = SQUEAK!! Rank</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>조각</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Shard</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>조각 ×3 = Shard ×3</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>연구자료 / 연구 자료</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>친구 / 친구들!!</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Buddy / Buddies!!</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>쥐들을 부르는 말, 도감 탭 = Buddies!!</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>탈출</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Escape</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>판 하나. 탈출 시도 = escape attempts</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>치즈</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Cheese</t>
         </is>
       </c>
+      <c r="C13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>치즈 창고</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Cheese Vault</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>공용 스킬 트리 화면</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>쳇바퀴 훈련</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Wheel Training</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>조각으로 쥐 레벨 올리기</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>아지트</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Hideout</t>
         </is>
       </c>
+      <c r="C16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>작전 회의 / 탈출 작전 회의</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>War Room / Escape War Room</t>
         </is>
       </c>
+      <c r="C17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>낮잠 침대</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Nap Bed</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>저장·설정</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>필살기</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Ultimate</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>짧은 칸은 ULT</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>특수 능력</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
+      <c r="C20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>특수 액션</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Special Action</t>
         </is>
       </c>
+      <c r="C21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>묘기</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Trick</t>
         </is>
       </c>
+      <c r="C22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>승급</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Promote</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>판 안에서 쥐 등급 올리기</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>번식</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Breeding</t>
         </is>
       </c>
+      <c r="C24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>갉다 / 갉는 힘</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>gnaw / Gnaw Power</t>
         </is>
       </c>
+      <c r="C25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>층</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>n층 = Floor n (좁은 칸은 nF)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>방 / 구역 / 계단</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Room / Zone / Stairs</t>
         </is>
       </c>
+      <c r="C27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>광란</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Frenzy</t>
         </is>
       </c>
+      <c r="C28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>기절</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Stun / Stunned</t>
         </is>
       </c>
+      <c r="C29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>크리티컬</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Crit / Critical!</t>
         </is>
       </c>
+      <c r="C30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>연구소</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>the Lab</t>
         </is>
       </c>
+      <c r="C31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>하수구 / 지하 하수구 / 하수구 뒷골목</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Sewer / the Sewers / Sewer Alley</t>
         </is>
       </c>
+      <c r="C32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>맨홀</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Manhole</t>
         </is>
       </c>
+      <c r="C33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>쥐구멍 암시장</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Rathole Black Market</t>
         </is>
       </c>
+      <c r="C34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>브로커</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
+      <c r="C35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>유전자 추출기</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Gene Extractor</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>뽑기 화면</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>비밀 실험실</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Secret Lab</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>뽑기 건물</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>뽑기 / 10회 뽑기</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Pull / 10x Pull</t>
         </is>
       </c>
+      <c r="C38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>천장</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Pity</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>신화 천장 = Mythic Pity</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>관심 (관심 종)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Wish</t>
         </is>
       </c>
+      <c r="C40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>일반 · 레어 · 에픽 · 유니크 · 전설 · 신화</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Common · Rare · Epic · Unique · Legendary · Mythic</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>등급</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>맘스땃쥐</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>McSqueak's</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>버거 체인 패러디 (사용자)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>쥐4</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Rat Jerky</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>쥐포 말장난 (사용자)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>줴리</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Jerreh</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>제리 짝퉁. '감사합니다' = 'Thank you very much.' (사용자)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>흐에~ 스트리머 쥐 / 쥐커드</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Heheh~ Streamer Rat / the Squeak Shuffle</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>영어권 방송 밈으로 (POG · KEKW 같은 채팅 말투) (사용자)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>해적 쥐</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Pirat</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>사용자 2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>근육 쥐</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Mouscle</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>사용자 2026-10-13</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>5G (쥐 이름)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Mi-Fi</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>사용자 2026-10-13. 설명의 "5G 속도" 는 그대로</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>총공격 (클릭 집결)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Rally</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>자리표시 {n} {name} …</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>중괄호 자리표시 · &lt;color&gt; &lt;size&gt; 태그 · 줄바꿈 · 대화 구분 | 는 바꾸지 말 것</t>
         </is>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -39511,12 +39511,12 @@
       </c>
       <c r="B1775" s="2" t="inlineStr">
         <is>
-          <t>끌어서 둘러보기 · 휠로 확대 · 찍으면 옆 노드가 드러나요</t>
+          <t>스킬을 찍으면 이어진 칸이 드러나요</t>
         </is>
       </c>
       <c r="C1775" s="2" t="inlineStr">
         <is>
-          <t>Drag to look around · Wheel to zoom · Unlocking reveals neighboring nodes</t>
+          <t>Unlock a skill to reveal the connected nodes</t>
         </is>
       </c>
       <c r="D1775" s="1" t="inlineStr">
@@ -46986,719 +46986,699 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>찍!찍!!찍!!!</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Squeak! Squeak!! Squeak!!!</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>게임 제목 (사용자 2026-10-13)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>찍 / 찍찍 / 찍?!</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Squeak / Squeak squeak / Squeak?!</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>쥐 소리. 짧은 소리는 Eep · Squee 도 섞어 말맛 살림</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>찍찍!! (무리 힘 수치)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>SQUEAK!!</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>HUD 'SQUEAK!! 1,234 / Rec. 2,000'. 적정 찍찍 = Rec. SQUEAK!!</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>적정</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Rec.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>recommended 줄임</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>훈장</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>훈장 승급/달기 = Rank Up · n훈장 = Rank n · 찍찍!! 훈장(탭) = SQUEAK!! Rank</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>조각</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Shard</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>조각 ×3 = Shard ×3</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>연구자료 / 연구 자료</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>친구 / 친구들!!</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Buddy / Buddies!!</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>쥐들을 부르는 말, 도감 탭 = Buddies!!</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>탈출</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Escape</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>판 하나. 탈출 시도 = escape attempts</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>치즈</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Cheese</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>치즈 창고</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Cheese Vault</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>공용 스킬 트리 화면</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>쳇바퀴 훈련</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Wheel Training</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>조각으로 쥐 레벨 올리기</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>아지트</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Hideout</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>작전 회의 / 탈출 작전 회의</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>War Room / Escape War Room</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>낮잠 침대</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Nap Bed</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>저장·설정</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>필살기</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Ultimate</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>짧은 칸은 ULT</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>특수 능력</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>특수 액션</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Special Action</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>묘기</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Trick</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>승급</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Promote</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>판 안에서 쥐 등급 올리기</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>번식</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Breeding</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>갉다 / 갉는 힘</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>gnaw / Gnaw Power</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>층</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>n층 = Floor n (좁은 칸은 nF)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>방 / 구역 / 계단</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Room / Zone / Stairs</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>광란</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Frenzy</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>기절</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Stun / Stunned</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>크리티컬</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Crit / Critical!</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>연구소</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>the Lab</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>하수구 / 지하 하수구 / 하수구 뒷골목</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Sewer / the Sewers / Sewer Alley</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>맨홀</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Manhole</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>쥐구멍 암시장</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Rathole Black Market</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>브로커</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>유전자 추출기</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Gene Extractor</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>뽑기 화면</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>비밀 실험실</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Secret Lab</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>뽑기 건물</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>뽑기 / 10회 뽑기</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Pull / 10x Pull</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>천장</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Pity</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>신화 천장 = Mythic Pity</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>관심 (관심 종)</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Wish</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>일반 · 레어 · 에픽 · 유니크 · 전설 · 신화</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Common · Rare · Epic · Unique · Legendary · Mythic</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>등급</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>맘스땃쥐</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>McSqueak's</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>버거 체인 패러디 (사용자)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>쥐4</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Rat Jerky</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>쥐포 말장난 (사용자)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>줴리</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Jerreh</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>제리 짝퉁. '감사합니다' = 'Thank you very much.' (사용자)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>흐에~ 스트리머 쥐 / 쥐커드</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Heheh~ Streamer Rat / the Squeak Shuffle</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>영어권 방송 밈으로 (POG · KEKW 같은 채팅 말투) (사용자)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>해적 쥐</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Pirat</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>사용자 2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>근육 쥐</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Mouscle</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>사용자 2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>5G (쥐 이름)</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Mi-Fi</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>사용자 2026-10-13. 설명의 "5G 속도" 는 그대로</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>총공격 (클릭 집결)</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Rally</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>자리표시 {n} {name} …</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>중괄호 자리표시 · &lt;color&gt; &lt;size&gt; 태그 · 줄바꿈 · 대화 구분 | 는 바꾸지 말 것</t>
         </is>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2109"/>
+  <dimension ref="A1:F2134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -35283,7 +35283,7 @@
       </c>
       <c r="D1583" s="1" t="inlineStr">
         <is>
-          <t>씬 · Title · UI/Confirm/Card/False/Text</t>
+          <t>씬 · Title · UI/Confirm/Card/False/Text | Lobby · UI/NickPopup/Window/Card/CancelButton/Label</t>
         </is>
       </c>
       <c r="E1583" s="1" t="n"/>
@@ -36235,7 +36235,7 @@
       </c>
       <c r="D1626" s="1" t="inlineStr">
         <is>
-          <t>씬 · Lobby · UI/Prep/Body/Page_run/CrewCard/Stats/Stat_최고 기록/Value</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_run/CrewCard/Stats/Stat_최고 기록/Value | Lobby · UI/Prep/Body/Page_lb/Card/Scroll/Viewport/Content/RowTemplate/Floor | Lobby · UI/Prep/Body/Page_lb/Card/MyRow/Floor</t>
         </is>
       </c>
       <c r="E1626" s="1" t="n"/>
@@ -36919,7 +36919,7 @@
       </c>
       <c r="D1657" s="1" t="inlineStr">
         <is>
-          <t>씬 · Lobby · Alley/AlleyRats · LobbyHome.pokeLines[0] | Lobby · Home · LobbyHome.pokeLines[0] | Lobby · Home/Fx/BubbleTemplate/Text | Lobby · Alley/BrokerBubble/Text 외 1곳</t>
+          <t>씬 · Lobby · Alley/AlleyRats · LobbyHome.pokeLines[0] | Lobby · Home · LobbyHome.pokeLines[0] | Lobby · Alley/BrokerBubble/Text | Game · ItemManager · ItemManager.smashWords[0]</t>
         </is>
       </c>
       <c r="E1657" s="1" t="n"/>
@@ -38703,7 +38703,7 @@
       </c>
       <c r="D1738" s="1" t="inlineStr">
         <is>
-          <t>씬 · Lobby · UI/GachaShow/Root/Ok/Label</t>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/OkButton/Label | Lobby · UI/GachaShow/Root/Ok/Label</t>
         </is>
       </c>
       <c r="E1738" s="1" t="n"/>
@@ -44035,21 +44035,21 @@
     </row>
     <row r="1979">
       <c r="A1979" s="1" t="n">
-        <v>9000001</v>
+        <v>8000405</v>
       </c>
       <c r="B1979" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power} / 적정 {need}</t>
+          <t>최고 층</t>
         </is>
       </c>
       <c r="C1979" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power} / Rec. {need}</t>
+          <t>Best Floor</t>
         </is>
       </c>
       <c r="D1979" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Header/Floor</t>
         </is>
       </c>
       <c r="E1979" s="1" t="n"/>
@@ -44057,21 +44057,21 @@
     </row>
     <row r="1980">
       <c r="A1980" s="1" t="n">
-        <v>9000002</v>
+        <v>8000406</v>
       </c>
       <c r="B1980" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>닉네임 바꾸기</t>
         </is>
       </c>
       <c r="C1980" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>Change Nickname</t>
         </is>
       </c>
       <c r="D1980" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/NickButton/Label</t>
         </is>
       </c>
       <c r="E1980" s="1" t="n"/>
@@ -44079,21 +44079,21 @@
     </row>
     <row r="1981">
       <c r="A1981" s="1" t="n">
-        <v>9000003</v>
+        <v>8000407</v>
       </c>
       <c r="B1981" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>바꾸기</t>
         </is>
       </c>
       <c r="C1981" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>Change</t>
         </is>
       </c>
       <c r="D1981" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_rec/Card/ServerRows/Row_닉네임/NickButton/Label</t>
         </is>
       </c>
       <c r="E1981" s="1" t="n"/>
@@ -44101,21 +44101,21 @@
     </row>
     <row r="1982">
       <c r="A1982" s="1" t="n">
-        <v>9000004</v>
+        <v>8000408</v>
       </c>
       <c r="B1982" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>닉네임 입력</t>
         </is>
       </c>
       <c r="C1982" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>Enter nickname</t>
         </is>
       </c>
       <c r="D1982" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/Input/Text Area/Placeholder</t>
         </is>
       </c>
       <c r="E1982" s="1" t="n"/>
@@ -44123,21 +44123,21 @@
     </row>
     <row r="1983">
       <c r="A1983" s="1" t="n">
-        <v>9000005</v>
+        <v>8000409</v>
       </c>
       <c r="B1983" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>순위</t>
         </is>
       </c>
       <c r="C1983" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>#</t>
         </is>
       </c>
       <c r="D1983" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Header/Rank</t>
         </is>
       </c>
       <c r="E1983" s="1" t="n"/>
@@ -44145,21 +44145,21 @@
     </row>
     <row r="1984">
       <c r="A1984" s="1" t="n">
-        <v>9000006</v>
+        <v>8000410</v>
       </c>
       <c r="B1984" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>닉네임 정하기</t>
         </is>
       </c>
       <c r="C1984" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>Choose a Nickname</t>
         </is>
       </c>
       <c r="D1984" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/Title</t>
         </is>
       </c>
       <c r="E1984" s="1" t="n"/>
@@ -44167,21 +44167,21 @@
     </row>
     <row r="1985">
       <c r="A1985" s="1" t="n">
-        <v>9000007</v>
+        <v>8000411</v>
       </c>
       <c r="B1985" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>아직 랭킹에 오른 쥐가 없어요. 첫 번째가 되어 보세요!</t>
         </is>
       </c>
       <c r="C1985" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>No rats on the board yet. Be the first!</t>
         </is>
       </c>
       <c r="D1985" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Scroll/Empty</t>
         </is>
       </c>
       <c r="E1985" s="1" t="n"/>
@@ -44189,21 +44189,21 @@
     </row>
     <row r="1986">
       <c r="A1986" s="1" t="n">
-        <v>9000008</v>
+        <v>8000412</v>
       </c>
       <c r="B1986" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>훈장</t>
         </is>
       </c>
       <c r="C1986" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Rank</t>
         </is>
       </c>
       <c r="D1986" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Header/Tier</t>
         </is>
       </c>
       <c r="E1986" s="1" t="n"/>
@@ -44211,21 +44211,21 @@
     </row>
     <row r="1987">
       <c r="A1987" s="1" t="n">
-        <v>9000009</v>
+        <v>8000413</v>
       </c>
       <c r="B1987" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>아직 없음</t>
         </is>
       </c>
       <c r="C1987" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>Not set</t>
         </is>
       </c>
       <c r="D1987" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_rec/Card/ServerRows/Row_닉네임/NoNick</t>
         </is>
       </c>
       <c r="E1987" s="1" t="n"/>
@@ -44233,21 +44233,21 @@
     </row>
     <row r="1988">
       <c r="A1988" s="1" t="n">
-        <v>9000010</v>
+        <v>8000414</v>
       </c>
       <c r="B1988" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>시도</t>
         </is>
       </c>
       <c r="C1988" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="D1988" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Header/Runs</t>
         </is>
       </c>
       <c r="E1988" s="1" t="n"/>
@@ -44255,21 +44255,21 @@
     </row>
     <row r="1989">
       <c r="A1989" s="1" t="n">
-        <v>9000011</v>
+        <v>8000415</v>
       </c>
       <c r="B1989" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>닉네임</t>
         </is>
       </c>
       <c r="C1989" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>Nickname</t>
         </is>
       </c>
       <c r="D1989" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_rec/Card/ServerRows/Row_닉네임/Label | Lobby · UI/Prep/Body/Page_lb/Card/Header/Name</t>
         </is>
       </c>
       <c r="E1989" s="1" t="n"/>
@@ -44277,21 +44277,21 @@
     </row>
     <row r="1990">
       <c r="A1990" s="1" t="n">
-        <v>9000012</v>
+        <v>8000416</v>
       </c>
       <c r="B1990" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>불러오는 중...</t>
         </is>
       </c>
       <c r="C1990" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>Loading...</t>
         </is>
       </c>
       <c r="D1990" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Scroll/Loading</t>
         </is>
       </c>
       <c r="E1990" s="1" t="n"/>
@@ -44299,21 +44299,21 @@
     </row>
     <row r="1991">
       <c r="A1991" s="1" t="n">
-        <v>9000013</v>
+        <v>8000417</v>
       </c>
       <c r="B1991" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>랭킹에 보일 이름이에요 (2~12자)</t>
         </is>
       </c>
       <c r="C1991" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>The name shown on the leaderboard (2-12 characters)</t>
         </is>
       </c>
       <c r="D1991" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/Desc</t>
         </is>
       </c>
       <c r="E1991" s="1" t="n"/>
@@ -44321,21 +44321,21 @@
     </row>
     <row r="1992">
       <c r="A1992" s="1" t="n">
-        <v>9000014</v>
+        <v>8000418</v>
       </c>
       <c r="B1992" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>지금은 서버에 연결할 수 없어요</t>
         </is>
       </c>
       <c r="C1992" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>Can't reach the server right now</t>
         </is>
       </c>
       <c r="D1992" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/ErrOffline</t>
         </is>
       </c>
       <c r="E1992" s="1" t="n"/>
@@ -44343,21 +44343,21 @@
     </row>
     <row r="1993">
       <c r="A1993" s="1" t="n">
-        <v>9000015</v>
+        <v>8000419</v>
       </c>
       <c r="B1993" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>새로고침</t>
         </is>
       </c>
       <c r="C1993" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>Refresh</t>
         </is>
       </c>
       <c r="D1993" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/RefreshButton/Label</t>
         </is>
       </c>
       <c r="E1993" s="1" t="n"/>
@@ -44365,21 +44365,21 @@
     </row>
     <row r="1994">
       <c r="A1994" s="1" t="n">
-        <v>9000016</v>
+        <v>8000420</v>
       </c>
       <c r="B1994" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>랭킹</t>
         </is>
       </c>
       <c r="C1994" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="D1994" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>씬 · Lobby · LobbyManager · LobbyManager.pages[8].label | Lobby · UI/Prep/Body/Page_lb/Card/Title | Lobby · UI/Prep/TopBar/Tabs/Tab_lb/Label</t>
         </is>
       </c>
       <c r="E1994" s="1" t="n"/>
@@ -44387,21 +44387,21 @@
     </row>
     <row r="1995">
       <c r="A1995" s="1" t="n">
-        <v>9000017</v>
+        <v>8000421</v>
       </c>
       <c r="B1995" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>랭킹을 불러오지 못했어요. 인터넷 연결을 확인해 주세요.</t>
         </is>
       </c>
       <c r="C1995" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>Couldn't load the leaderboard. Please check your connection.</t>
         </is>
       </c>
       <c r="D1995" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Scroll/Offline</t>
         </is>
       </c>
       <c r="E1995" s="1" t="n"/>
@@ -44409,21 +44409,21 @@
     </row>
     <row r="1996">
       <c r="A1996" s="1" t="n">
-        <v>9000018</v>
+        <v>8000422</v>
       </c>
       <c r="B1996" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>{n}회</t>
         </is>
       </c>
       <c r="C1996" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>{n}</t>
         </is>
       </c>
       <c r="D1996" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/MyRow/Runs | Lobby · UI/Prep/Body/Page_lb/Card/Scroll/Viewport/Content/RowTemplate/Runs</t>
         </is>
       </c>
       <c r="E1996" s="1" t="n"/>
@@ -44431,21 +44431,21 @@
     </row>
     <row r="1997">
       <c r="A1997" s="1" t="n">
-        <v>9000019</v>
+        <v>8000423</v>
       </c>
       <c r="B1997" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>최고 층이 높은 순 · 같은 층이면 더 적은 시도로 닿은 순</t>
         </is>
       </c>
       <c r="C1997" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>Highest floor first · ties go to fewer runs</t>
         </is>
       </c>
       <c r="D1997" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Sub</t>
         </is>
       </c>
       <c r="E1997" s="1" t="n"/>
@@ -44453,21 +44453,21 @@
     </row>
     <row r="1998">
       <c r="A1998" s="1" t="n">
-        <v>9000020</v>
+        <v>8000424</v>
       </c>
       <c r="B1998" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>내 기록</t>
         </is>
       </c>
       <c r="C1998" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>My Record</t>
         </is>
       </c>
       <c r="D1998" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/MyLabel</t>
         </is>
       </c>
       <c r="E1998" s="1" t="n"/>
@@ -44475,21 +44475,21 @@
     </row>
     <row r="1999">
       <c r="A1999" s="1" t="n">
-        <v>9000021</v>
+        <v>8000425</v>
       </c>
       <c r="B1999" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>익명 통계 보내기</t>
         </is>
       </c>
       <c r="C1999" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Send anonymous stats</t>
         </is>
       </c>
       <c r="D1999" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_rec/Card/ServerRows/Row_통계/Label</t>
         </is>
       </c>
       <c r="E1999" s="1" t="n"/>
@@ -44497,21 +44497,21 @@
     </row>
     <row r="2000">
       <c r="A2000" s="1" t="n">
-        <v>9000022</v>
+        <v>8000426</v>
       </c>
       <c r="B2000" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>100위 밖</t>
         </is>
       </c>
       <c r="C2000" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>100+</t>
         </is>
       </c>
       <c r="D2000" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/OutWord</t>
         </is>
       </c>
       <c r="E2000" s="1" t="n"/>
@@ -44519,21 +44519,21 @@
     </row>
     <row r="2001">
       <c r="A2001" s="1" t="n">
-        <v>9000023</v>
+        <v>8000427</v>
       </c>
       <c r="B2001" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>닉네임을 정하면 내 기록이 랭킹에 올라가요</t>
         </is>
       </c>
       <c r="C2001" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>Set a nickname to put your record on the board</t>
         </is>
       </c>
       <c r="D2001" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/NoNick</t>
         </is>
       </c>
       <c r="E2001" s="1" t="n"/>
@@ -44541,21 +44541,21 @@
     </row>
     <row r="2002">
       <c r="A2002" s="1" t="n">
-        <v>9000024</v>
+        <v>8000428</v>
       </c>
       <c r="B2002" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>2~12자로 정해 주세요</t>
         </is>
       </c>
       <c r="C2002" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>Use 2-12 characters</t>
         </is>
       </c>
       <c r="D2002" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/ErrLength</t>
         </is>
       </c>
       <c r="E2002" s="1" t="n"/>
@@ -44563,21 +44563,21 @@
     </row>
     <row r="2003">
       <c r="A2003" s="1" t="n">
-        <v>9000025</v>
+        <v>8000429</v>
       </c>
       <c r="B2003" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>쓸 수 없는 말이 들어 있어요</t>
         </is>
       </c>
       <c r="C2003" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>That name contains a word we can't use</t>
         </is>
       </c>
       <c r="D2003" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/ErrBanned</t>
         </is>
       </c>
       <c r="E2003" s="1" t="n"/>
@@ -44585,21 +44585,21 @@
     </row>
     <row r="2004">
       <c r="A2004" s="1" t="n">
-        <v>9000026</v>
+        <v>9000001</v>
       </c>
       <c r="B2004" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>찍찍!! {power} / 적정 {need}</t>
         </is>
       </c>
       <c r="C2004" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>SQUEAK!! {power} / Rec. {need}</t>
         </is>
       </c>
       <c r="D2004" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E2004" s="1" t="n"/>
@@ -44607,21 +44607,21 @@
     </row>
     <row r="2005">
       <c r="A2005" s="1" t="n">
-        <v>9000027</v>
+        <v>9000002</v>
       </c>
       <c r="B2005" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C2005" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D2005" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2005" s="1" t="n"/>
@@ -44629,21 +44629,21 @@
     </row>
     <row r="2006">
       <c r="A2006" s="1" t="n">
-        <v>9000028</v>
+        <v>9000003</v>
       </c>
       <c r="B2006" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C2006" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D2006" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E2006" s="1" t="n"/>
@@ -44651,21 +44651,21 @@
     </row>
     <row r="2007">
       <c r="A2007" s="1" t="n">
-        <v>9000029</v>
+        <v>9000004</v>
       </c>
       <c r="B2007" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C2007" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D2007" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E2007" s="1" t="n"/>
@@ -44673,21 +44673,21 @@
     </row>
     <row r="2008">
       <c r="A2008" s="1" t="n">
-        <v>9000030</v>
+        <v>9000005</v>
       </c>
       <c r="B2008" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C2008" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D2008" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E2008" s="1" t="n"/>
@@ -44695,21 +44695,21 @@
     </row>
     <row r="2009">
       <c r="A2009" s="1" t="n">
-        <v>9000031</v>
+        <v>9000006</v>
       </c>
       <c r="B2009" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C2009" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D2009" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E2009" s="1" t="n"/>
@@ -44717,21 +44717,21 @@
     </row>
     <row r="2010">
       <c r="A2010" s="1" t="n">
-        <v>9000032</v>
+        <v>9000007</v>
       </c>
       <c r="B2010" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C2010" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D2010" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E2010" s="1" t="n"/>
@@ -44739,21 +44739,21 @@
     </row>
     <row r="2011">
       <c r="A2011" s="1" t="n">
-        <v>9000033</v>
+        <v>9000008</v>
       </c>
       <c r="B2011" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C2011" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D2011" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2011" s="1" t="n"/>
@@ -44761,21 +44761,21 @@
     </row>
     <row r="2012">
       <c r="A2012" s="1" t="n">
-        <v>9000034</v>
+        <v>9000009</v>
       </c>
       <c r="B2012" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C2012" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D2012" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2012" s="1" t="n"/>
@@ -44783,21 +44783,21 @@
     </row>
     <row r="2013">
       <c r="A2013" s="1" t="n">
-        <v>9000035</v>
+        <v>9000010</v>
       </c>
       <c r="B2013" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C2013" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D2013" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2013" s="1" t="n"/>
@@ -44805,21 +44805,21 @@
     </row>
     <row r="2014">
       <c r="A2014" s="1" t="n">
-        <v>9000036</v>
+        <v>9000011</v>
       </c>
       <c r="B2014" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C2014" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D2014" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2014" s="1" t="n"/>
@@ -44827,21 +44827,21 @@
     </row>
     <row r="2015">
       <c r="A2015" s="1" t="n">
-        <v>9000037</v>
+        <v>9000012</v>
       </c>
       <c r="B2015" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C2015" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D2015" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2015" s="1" t="n"/>
@@ -44849,21 +44849,21 @@
     </row>
     <row r="2016">
       <c r="A2016" s="1" t="n">
-        <v>9000038</v>
+        <v>9000013</v>
       </c>
       <c r="B2016" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C2016" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D2016" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2016" s="1" t="n"/>
@@ -44871,21 +44871,21 @@
     </row>
     <row r="2017">
       <c r="A2017" s="1" t="n">
-        <v>9000039</v>
+        <v>9000014</v>
       </c>
       <c r="B2017" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C2017" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D2017" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E2017" s="1" t="n"/>
@@ -44893,21 +44893,21 @@
     </row>
     <row r="2018">
       <c r="A2018" s="1" t="n">
-        <v>9000040</v>
+        <v>9000015</v>
       </c>
       <c r="B2018" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C2018" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D2018" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2018" s="1" t="n"/>
@@ -44915,21 +44915,21 @@
     </row>
     <row r="2019">
       <c r="A2019" s="1" t="n">
-        <v>9000041</v>
+        <v>9000016</v>
       </c>
       <c r="B2019" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C2019" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D2019" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2019" s="1" t="n"/>
@@ -44937,21 +44937,21 @@
     </row>
     <row r="2020">
       <c r="A2020" s="1" t="n">
-        <v>9000042</v>
+        <v>9000017</v>
       </c>
       <c r="B2020" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C2020" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D2020" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E2020" s="1" t="n"/>
@@ -44959,21 +44959,21 @@
     </row>
     <row r="2021">
       <c r="A2021" s="1" t="n">
-        <v>9000043</v>
+        <v>9000018</v>
       </c>
       <c r="B2021" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C2021" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D2021" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2021" s="1" t="n"/>
@@ -44981,21 +44981,21 @@
     </row>
     <row r="2022">
       <c r="A2022" s="1" t="n">
-        <v>9000044</v>
+        <v>9000019</v>
       </c>
       <c r="B2022" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C2022" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D2022" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2022" s="1" t="n"/>
@@ -45003,21 +45003,21 @@
     </row>
     <row r="2023">
       <c r="A2023" s="1" t="n">
-        <v>9000045</v>
+        <v>9000020</v>
       </c>
       <c r="B2023" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C2023" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D2023" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2023" s="1" t="n"/>
@@ -45025,21 +45025,21 @@
     </row>
     <row r="2024">
       <c r="A2024" s="1" t="n">
-        <v>9000046</v>
+        <v>9000021</v>
       </c>
       <c r="B2024" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C2024" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D2024" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E2024" s="1" t="n"/>
@@ -45047,21 +45047,21 @@
     </row>
     <row r="2025">
       <c r="A2025" s="1" t="n">
-        <v>9000047</v>
+        <v>9000022</v>
       </c>
       <c r="B2025" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C2025" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D2025" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2025" s="1" t="n"/>
@@ -45069,21 +45069,21 @@
     </row>
     <row r="2026">
       <c r="A2026" s="1" t="n">
-        <v>9000048</v>
+        <v>9000023</v>
       </c>
       <c r="B2026" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C2026" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D2026" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2026" s="1" t="n"/>
@@ -45091,21 +45091,21 @@
     </row>
     <row r="2027">
       <c r="A2027" s="1" t="n">
-        <v>9000049</v>
+        <v>9000024</v>
       </c>
       <c r="B2027" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C2027" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D2027" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2027" s="1" t="n"/>
@@ -45113,21 +45113,21 @@
     </row>
     <row r="2028">
       <c r="A2028" s="1" t="n">
-        <v>9000050</v>
+        <v>9000025</v>
       </c>
       <c r="B2028" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C2028" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D2028" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2028" s="1" t="n"/>
@@ -45135,21 +45135,21 @@
     </row>
     <row r="2029">
       <c r="A2029" s="1" t="n">
-        <v>9000051</v>
+        <v>9000026</v>
       </c>
       <c r="B2029" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C2029" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D2029" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E2029" s="1" t="n"/>
@@ -45157,21 +45157,21 @@
     </row>
     <row r="2030">
       <c r="A2030" s="1" t="n">
-        <v>9000052</v>
+        <v>9000027</v>
       </c>
       <c r="B2030" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C2030" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D2030" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2030" s="1" t="n"/>
@@ -45179,21 +45179,21 @@
     </row>
     <row r="2031">
       <c r="A2031" s="1" t="n">
-        <v>9000053</v>
+        <v>9000028</v>
       </c>
       <c r="B2031" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C2031" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D2031" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2031" s="1" t="n"/>
@@ -45201,21 +45201,21 @@
     </row>
     <row r="2032">
       <c r="A2032" s="1" t="n">
-        <v>9000054</v>
+        <v>9000029</v>
       </c>
       <c r="B2032" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C2032" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D2032" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2032" s="1" t="n"/>
@@ -45223,21 +45223,21 @@
     </row>
     <row r="2033">
       <c r="A2033" s="1" t="n">
-        <v>9000055</v>
+        <v>9000030</v>
       </c>
       <c r="B2033" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C2033" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D2033" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E2033" s="1" t="n"/>
@@ -45245,21 +45245,21 @@
     </row>
     <row r="2034">
       <c r="A2034" s="1" t="n">
-        <v>9000056</v>
+        <v>9000031</v>
       </c>
       <c r="B2034" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C2034" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D2034" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E2034" s="1" t="n"/>
@@ -45267,21 +45267,21 @@
     </row>
     <row r="2035">
       <c r="A2035" s="1" t="n">
-        <v>9000057</v>
+        <v>9000032</v>
       </c>
       <c r="B2035" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C2035" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D2035" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2035" s="1" t="n"/>
@@ -45289,21 +45289,21 @@
     </row>
     <row r="2036">
       <c r="A2036" s="1" t="n">
-        <v>9000058</v>
+        <v>9000033</v>
       </c>
       <c r="B2036" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C2036" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D2036" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2036" s="1" t="n"/>
@@ -45311,21 +45311,21 @@
     </row>
     <row r="2037">
       <c r="A2037" s="1" t="n">
-        <v>9000059</v>
+        <v>9000034</v>
       </c>
       <c r="B2037" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C2037" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D2037" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2037" s="1" t="n"/>
@@ -45333,21 +45333,21 @@
     </row>
     <row r="2038">
       <c r="A2038" s="1" t="n">
-        <v>9000060</v>
+        <v>9000035</v>
       </c>
       <c r="B2038" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C2038" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D2038" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E2038" s="1" t="n"/>
@@ -45355,21 +45355,21 @@
     </row>
     <row r="2039">
       <c r="A2039" s="1" t="n">
-        <v>9000061</v>
+        <v>9000036</v>
       </c>
       <c r="B2039" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C2039" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D2039" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E2039" s="1" t="n"/>
@@ -45377,21 +45377,21 @@
     </row>
     <row r="2040">
       <c r="A2040" s="1" t="n">
-        <v>9000062</v>
+        <v>9000037</v>
       </c>
       <c r="B2040" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C2040" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D2040" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E2040" s="1" t="n"/>
@@ -45399,21 +45399,21 @@
     </row>
     <row r="2041">
       <c r="A2041" s="1" t="n">
-        <v>9000063</v>
+        <v>9000038</v>
       </c>
       <c r="B2041" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C2041" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D2041" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E2041" s="1" t="n"/>
@@ -45421,21 +45421,21 @@
     </row>
     <row r="2042">
       <c r="A2042" s="1" t="n">
-        <v>9000064</v>
+        <v>9000039</v>
       </c>
       <c r="B2042" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C2042" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D2042" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E2042" s="1" t="n"/>
@@ -45443,21 +45443,21 @@
     </row>
     <row r="2043">
       <c r="A2043" s="1" t="n">
-        <v>9000065</v>
+        <v>9000040</v>
       </c>
       <c r="B2043" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C2043" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D2043" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E2043" s="1" t="n"/>
@@ -45465,21 +45465,21 @@
     </row>
     <row r="2044">
       <c r="A2044" s="1" t="n">
-        <v>9000066</v>
+        <v>9000041</v>
       </c>
       <c r="B2044" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C2044" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D2044" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2044" s="1" t="n"/>
@@ -45487,21 +45487,21 @@
     </row>
     <row r="2045">
       <c r="A2045" s="1" t="n">
-        <v>9000067</v>
+        <v>9000042</v>
       </c>
       <c r="B2045" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C2045" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D2045" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2045" s="1" t="n"/>
@@ -45509,21 +45509,21 @@
     </row>
     <row r="2046">
       <c r="A2046" s="1" t="n">
-        <v>9000068</v>
+        <v>9000043</v>
       </c>
       <c r="B2046" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C2046" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D2046" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2046" s="1" t="n"/>
@@ -45531,21 +45531,21 @@
     </row>
     <row r="2047">
       <c r="A2047" s="1" t="n">
-        <v>9000069</v>
+        <v>9000044</v>
       </c>
       <c r="B2047" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C2047" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D2047" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2047" s="1" t="n"/>
@@ -45553,21 +45553,21 @@
     </row>
     <row r="2048">
       <c r="A2048" s="1" t="n">
-        <v>9000070</v>
+        <v>9000045</v>
       </c>
       <c r="B2048" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C2048" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D2048" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2048" s="1" t="n"/>
@@ -45575,21 +45575,21 @@
     </row>
     <row r="2049">
       <c r="A2049" s="1" t="n">
-        <v>9000071</v>
+        <v>9000046</v>
       </c>
       <c r="B2049" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C2049" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D2049" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2049" s="1" t="n"/>
@@ -45597,21 +45597,21 @@
     </row>
     <row r="2050">
       <c r="A2050" s="1" t="n">
-        <v>9000072</v>
+        <v>9000047</v>
       </c>
       <c r="B2050" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C2050" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D2050" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2050" s="1" t="n"/>
@@ -45619,21 +45619,21 @@
     </row>
     <row r="2051">
       <c r="A2051" s="1" t="n">
-        <v>9000073</v>
+        <v>9000048</v>
       </c>
       <c r="B2051" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C2051" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D2051" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2051" s="1" t="n"/>
@@ -45641,21 +45641,21 @@
     </row>
     <row r="2052">
       <c r="A2052" s="1" t="n">
-        <v>9000074</v>
+        <v>9000049</v>
       </c>
       <c r="B2052" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C2052" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D2052" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E2052" s="1" t="n"/>
@@ -45663,21 +45663,21 @@
     </row>
     <row r="2053">
       <c r="A2053" s="1" t="n">
-        <v>9000075</v>
+        <v>9000050</v>
       </c>
       <c r="B2053" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C2053" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D2053" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E2053" s="1" t="n"/>
@@ -45685,21 +45685,21 @@
     </row>
     <row r="2054">
       <c r="A2054" s="1" t="n">
-        <v>9000076</v>
+        <v>9000051</v>
       </c>
       <c r="B2054" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C2054" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D2054" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2054" s="1" t="n"/>
@@ -45707,21 +45707,21 @@
     </row>
     <row r="2055">
       <c r="A2055" s="1" t="n">
-        <v>9000077</v>
+        <v>9000052</v>
       </c>
       <c r="B2055" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C2055" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D2055" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2055" s="1" t="n"/>
@@ -45729,21 +45729,21 @@
     </row>
     <row r="2056">
       <c r="A2056" s="1" t="n">
-        <v>9000078</v>
+        <v>9000053</v>
       </c>
       <c r="B2056" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C2056" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D2056" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E2056" s="1" t="n"/>
@@ -45751,21 +45751,21 @@
     </row>
     <row r="2057">
       <c r="A2057" s="1" t="n">
-        <v>9000079</v>
+        <v>9000054</v>
       </c>
       <c r="B2057" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C2057" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D2057" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2057" s="1" t="n"/>
@@ -45773,21 +45773,21 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>9000080</v>
+        <v>9000055</v>
       </c>
       <c r="B2058" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C2058" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D2058" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2058" s="1" t="n"/>
@@ -45795,21 +45795,21 @@
     </row>
     <row r="2059">
       <c r="A2059" s="1" t="n">
-        <v>9000081</v>
+        <v>9000056</v>
       </c>
       <c r="B2059" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C2059" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D2059" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2059" s="1" t="n"/>
@@ -45817,21 +45817,21 @@
     </row>
     <row r="2060">
       <c r="A2060" s="1" t="n">
-        <v>9000082</v>
+        <v>9000057</v>
       </c>
       <c r="B2060" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C2060" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D2060" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2060" s="1" t="n"/>
@@ -45839,21 +45839,21 @@
     </row>
     <row r="2061">
       <c r="A2061" s="1" t="n">
-        <v>9000083</v>
+        <v>9000058</v>
       </c>
       <c r="B2061" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C2061" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D2061" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2061" s="1" t="n"/>
@@ -45861,21 +45861,21 @@
     </row>
     <row r="2062">
       <c r="A2062" s="1" t="n">
-        <v>9000084</v>
+        <v>9000059</v>
       </c>
       <c r="B2062" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C2062" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D2062" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2062" s="1" t="n"/>
@@ -45883,21 +45883,21 @@
     </row>
     <row r="2063">
       <c r="A2063" s="1" t="n">
-        <v>9000085</v>
+        <v>9000060</v>
       </c>
       <c r="B2063" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C2063" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D2063" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2063" s="1" t="n"/>
@@ -45905,21 +45905,21 @@
     </row>
     <row r="2064">
       <c r="A2064" s="1" t="n">
-        <v>9000086</v>
+        <v>9000061</v>
       </c>
       <c r="B2064" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C2064" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D2064" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2064" s="1" t="n"/>
@@ -45927,21 +45927,21 @@
     </row>
     <row r="2065">
       <c r="A2065" s="1" t="n">
-        <v>9000087</v>
+        <v>9000062</v>
       </c>
       <c r="B2065" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C2065" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D2065" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2065" s="1" t="n"/>
@@ -45949,21 +45949,21 @@
     </row>
     <row r="2066">
       <c r="A2066" s="1" t="n">
-        <v>9000088</v>
+        <v>9000063</v>
       </c>
       <c r="B2066" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C2066" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D2066" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2066" s="1" t="n"/>
@@ -45971,21 +45971,21 @@
     </row>
     <row r="2067">
       <c r="A2067" s="1" t="n">
-        <v>9000089</v>
+        <v>9000064</v>
       </c>
       <c r="B2067" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C2067" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D2067" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2067" s="1" t="n"/>
@@ -45993,21 +45993,21 @@
     </row>
     <row r="2068">
       <c r="A2068" s="1" t="n">
-        <v>9000090</v>
+        <v>9000065</v>
       </c>
       <c r="B2068" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C2068" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D2068" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2068" s="1" t="n"/>
@@ -46015,21 +46015,21 @@
     </row>
     <row r="2069">
       <c r="A2069" s="1" t="n">
-        <v>9000091</v>
+        <v>9000066</v>
       </c>
       <c r="B2069" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C2069" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D2069" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2069" s="1" t="n"/>
@@ -46037,21 +46037,21 @@
     </row>
     <row r="2070">
       <c r="A2070" s="1" t="n">
-        <v>9000092</v>
+        <v>9000067</v>
       </c>
       <c r="B2070" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C2070" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D2070" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2070" s="1" t="n"/>
@@ -46059,21 +46059,21 @@
     </row>
     <row r="2071">
       <c r="A2071" s="1" t="n">
-        <v>9000093</v>
+        <v>9000068</v>
       </c>
       <c r="B2071" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C2071" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D2071" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2071" s="1" t="n"/>
@@ -46081,21 +46081,21 @@
     </row>
     <row r="2072">
       <c r="A2072" s="1" t="n">
-        <v>9000094</v>
+        <v>9000069</v>
       </c>
       <c r="B2072" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C2072" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D2072" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2072" s="1" t="n"/>
@@ -46103,21 +46103,21 @@
     </row>
     <row r="2073">
       <c r="A2073" s="1" t="n">
-        <v>9000095</v>
+        <v>9000070</v>
       </c>
       <c r="B2073" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C2073" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D2073" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2073" s="1" t="n"/>
@@ -46125,21 +46125,21 @@
     </row>
     <row r="2074">
       <c r="A2074" s="1" t="n">
-        <v>9000096</v>
+        <v>9000071</v>
       </c>
       <c r="B2074" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C2074" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D2074" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2074" s="1" t="n"/>
@@ -46147,21 +46147,21 @@
     </row>
     <row r="2075">
       <c r="A2075" s="1" t="n">
-        <v>9000097</v>
+        <v>9000072</v>
       </c>
       <c r="B2075" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C2075" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D2075" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2075" s="1" t="n"/>
@@ -46169,21 +46169,21 @@
     </row>
     <row r="2076">
       <c r="A2076" s="1" t="n">
-        <v>9000098</v>
+        <v>9000073</v>
       </c>
       <c r="B2076" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C2076" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D2076" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2076" s="1" t="n"/>
@@ -46191,21 +46191,21 @@
     </row>
     <row r="2077">
       <c r="A2077" s="1" t="n">
-        <v>9000099</v>
+        <v>9000074</v>
       </c>
       <c r="B2077" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C2077" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D2077" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2077" s="1" t="n"/>
@@ -46213,21 +46213,21 @@
     </row>
     <row r="2078">
       <c r="A2078" s="1" t="n">
-        <v>9000100</v>
+        <v>9000075</v>
       </c>
       <c r="B2078" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C2078" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D2078" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2078" s="1" t="n"/>
@@ -46235,21 +46235,21 @@
     </row>
     <row r="2079">
       <c r="A2079" s="1" t="n">
-        <v>9000101</v>
+        <v>9000076</v>
       </c>
       <c r="B2079" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C2079" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D2079" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2079" s="1" t="n"/>
@@ -46257,21 +46257,21 @@
     </row>
     <row r="2080">
       <c r="A2080" s="1" t="n">
-        <v>9000102</v>
+        <v>9000077</v>
       </c>
       <c r="B2080" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C2080" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D2080" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2080" s="1" t="n"/>
@@ -46279,21 +46279,21 @@
     </row>
     <row r="2081">
       <c r="A2081" s="1" t="n">
-        <v>9000103</v>
+        <v>9000078</v>
       </c>
       <c r="B2081" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C2081" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D2081" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2081" s="1" t="n"/>
@@ -46301,21 +46301,21 @@
     </row>
     <row r="2082">
       <c r="A2082" s="1" t="n">
-        <v>9000104</v>
+        <v>9000079</v>
       </c>
       <c r="B2082" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C2082" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D2082" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2082" s="1" t="n"/>
@@ -46323,21 +46323,21 @@
     </row>
     <row r="2083">
       <c r="A2083" s="1" t="n">
-        <v>9000105</v>
+        <v>9000080</v>
       </c>
       <c r="B2083" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C2083" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D2083" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2083" s="1" t="n"/>
@@ -46345,21 +46345,21 @@
     </row>
     <row r="2084">
       <c r="A2084" s="1" t="n">
-        <v>9000106</v>
+        <v>9000081</v>
       </c>
       <c r="B2084" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C2084" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D2084" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2084" s="1" t="n"/>
@@ -46367,21 +46367,21 @@
     </row>
     <row r="2085">
       <c r="A2085" s="1" t="n">
-        <v>9000107</v>
+        <v>9000082</v>
       </c>
       <c r="B2085" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C2085" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D2085" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2085" s="1" t="n"/>
@@ -46389,21 +46389,21 @@
     </row>
     <row r="2086">
       <c r="A2086" s="1" t="n">
-        <v>9000108</v>
+        <v>9000083</v>
       </c>
       <c r="B2086" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>헉헉</t>
         </is>
       </c>
       <c r="C2086" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>Huff puff</t>
         </is>
       </c>
       <c r="D2086" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2086" s="1" t="n"/>
@@ -46411,21 +46411,21 @@
     </row>
     <row r="2087">
       <c r="A2087" s="1" t="n">
-        <v>9000109</v>
+        <v>9000084</v>
       </c>
       <c r="B2087" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>더 빨리!</t>
         </is>
       </c>
       <c r="C2087" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>Faster!</t>
         </is>
       </c>
       <c r="D2087" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2087" s="1" t="n"/>
@@ -46433,21 +46433,21 @@
     </row>
     <row r="2088">
       <c r="A2088" s="1" t="n">
-        <v>9000110</v>
+        <v>9000085</v>
       </c>
       <c r="B2088" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>근육 붙는 중</t>
         </is>
       </c>
       <c r="C2088" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>Gains incoming</t>
         </is>
       </c>
       <c r="D2088" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2088" s="1" t="n"/>
@@ -46455,21 +46455,21 @@
     </row>
     <row r="2089">
       <c r="A2089" s="1" t="n">
-        <v>9000111</v>
+        <v>9000086</v>
       </c>
       <c r="B2089" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>찍찍찍찍</t>
         </is>
       </c>
       <c r="C2089" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>Squeak squeak squeak squeak</t>
         </is>
       </c>
       <c r="D2089" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2089" s="1" t="n"/>
@@ -46477,21 +46477,21 @@
     </row>
     <row r="2090">
       <c r="A2090" s="1" t="n">
-        <v>9000112</v>
+        <v>9000087</v>
       </c>
       <c r="B2090" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>으아아아~!</t>
         </is>
       </c>
       <c r="C2090" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>Waaaaah~!</t>
         </is>
       </c>
       <c r="D2090" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2090" s="1" t="n"/>
@@ -46499,21 +46499,21 @@
     </row>
     <row r="2091">
       <c r="A2091" s="1" t="n">
-        <v>9000113</v>
+        <v>9000088</v>
       </c>
       <c r="B2091" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>하암~ 잘 잤다</t>
         </is>
       </c>
       <c r="C2091" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>Yawn~ what a nap</t>
         </is>
       </c>
       <c r="D2091" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2091" s="1" t="n"/>
@@ -46521,21 +46521,21 @@
     </row>
     <row r="2092">
       <c r="A2092" s="1" t="n">
-        <v>9000114</v>
+        <v>9000089</v>
       </c>
       <c r="B2092" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>냠, 배부르다</t>
         </is>
       </c>
       <c r="C2092" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>Nom, so full</t>
         </is>
       </c>
       <c r="D2092" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2092" s="1" t="n"/>
@@ -46543,21 +46543,21 @@
     </row>
     <row r="2093">
       <c r="A2093" s="1" t="n">
-        <v>9000115</v>
+        <v>9000090</v>
       </c>
       <c r="B2093" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>휴…</t>
         </is>
       </c>
       <c r="C2093" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>Phew...</t>
         </is>
       </c>
       <c r="D2093" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2093" s="1" t="n"/>
@@ -46565,21 +46565,21 @@
     </row>
     <row r="2094">
       <c r="A2094" s="1" t="n">
-        <v>9000116</v>
+        <v>9000091</v>
       </c>
       <c r="B2094" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>찍</t>
         </is>
       </c>
       <c r="C2094" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>Squeak</t>
         </is>
       </c>
       <c r="D2094" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
         </is>
       </c>
       <c r="E2094" s="1" t="n"/>
@@ -46587,21 +46587,21 @@
     </row>
     <row r="2095">
       <c r="A2095" s="1" t="n">
-        <v>9000117</v>
+        <v>9000092</v>
       </c>
       <c r="B2095" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C2095" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D2095" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Lobby/RunPage.cs:99</t>
         </is>
       </c>
       <c r="E2095" s="1" t="n"/>
@@ -46609,21 +46609,21 @@
     </row>
     <row r="2096">
       <c r="A2096" s="1" t="n">
-        <v>9000118</v>
+        <v>9000093</v>
       </c>
       <c r="B2096" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="C2096" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D2096" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
         </is>
       </c>
       <c r="E2096" s="1" t="n"/>
@@ -46631,21 +46631,21 @@
     </row>
     <row r="2097">
       <c r="A2097" s="1" t="n">
-        <v>9000119</v>
+        <v>9000094</v>
       </c>
       <c r="B2097" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>찌릿!!</t>
         </is>
       </c>
       <c r="C2097" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>ZAP!!</t>
         </is>
       </c>
       <c r="D2097" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2097" s="1" t="n"/>
@@ -46653,21 +46653,21 @@
     </row>
     <row r="2098">
       <c r="A2098" s="1" t="n">
-        <v>9000120</v>
+        <v>9000095</v>
       </c>
       <c r="B2098" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>콰릉!</t>
         </is>
       </c>
       <c r="C2098" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>Ka-boom!</t>
         </is>
       </c>
       <c r="D2098" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2098" s="1" t="n"/>
@@ -46675,21 +46675,21 @@
     </row>
     <row r="2099">
       <c r="A2099" s="1" t="n">
-        <v>9000121</v>
+        <v>9000096</v>
       </c>
       <c r="B2099" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>냠!</t>
         </is>
       </c>
       <c r="C2099" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>Nom!</t>
         </is>
       </c>
       <c r="D2099" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2099" s="1" t="n"/>
@@ -46697,21 +46697,21 @@
     </row>
     <row r="2100">
       <c r="A2100" s="1" t="n">
-        <v>9000122</v>
+        <v>9000097</v>
       </c>
       <c r="B2100" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>다닥!</t>
         </is>
       </c>
       <c r="C2100" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>Scurry!</t>
         </is>
       </c>
       <c r="D2100" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2100" s="1" t="n"/>
@@ -46719,21 +46719,21 @@
     </row>
     <row r="2101">
       <c r="A2101" s="1" t="n">
-        <v>9000123</v>
+        <v>9000098</v>
       </c>
       <c r="B2101" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>메리 쥐스마스!</t>
         </is>
       </c>
       <c r="C2101" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>Merry Ratmas!</t>
         </is>
       </c>
       <c r="D2101" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2101" s="1" t="n"/>
@@ -46741,21 +46741,21 @@
     </row>
     <row r="2102">
       <c r="A2102" s="1" t="n">
-        <v>9000124</v>
+        <v>9000099</v>
       </c>
       <c r="B2102" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>흐에~ 후원 감사합니다~!</t>
         </is>
       </c>
       <c r="C2102" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>Heheh~ thanks for the dono~!</t>
         </is>
       </c>
       <c r="D2102" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2102" s="1" t="n"/>
@@ -46763,21 +46763,21 @@
     </row>
     <row r="2103">
       <c r="A2103" s="1" t="n">
-        <v>9000125</v>
+        <v>9000100</v>
       </c>
       <c r="B2103" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>배달 왔습니다~</t>
         </is>
       </c>
       <c r="C2103" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>Delivery~!</t>
         </is>
       </c>
       <c r="D2103" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2103" s="1" t="n"/>
@@ -46785,21 +46785,21 @@
     </row>
     <row r="2104">
       <c r="A2104" s="1" t="n">
-        <v>9000126</v>
+        <v>9000101</v>
       </c>
       <c r="B2104" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>백덤블링!</t>
         </is>
       </c>
       <c r="C2104" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>Backflip!</t>
         </is>
       </c>
       <c r="D2104" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2104" s="1" t="n"/>
@@ -46807,21 +46807,21 @@
     </row>
     <row r="2105">
       <c r="A2105" s="1" t="n">
-        <v>9000127</v>
+        <v>9000102</v>
       </c>
       <c r="B2105" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>공중제비!</t>
         </is>
       </c>
       <c r="C2105" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>Somersault!</t>
         </is>
       </c>
       <c r="D2105" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2105" s="1" t="n"/>
@@ -46829,21 +46829,21 @@
     </row>
     <row r="2106">
       <c r="A2106" s="1" t="n">
-        <v>9000128</v>
+        <v>9000103</v>
       </c>
       <c r="B2106" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>찍-공중회전!</t>
         </is>
       </c>
       <c r="C2106" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>Squeak-flip!</t>
         </is>
       </c>
       <c r="D2106" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2106" s="1" t="n"/>
@@ -46851,21 +46851,21 @@
     </row>
     <row r="2107">
       <c r="A2107" s="1" t="n">
-        <v>9000129</v>
+        <v>9000104</v>
       </c>
       <c r="B2107" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>트리플 악셀!!</t>
         </is>
       </c>
       <c r="C2107" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>TRIPLE AXEL!!</t>
         </is>
       </c>
       <c r="D2107" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2107" s="1" t="n"/>
@@ -46873,21 +46873,21 @@
     </row>
     <row r="2108">
       <c r="A2108" s="1" t="n">
-        <v>9000130</v>
+        <v>9000105</v>
       </c>
       <c r="B2108" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>3회전 성공!</t>
         </is>
       </c>
       <c r="C2108" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Triple spin landed!</t>
         </is>
       </c>
       <c r="D2108" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2108" s="1" t="n"/>
@@ -46895,25 +46895,575 @@
     </row>
     <row r="2109">
       <c r="A2109" s="1" t="n">
-        <v>9000131</v>
+        <v>9000106</v>
       </c>
       <c r="B2109" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>심사위원 전원 10점!</t>
         </is>
       </c>
       <c r="C2109" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>Perfect 10s from every judge!</t>
         </is>
       </c>
       <c r="D2109" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2109" s="1" t="n"/>
       <c r="F2109" s="1" t="n"/>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="1" t="n">
+        <v>9000107</v>
+      </c>
+      <c r="B2110" s="2" t="inlineStr">
+        <is>
+          <t>윈드밀!!</t>
+        </is>
+      </c>
+      <c r="C2110" s="2" t="inlineStr">
+        <is>
+          <t>WINDMILL!!</t>
+        </is>
+      </c>
+      <c r="D2110" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
+        </is>
+      </c>
+      <c r="E2110" s="1" t="n"/>
+      <c r="F2110" s="1" t="n"/>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="1" t="n">
+        <v>9000108</v>
+      </c>
+      <c r="B2111" s="2" t="inlineStr">
+        <is>
+          <t>브레이크 댄스!</t>
+        </is>
+      </c>
+      <c r="C2111" s="2" t="inlineStr">
+        <is>
+          <t>Breakdance!</t>
+        </is>
+      </c>
+      <c r="D2111" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
+        </is>
+      </c>
+      <c r="E2111" s="1" t="n"/>
+      <c r="F2111" s="1" t="n"/>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="1" t="n">
+        <v>9000109</v>
+      </c>
+      <c r="B2112" s="2" t="inlineStr">
+        <is>
+          <t>빙글빙글 파괴!</t>
+        </is>
+      </c>
+      <c r="C2112" s="2" t="inlineStr">
+        <is>
+          <t>Spin-to-win destruction!</t>
+        </is>
+      </c>
+      <c r="D2112" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
+        </is>
+      </c>
+      <c r="E2112" s="1" t="n"/>
+      <c r="F2112" s="1" t="n"/>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="1" t="n">
+        <v>9000110</v>
+      </c>
+      <c r="B2113" s="2" t="inlineStr">
+        <is>
+          <t>쥐 대포알!</t>
+        </is>
+      </c>
+      <c r="C2113" s="2" t="inlineStr">
+        <is>
+          <t>Rat Cannonball!</t>
+        </is>
+      </c>
+      <c r="D2113" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
+        </is>
+      </c>
+      <c r="E2113" s="1" t="n"/>
+      <c r="F2113" s="1" t="n"/>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="1" t="n">
+        <v>9000111</v>
+      </c>
+      <c r="B2114" s="2" t="inlineStr">
+        <is>
+          <t>데굴데굴!</t>
+        </is>
+      </c>
+      <c r="C2114" s="2" t="inlineStr">
+        <is>
+          <t>Roll roll!</t>
+        </is>
+      </c>
+      <c r="D2114" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
+        </is>
+      </c>
+      <c r="E2114" s="1" t="n"/>
+      <c r="F2114" s="1" t="n"/>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="1" t="n">
+        <v>9000112</v>
+      </c>
+      <c r="B2115" s="2" t="inlineStr">
+        <is>
+          <t>핀볼 모드!</t>
+        </is>
+      </c>
+      <c r="C2115" s="2" t="inlineStr">
+        <is>
+          <t>Pinball mode!</t>
+        </is>
+      </c>
+      <c r="D2115" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
+        </is>
+      </c>
+      <c r="E2115" s="1" t="n"/>
+      <c r="F2115" s="1" t="n"/>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="1" t="n">
+        <v>9000113</v>
+      </c>
+      <c r="B2116" s="2" t="inlineStr">
+        <is>
+          <t>쳇바퀴 돌기!!</t>
+        </is>
+      </c>
+      <c r="C2116" s="2" t="inlineStr">
+        <is>
+          <t>WHEEL SPIN!!</t>
+        </is>
+      </c>
+      <c r="D2116" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
+        </is>
+      </c>
+      <c r="E2116" s="1" t="n"/>
+      <c r="F2116" s="1" t="n"/>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="1" t="n">
+        <v>9000114</v>
+      </c>
+      <c r="B2117" s="2" t="inlineStr">
+        <is>
+          <t>빙글빙글~</t>
+        </is>
+      </c>
+      <c r="C2117" s="2" t="inlineStr">
+        <is>
+          <t>Round and round~</t>
+        </is>
+      </c>
+      <c r="D2117" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
+        </is>
+      </c>
+      <c r="E2117" s="1" t="n"/>
+      <c r="F2117" s="1" t="n"/>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="1" t="n">
+        <v>9000115</v>
+      </c>
+      <c r="B2118" s="2" t="inlineStr">
+        <is>
+          <t>어지러워!!</t>
+        </is>
+      </c>
+      <c r="C2118" s="2" t="inlineStr">
+        <is>
+          <t>So DIZZY!!</t>
+        </is>
+      </c>
+      <c r="D2118" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
+        </is>
+      </c>
+      <c r="E2118" s="1" t="n"/>
+      <c r="F2118" s="1" t="n"/>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="1" t="n">
+        <v>9000116</v>
+      </c>
+      <c r="B2119" s="2" t="inlineStr">
+        <is>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
+        </is>
+      </c>
+      <c r="C2119" s="2" t="inlineStr">
+        <is>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+        </is>
+      </c>
+      <c r="D2119" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
+        </is>
+      </c>
+      <c r="E2119" s="1" t="n"/>
+      <c r="F2119" s="1" t="n"/>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="1" t="n">
+        <v>9000117</v>
+      </c>
+      <c r="B2120" s="2" t="inlineStr">
+        <is>
+          <t>기절!!</t>
+        </is>
+      </c>
+      <c r="C2120" s="2" t="inlineStr">
+        <is>
+          <t>Stunned!!</t>
+        </is>
+      </c>
+      <c r="D2120" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:38</t>
+        </is>
+      </c>
+      <c r="E2120" s="1" t="n"/>
+      <c r="F2120" s="1" t="n"/>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="1" t="n">
+        <v>9000118</v>
+      </c>
+      <c r="B2121" s="2" t="inlineStr">
+        <is>
+          <t>소품이 떨어졌다!</t>
+        </is>
+      </c>
+      <c r="C2121" s="2" t="inlineStr">
+        <is>
+          <t>A prop dropped!</t>
+        </is>
+      </c>
+      <c r="D2121" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:397</t>
+        </is>
+      </c>
+      <c r="E2121" s="1" t="n"/>
+      <c r="F2121" s="1" t="n"/>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="1" t="n">
+        <v>9000119</v>
+      </c>
+      <c r="B2122" s="2" t="inlineStr">
+        <is>
+          <t>조각 +1</t>
+        </is>
+      </c>
+      <c r="C2122" s="2" t="inlineStr">
+        <is>
+          <t>Shard +1</t>
+        </is>
+      </c>
+      <c r="D2122" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:460</t>
+        </is>
+      </c>
+      <c r="E2122" s="1" t="n"/>
+      <c r="F2122" s="1" t="n"/>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="1" t="n">
+        <v>9000120</v>
+      </c>
+      <c r="B2123" s="2" t="inlineStr">
+        <is>
+          <t>{name} 강화! Lv {lv}</t>
+        </is>
+      </c>
+      <c r="C2123" s="2" t="inlineStr">
+        <is>
+          <t>{name} powered up! Lv {lv}</t>
+        </is>
+      </c>
+      <c r="D2123" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:461</t>
+        </is>
+      </c>
+      <c r="E2123" s="1" t="n"/>
+      <c r="F2123" s="1" t="n"/>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="1" t="n">
+        <v>9000121</v>
+      </c>
+      <c r="B2124" s="2" t="inlineStr">
+        <is>
+          <t>{grade} 탄생!</t>
+        </is>
+      </c>
+      <c r="C2124" s="2" t="inlineStr">
+        <is>
+          <t>{grade} born!</t>
+        </is>
+      </c>
+      <c r="D2124" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:561</t>
+        </is>
+      </c>
+      <c r="E2124" s="1" t="n"/>
+      <c r="F2124" s="1" t="n"/>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="1" t="n">
+        <v>9000122</v>
+      </c>
+      <c r="B2125" s="2" t="inlineStr">
+        <is>
+          <t>쌍둥이!</t>
+        </is>
+      </c>
+      <c r="C2125" s="2" t="inlineStr">
+        <is>
+          <t>Twins!</t>
+        </is>
+      </c>
+      <c r="D2125" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:566</t>
+        </is>
+      </c>
+      <c r="E2125" s="1" t="n"/>
+      <c r="F2125" s="1" t="n"/>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="1" t="n">
+        <v>9000123</v>
+      </c>
+      <c r="B2126" s="2" t="inlineStr">
+        <is>
+          <t>치즈 운석!</t>
+        </is>
+      </c>
+      <c r="C2126" s="2" t="inlineStr">
+        <is>
+          <t>Cheese Meteor!</t>
+        </is>
+      </c>
+      <c r="D2126" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:627</t>
+        </is>
+      </c>
+      <c r="E2126" s="1" t="n"/>
+      <c r="F2126" s="1" t="n"/>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="1" t="n">
+        <v>9000124</v>
+      </c>
+      <c r="B2127" s="2" t="inlineStr">
+        <is>
+          <t>{floor}층 · {zone}</t>
+        </is>
+      </c>
+      <c r="C2127" s="2" t="inlineStr">
+        <is>
+          <t>Floor {floor} · {zone}</t>
+        </is>
+      </c>
+      <c r="D2127" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+        </is>
+      </c>
+      <c r="E2127" s="1" t="n"/>
+      <c r="F2127" s="1" t="n"/>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="1" t="n">
+        <v>9000125</v>
+      </c>
+      <c r="B2128" s="2" t="inlineStr">
+        <is>
+          <t>계단 방 벽을 부숴라!</t>
+        </is>
+      </c>
+      <c r="C2128" s="2" t="inlineStr">
+        <is>
+          <t>Smash the wall to the stairs room!</t>
+        </is>
+      </c>
+      <c r="D2128" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:187</t>
+        </is>
+      </c>
+      <c r="E2128" s="1" t="n"/>
+      <c r="F2128" s="1" t="n"/>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="1" t="n">
+        <v>9000126</v>
+      </c>
+      <c r="B2129" s="2" t="inlineStr">
+        <is>
+          <t>벽 붕괴! 방 확장</t>
+        </is>
+      </c>
+      <c r="C2129" s="2" t="inlineStr">
+        <is>
+          <t>Wall down! Room expanded</t>
+        </is>
+      </c>
+      <c r="D2129" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:332</t>
+        </is>
+      </c>
+      <c r="E2129" s="1" t="n"/>
+      <c r="F2129" s="1" t="n"/>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="1" t="n">
+        <v>9000127</v>
+      </c>
+      <c r="B2130" s="2" t="inlineStr">
+        <is>
+          <t>계단 발견!</t>
+        </is>
+      </c>
+      <c r="C2130" s="2" t="inlineStr">
+        <is>
+          <t>Stairs found!</t>
+        </is>
+      </c>
+      <c r="D2130" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:338</t>
+        </is>
+      </c>
+      <c r="E2130" s="1" t="n"/>
+      <c r="F2130" s="1" t="n"/>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="1" t="n">
+        <v>9000128</v>
+      </c>
+      <c r="B2131" s="2" t="inlineStr">
+        <is>
+          <t>계단에 닿으면 {next}층으로</t>
+        </is>
+      </c>
+      <c r="C2131" s="2" t="inlineStr">
+        <is>
+          <t>Touch the stairs to go to Floor {next}</t>
+        </is>
+      </c>
+      <c r="D2131" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:338</t>
+        </is>
+      </c>
+      <c r="E2131" s="1" t="n"/>
+      <c r="F2131" s="1" t="n"/>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="1" t="n">
+        <v>9000129</v>
+      </c>
+      <c r="B2132" s="2" t="inlineStr">
+        <is>
+          <t>와르르!!</t>
+        </is>
+      </c>
+      <c r="C2132" s="2" t="inlineStr">
+        <is>
+          <t>Crumble!!</t>
+        </is>
+      </c>
+      <c r="D2132" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E2132" s="1" t="n"/>
+      <c r="F2132" s="1" t="n"/>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="1" t="n">
+        <v>9000130</v>
+      </c>
+      <c r="B2133" s="2" t="inlineStr">
+        <is>
+          <t>콰광!!</t>
+        </is>
+      </c>
+      <c r="C2133" s="2" t="inlineStr">
+        <is>
+          <t>KA-BOOM!!</t>
+        </is>
+      </c>
+      <c r="D2133" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E2133" s="1" t="n"/>
+      <c r="F2133" s="1" t="n"/>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B2134" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C2134" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D2134" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E2134" s="1" t="n"/>
+      <c r="F2134" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2134"/>
+  <dimension ref="A1:F2135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -44585,21 +44585,21 @@
     </row>
     <row r="2004">
       <c r="A2004" s="1" t="n">
-        <v>9000001</v>
+        <v>8000430</v>
       </c>
       <c r="B2004" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power} / 적정 {need}</t>
+          <t>스테이지 스킵: {floor}층을 클리어하면 {n}층부터 출발할 수 있어요</t>
         </is>
       </c>
       <c r="C2004" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power} / Rec. {need}</t>
+          <t>Floor Skip: Clear Floor {floor} to start from Floor {n}</t>
         </is>
       </c>
       <c r="D2004" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_run/PlanCard/Info/SkipHint</t>
         </is>
       </c>
       <c r="E2004" s="1" t="n"/>
@@ -44607,21 +44607,21 @@
     </row>
     <row r="2005">
       <c r="A2005" s="1" t="n">
-        <v>9000002</v>
+        <v>9000001</v>
       </c>
       <c r="B2005" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>찍찍!! {power} / 적정 {need}</t>
         </is>
       </c>
       <c r="C2005" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>SQUEAK!! {power} / Rec. {need}</t>
         </is>
       </c>
       <c r="D2005" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E2005" s="1" t="n"/>
@@ -44629,21 +44629,21 @@
     </row>
     <row r="2006">
       <c r="A2006" s="1" t="n">
-        <v>9000003</v>
+        <v>9000002</v>
       </c>
       <c r="B2006" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C2006" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D2006" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2006" s="1" t="n"/>
@@ -44651,21 +44651,21 @@
     </row>
     <row r="2007">
       <c r="A2007" s="1" t="n">
-        <v>9000004</v>
+        <v>9000003</v>
       </c>
       <c r="B2007" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C2007" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D2007" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E2007" s="1" t="n"/>
@@ -44673,21 +44673,21 @@
     </row>
     <row r="2008">
       <c r="A2008" s="1" t="n">
-        <v>9000005</v>
+        <v>9000004</v>
       </c>
       <c r="B2008" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C2008" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D2008" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E2008" s="1" t="n"/>
@@ -44695,21 +44695,21 @@
     </row>
     <row r="2009">
       <c r="A2009" s="1" t="n">
-        <v>9000006</v>
+        <v>9000005</v>
       </c>
       <c r="B2009" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C2009" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D2009" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E2009" s="1" t="n"/>
@@ -44717,21 +44717,21 @@
     </row>
     <row r="2010">
       <c r="A2010" s="1" t="n">
-        <v>9000007</v>
+        <v>9000006</v>
       </c>
       <c r="B2010" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C2010" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D2010" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E2010" s="1" t="n"/>
@@ -44739,21 +44739,21 @@
     </row>
     <row r="2011">
       <c r="A2011" s="1" t="n">
-        <v>9000008</v>
+        <v>9000007</v>
       </c>
       <c r="B2011" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C2011" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D2011" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E2011" s="1" t="n"/>
@@ -44761,16 +44761,16 @@
     </row>
     <row r="2012">
       <c r="A2012" s="1" t="n">
-        <v>9000009</v>
+        <v>9000008</v>
       </c>
       <c r="B2012" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C2012" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D2012" s="1" t="inlineStr">
@@ -44783,16 +44783,16 @@
     </row>
     <row r="2013">
       <c r="A2013" s="1" t="n">
-        <v>9000010</v>
+        <v>9000009</v>
       </c>
       <c r="B2013" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C2013" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D2013" s="1" t="inlineStr">
@@ -44805,16 +44805,16 @@
     </row>
     <row r="2014">
       <c r="A2014" s="1" t="n">
-        <v>9000011</v>
+        <v>9000010</v>
       </c>
       <c r="B2014" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C2014" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D2014" s="1" t="inlineStr">
@@ -44827,21 +44827,21 @@
     </row>
     <row r="2015">
       <c r="A2015" s="1" t="n">
-        <v>9000012</v>
+        <v>9000011</v>
       </c>
       <c r="B2015" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C2015" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D2015" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2015" s="1" t="n"/>
@@ -44849,16 +44849,16 @@
     </row>
     <row r="2016">
       <c r="A2016" s="1" t="n">
-        <v>9000013</v>
+        <v>9000012</v>
       </c>
       <c r="B2016" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C2016" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D2016" s="1" t="inlineStr">
@@ -44871,21 +44871,21 @@
     </row>
     <row r="2017">
       <c r="A2017" s="1" t="n">
-        <v>9000014</v>
+        <v>9000013</v>
       </c>
       <c r="B2017" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C2017" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D2017" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2017" s="1" t="n"/>
@@ -44893,21 +44893,21 @@
     </row>
     <row r="2018">
       <c r="A2018" s="1" t="n">
-        <v>9000015</v>
+        <v>9000014</v>
       </c>
       <c r="B2018" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C2018" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D2018" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E2018" s="1" t="n"/>
@@ -44915,16 +44915,16 @@
     </row>
     <row r="2019">
       <c r="A2019" s="1" t="n">
-        <v>9000016</v>
+        <v>9000015</v>
       </c>
       <c r="B2019" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C2019" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D2019" s="1" t="inlineStr">
@@ -44937,21 +44937,21 @@
     </row>
     <row r="2020">
       <c r="A2020" s="1" t="n">
-        <v>9000017</v>
+        <v>9000016</v>
       </c>
       <c r="B2020" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C2020" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D2020" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2020" s="1" t="n"/>
@@ -44959,21 +44959,21 @@
     </row>
     <row r="2021">
       <c r="A2021" s="1" t="n">
-        <v>9000018</v>
+        <v>9000017</v>
       </c>
       <c r="B2021" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C2021" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D2021" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E2021" s="1" t="n"/>
@@ -44981,16 +44981,16 @@
     </row>
     <row r="2022">
       <c r="A2022" s="1" t="n">
-        <v>9000019</v>
+        <v>9000018</v>
       </c>
       <c r="B2022" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C2022" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D2022" s="1" t="inlineStr">
@@ -45003,16 +45003,16 @@
     </row>
     <row r="2023">
       <c r="A2023" s="1" t="n">
-        <v>9000020</v>
+        <v>9000019</v>
       </c>
       <c r="B2023" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C2023" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D2023" s="1" t="inlineStr">
@@ -45025,21 +45025,21 @@
     </row>
     <row r="2024">
       <c r="A2024" s="1" t="n">
-        <v>9000021</v>
+        <v>9000020</v>
       </c>
       <c r="B2024" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C2024" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D2024" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2024" s="1" t="n"/>
@@ -45047,21 +45047,21 @@
     </row>
     <row r="2025">
       <c r="A2025" s="1" t="n">
-        <v>9000022</v>
+        <v>9000021</v>
       </c>
       <c r="B2025" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C2025" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D2025" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E2025" s="1" t="n"/>
@@ -45069,16 +45069,16 @@
     </row>
     <row r="2026">
       <c r="A2026" s="1" t="n">
-        <v>9000023</v>
+        <v>9000022</v>
       </c>
       <c r="B2026" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C2026" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D2026" s="1" t="inlineStr">
@@ -45091,16 +45091,16 @@
     </row>
     <row r="2027">
       <c r="A2027" s="1" t="n">
-        <v>9000024</v>
+        <v>9000023</v>
       </c>
       <c r="B2027" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C2027" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D2027" s="1" t="inlineStr">
@@ -45113,16 +45113,16 @@
     </row>
     <row r="2028">
       <c r="A2028" s="1" t="n">
-        <v>9000025</v>
+        <v>9000024</v>
       </c>
       <c r="B2028" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C2028" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D2028" s="1" t="inlineStr">
@@ -45135,21 +45135,21 @@
     </row>
     <row r="2029">
       <c r="A2029" s="1" t="n">
-        <v>9000026</v>
+        <v>9000025</v>
       </c>
       <c r="B2029" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C2029" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D2029" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2029" s="1" t="n"/>
@@ -45157,21 +45157,21 @@
     </row>
     <row r="2030">
       <c r="A2030" s="1" t="n">
-        <v>9000027</v>
+        <v>9000026</v>
       </c>
       <c r="B2030" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C2030" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D2030" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E2030" s="1" t="n"/>
@@ -45179,16 +45179,16 @@
     </row>
     <row r="2031">
       <c r="A2031" s="1" t="n">
-        <v>9000028</v>
+        <v>9000027</v>
       </c>
       <c r="B2031" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C2031" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D2031" s="1" t="inlineStr">
@@ -45201,21 +45201,21 @@
     </row>
     <row r="2032">
       <c r="A2032" s="1" t="n">
-        <v>9000029</v>
+        <v>9000028</v>
       </c>
       <c r="B2032" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C2032" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D2032" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2032" s="1" t="n"/>
@@ -45223,21 +45223,21 @@
     </row>
     <row r="2033">
       <c r="A2033" s="1" t="n">
-        <v>9000030</v>
+        <v>9000029</v>
       </c>
       <c r="B2033" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C2033" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D2033" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2033" s="1" t="n"/>
@@ -45245,21 +45245,21 @@
     </row>
     <row r="2034">
       <c r="A2034" s="1" t="n">
-        <v>9000031</v>
+        <v>9000030</v>
       </c>
       <c r="B2034" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C2034" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D2034" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E2034" s="1" t="n"/>
@@ -45267,21 +45267,21 @@
     </row>
     <row r="2035">
       <c r="A2035" s="1" t="n">
-        <v>9000032</v>
+        <v>9000031</v>
       </c>
       <c r="B2035" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C2035" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D2035" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E2035" s="1" t="n"/>
@@ -45289,16 +45289,16 @@
     </row>
     <row r="2036">
       <c r="A2036" s="1" t="n">
-        <v>9000033</v>
+        <v>9000032</v>
       </c>
       <c r="B2036" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C2036" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D2036" s="1" t="inlineStr">
@@ -45311,16 +45311,16 @@
     </row>
     <row r="2037">
       <c r="A2037" s="1" t="n">
-        <v>9000034</v>
+        <v>9000033</v>
       </c>
       <c r="B2037" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C2037" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D2037" s="1" t="inlineStr">
@@ -45333,21 +45333,21 @@
     </row>
     <row r="2038">
       <c r="A2038" s="1" t="n">
-        <v>9000035</v>
+        <v>9000034</v>
       </c>
       <c r="B2038" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C2038" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D2038" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2038" s="1" t="n"/>
@@ -45355,21 +45355,21 @@
     </row>
     <row r="2039">
       <c r="A2039" s="1" t="n">
-        <v>9000036</v>
+        <v>9000035</v>
       </c>
       <c r="B2039" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C2039" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D2039" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E2039" s="1" t="n"/>
@@ -45377,21 +45377,21 @@
     </row>
     <row r="2040">
       <c r="A2040" s="1" t="n">
-        <v>9000037</v>
+        <v>9000036</v>
       </c>
       <c r="B2040" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C2040" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D2040" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E2040" s="1" t="n"/>
@@ -45399,21 +45399,21 @@
     </row>
     <row r="2041">
       <c r="A2041" s="1" t="n">
-        <v>9000038</v>
+        <v>9000037</v>
       </c>
       <c r="B2041" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C2041" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D2041" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E2041" s="1" t="n"/>
@@ -45421,21 +45421,21 @@
     </row>
     <row r="2042">
       <c r="A2042" s="1" t="n">
-        <v>9000039</v>
+        <v>9000038</v>
       </c>
       <c r="B2042" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C2042" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D2042" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E2042" s="1" t="n"/>
@@ -45443,21 +45443,21 @@
     </row>
     <row r="2043">
       <c r="A2043" s="1" t="n">
-        <v>9000040</v>
+        <v>9000039</v>
       </c>
       <c r="B2043" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C2043" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D2043" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E2043" s="1" t="n"/>
@@ -45465,21 +45465,21 @@
     </row>
     <row r="2044">
       <c r="A2044" s="1" t="n">
-        <v>9000041</v>
+        <v>9000040</v>
       </c>
       <c r="B2044" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C2044" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D2044" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E2044" s="1" t="n"/>
@@ -45487,21 +45487,21 @@
     </row>
     <row r="2045">
       <c r="A2045" s="1" t="n">
-        <v>9000042</v>
+        <v>9000041</v>
       </c>
       <c r="B2045" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C2045" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D2045" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2045" s="1" t="n"/>
@@ -45509,16 +45509,16 @@
     </row>
     <row r="2046">
       <c r="A2046" s="1" t="n">
-        <v>9000043</v>
+        <v>9000042</v>
       </c>
       <c r="B2046" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C2046" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D2046" s="1" t="inlineStr">
@@ -45531,16 +45531,16 @@
     </row>
     <row r="2047">
       <c r="A2047" s="1" t="n">
-        <v>9000044</v>
+        <v>9000043</v>
       </c>
       <c r="B2047" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C2047" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D2047" s="1" t="inlineStr">
@@ -45553,16 +45553,16 @@
     </row>
     <row r="2048">
       <c r="A2048" s="1" t="n">
-        <v>9000045</v>
+        <v>9000044</v>
       </c>
       <c r="B2048" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C2048" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D2048" s="1" t="inlineStr">
@@ -45575,21 +45575,21 @@
     </row>
     <row r="2049">
       <c r="A2049" s="1" t="n">
-        <v>9000046</v>
+        <v>9000045</v>
       </c>
       <c r="B2049" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C2049" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D2049" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2049" s="1" t="n"/>
@@ -45597,16 +45597,16 @@
     </row>
     <row r="2050">
       <c r="A2050" s="1" t="n">
-        <v>9000047</v>
+        <v>9000046</v>
       </c>
       <c r="B2050" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C2050" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D2050" s="1" t="inlineStr">
@@ -45619,16 +45619,16 @@
     </row>
     <row r="2051">
       <c r="A2051" s="1" t="n">
-        <v>9000048</v>
+        <v>9000047</v>
       </c>
       <c r="B2051" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C2051" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D2051" s="1" t="inlineStr">
@@ -45641,21 +45641,21 @@
     </row>
     <row r="2052">
       <c r="A2052" s="1" t="n">
-        <v>9000049</v>
+        <v>9000048</v>
       </c>
       <c r="B2052" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C2052" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D2052" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2052" s="1" t="n"/>
@@ -45663,21 +45663,21 @@
     </row>
     <row r="2053">
       <c r="A2053" s="1" t="n">
-        <v>9000050</v>
+        <v>9000049</v>
       </c>
       <c r="B2053" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C2053" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D2053" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E2053" s="1" t="n"/>
@@ -45685,21 +45685,21 @@
     </row>
     <row r="2054">
       <c r="A2054" s="1" t="n">
-        <v>9000051</v>
+        <v>9000050</v>
       </c>
       <c r="B2054" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C2054" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D2054" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E2054" s="1" t="n"/>
@@ -45707,16 +45707,16 @@
     </row>
     <row r="2055">
       <c r="A2055" s="1" t="n">
-        <v>9000052</v>
+        <v>9000051</v>
       </c>
       <c r="B2055" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C2055" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D2055" s="1" t="inlineStr">
@@ -45729,21 +45729,21 @@
     </row>
     <row r="2056">
       <c r="A2056" s="1" t="n">
-        <v>9000053</v>
+        <v>9000052</v>
       </c>
       <c r="B2056" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C2056" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D2056" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2056" s="1" t="n"/>
@@ -45751,21 +45751,21 @@
     </row>
     <row r="2057">
       <c r="A2057" s="1" t="n">
-        <v>9000054</v>
+        <v>9000053</v>
       </c>
       <c r="B2057" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C2057" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D2057" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E2057" s="1" t="n"/>
@@ -45773,16 +45773,16 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>9000055</v>
+        <v>9000054</v>
       </c>
       <c r="B2058" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C2058" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D2058" s="1" t="inlineStr">
@@ -45795,21 +45795,21 @@
     </row>
     <row r="2059">
       <c r="A2059" s="1" t="n">
-        <v>9000056</v>
+        <v>9000055</v>
       </c>
       <c r="B2059" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C2059" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D2059" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2059" s="1" t="n"/>
@@ -45817,16 +45817,16 @@
     </row>
     <row r="2060">
       <c r="A2060" s="1" t="n">
-        <v>9000057</v>
+        <v>9000056</v>
       </c>
       <c r="B2060" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C2060" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D2060" s="1" t="inlineStr">
@@ -45839,16 +45839,16 @@
     </row>
     <row r="2061">
       <c r="A2061" s="1" t="n">
-        <v>9000058</v>
+        <v>9000057</v>
       </c>
       <c r="B2061" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C2061" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D2061" s="1" t="inlineStr">
@@ -45861,16 +45861,16 @@
     </row>
     <row r="2062">
       <c r="A2062" s="1" t="n">
-        <v>9000059</v>
+        <v>9000058</v>
       </c>
       <c r="B2062" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C2062" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D2062" s="1" t="inlineStr">
@@ -45883,21 +45883,21 @@
     </row>
     <row r="2063">
       <c r="A2063" s="1" t="n">
-        <v>9000060</v>
+        <v>9000059</v>
       </c>
       <c r="B2063" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C2063" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D2063" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2063" s="1" t="n"/>
@@ -45905,16 +45905,16 @@
     </row>
     <row r="2064">
       <c r="A2064" s="1" t="n">
-        <v>9000061</v>
+        <v>9000060</v>
       </c>
       <c r="B2064" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C2064" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D2064" s="1" t="inlineStr">
@@ -45927,16 +45927,16 @@
     </row>
     <row r="2065">
       <c r="A2065" s="1" t="n">
-        <v>9000062</v>
+        <v>9000061</v>
       </c>
       <c r="B2065" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C2065" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D2065" s="1" t="inlineStr">
@@ -45949,16 +45949,16 @@
     </row>
     <row r="2066">
       <c r="A2066" s="1" t="n">
-        <v>9000063</v>
+        <v>9000062</v>
       </c>
       <c r="B2066" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C2066" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D2066" s="1" t="inlineStr">
@@ -45971,16 +45971,16 @@
     </row>
     <row r="2067">
       <c r="A2067" s="1" t="n">
-        <v>9000064</v>
+        <v>9000063</v>
       </c>
       <c r="B2067" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C2067" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D2067" s="1" t="inlineStr">
@@ -45993,21 +45993,21 @@
     </row>
     <row r="2068">
       <c r="A2068" s="1" t="n">
-        <v>9000065</v>
+        <v>9000064</v>
       </c>
       <c r="B2068" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C2068" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D2068" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2068" s="1" t="n"/>
@@ -46015,16 +46015,16 @@
     </row>
     <row r="2069">
       <c r="A2069" s="1" t="n">
-        <v>9000066</v>
+        <v>9000065</v>
       </c>
       <c r="B2069" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C2069" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D2069" s="1" t="inlineStr">
@@ -46037,16 +46037,16 @@
     </row>
     <row r="2070">
       <c r="A2070" s="1" t="n">
-        <v>9000067</v>
+        <v>9000066</v>
       </c>
       <c r="B2070" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C2070" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D2070" s="1" t="inlineStr">
@@ -46059,16 +46059,16 @@
     </row>
     <row r="2071">
       <c r="A2071" s="1" t="n">
-        <v>9000068</v>
+        <v>9000067</v>
       </c>
       <c r="B2071" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C2071" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D2071" s="1" t="inlineStr">
@@ -46081,16 +46081,16 @@
     </row>
     <row r="2072">
       <c r="A2072" s="1" t="n">
-        <v>9000069</v>
+        <v>9000068</v>
       </c>
       <c r="B2072" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C2072" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D2072" s="1" t="inlineStr">
@@ -46103,16 +46103,16 @@
     </row>
     <row r="2073">
       <c r="A2073" s="1" t="n">
-        <v>9000070</v>
+        <v>9000069</v>
       </c>
       <c r="B2073" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C2073" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D2073" s="1" t="inlineStr">
@@ -46125,16 +46125,16 @@
     </row>
     <row r="2074">
       <c r="A2074" s="1" t="n">
-        <v>9000071</v>
+        <v>9000070</v>
       </c>
       <c r="B2074" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C2074" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D2074" s="1" t="inlineStr">
@@ -46147,21 +46147,21 @@
     </row>
     <row r="2075">
       <c r="A2075" s="1" t="n">
-        <v>9000072</v>
+        <v>9000071</v>
       </c>
       <c r="B2075" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C2075" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D2075" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2075" s="1" t="n"/>
@@ -46169,16 +46169,16 @@
     </row>
     <row r="2076">
       <c r="A2076" s="1" t="n">
-        <v>9000073</v>
+        <v>9000072</v>
       </c>
       <c r="B2076" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C2076" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D2076" s="1" t="inlineStr">
@@ -46191,16 +46191,16 @@
     </row>
     <row r="2077">
       <c r="A2077" s="1" t="n">
-        <v>9000074</v>
+        <v>9000073</v>
       </c>
       <c r="B2077" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C2077" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D2077" s="1" t="inlineStr">
@@ -46213,16 +46213,16 @@
     </row>
     <row r="2078">
       <c r="A2078" s="1" t="n">
-        <v>9000075</v>
+        <v>9000074</v>
       </c>
       <c r="B2078" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C2078" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D2078" s="1" t="inlineStr">
@@ -46235,16 +46235,16 @@
     </row>
     <row r="2079">
       <c r="A2079" s="1" t="n">
-        <v>9000076</v>
+        <v>9000075</v>
       </c>
       <c r="B2079" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C2079" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D2079" s="1" t="inlineStr">
@@ -46257,21 +46257,21 @@
     </row>
     <row r="2080">
       <c r="A2080" s="1" t="n">
-        <v>9000077</v>
+        <v>9000076</v>
       </c>
       <c r="B2080" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C2080" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D2080" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2080" s="1" t="n"/>
@@ -46279,16 +46279,16 @@
     </row>
     <row r="2081">
       <c r="A2081" s="1" t="n">
-        <v>9000078</v>
+        <v>9000077</v>
       </c>
       <c r="B2081" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C2081" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D2081" s="1" t="inlineStr">
@@ -46301,16 +46301,16 @@
     </row>
     <row r="2082">
       <c r="A2082" s="1" t="n">
-        <v>9000079</v>
+        <v>9000078</v>
       </c>
       <c r="B2082" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C2082" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D2082" s="1" t="inlineStr">
@@ -46323,16 +46323,16 @@
     </row>
     <row r="2083">
       <c r="A2083" s="1" t="n">
-        <v>9000080</v>
+        <v>9000079</v>
       </c>
       <c r="B2083" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C2083" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D2083" s="1" t="inlineStr">
@@ -46345,21 +46345,21 @@
     </row>
     <row r="2084">
       <c r="A2084" s="1" t="n">
-        <v>9000081</v>
+        <v>9000080</v>
       </c>
       <c r="B2084" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C2084" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D2084" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2084" s="1" t="n"/>
@@ -46367,16 +46367,16 @@
     </row>
     <row r="2085">
       <c r="A2085" s="1" t="n">
-        <v>9000082</v>
+        <v>9000081</v>
       </c>
       <c r="B2085" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C2085" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D2085" s="1" t="inlineStr">
@@ -46389,21 +46389,21 @@
     </row>
     <row r="2086">
       <c r="A2086" s="1" t="n">
-        <v>9000083</v>
+        <v>9000082</v>
       </c>
       <c r="B2086" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C2086" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D2086" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2086" s="1" t="n"/>
@@ -46411,16 +46411,16 @@
     </row>
     <row r="2087">
       <c r="A2087" s="1" t="n">
-        <v>9000084</v>
+        <v>9000083</v>
       </c>
       <c r="B2087" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>헉헉</t>
         </is>
       </c>
       <c r="C2087" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>Huff puff</t>
         </is>
       </c>
       <c r="D2087" s="1" t="inlineStr">
@@ -46433,16 +46433,16 @@
     </row>
     <row r="2088">
       <c r="A2088" s="1" t="n">
-        <v>9000085</v>
+        <v>9000084</v>
       </c>
       <c r="B2088" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>더 빨리!</t>
         </is>
       </c>
       <c r="C2088" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>Faster!</t>
         </is>
       </c>
       <c r="D2088" s="1" t="inlineStr">
@@ -46455,16 +46455,16 @@
     </row>
     <row r="2089">
       <c r="A2089" s="1" t="n">
-        <v>9000086</v>
+        <v>9000085</v>
       </c>
       <c r="B2089" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>근육 붙는 중</t>
         </is>
       </c>
       <c r="C2089" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>Gains incoming</t>
         </is>
       </c>
       <c r="D2089" s="1" t="inlineStr">
@@ -46477,21 +46477,21 @@
     </row>
     <row r="2090">
       <c r="A2090" s="1" t="n">
-        <v>9000087</v>
+        <v>9000086</v>
       </c>
       <c r="B2090" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>찍찍찍찍</t>
         </is>
       </c>
       <c r="C2090" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>Squeak squeak squeak squeak</t>
         </is>
       </c>
       <c r="D2090" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2090" s="1" t="n"/>
@@ -46499,16 +46499,16 @@
     </row>
     <row r="2091">
       <c r="A2091" s="1" t="n">
-        <v>9000088</v>
+        <v>9000087</v>
       </c>
       <c r="B2091" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>으아아아~!</t>
         </is>
       </c>
       <c r="C2091" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>Waaaaah~!</t>
         </is>
       </c>
       <c r="D2091" s="1" t="inlineStr">
@@ -46521,16 +46521,16 @@
     </row>
     <row r="2092">
       <c r="A2092" s="1" t="n">
-        <v>9000089</v>
+        <v>9000088</v>
       </c>
       <c r="B2092" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>하암~ 잘 잤다</t>
         </is>
       </c>
       <c r="C2092" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>Yawn~ what a nap</t>
         </is>
       </c>
       <c r="D2092" s="1" t="inlineStr">
@@ -46543,16 +46543,16 @@
     </row>
     <row r="2093">
       <c r="A2093" s="1" t="n">
-        <v>9000090</v>
+        <v>9000089</v>
       </c>
       <c r="B2093" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>냠, 배부르다</t>
         </is>
       </c>
       <c r="C2093" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>Nom, so full</t>
         </is>
       </c>
       <c r="D2093" s="1" t="inlineStr">
@@ -46565,21 +46565,21 @@
     </row>
     <row r="2094">
       <c r="A2094" s="1" t="n">
-        <v>9000091</v>
+        <v>9000090</v>
       </c>
       <c r="B2094" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>휴…</t>
         </is>
       </c>
       <c r="C2094" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Phew...</t>
         </is>
       </c>
       <c r="D2094" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2094" s="1" t="n"/>
@@ -46587,21 +46587,21 @@
     </row>
     <row r="2095">
       <c r="A2095" s="1" t="n">
-        <v>9000092</v>
+        <v>9000091</v>
       </c>
       <c r="B2095" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>찍</t>
         </is>
       </c>
       <c r="C2095" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Squeak</t>
         </is>
       </c>
       <c r="D2095" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
         </is>
       </c>
       <c r="E2095" s="1" t="n"/>
@@ -46609,21 +46609,21 @@
     </row>
     <row r="2096">
       <c r="A2096" s="1" t="n">
-        <v>9000093</v>
+        <v>9000092</v>
       </c>
       <c r="B2096" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C2096" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D2096" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Lobby/RunPage.cs:99</t>
         </is>
       </c>
       <c r="E2096" s="1" t="n"/>
@@ -46631,21 +46631,21 @@
     </row>
     <row r="2097">
       <c r="A2097" s="1" t="n">
-        <v>9000094</v>
+        <v>9000093</v>
       </c>
       <c r="B2097" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="C2097" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D2097" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
         </is>
       </c>
       <c r="E2097" s="1" t="n"/>
@@ -46653,16 +46653,16 @@
     </row>
     <row r="2098">
       <c r="A2098" s="1" t="n">
-        <v>9000095</v>
+        <v>9000094</v>
       </c>
       <c r="B2098" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>찌릿!!</t>
         </is>
       </c>
       <c r="C2098" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>ZAP!!</t>
         </is>
       </c>
       <c r="D2098" s="1" t="inlineStr">
@@ -46675,21 +46675,21 @@
     </row>
     <row r="2099">
       <c r="A2099" s="1" t="n">
-        <v>9000096</v>
+        <v>9000095</v>
       </c>
       <c r="B2099" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>콰릉!</t>
         </is>
       </c>
       <c r="C2099" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>Ka-boom!</t>
         </is>
       </c>
       <c r="D2099" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2099" s="1" t="n"/>
@@ -46697,16 +46697,16 @@
     </row>
     <row r="2100">
       <c r="A2100" s="1" t="n">
-        <v>9000097</v>
+        <v>9000096</v>
       </c>
       <c r="B2100" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>냠!</t>
         </is>
       </c>
       <c r="C2100" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>Nom!</t>
         </is>
       </c>
       <c r="D2100" s="1" t="inlineStr">
@@ -46719,21 +46719,21 @@
     </row>
     <row r="2101">
       <c r="A2101" s="1" t="n">
-        <v>9000098</v>
+        <v>9000097</v>
       </c>
       <c r="B2101" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>다닥!</t>
         </is>
       </c>
       <c r="C2101" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>Scurry!</t>
         </is>
       </c>
       <c r="D2101" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2101" s="1" t="n"/>
@@ -46741,16 +46741,16 @@
     </row>
     <row r="2102">
       <c r="A2102" s="1" t="n">
-        <v>9000099</v>
+        <v>9000098</v>
       </c>
       <c r="B2102" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>메리 쥐스마스!</t>
         </is>
       </c>
       <c r="C2102" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>Merry Ratmas!</t>
         </is>
       </c>
       <c r="D2102" s="1" t="inlineStr">
@@ -46763,16 +46763,16 @@
     </row>
     <row r="2103">
       <c r="A2103" s="1" t="n">
-        <v>9000100</v>
+        <v>9000099</v>
       </c>
       <c r="B2103" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>흐에~ 후원 감사합니다~!</t>
         </is>
       </c>
       <c r="C2103" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>Heheh~ thanks for the dono~!</t>
         </is>
       </c>
       <c r="D2103" s="1" t="inlineStr">
@@ -46785,21 +46785,21 @@
     </row>
     <row r="2104">
       <c r="A2104" s="1" t="n">
-        <v>9000101</v>
+        <v>9000100</v>
       </c>
       <c r="B2104" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>배달 왔습니다~</t>
         </is>
       </c>
       <c r="C2104" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>Delivery~!</t>
         </is>
       </c>
       <c r="D2104" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2104" s="1" t="n"/>
@@ -46807,16 +46807,16 @@
     </row>
     <row r="2105">
       <c r="A2105" s="1" t="n">
-        <v>9000102</v>
+        <v>9000101</v>
       </c>
       <c r="B2105" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>백덤블링!</t>
         </is>
       </c>
       <c r="C2105" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>Backflip!</t>
         </is>
       </c>
       <c r="D2105" s="1" t="inlineStr">
@@ -46829,16 +46829,16 @@
     </row>
     <row r="2106">
       <c r="A2106" s="1" t="n">
-        <v>9000103</v>
+        <v>9000102</v>
       </c>
       <c r="B2106" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>공중제비!</t>
         </is>
       </c>
       <c r="C2106" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Somersault!</t>
         </is>
       </c>
       <c r="D2106" s="1" t="inlineStr">
@@ -46851,21 +46851,21 @@
     </row>
     <row r="2107">
       <c r="A2107" s="1" t="n">
-        <v>9000104</v>
+        <v>9000103</v>
       </c>
       <c r="B2107" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>찍-공중회전!</t>
         </is>
       </c>
       <c r="C2107" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Squeak-flip!</t>
         </is>
       </c>
       <c r="D2107" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2107" s="1" t="n"/>
@@ -46873,16 +46873,16 @@
     </row>
     <row r="2108">
       <c r="A2108" s="1" t="n">
-        <v>9000105</v>
+        <v>9000104</v>
       </c>
       <c r="B2108" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>트리플 악셀!!</t>
         </is>
       </c>
       <c r="C2108" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>TRIPLE AXEL!!</t>
         </is>
       </c>
       <c r="D2108" s="1" t="inlineStr">
@@ -46895,16 +46895,16 @@
     </row>
     <row r="2109">
       <c r="A2109" s="1" t="n">
-        <v>9000106</v>
+        <v>9000105</v>
       </c>
       <c r="B2109" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>3회전 성공!</t>
         </is>
       </c>
       <c r="C2109" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>Triple spin landed!</t>
         </is>
       </c>
       <c r="D2109" s="1" t="inlineStr">
@@ -46917,21 +46917,21 @@
     </row>
     <row r="2110">
       <c r="A2110" s="1" t="n">
-        <v>9000107</v>
+        <v>9000106</v>
       </c>
       <c r="B2110" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>심사위원 전원 10점!</t>
         </is>
       </c>
       <c r="C2110" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>Perfect 10s from every judge!</t>
         </is>
       </c>
       <c r="D2110" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2110" s="1" t="n"/>
@@ -46939,16 +46939,16 @@
     </row>
     <row r="2111">
       <c r="A2111" s="1" t="n">
-        <v>9000108</v>
+        <v>9000107</v>
       </c>
       <c r="B2111" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>윈드밀!!</t>
         </is>
       </c>
       <c r="C2111" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>WINDMILL!!</t>
         </is>
       </c>
       <c r="D2111" s="1" t="inlineStr">
@@ -46961,16 +46961,16 @@
     </row>
     <row r="2112">
       <c r="A2112" s="1" t="n">
-        <v>9000109</v>
+        <v>9000108</v>
       </c>
       <c r="B2112" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>브레이크 댄스!</t>
         </is>
       </c>
       <c r="C2112" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>Breakdance!</t>
         </is>
       </c>
       <c r="D2112" s="1" t="inlineStr">
@@ -46983,21 +46983,21 @@
     </row>
     <row r="2113">
       <c r="A2113" s="1" t="n">
-        <v>9000110</v>
+        <v>9000109</v>
       </c>
       <c r="B2113" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>빙글빙글 파괴!</t>
         </is>
       </c>
       <c r="C2113" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>Spin-to-win destruction!</t>
         </is>
       </c>
       <c r="D2113" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2113" s="1" t="n"/>
@@ -47005,16 +47005,16 @@
     </row>
     <row r="2114">
       <c r="A2114" s="1" t="n">
-        <v>9000111</v>
+        <v>9000110</v>
       </c>
       <c r="B2114" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>쥐 대포알!</t>
         </is>
       </c>
       <c r="C2114" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>Rat Cannonball!</t>
         </is>
       </c>
       <c r="D2114" s="1" t="inlineStr">
@@ -47027,16 +47027,16 @@
     </row>
     <row r="2115">
       <c r="A2115" s="1" t="n">
-        <v>9000112</v>
+        <v>9000111</v>
       </c>
       <c r="B2115" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>데굴데굴!</t>
         </is>
       </c>
       <c r="C2115" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>Roll roll!</t>
         </is>
       </c>
       <c r="D2115" s="1" t="inlineStr">
@@ -47049,21 +47049,21 @@
     </row>
     <row r="2116">
       <c r="A2116" s="1" t="n">
-        <v>9000113</v>
+        <v>9000112</v>
       </c>
       <c r="B2116" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>핀볼 모드!</t>
         </is>
       </c>
       <c r="C2116" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>Pinball mode!</t>
         </is>
       </c>
       <c r="D2116" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2116" s="1" t="n"/>
@@ -47071,16 +47071,16 @@
     </row>
     <row r="2117">
       <c r="A2117" s="1" t="n">
-        <v>9000114</v>
+        <v>9000113</v>
       </c>
       <c r="B2117" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>쳇바퀴 돌기!!</t>
         </is>
       </c>
       <c r="C2117" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>WHEEL SPIN!!</t>
         </is>
       </c>
       <c r="D2117" s="1" t="inlineStr">
@@ -47093,16 +47093,16 @@
     </row>
     <row r="2118">
       <c r="A2118" s="1" t="n">
-        <v>9000115</v>
+        <v>9000114</v>
       </c>
       <c r="B2118" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>빙글빙글~</t>
         </is>
       </c>
       <c r="C2118" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>Round and round~</t>
         </is>
       </c>
       <c r="D2118" s="1" t="inlineStr">
@@ -47115,21 +47115,21 @@
     </row>
     <row r="2119">
       <c r="A2119" s="1" t="n">
-        <v>9000116</v>
+        <v>9000115</v>
       </c>
       <c r="B2119" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>어지러워!!</t>
         </is>
       </c>
       <c r="C2119" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>So DIZZY!!</t>
         </is>
       </c>
       <c r="D2119" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2119" s="1" t="n"/>
@@ -47137,21 +47137,21 @@
     </row>
     <row r="2120">
       <c r="A2120" s="1" t="n">
-        <v>9000117</v>
+        <v>9000116</v>
       </c>
       <c r="B2120" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="C2120" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="D2120" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
         </is>
       </c>
       <c r="E2120" s="1" t="n"/>
@@ -47159,21 +47159,21 @@
     </row>
     <row r="2121">
       <c r="A2121" s="1" t="n">
-        <v>9000118</v>
+        <v>9000117</v>
       </c>
       <c r="B2121" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>기절!!</t>
         </is>
       </c>
       <c r="C2121" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>Stunned!!</t>
         </is>
       </c>
       <c r="D2121" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Rats/RatManager.cs:38</t>
         </is>
       </c>
       <c r="E2121" s="1" t="n"/>
@@ -47181,21 +47181,21 @@
     </row>
     <row r="2122">
       <c r="A2122" s="1" t="n">
-        <v>9000119</v>
+        <v>9000118</v>
       </c>
       <c r="B2122" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>소품이 떨어졌다!</t>
         </is>
       </c>
       <c r="C2122" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>A prop dropped!</t>
         </is>
       </c>
       <c r="D2122" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Rats/RatManager.cs:397</t>
         </is>
       </c>
       <c r="E2122" s="1" t="n"/>
@@ -47203,21 +47203,21 @@
     </row>
     <row r="2123">
       <c r="A2123" s="1" t="n">
-        <v>9000120</v>
+        <v>9000119</v>
       </c>
       <c r="B2123" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>조각 +1</t>
         </is>
       </c>
       <c r="C2123" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>Shard +1</t>
         </is>
       </c>
       <c r="D2123" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Rats/RatManager.cs:460</t>
         </is>
       </c>
       <c r="E2123" s="1" t="n"/>
@@ -47225,21 +47225,21 @@
     </row>
     <row r="2124">
       <c r="A2124" s="1" t="n">
-        <v>9000121</v>
+        <v>9000120</v>
       </c>
       <c r="B2124" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>{name} 강화! Lv {lv}</t>
         </is>
       </c>
       <c r="C2124" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>{name} powered up! Lv {lv}</t>
         </is>
       </c>
       <c r="D2124" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Rats/RatManager.cs:461</t>
         </is>
       </c>
       <c r="E2124" s="1" t="n"/>
@@ -47247,21 +47247,21 @@
     </row>
     <row r="2125">
       <c r="A2125" s="1" t="n">
-        <v>9000122</v>
+        <v>9000121</v>
       </c>
       <c r="B2125" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>{grade} 탄생!</t>
         </is>
       </c>
       <c r="C2125" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>{grade} born!</t>
         </is>
       </c>
       <c r="D2125" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Rats/RatManager.cs:561</t>
         </is>
       </c>
       <c r="E2125" s="1" t="n"/>
@@ -47269,21 +47269,21 @@
     </row>
     <row r="2126">
       <c r="A2126" s="1" t="n">
-        <v>9000123</v>
+        <v>9000122</v>
       </c>
       <c r="B2126" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>쌍둥이!</t>
         </is>
       </c>
       <c r="C2126" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>Twins!</t>
         </is>
       </c>
       <c r="D2126" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Rats/RatManager.cs:566</t>
         </is>
       </c>
       <c r="E2126" s="1" t="n"/>
@@ -47291,21 +47291,21 @@
     </row>
     <row r="2127">
       <c r="A2127" s="1" t="n">
-        <v>9000124</v>
+        <v>9000123</v>
       </c>
       <c r="B2127" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>치즈 운석!</t>
         </is>
       </c>
       <c r="C2127" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>Cheese Meteor!</t>
         </is>
       </c>
       <c r="D2127" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:627</t>
         </is>
       </c>
       <c r="E2127" s="1" t="n"/>
@@ -47313,21 +47313,21 @@
     </row>
     <row r="2128">
       <c r="A2128" s="1" t="n">
-        <v>9000125</v>
+        <v>9000124</v>
       </c>
       <c r="B2128" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>{floor}층 · {zone}</t>
         </is>
       </c>
       <c r="C2128" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>Floor {floor} · {zone}</t>
         </is>
       </c>
       <c r="D2128" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E2128" s="1" t="n"/>
@@ -47335,21 +47335,21 @@
     </row>
     <row r="2129">
       <c r="A2129" s="1" t="n">
-        <v>9000126</v>
+        <v>9000125</v>
       </c>
       <c r="B2129" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>계단 방 벽을 부숴라!</t>
         </is>
       </c>
       <c r="C2129" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>Smash the wall to the stairs room!</t>
         </is>
       </c>
       <c r="D2129" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E2129" s="1" t="n"/>
@@ -47357,21 +47357,21 @@
     </row>
     <row r="2130">
       <c r="A2130" s="1" t="n">
-        <v>9000127</v>
+        <v>9000126</v>
       </c>
       <c r="B2130" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>벽 붕괴! 방 확장</t>
         </is>
       </c>
       <c r="C2130" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>Wall down! Room expanded</t>
         </is>
       </c>
       <c r="D2130" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2130" s="1" t="n"/>
@@ -47379,16 +47379,16 @@
     </row>
     <row r="2131">
       <c r="A2131" s="1" t="n">
-        <v>9000128</v>
+        <v>9000127</v>
       </c>
       <c r="B2131" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>계단 발견!</t>
         </is>
       </c>
       <c r="C2131" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>Stairs found!</t>
         </is>
       </c>
       <c r="D2131" s="1" t="inlineStr">
@@ -47401,21 +47401,21 @@
     </row>
     <row r="2132">
       <c r="A2132" s="1" t="n">
-        <v>9000129</v>
+        <v>9000128</v>
       </c>
       <c r="B2132" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>계단에 닿으면 {next}층으로</t>
         </is>
       </c>
       <c r="C2132" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>Touch the stairs to go to Floor {next}</t>
         </is>
       </c>
       <c r="D2132" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:338</t>
         </is>
       </c>
       <c r="E2132" s="1" t="n"/>
@@ -47423,16 +47423,16 @@
     </row>
     <row r="2133">
       <c r="A2133" s="1" t="n">
-        <v>9000130</v>
+        <v>9000129</v>
       </c>
       <c r="B2133" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>와르르!!</t>
         </is>
       </c>
       <c r="C2133" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Crumble!!</t>
         </is>
       </c>
       <c r="D2133" s="1" t="inlineStr">
@@ -47445,16 +47445,16 @@
     </row>
     <row r="2134">
       <c r="A2134" s="1" t="n">
-        <v>9000131</v>
+        <v>9000130</v>
       </c>
       <c r="B2134" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>콰광!!</t>
         </is>
       </c>
       <c r="C2134" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>KA-BOOM!!</t>
         </is>
       </c>
       <c r="D2134" s="1" t="inlineStr">
@@ -47464,6 +47464,28 @@
       </c>
       <c r="E2134" s="1" t="n"/>
       <c r="F2134" s="1" t="n"/>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B2135" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C2135" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D2135" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E2135" s="1" t="n"/>
+      <c r="F2135" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2109"/>
+  <dimension ref="A1:F2110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -44035,21 +44035,21 @@
     </row>
     <row r="1979">
       <c r="A1979" s="1" t="n">
-        <v>9000001</v>
+        <v>8000430</v>
       </c>
       <c r="B1979" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power} / 적정 {need}</t>
+          <t>스테이지 스킵: {floor}층을 클리어하면 {n}층부터 출발할 수 있어요</t>
         </is>
       </c>
       <c r="C1979" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power} / Rec. {need}</t>
+          <t>Floor Skip: Clear Floor {floor} to start from Floor {n}</t>
         </is>
       </c>
       <c r="D1979" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_run/PlanCard/Info/SkipHint</t>
         </is>
       </c>
       <c r="E1979" s="1" t="n"/>
@@ -44057,21 +44057,21 @@
     </row>
     <row r="1980">
       <c r="A1980" s="1" t="n">
-        <v>9000002</v>
+        <v>9000001</v>
       </c>
       <c r="B1980" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>찍찍!! {power} / 적정 {need}</t>
         </is>
       </c>
       <c r="C1980" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>SQUEAK!! {power} / Rec. {need}</t>
         </is>
       </c>
       <c r="D1980" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E1980" s="1" t="n"/>
@@ -44079,21 +44079,21 @@
     </row>
     <row r="1981">
       <c r="A1981" s="1" t="n">
-        <v>9000003</v>
+        <v>9000002</v>
       </c>
       <c r="B1981" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C1981" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D1981" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E1981" s="1" t="n"/>
@@ -44101,21 +44101,21 @@
     </row>
     <row r="1982">
       <c r="A1982" s="1" t="n">
-        <v>9000004</v>
+        <v>9000003</v>
       </c>
       <c r="B1982" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C1982" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D1982" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E1982" s="1" t="n"/>
@@ -44123,21 +44123,21 @@
     </row>
     <row r="1983">
       <c r="A1983" s="1" t="n">
-        <v>9000005</v>
+        <v>9000004</v>
       </c>
       <c r="B1983" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C1983" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D1983" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E1983" s="1" t="n"/>
@@ -44145,21 +44145,21 @@
     </row>
     <row r="1984">
       <c r="A1984" s="1" t="n">
-        <v>9000006</v>
+        <v>9000005</v>
       </c>
       <c r="B1984" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C1984" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D1984" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E1984" s="1" t="n"/>
@@ -44167,21 +44167,21 @@
     </row>
     <row r="1985">
       <c r="A1985" s="1" t="n">
-        <v>9000007</v>
+        <v>9000006</v>
       </c>
       <c r="B1985" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C1985" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D1985" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E1985" s="1" t="n"/>
@@ -44189,21 +44189,21 @@
     </row>
     <row r="1986">
       <c r="A1986" s="1" t="n">
-        <v>9000008</v>
+        <v>9000007</v>
       </c>
       <c r="B1986" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C1986" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D1986" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E1986" s="1" t="n"/>
@@ -44211,16 +44211,16 @@
     </row>
     <row r="1987">
       <c r="A1987" s="1" t="n">
-        <v>9000009</v>
+        <v>9000008</v>
       </c>
       <c r="B1987" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C1987" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D1987" s="1" t="inlineStr">
@@ -44233,16 +44233,16 @@
     </row>
     <row r="1988">
       <c r="A1988" s="1" t="n">
-        <v>9000010</v>
+        <v>9000009</v>
       </c>
       <c r="B1988" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C1988" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D1988" s="1" t="inlineStr">
@@ -44255,16 +44255,16 @@
     </row>
     <row r="1989">
       <c r="A1989" s="1" t="n">
-        <v>9000011</v>
+        <v>9000010</v>
       </c>
       <c r="B1989" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C1989" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D1989" s="1" t="inlineStr">
@@ -44277,21 +44277,21 @@
     </row>
     <row r="1990">
       <c r="A1990" s="1" t="n">
-        <v>9000012</v>
+        <v>9000011</v>
       </c>
       <c r="B1990" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C1990" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D1990" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E1990" s="1" t="n"/>
@@ -44299,16 +44299,16 @@
     </row>
     <row r="1991">
       <c r="A1991" s="1" t="n">
-        <v>9000013</v>
+        <v>9000012</v>
       </c>
       <c r="B1991" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C1991" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D1991" s="1" t="inlineStr">
@@ -44321,21 +44321,21 @@
     </row>
     <row r="1992">
       <c r="A1992" s="1" t="n">
-        <v>9000014</v>
+        <v>9000013</v>
       </c>
       <c r="B1992" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C1992" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D1992" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E1992" s="1" t="n"/>
@@ -44343,21 +44343,21 @@
     </row>
     <row r="1993">
       <c r="A1993" s="1" t="n">
-        <v>9000015</v>
+        <v>9000014</v>
       </c>
       <c r="B1993" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C1993" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D1993" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E1993" s="1" t="n"/>
@@ -44365,16 +44365,16 @@
     </row>
     <row r="1994">
       <c r="A1994" s="1" t="n">
-        <v>9000016</v>
+        <v>9000015</v>
       </c>
       <c r="B1994" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C1994" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D1994" s="1" t="inlineStr">
@@ -44387,21 +44387,21 @@
     </row>
     <row r="1995">
       <c r="A1995" s="1" t="n">
-        <v>9000017</v>
+        <v>9000016</v>
       </c>
       <c r="B1995" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C1995" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D1995" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E1995" s="1" t="n"/>
@@ -44409,21 +44409,21 @@
     </row>
     <row r="1996">
       <c r="A1996" s="1" t="n">
-        <v>9000018</v>
+        <v>9000017</v>
       </c>
       <c r="B1996" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C1996" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D1996" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E1996" s="1" t="n"/>
@@ -44431,16 +44431,16 @@
     </row>
     <row r="1997">
       <c r="A1997" s="1" t="n">
-        <v>9000019</v>
+        <v>9000018</v>
       </c>
       <c r="B1997" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C1997" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D1997" s="1" t="inlineStr">
@@ -44453,16 +44453,16 @@
     </row>
     <row r="1998">
       <c r="A1998" s="1" t="n">
-        <v>9000020</v>
+        <v>9000019</v>
       </c>
       <c r="B1998" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C1998" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D1998" s="1" t="inlineStr">
@@ -44475,21 +44475,21 @@
     </row>
     <row r="1999">
       <c r="A1999" s="1" t="n">
-        <v>9000021</v>
+        <v>9000020</v>
       </c>
       <c r="B1999" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C1999" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D1999" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E1999" s="1" t="n"/>
@@ -44497,21 +44497,21 @@
     </row>
     <row r="2000">
       <c r="A2000" s="1" t="n">
-        <v>9000022</v>
+        <v>9000021</v>
       </c>
       <c r="B2000" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C2000" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D2000" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E2000" s="1" t="n"/>
@@ -44519,16 +44519,16 @@
     </row>
     <row r="2001">
       <c r="A2001" s="1" t="n">
-        <v>9000023</v>
+        <v>9000022</v>
       </c>
       <c r="B2001" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C2001" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D2001" s="1" t="inlineStr">
@@ -44541,16 +44541,16 @@
     </row>
     <row r="2002">
       <c r="A2002" s="1" t="n">
-        <v>9000024</v>
+        <v>9000023</v>
       </c>
       <c r="B2002" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C2002" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D2002" s="1" t="inlineStr">
@@ -44563,16 +44563,16 @@
     </row>
     <row r="2003">
       <c r="A2003" s="1" t="n">
-        <v>9000025</v>
+        <v>9000024</v>
       </c>
       <c r="B2003" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C2003" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D2003" s="1" t="inlineStr">
@@ -44585,21 +44585,21 @@
     </row>
     <row r="2004">
       <c r="A2004" s="1" t="n">
-        <v>9000026</v>
+        <v>9000025</v>
       </c>
       <c r="B2004" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C2004" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D2004" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2004" s="1" t="n"/>
@@ -44607,21 +44607,21 @@
     </row>
     <row r="2005">
       <c r="A2005" s="1" t="n">
-        <v>9000027</v>
+        <v>9000026</v>
       </c>
       <c r="B2005" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C2005" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D2005" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E2005" s="1" t="n"/>
@@ -44629,16 +44629,16 @@
     </row>
     <row r="2006">
       <c r="A2006" s="1" t="n">
-        <v>9000028</v>
+        <v>9000027</v>
       </c>
       <c r="B2006" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C2006" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D2006" s="1" t="inlineStr">
@@ -44651,21 +44651,21 @@
     </row>
     <row r="2007">
       <c r="A2007" s="1" t="n">
-        <v>9000029</v>
+        <v>9000028</v>
       </c>
       <c r="B2007" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C2007" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D2007" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2007" s="1" t="n"/>
@@ -44673,21 +44673,21 @@
     </row>
     <row r="2008">
       <c r="A2008" s="1" t="n">
-        <v>9000030</v>
+        <v>9000029</v>
       </c>
       <c r="B2008" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C2008" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D2008" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2008" s="1" t="n"/>
@@ -44695,21 +44695,21 @@
     </row>
     <row r="2009">
       <c r="A2009" s="1" t="n">
-        <v>9000031</v>
+        <v>9000030</v>
       </c>
       <c r="B2009" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C2009" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D2009" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E2009" s="1" t="n"/>
@@ -44717,21 +44717,21 @@
     </row>
     <row r="2010">
       <c r="A2010" s="1" t="n">
-        <v>9000032</v>
+        <v>9000031</v>
       </c>
       <c r="B2010" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C2010" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D2010" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E2010" s="1" t="n"/>
@@ -44739,16 +44739,16 @@
     </row>
     <row r="2011">
       <c r="A2011" s="1" t="n">
-        <v>9000033</v>
+        <v>9000032</v>
       </c>
       <c r="B2011" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C2011" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D2011" s="1" t="inlineStr">
@@ -44761,16 +44761,16 @@
     </row>
     <row r="2012">
       <c r="A2012" s="1" t="n">
-        <v>9000034</v>
+        <v>9000033</v>
       </c>
       <c r="B2012" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C2012" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D2012" s="1" t="inlineStr">
@@ -44783,21 +44783,21 @@
     </row>
     <row r="2013">
       <c r="A2013" s="1" t="n">
-        <v>9000035</v>
+        <v>9000034</v>
       </c>
       <c r="B2013" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C2013" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D2013" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2013" s="1" t="n"/>
@@ -44805,21 +44805,21 @@
     </row>
     <row r="2014">
       <c r="A2014" s="1" t="n">
-        <v>9000036</v>
+        <v>9000035</v>
       </c>
       <c r="B2014" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C2014" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D2014" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E2014" s="1" t="n"/>
@@ -44827,21 +44827,21 @@
     </row>
     <row r="2015">
       <c r="A2015" s="1" t="n">
-        <v>9000037</v>
+        <v>9000036</v>
       </c>
       <c r="B2015" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C2015" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D2015" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E2015" s="1" t="n"/>
@@ -44849,21 +44849,21 @@
     </row>
     <row r="2016">
       <c r="A2016" s="1" t="n">
-        <v>9000038</v>
+        <v>9000037</v>
       </c>
       <c r="B2016" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C2016" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D2016" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E2016" s="1" t="n"/>
@@ -44871,21 +44871,21 @@
     </row>
     <row r="2017">
       <c r="A2017" s="1" t="n">
-        <v>9000039</v>
+        <v>9000038</v>
       </c>
       <c r="B2017" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C2017" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D2017" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E2017" s="1" t="n"/>
@@ -44893,21 +44893,21 @@
     </row>
     <row r="2018">
       <c r="A2018" s="1" t="n">
-        <v>9000040</v>
+        <v>9000039</v>
       </c>
       <c r="B2018" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C2018" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D2018" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E2018" s="1" t="n"/>
@@ -44915,21 +44915,21 @@
     </row>
     <row r="2019">
       <c r="A2019" s="1" t="n">
-        <v>9000041</v>
+        <v>9000040</v>
       </c>
       <c r="B2019" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C2019" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D2019" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E2019" s="1" t="n"/>
@@ -44937,21 +44937,21 @@
     </row>
     <row r="2020">
       <c r="A2020" s="1" t="n">
-        <v>9000042</v>
+        <v>9000041</v>
       </c>
       <c r="B2020" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C2020" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D2020" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2020" s="1" t="n"/>
@@ -44959,16 +44959,16 @@
     </row>
     <row r="2021">
       <c r="A2021" s="1" t="n">
-        <v>9000043</v>
+        <v>9000042</v>
       </c>
       <c r="B2021" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C2021" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D2021" s="1" t="inlineStr">
@@ -44981,16 +44981,16 @@
     </row>
     <row r="2022">
       <c r="A2022" s="1" t="n">
-        <v>9000044</v>
+        <v>9000043</v>
       </c>
       <c r="B2022" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C2022" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D2022" s="1" t="inlineStr">
@@ -45003,16 +45003,16 @@
     </row>
     <row r="2023">
       <c r="A2023" s="1" t="n">
-        <v>9000045</v>
+        <v>9000044</v>
       </c>
       <c r="B2023" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C2023" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D2023" s="1" t="inlineStr">
@@ -45025,21 +45025,21 @@
     </row>
     <row r="2024">
       <c r="A2024" s="1" t="n">
-        <v>9000046</v>
+        <v>9000045</v>
       </c>
       <c r="B2024" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C2024" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D2024" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2024" s="1" t="n"/>
@@ -45047,16 +45047,16 @@
     </row>
     <row r="2025">
       <c r="A2025" s="1" t="n">
-        <v>9000047</v>
+        <v>9000046</v>
       </c>
       <c r="B2025" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C2025" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D2025" s="1" t="inlineStr">
@@ -45069,16 +45069,16 @@
     </row>
     <row r="2026">
       <c r="A2026" s="1" t="n">
-        <v>9000048</v>
+        <v>9000047</v>
       </c>
       <c r="B2026" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C2026" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D2026" s="1" t="inlineStr">
@@ -45091,21 +45091,21 @@
     </row>
     <row r="2027">
       <c r="A2027" s="1" t="n">
-        <v>9000049</v>
+        <v>9000048</v>
       </c>
       <c r="B2027" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C2027" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D2027" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2027" s="1" t="n"/>
@@ -45113,21 +45113,21 @@
     </row>
     <row r="2028">
       <c r="A2028" s="1" t="n">
-        <v>9000050</v>
+        <v>9000049</v>
       </c>
       <c r="B2028" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C2028" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D2028" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E2028" s="1" t="n"/>
@@ -45135,21 +45135,21 @@
     </row>
     <row r="2029">
       <c r="A2029" s="1" t="n">
-        <v>9000051</v>
+        <v>9000050</v>
       </c>
       <c r="B2029" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C2029" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D2029" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E2029" s="1" t="n"/>
@@ -45157,16 +45157,16 @@
     </row>
     <row r="2030">
       <c r="A2030" s="1" t="n">
-        <v>9000052</v>
+        <v>9000051</v>
       </c>
       <c r="B2030" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C2030" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D2030" s="1" t="inlineStr">
@@ -45179,21 +45179,21 @@
     </row>
     <row r="2031">
       <c r="A2031" s="1" t="n">
-        <v>9000053</v>
+        <v>9000052</v>
       </c>
       <c r="B2031" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C2031" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D2031" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2031" s="1" t="n"/>
@@ -45201,21 +45201,21 @@
     </row>
     <row r="2032">
       <c r="A2032" s="1" t="n">
-        <v>9000054</v>
+        <v>9000053</v>
       </c>
       <c r="B2032" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C2032" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D2032" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E2032" s="1" t="n"/>
@@ -45223,16 +45223,16 @@
     </row>
     <row r="2033">
       <c r="A2033" s="1" t="n">
-        <v>9000055</v>
+        <v>9000054</v>
       </c>
       <c r="B2033" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C2033" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D2033" s="1" t="inlineStr">
@@ -45245,21 +45245,21 @@
     </row>
     <row r="2034">
       <c r="A2034" s="1" t="n">
-        <v>9000056</v>
+        <v>9000055</v>
       </c>
       <c r="B2034" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C2034" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D2034" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2034" s="1" t="n"/>
@@ -45267,16 +45267,16 @@
     </row>
     <row r="2035">
       <c r="A2035" s="1" t="n">
-        <v>9000057</v>
+        <v>9000056</v>
       </c>
       <c r="B2035" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C2035" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D2035" s="1" t="inlineStr">
@@ -45289,16 +45289,16 @@
     </row>
     <row r="2036">
       <c r="A2036" s="1" t="n">
-        <v>9000058</v>
+        <v>9000057</v>
       </c>
       <c r="B2036" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C2036" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D2036" s="1" t="inlineStr">
@@ -45311,16 +45311,16 @@
     </row>
     <row r="2037">
       <c r="A2037" s="1" t="n">
-        <v>9000059</v>
+        <v>9000058</v>
       </c>
       <c r="B2037" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C2037" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D2037" s="1" t="inlineStr">
@@ -45333,21 +45333,21 @@
     </row>
     <row r="2038">
       <c r="A2038" s="1" t="n">
-        <v>9000060</v>
+        <v>9000059</v>
       </c>
       <c r="B2038" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C2038" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D2038" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2038" s="1" t="n"/>
@@ -45355,16 +45355,16 @@
     </row>
     <row r="2039">
       <c r="A2039" s="1" t="n">
-        <v>9000061</v>
+        <v>9000060</v>
       </c>
       <c r="B2039" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C2039" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D2039" s="1" t="inlineStr">
@@ -45377,16 +45377,16 @@
     </row>
     <row r="2040">
       <c r="A2040" s="1" t="n">
-        <v>9000062</v>
+        <v>9000061</v>
       </c>
       <c r="B2040" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C2040" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D2040" s="1" t="inlineStr">
@@ -45399,16 +45399,16 @@
     </row>
     <row r="2041">
       <c r="A2041" s="1" t="n">
-        <v>9000063</v>
+        <v>9000062</v>
       </c>
       <c r="B2041" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C2041" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D2041" s="1" t="inlineStr">
@@ -45421,16 +45421,16 @@
     </row>
     <row r="2042">
       <c r="A2042" s="1" t="n">
-        <v>9000064</v>
+        <v>9000063</v>
       </c>
       <c r="B2042" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C2042" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D2042" s="1" t="inlineStr">
@@ -45443,21 +45443,21 @@
     </row>
     <row r="2043">
       <c r="A2043" s="1" t="n">
-        <v>9000065</v>
+        <v>9000064</v>
       </c>
       <c r="B2043" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C2043" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D2043" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2043" s="1" t="n"/>
@@ -45465,16 +45465,16 @@
     </row>
     <row r="2044">
       <c r="A2044" s="1" t="n">
-        <v>9000066</v>
+        <v>9000065</v>
       </c>
       <c r="B2044" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C2044" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D2044" s="1" t="inlineStr">
@@ -45487,16 +45487,16 @@
     </row>
     <row r="2045">
       <c r="A2045" s="1" t="n">
-        <v>9000067</v>
+        <v>9000066</v>
       </c>
       <c r="B2045" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C2045" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D2045" s="1" t="inlineStr">
@@ -45509,16 +45509,16 @@
     </row>
     <row r="2046">
       <c r="A2046" s="1" t="n">
-        <v>9000068</v>
+        <v>9000067</v>
       </c>
       <c r="B2046" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C2046" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D2046" s="1" t="inlineStr">
@@ -45531,16 +45531,16 @@
     </row>
     <row r="2047">
       <c r="A2047" s="1" t="n">
-        <v>9000069</v>
+        <v>9000068</v>
       </c>
       <c r="B2047" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C2047" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D2047" s="1" t="inlineStr">
@@ -45553,16 +45553,16 @@
     </row>
     <row r="2048">
       <c r="A2048" s="1" t="n">
-        <v>9000070</v>
+        <v>9000069</v>
       </c>
       <c r="B2048" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C2048" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D2048" s="1" t="inlineStr">
@@ -45575,16 +45575,16 @@
     </row>
     <row r="2049">
       <c r="A2049" s="1" t="n">
-        <v>9000071</v>
+        <v>9000070</v>
       </c>
       <c r="B2049" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C2049" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D2049" s="1" t="inlineStr">
@@ -45597,21 +45597,21 @@
     </row>
     <row r="2050">
       <c r="A2050" s="1" t="n">
-        <v>9000072</v>
+        <v>9000071</v>
       </c>
       <c r="B2050" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C2050" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D2050" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2050" s="1" t="n"/>
@@ -45619,16 +45619,16 @@
     </row>
     <row r="2051">
       <c r="A2051" s="1" t="n">
-        <v>9000073</v>
+        <v>9000072</v>
       </c>
       <c r="B2051" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C2051" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D2051" s="1" t="inlineStr">
@@ -45641,16 +45641,16 @@
     </row>
     <row r="2052">
       <c r="A2052" s="1" t="n">
-        <v>9000074</v>
+        <v>9000073</v>
       </c>
       <c r="B2052" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C2052" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D2052" s="1" t="inlineStr">
@@ -45663,16 +45663,16 @@
     </row>
     <row r="2053">
       <c r="A2053" s="1" t="n">
-        <v>9000075</v>
+        <v>9000074</v>
       </c>
       <c r="B2053" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C2053" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D2053" s="1" t="inlineStr">
@@ -45685,16 +45685,16 @@
     </row>
     <row r="2054">
       <c r="A2054" s="1" t="n">
-        <v>9000076</v>
+        <v>9000075</v>
       </c>
       <c r="B2054" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C2054" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D2054" s="1" t="inlineStr">
@@ -45707,21 +45707,21 @@
     </row>
     <row r="2055">
       <c r="A2055" s="1" t="n">
-        <v>9000077</v>
+        <v>9000076</v>
       </c>
       <c r="B2055" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C2055" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D2055" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2055" s="1" t="n"/>
@@ -45729,16 +45729,16 @@
     </row>
     <row r="2056">
       <c r="A2056" s="1" t="n">
-        <v>9000078</v>
+        <v>9000077</v>
       </c>
       <c r="B2056" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C2056" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D2056" s="1" t="inlineStr">
@@ -45751,16 +45751,16 @@
     </row>
     <row r="2057">
       <c r="A2057" s="1" t="n">
-        <v>9000079</v>
+        <v>9000078</v>
       </c>
       <c r="B2057" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C2057" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D2057" s="1" t="inlineStr">
@@ -45773,16 +45773,16 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>9000080</v>
+        <v>9000079</v>
       </c>
       <c r="B2058" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C2058" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D2058" s="1" t="inlineStr">
@@ -45795,21 +45795,21 @@
     </row>
     <row r="2059">
       <c r="A2059" s="1" t="n">
-        <v>9000081</v>
+        <v>9000080</v>
       </c>
       <c r="B2059" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C2059" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D2059" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2059" s="1" t="n"/>
@@ -45817,16 +45817,16 @@
     </row>
     <row r="2060">
       <c r="A2060" s="1" t="n">
-        <v>9000082</v>
+        <v>9000081</v>
       </c>
       <c r="B2060" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C2060" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D2060" s="1" t="inlineStr">
@@ -45839,21 +45839,21 @@
     </row>
     <row r="2061">
       <c r="A2061" s="1" t="n">
-        <v>9000083</v>
+        <v>9000082</v>
       </c>
       <c r="B2061" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C2061" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D2061" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2061" s="1" t="n"/>
@@ -45861,16 +45861,16 @@
     </row>
     <row r="2062">
       <c r="A2062" s="1" t="n">
-        <v>9000084</v>
+        <v>9000083</v>
       </c>
       <c r="B2062" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>헉헉</t>
         </is>
       </c>
       <c r="C2062" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>Huff puff</t>
         </is>
       </c>
       <c r="D2062" s="1" t="inlineStr">
@@ -45883,16 +45883,16 @@
     </row>
     <row r="2063">
       <c r="A2063" s="1" t="n">
-        <v>9000085</v>
+        <v>9000084</v>
       </c>
       <c r="B2063" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>더 빨리!</t>
         </is>
       </c>
       <c r="C2063" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>Faster!</t>
         </is>
       </c>
       <c r="D2063" s="1" t="inlineStr">
@@ -45905,16 +45905,16 @@
     </row>
     <row r="2064">
       <c r="A2064" s="1" t="n">
-        <v>9000086</v>
+        <v>9000085</v>
       </c>
       <c r="B2064" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>근육 붙는 중</t>
         </is>
       </c>
       <c r="C2064" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>Gains incoming</t>
         </is>
       </c>
       <c r="D2064" s="1" t="inlineStr">
@@ -45927,21 +45927,21 @@
     </row>
     <row r="2065">
       <c r="A2065" s="1" t="n">
-        <v>9000087</v>
+        <v>9000086</v>
       </c>
       <c r="B2065" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>찍찍찍찍</t>
         </is>
       </c>
       <c r="C2065" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>Squeak squeak squeak squeak</t>
         </is>
       </c>
       <c r="D2065" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2065" s="1" t="n"/>
@@ -45949,16 +45949,16 @@
     </row>
     <row r="2066">
       <c r="A2066" s="1" t="n">
-        <v>9000088</v>
+        <v>9000087</v>
       </c>
       <c r="B2066" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>으아아아~!</t>
         </is>
       </c>
       <c r="C2066" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>Waaaaah~!</t>
         </is>
       </c>
       <c r="D2066" s="1" t="inlineStr">
@@ -45971,16 +45971,16 @@
     </row>
     <row r="2067">
       <c r="A2067" s="1" t="n">
-        <v>9000089</v>
+        <v>9000088</v>
       </c>
       <c r="B2067" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>하암~ 잘 잤다</t>
         </is>
       </c>
       <c r="C2067" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>Yawn~ what a nap</t>
         </is>
       </c>
       <c r="D2067" s="1" t="inlineStr">
@@ -45993,16 +45993,16 @@
     </row>
     <row r="2068">
       <c r="A2068" s="1" t="n">
-        <v>9000090</v>
+        <v>9000089</v>
       </c>
       <c r="B2068" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>냠, 배부르다</t>
         </is>
       </c>
       <c r="C2068" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>Nom, so full</t>
         </is>
       </c>
       <c r="D2068" s="1" t="inlineStr">
@@ -46015,21 +46015,21 @@
     </row>
     <row r="2069">
       <c r="A2069" s="1" t="n">
-        <v>9000091</v>
+        <v>9000090</v>
       </c>
       <c r="B2069" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>휴…</t>
         </is>
       </c>
       <c r="C2069" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Phew...</t>
         </is>
       </c>
       <c r="D2069" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2069" s="1" t="n"/>
@@ -46037,21 +46037,21 @@
     </row>
     <row r="2070">
       <c r="A2070" s="1" t="n">
-        <v>9000092</v>
+        <v>9000091</v>
       </c>
       <c r="B2070" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>찍</t>
         </is>
       </c>
       <c r="C2070" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Squeak</t>
         </is>
       </c>
       <c r="D2070" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
         </is>
       </c>
       <c r="E2070" s="1" t="n"/>
@@ -46059,21 +46059,21 @@
     </row>
     <row r="2071">
       <c r="A2071" s="1" t="n">
-        <v>9000093</v>
+        <v>9000092</v>
       </c>
       <c r="B2071" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C2071" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D2071" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Lobby/RunPage.cs:99</t>
         </is>
       </c>
       <c r="E2071" s="1" t="n"/>
@@ -46081,21 +46081,21 @@
     </row>
     <row r="2072">
       <c r="A2072" s="1" t="n">
-        <v>9000094</v>
+        <v>9000093</v>
       </c>
       <c r="B2072" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="C2072" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D2072" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
         </is>
       </c>
       <c r="E2072" s="1" t="n"/>
@@ -46103,16 +46103,16 @@
     </row>
     <row r="2073">
       <c r="A2073" s="1" t="n">
-        <v>9000095</v>
+        <v>9000094</v>
       </c>
       <c r="B2073" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>찌릿!!</t>
         </is>
       </c>
       <c r="C2073" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>ZAP!!</t>
         </is>
       </c>
       <c r="D2073" s="1" t="inlineStr">
@@ -46125,21 +46125,21 @@
     </row>
     <row r="2074">
       <c r="A2074" s="1" t="n">
-        <v>9000096</v>
+        <v>9000095</v>
       </c>
       <c r="B2074" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>콰릉!</t>
         </is>
       </c>
       <c r="C2074" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>Ka-boom!</t>
         </is>
       </c>
       <c r="D2074" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2074" s="1" t="n"/>
@@ -46147,16 +46147,16 @@
     </row>
     <row r="2075">
       <c r="A2075" s="1" t="n">
-        <v>9000097</v>
+        <v>9000096</v>
       </c>
       <c r="B2075" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>냠!</t>
         </is>
       </c>
       <c r="C2075" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>Nom!</t>
         </is>
       </c>
       <c r="D2075" s="1" t="inlineStr">
@@ -46169,21 +46169,21 @@
     </row>
     <row r="2076">
       <c r="A2076" s="1" t="n">
-        <v>9000098</v>
+        <v>9000097</v>
       </c>
       <c r="B2076" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>다닥!</t>
         </is>
       </c>
       <c r="C2076" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>Scurry!</t>
         </is>
       </c>
       <c r="D2076" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2076" s="1" t="n"/>
@@ -46191,16 +46191,16 @@
     </row>
     <row r="2077">
       <c r="A2077" s="1" t="n">
-        <v>9000099</v>
+        <v>9000098</v>
       </c>
       <c r="B2077" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>메리 쥐스마스!</t>
         </is>
       </c>
       <c r="C2077" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>Merry Ratmas!</t>
         </is>
       </c>
       <c r="D2077" s="1" t="inlineStr">
@@ -46213,16 +46213,16 @@
     </row>
     <row r="2078">
       <c r="A2078" s="1" t="n">
-        <v>9000100</v>
+        <v>9000099</v>
       </c>
       <c r="B2078" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>흐에~ 후원 감사합니다~!</t>
         </is>
       </c>
       <c r="C2078" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>Heheh~ thanks for the dono~!</t>
         </is>
       </c>
       <c r="D2078" s="1" t="inlineStr">
@@ -46235,21 +46235,21 @@
     </row>
     <row r="2079">
       <c r="A2079" s="1" t="n">
-        <v>9000101</v>
+        <v>9000100</v>
       </c>
       <c r="B2079" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>배달 왔습니다~</t>
         </is>
       </c>
       <c r="C2079" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>Delivery~!</t>
         </is>
       </c>
       <c r="D2079" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2079" s="1" t="n"/>
@@ -46257,16 +46257,16 @@
     </row>
     <row r="2080">
       <c r="A2080" s="1" t="n">
-        <v>9000102</v>
+        <v>9000101</v>
       </c>
       <c r="B2080" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>백덤블링!</t>
         </is>
       </c>
       <c r="C2080" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>Backflip!</t>
         </is>
       </c>
       <c r="D2080" s="1" t="inlineStr">
@@ -46279,16 +46279,16 @@
     </row>
     <row r="2081">
       <c r="A2081" s="1" t="n">
-        <v>9000103</v>
+        <v>9000102</v>
       </c>
       <c r="B2081" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>공중제비!</t>
         </is>
       </c>
       <c r="C2081" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Somersault!</t>
         </is>
       </c>
       <c r="D2081" s="1" t="inlineStr">
@@ -46301,21 +46301,21 @@
     </row>
     <row r="2082">
       <c r="A2082" s="1" t="n">
-        <v>9000104</v>
+        <v>9000103</v>
       </c>
       <c r="B2082" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>찍-공중회전!</t>
         </is>
       </c>
       <c r="C2082" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Squeak-flip!</t>
         </is>
       </c>
       <c r="D2082" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2082" s="1" t="n"/>
@@ -46323,16 +46323,16 @@
     </row>
     <row r="2083">
       <c r="A2083" s="1" t="n">
-        <v>9000105</v>
+        <v>9000104</v>
       </c>
       <c r="B2083" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>트리플 악셀!!</t>
         </is>
       </c>
       <c r="C2083" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>TRIPLE AXEL!!</t>
         </is>
       </c>
       <c r="D2083" s="1" t="inlineStr">
@@ -46345,16 +46345,16 @@
     </row>
     <row r="2084">
       <c r="A2084" s="1" t="n">
-        <v>9000106</v>
+        <v>9000105</v>
       </c>
       <c r="B2084" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>3회전 성공!</t>
         </is>
       </c>
       <c r="C2084" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>Triple spin landed!</t>
         </is>
       </c>
       <c r="D2084" s="1" t="inlineStr">
@@ -46367,21 +46367,21 @@
     </row>
     <row r="2085">
       <c r="A2085" s="1" t="n">
-        <v>9000107</v>
+        <v>9000106</v>
       </c>
       <c r="B2085" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>심사위원 전원 10점!</t>
         </is>
       </c>
       <c r="C2085" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>Perfect 10s from every judge!</t>
         </is>
       </c>
       <c r="D2085" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2085" s="1" t="n"/>
@@ -46389,16 +46389,16 @@
     </row>
     <row r="2086">
       <c r="A2086" s="1" t="n">
-        <v>9000108</v>
+        <v>9000107</v>
       </c>
       <c r="B2086" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>윈드밀!!</t>
         </is>
       </c>
       <c r="C2086" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>WINDMILL!!</t>
         </is>
       </c>
       <c r="D2086" s="1" t="inlineStr">
@@ -46411,16 +46411,16 @@
     </row>
     <row r="2087">
       <c r="A2087" s="1" t="n">
-        <v>9000109</v>
+        <v>9000108</v>
       </c>
       <c r="B2087" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>브레이크 댄스!</t>
         </is>
       </c>
       <c r="C2087" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>Breakdance!</t>
         </is>
       </c>
       <c r="D2087" s="1" t="inlineStr">
@@ -46433,21 +46433,21 @@
     </row>
     <row r="2088">
       <c r="A2088" s="1" t="n">
-        <v>9000110</v>
+        <v>9000109</v>
       </c>
       <c r="B2088" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>빙글빙글 파괴!</t>
         </is>
       </c>
       <c r="C2088" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>Spin-to-win destruction!</t>
         </is>
       </c>
       <c r="D2088" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2088" s="1" t="n"/>
@@ -46455,16 +46455,16 @@
     </row>
     <row r="2089">
       <c r="A2089" s="1" t="n">
-        <v>9000111</v>
+        <v>9000110</v>
       </c>
       <c r="B2089" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>쥐 대포알!</t>
         </is>
       </c>
       <c r="C2089" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>Rat Cannonball!</t>
         </is>
       </c>
       <c r="D2089" s="1" t="inlineStr">
@@ -46477,16 +46477,16 @@
     </row>
     <row r="2090">
       <c r="A2090" s="1" t="n">
-        <v>9000112</v>
+        <v>9000111</v>
       </c>
       <c r="B2090" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>데굴데굴!</t>
         </is>
       </c>
       <c r="C2090" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>Roll roll!</t>
         </is>
       </c>
       <c r="D2090" s="1" t="inlineStr">
@@ -46499,21 +46499,21 @@
     </row>
     <row r="2091">
       <c r="A2091" s="1" t="n">
-        <v>9000113</v>
+        <v>9000112</v>
       </c>
       <c r="B2091" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>핀볼 모드!</t>
         </is>
       </c>
       <c r="C2091" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>Pinball mode!</t>
         </is>
       </c>
       <c r="D2091" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2091" s="1" t="n"/>
@@ -46521,16 +46521,16 @@
     </row>
     <row r="2092">
       <c r="A2092" s="1" t="n">
-        <v>9000114</v>
+        <v>9000113</v>
       </c>
       <c r="B2092" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>쳇바퀴 돌기!!</t>
         </is>
       </c>
       <c r="C2092" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>WHEEL SPIN!!</t>
         </is>
       </c>
       <c r="D2092" s="1" t="inlineStr">
@@ -46543,16 +46543,16 @@
     </row>
     <row r="2093">
       <c r="A2093" s="1" t="n">
-        <v>9000115</v>
+        <v>9000114</v>
       </c>
       <c r="B2093" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>빙글빙글~</t>
         </is>
       </c>
       <c r="C2093" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>Round and round~</t>
         </is>
       </c>
       <c r="D2093" s="1" t="inlineStr">
@@ -46565,21 +46565,21 @@
     </row>
     <row r="2094">
       <c r="A2094" s="1" t="n">
-        <v>9000116</v>
+        <v>9000115</v>
       </c>
       <c r="B2094" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>어지러워!!</t>
         </is>
       </c>
       <c r="C2094" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>So DIZZY!!</t>
         </is>
       </c>
       <c r="D2094" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2094" s="1" t="n"/>
@@ -46587,21 +46587,21 @@
     </row>
     <row r="2095">
       <c r="A2095" s="1" t="n">
-        <v>9000117</v>
+        <v>9000116</v>
       </c>
       <c r="B2095" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="C2095" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="D2095" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
         </is>
       </c>
       <c r="E2095" s="1" t="n"/>
@@ -46609,21 +46609,21 @@
     </row>
     <row r="2096">
       <c r="A2096" s="1" t="n">
-        <v>9000118</v>
+        <v>9000117</v>
       </c>
       <c r="B2096" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>기절!!</t>
         </is>
       </c>
       <c r="C2096" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>Stunned!!</t>
         </is>
       </c>
       <c r="D2096" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Rats/RatManager.cs:38</t>
         </is>
       </c>
       <c r="E2096" s="1" t="n"/>
@@ -46631,21 +46631,21 @@
     </row>
     <row r="2097">
       <c r="A2097" s="1" t="n">
-        <v>9000119</v>
+        <v>9000118</v>
       </c>
       <c r="B2097" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>소품이 떨어졌다!</t>
         </is>
       </c>
       <c r="C2097" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>A prop dropped!</t>
         </is>
       </c>
       <c r="D2097" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Rats/RatManager.cs:397</t>
         </is>
       </c>
       <c r="E2097" s="1" t="n"/>
@@ -46653,21 +46653,21 @@
     </row>
     <row r="2098">
       <c r="A2098" s="1" t="n">
-        <v>9000120</v>
+        <v>9000119</v>
       </c>
       <c r="B2098" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>조각 +1</t>
         </is>
       </c>
       <c r="C2098" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>Shard +1</t>
         </is>
       </c>
       <c r="D2098" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Rats/RatManager.cs:460</t>
         </is>
       </c>
       <c r="E2098" s="1" t="n"/>
@@ -46675,21 +46675,21 @@
     </row>
     <row r="2099">
       <c r="A2099" s="1" t="n">
-        <v>9000121</v>
+        <v>9000120</v>
       </c>
       <c r="B2099" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>{name} 강화! Lv {lv}</t>
         </is>
       </c>
       <c r="C2099" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>{name} powered up! Lv {lv}</t>
         </is>
       </c>
       <c r="D2099" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Rats/RatManager.cs:461</t>
         </is>
       </c>
       <c r="E2099" s="1" t="n"/>
@@ -46697,21 +46697,21 @@
     </row>
     <row r="2100">
       <c r="A2100" s="1" t="n">
-        <v>9000122</v>
+        <v>9000121</v>
       </c>
       <c r="B2100" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>{grade} 탄생!</t>
         </is>
       </c>
       <c r="C2100" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>{grade} born!</t>
         </is>
       </c>
       <c r="D2100" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Rats/RatManager.cs:561</t>
         </is>
       </c>
       <c r="E2100" s="1" t="n"/>
@@ -46719,21 +46719,21 @@
     </row>
     <row r="2101">
       <c r="A2101" s="1" t="n">
-        <v>9000123</v>
+        <v>9000122</v>
       </c>
       <c r="B2101" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>쌍둥이!</t>
         </is>
       </c>
       <c r="C2101" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>Twins!</t>
         </is>
       </c>
       <c r="D2101" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Rats/RatManager.cs:566</t>
         </is>
       </c>
       <c r="E2101" s="1" t="n"/>
@@ -46741,21 +46741,21 @@
     </row>
     <row r="2102">
       <c r="A2102" s="1" t="n">
-        <v>9000124</v>
+        <v>9000123</v>
       </c>
       <c r="B2102" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>치즈 운석!</t>
         </is>
       </c>
       <c r="C2102" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>Cheese Meteor!</t>
         </is>
       </c>
       <c r="D2102" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:627</t>
         </is>
       </c>
       <c r="E2102" s="1" t="n"/>
@@ -46763,21 +46763,21 @@
     </row>
     <row r="2103">
       <c r="A2103" s="1" t="n">
-        <v>9000125</v>
+        <v>9000124</v>
       </c>
       <c r="B2103" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>{floor}층 · {zone}</t>
         </is>
       </c>
       <c r="C2103" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>Floor {floor} · {zone}</t>
         </is>
       </c>
       <c r="D2103" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E2103" s="1" t="n"/>
@@ -46785,21 +46785,21 @@
     </row>
     <row r="2104">
       <c r="A2104" s="1" t="n">
-        <v>9000126</v>
+        <v>9000125</v>
       </c>
       <c r="B2104" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>계단 방 벽을 부숴라!</t>
         </is>
       </c>
       <c r="C2104" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>Smash the wall to the stairs room!</t>
         </is>
       </c>
       <c r="D2104" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E2104" s="1" t="n"/>
@@ -46807,21 +46807,21 @@
     </row>
     <row r="2105">
       <c r="A2105" s="1" t="n">
-        <v>9000127</v>
+        <v>9000126</v>
       </c>
       <c r="B2105" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>벽 붕괴! 방 확장</t>
         </is>
       </c>
       <c r="C2105" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>Wall down! Room expanded</t>
         </is>
       </c>
       <c r="D2105" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2105" s="1" t="n"/>
@@ -46829,16 +46829,16 @@
     </row>
     <row r="2106">
       <c r="A2106" s="1" t="n">
-        <v>9000128</v>
+        <v>9000127</v>
       </c>
       <c r="B2106" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>계단 발견!</t>
         </is>
       </c>
       <c r="C2106" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>Stairs found!</t>
         </is>
       </c>
       <c r="D2106" s="1" t="inlineStr">
@@ -46851,21 +46851,21 @@
     </row>
     <row r="2107">
       <c r="A2107" s="1" t="n">
-        <v>9000129</v>
+        <v>9000128</v>
       </c>
       <c r="B2107" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>계단에 닿으면 {next}층으로</t>
         </is>
       </c>
       <c r="C2107" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>Touch the stairs to go to Floor {next}</t>
         </is>
       </c>
       <c r="D2107" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:338</t>
         </is>
       </c>
       <c r="E2107" s="1" t="n"/>
@@ -46873,16 +46873,16 @@
     </row>
     <row r="2108">
       <c r="A2108" s="1" t="n">
-        <v>9000130</v>
+        <v>9000129</v>
       </c>
       <c r="B2108" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>와르르!!</t>
         </is>
       </c>
       <c r="C2108" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Crumble!!</t>
         </is>
       </c>
       <c r="D2108" s="1" t="inlineStr">
@@ -46895,16 +46895,16 @@
     </row>
     <row r="2109">
       <c r="A2109" s="1" t="n">
-        <v>9000131</v>
+        <v>9000130</v>
       </c>
       <c r="B2109" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>콰광!!</t>
         </is>
       </c>
       <c r="C2109" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>KA-BOOM!!</t>
         </is>
       </c>
       <c r="D2109" s="1" t="inlineStr">
@@ -46914,6 +46914,28 @@
       </c>
       <c r="E2109" s="1" t="n"/>
       <c r="F2109" s="1" t="n"/>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B2110" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C2110" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D2110" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E2110" s="1" t="n"/>
+      <c r="F2110" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -38937,12 +38937,12 @@
       </c>
       <c r="B1749" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! 훈장 달기!</t>
+          <t>찍찍!! 훈장 보러 가기!</t>
         </is>
       </c>
       <c r="C1749" s="2" t="inlineStr">
         <is>
-          <t>Earn SQUEAK!! Rank!</t>
+          <t>Go to SQUEAK!! Rank!</t>
         </is>
       </c>
       <c r="D1749" s="1" t="inlineStr">

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2166"/>
+  <dimension ref="A1:F2179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -45289,21 +45289,21 @@
     </row>
     <row r="2036">
       <c r="A2036" s="1" t="n">
-        <v>9000001</v>
+        <v>8000440</v>
       </c>
       <c r="B2036" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power} / 적정 {need}</t>
+          <t>※ 다람쥐 헌 쳇바퀴에 타고파~</t>
         </is>
       </c>
       <c r="C2036" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power} / Rec. {need}</t>
+          <t>※ Squirrel wants a spin on the old wheel~</t>
         </is>
       </c>
       <c r="D2036" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Ramjui/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2036" s="1" t="n"/>
@@ -45311,21 +45311,21 @@
     </row>
     <row r="2037">
       <c r="A2037" s="1" t="n">
-        <v>9000002</v>
+        <v>8000441</v>
       </c>
       <c r="B2037" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>{n}명</t>
         </is>
       </c>
       <c r="C2037" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>{n} subs</t>
         </is>
       </c>
       <c r="D2037" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/StreamRat/Intro/Counter/Text</t>
         </is>
       </c>
       <c r="E2037" s="1" t="n"/>
@@ -45333,21 +45333,21 @@
     </row>
     <row r="2038">
       <c r="A2038" s="1" t="n">
-        <v>9000003</v>
+        <v>8000442</v>
       </c>
       <c r="B2038" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>※ 앵콜 요청은 마음속으로만</t>
         </is>
       </c>
       <c r="C2038" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>※ Please keep encore requests in your heart</t>
         </is>
       </c>
       <c r="D2038" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Jwerry/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2038" s="1" t="n"/>
@@ -45355,21 +45355,21 @@
     </row>
     <row r="2039">
       <c r="A2039" s="1" t="n">
-        <v>9000004</v>
+        <v>8000443</v>
       </c>
       <c r="B2039" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>※ 소원 추가 요청은 반려되었습니다</t>
         </is>
       </c>
       <c r="C2039" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>※ Request for more wishes: DENIED</t>
         </is>
       </c>
       <c r="D2039" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Sultan/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2039" s="1" t="n"/>
@@ -45377,21 +45377,21 @@
     </row>
     <row r="2040">
       <c r="A2040" s="1" t="n">
-        <v>9000005</v>
+        <v>8000444</v>
       </c>
       <c r="B2040" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>※ 얼어 죽어도 아이스 아메리카노</t>
         </is>
       </c>
       <c r="C2040" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>※ Iced Americano, even if I freeze</t>
         </is>
       </c>
       <c r="D2040" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/IceQueen/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2040" s="1" t="n"/>
@@ -45399,21 +45399,21 @@
     </row>
     <row r="2041">
       <c r="A2041" s="1" t="n">
-        <v>9000006</v>
+        <v>8000445</v>
       </c>
       <c r="B2041" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>※ 쭈욱~ 늘어나는 건 국룰</t>
         </is>
       </c>
       <c r="C2041" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>※ The cheese pull is mandatory</t>
         </is>
       </c>
       <c r="D2041" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Fondue/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2041" s="1" t="n"/>
@@ -45421,21 +45421,21 @@
     </row>
     <row r="2042">
       <c r="A2042" s="1" t="n">
-        <v>9000007</v>
+        <v>8000446</v>
       </c>
       <c r="B2042" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>※ 범인은 이 안에 있다!</t>
         </is>
       </c>
       <c r="C2042" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>※ The culprit is among us!</t>
         </is>
       </c>
       <c r="D2042" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/JJDetective/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2042" s="1" t="n"/>
@@ -45443,21 +45443,21 @@
     </row>
     <row r="2043">
       <c r="A2043" s="1" t="n">
-        <v>9000008</v>
+        <v>8000447</v>
       </c>
       <c r="B2043" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>※ 구독 · 좋아요 · 알림 설정까지!</t>
         </is>
       </c>
       <c r="C2043" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>※ Like, subscribe and hit the bell!</t>
         </is>
       </c>
       <c r="D2043" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/StreamRat/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2043" s="1" t="n"/>
@@ -45465,21 +45465,21 @@
     </row>
     <row r="2044">
       <c r="A2044" s="1" t="n">
-        <v>9000009</v>
+        <v>8000448</v>
       </c>
       <c r="B2044" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>※ 자외선 지수: 매우 위험</t>
         </is>
       </c>
       <c r="C2044" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>※ UV index: EXTREME</t>
         </is>
       </c>
       <c r="D2044" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Pharaoh/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2044" s="1" t="n"/>
@@ -45487,21 +45487,21 @@
     </row>
     <row r="2045">
       <c r="A2045" s="1" t="n">
-        <v>9000010</v>
+        <v>8000449</v>
       </c>
       <c r="B2045" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>※ 소는 촬영 후 무사히 돌려보냈습니다</t>
         </is>
       </c>
       <c r="C2045" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>※ The cow was safely returned after filming</t>
         </is>
       </c>
       <c r="D2045" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Alien/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2045" s="1" t="n"/>
@@ -45509,21 +45509,21 @@
     </row>
     <row r="2046">
       <c r="A2046" s="1" t="n">
-        <v>9000011</v>
+        <v>8000450</v>
       </c>
       <c r="B2046" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>※ 익힘 정도: 완벽하게 이븐함</t>
         </is>
       </c>
       <c r="C2046" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>※ Doneness: perfectly even</t>
         </is>
       </c>
       <c r="D2046" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/StarChef/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2046" s="1" t="n"/>
@@ -45531,21 +45531,21 @@
     </row>
     <row r="2047">
       <c r="A2047" s="1" t="n">
-        <v>9000012</v>
+        <v>8000451</v>
       </c>
       <c r="B2047" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>※ 시전 후 MP 0 · 이동 불가</t>
         </is>
       </c>
       <c r="C2047" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>※ After casting: MP 0 · cannot move</t>
         </is>
       </c>
       <c r="D2047" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Bomber/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2047" s="1" t="n"/>
@@ -45553,21 +45553,21 @@
     </row>
     <row r="2048">
       <c r="A2048" s="1" t="n">
-        <v>9000013</v>
+        <v>8000452</v>
       </c>
       <c r="B2048" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>※ 원탁이라 상석 다툼 없음 (아마도)</t>
         </is>
       </c>
       <c r="C2048" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>※ Round table, so no fighting over seats (probably)</t>
         </is>
       </c>
       <c r="D2048" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Knight/Finish/MemeText/Text</t>
         </is>
       </c>
       <c r="E2048" s="1" t="n"/>
@@ -45575,21 +45575,21 @@
     </row>
     <row r="2049">
       <c r="A2049" s="1" t="n">
-        <v>9000014</v>
+        <v>9000001</v>
       </c>
       <c r="B2049" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>찍찍!! {power} / 적정 {need}</t>
         </is>
       </c>
       <c r="C2049" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>SQUEAK!! {power} / Rec. {need}</t>
         </is>
       </c>
       <c r="D2049" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E2049" s="1" t="n"/>
@@ -45597,21 +45597,21 @@
     </row>
     <row r="2050">
       <c r="A2050" s="1" t="n">
-        <v>9000015</v>
+        <v>9000002</v>
       </c>
       <c r="B2050" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C2050" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D2050" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2050" s="1" t="n"/>
@@ -45619,21 +45619,21 @@
     </row>
     <row r="2051">
       <c r="A2051" s="1" t="n">
-        <v>9000016</v>
+        <v>9000003</v>
       </c>
       <c r="B2051" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C2051" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D2051" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E2051" s="1" t="n"/>
@@ -45641,21 +45641,21 @@
     </row>
     <row r="2052">
       <c r="A2052" s="1" t="n">
-        <v>9000017</v>
+        <v>9000004</v>
       </c>
       <c r="B2052" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C2052" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D2052" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E2052" s="1" t="n"/>
@@ -45663,21 +45663,21 @@
     </row>
     <row r="2053">
       <c r="A2053" s="1" t="n">
-        <v>9000018</v>
+        <v>9000005</v>
       </c>
       <c r="B2053" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C2053" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D2053" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E2053" s="1" t="n"/>
@@ -45685,21 +45685,21 @@
     </row>
     <row r="2054">
       <c r="A2054" s="1" t="n">
-        <v>9000019</v>
+        <v>9000006</v>
       </c>
       <c r="B2054" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C2054" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D2054" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E2054" s="1" t="n"/>
@@ -45707,21 +45707,21 @@
     </row>
     <row r="2055">
       <c r="A2055" s="1" t="n">
-        <v>9000020</v>
+        <v>9000007</v>
       </c>
       <c r="B2055" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C2055" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D2055" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E2055" s="1" t="n"/>
@@ -45729,21 +45729,21 @@
     </row>
     <row r="2056">
       <c r="A2056" s="1" t="n">
-        <v>9000021</v>
+        <v>9000008</v>
       </c>
       <c r="B2056" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C2056" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D2056" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2056" s="1" t="n"/>
@@ -45751,21 +45751,21 @@
     </row>
     <row r="2057">
       <c r="A2057" s="1" t="n">
-        <v>9000022</v>
+        <v>9000009</v>
       </c>
       <c r="B2057" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C2057" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D2057" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2057" s="1" t="n"/>
@@ -45773,21 +45773,21 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>9000023</v>
+        <v>9000010</v>
       </c>
       <c r="B2058" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C2058" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D2058" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2058" s="1" t="n"/>
@@ -45795,21 +45795,21 @@
     </row>
     <row r="2059">
       <c r="A2059" s="1" t="n">
-        <v>9000024</v>
+        <v>9000011</v>
       </c>
       <c r="B2059" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C2059" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D2059" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2059" s="1" t="n"/>
@@ -45817,21 +45817,21 @@
     </row>
     <row r="2060">
       <c r="A2060" s="1" t="n">
-        <v>9000025</v>
+        <v>9000012</v>
       </c>
       <c r="B2060" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C2060" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D2060" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2060" s="1" t="n"/>
@@ -45839,21 +45839,21 @@
     </row>
     <row r="2061">
       <c r="A2061" s="1" t="n">
-        <v>9000026</v>
+        <v>9000013</v>
       </c>
       <c r="B2061" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C2061" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D2061" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2061" s="1" t="n"/>
@@ -45861,21 +45861,21 @@
     </row>
     <row r="2062">
       <c r="A2062" s="1" t="n">
-        <v>9000027</v>
+        <v>9000014</v>
       </c>
       <c r="B2062" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C2062" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D2062" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E2062" s="1" t="n"/>
@@ -45883,21 +45883,21 @@
     </row>
     <row r="2063">
       <c r="A2063" s="1" t="n">
-        <v>9000028</v>
+        <v>9000015</v>
       </c>
       <c r="B2063" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C2063" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D2063" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2063" s="1" t="n"/>
@@ -45905,21 +45905,21 @@
     </row>
     <row r="2064">
       <c r="A2064" s="1" t="n">
-        <v>9000029</v>
+        <v>9000016</v>
       </c>
       <c r="B2064" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C2064" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D2064" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2064" s="1" t="n"/>
@@ -45927,21 +45927,21 @@
     </row>
     <row r="2065">
       <c r="A2065" s="1" t="n">
-        <v>9000030</v>
+        <v>9000017</v>
       </c>
       <c r="B2065" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C2065" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D2065" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E2065" s="1" t="n"/>
@@ -45949,21 +45949,21 @@
     </row>
     <row r="2066">
       <c r="A2066" s="1" t="n">
-        <v>9000031</v>
+        <v>9000018</v>
       </c>
       <c r="B2066" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C2066" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D2066" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2066" s="1" t="n"/>
@@ -45971,21 +45971,21 @@
     </row>
     <row r="2067">
       <c r="A2067" s="1" t="n">
-        <v>9000032</v>
+        <v>9000019</v>
       </c>
       <c r="B2067" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C2067" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D2067" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2067" s="1" t="n"/>
@@ -45993,21 +45993,21 @@
     </row>
     <row r="2068">
       <c r="A2068" s="1" t="n">
-        <v>9000033</v>
+        <v>9000020</v>
       </c>
       <c r="B2068" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C2068" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D2068" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2068" s="1" t="n"/>
@@ -46015,21 +46015,21 @@
     </row>
     <row r="2069">
       <c r="A2069" s="1" t="n">
-        <v>9000034</v>
+        <v>9000021</v>
       </c>
       <c r="B2069" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C2069" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D2069" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E2069" s="1" t="n"/>
@@ -46037,21 +46037,21 @@
     </row>
     <row r="2070">
       <c r="A2070" s="1" t="n">
-        <v>9000035</v>
+        <v>9000022</v>
       </c>
       <c r="B2070" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C2070" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D2070" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2070" s="1" t="n"/>
@@ -46059,21 +46059,21 @@
     </row>
     <row r="2071">
       <c r="A2071" s="1" t="n">
-        <v>9000036</v>
+        <v>9000023</v>
       </c>
       <c r="B2071" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C2071" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D2071" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2071" s="1" t="n"/>
@@ -46081,21 +46081,21 @@
     </row>
     <row r="2072">
       <c r="A2072" s="1" t="n">
-        <v>9000037</v>
+        <v>9000024</v>
       </c>
       <c r="B2072" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C2072" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D2072" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2072" s="1" t="n"/>
@@ -46103,21 +46103,21 @@
     </row>
     <row r="2073">
       <c r="A2073" s="1" t="n">
-        <v>9000038</v>
+        <v>9000025</v>
       </c>
       <c r="B2073" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C2073" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D2073" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2073" s="1" t="n"/>
@@ -46125,21 +46125,21 @@
     </row>
     <row r="2074">
       <c r="A2074" s="1" t="n">
-        <v>9000039</v>
+        <v>9000026</v>
       </c>
       <c r="B2074" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C2074" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D2074" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E2074" s="1" t="n"/>
@@ -46147,21 +46147,21 @@
     </row>
     <row r="2075">
       <c r="A2075" s="1" t="n">
-        <v>9000040</v>
+        <v>9000027</v>
       </c>
       <c r="B2075" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C2075" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D2075" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2075" s="1" t="n"/>
@@ -46169,21 +46169,21 @@
     </row>
     <row r="2076">
       <c r="A2076" s="1" t="n">
-        <v>9000041</v>
+        <v>9000028</v>
       </c>
       <c r="B2076" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C2076" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D2076" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2076" s="1" t="n"/>
@@ -46191,21 +46191,21 @@
     </row>
     <row r="2077">
       <c r="A2077" s="1" t="n">
-        <v>9000042</v>
+        <v>9000029</v>
       </c>
       <c r="B2077" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C2077" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D2077" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2077" s="1" t="n"/>
@@ -46213,21 +46213,21 @@
     </row>
     <row r="2078">
       <c r="A2078" s="1" t="n">
-        <v>9000043</v>
+        <v>9000030</v>
       </c>
       <c r="B2078" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C2078" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D2078" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E2078" s="1" t="n"/>
@@ -46235,21 +46235,21 @@
     </row>
     <row r="2079">
       <c r="A2079" s="1" t="n">
-        <v>9000044</v>
+        <v>9000031</v>
       </c>
       <c r="B2079" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C2079" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D2079" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E2079" s="1" t="n"/>
@@ -46257,21 +46257,21 @@
     </row>
     <row r="2080">
       <c r="A2080" s="1" t="n">
-        <v>9000045</v>
+        <v>9000032</v>
       </c>
       <c r="B2080" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C2080" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D2080" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2080" s="1" t="n"/>
@@ -46279,21 +46279,21 @@
     </row>
     <row r="2081">
       <c r="A2081" s="1" t="n">
-        <v>9000046</v>
+        <v>9000033</v>
       </c>
       <c r="B2081" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C2081" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D2081" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2081" s="1" t="n"/>
@@ -46301,21 +46301,21 @@
     </row>
     <row r="2082">
       <c r="A2082" s="1" t="n">
-        <v>9000047</v>
+        <v>9000034</v>
       </c>
       <c r="B2082" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C2082" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D2082" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2082" s="1" t="n"/>
@@ -46323,21 +46323,21 @@
     </row>
     <row r="2083">
       <c r="A2083" s="1" t="n">
-        <v>9000048</v>
+        <v>9000035</v>
       </c>
       <c r="B2083" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C2083" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D2083" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E2083" s="1" t="n"/>
@@ -46345,21 +46345,21 @@
     </row>
     <row r="2084">
       <c r="A2084" s="1" t="n">
-        <v>9000049</v>
+        <v>9000036</v>
       </c>
       <c r="B2084" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C2084" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D2084" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E2084" s="1" t="n"/>
@@ -46367,21 +46367,21 @@
     </row>
     <row r="2085">
       <c r="A2085" s="1" t="n">
-        <v>9000050</v>
+        <v>9000037</v>
       </c>
       <c r="B2085" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C2085" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D2085" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E2085" s="1" t="n"/>
@@ -46389,21 +46389,21 @@
     </row>
     <row r="2086">
       <c r="A2086" s="1" t="n">
-        <v>9000051</v>
+        <v>9000038</v>
       </c>
       <c r="B2086" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C2086" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D2086" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E2086" s="1" t="n"/>
@@ -46411,21 +46411,21 @@
     </row>
     <row r="2087">
       <c r="A2087" s="1" t="n">
-        <v>9000052</v>
+        <v>9000039</v>
       </c>
       <c r="B2087" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C2087" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D2087" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E2087" s="1" t="n"/>
@@ -46433,21 +46433,21 @@
     </row>
     <row r="2088">
       <c r="A2088" s="1" t="n">
-        <v>9000053</v>
+        <v>9000040</v>
       </c>
       <c r="B2088" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C2088" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D2088" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E2088" s="1" t="n"/>
@@ -46455,21 +46455,21 @@
     </row>
     <row r="2089">
       <c r="A2089" s="1" t="n">
-        <v>9000054</v>
+        <v>9000041</v>
       </c>
       <c r="B2089" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C2089" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D2089" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2089" s="1" t="n"/>
@@ -46477,21 +46477,21 @@
     </row>
     <row r="2090">
       <c r="A2090" s="1" t="n">
-        <v>9000055</v>
+        <v>9000042</v>
       </c>
       <c r="B2090" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C2090" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D2090" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2090" s="1" t="n"/>
@@ -46499,21 +46499,21 @@
     </row>
     <row r="2091">
       <c r="A2091" s="1" t="n">
-        <v>9000056</v>
+        <v>9000043</v>
       </c>
       <c r="B2091" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C2091" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D2091" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2091" s="1" t="n"/>
@@ -46521,21 +46521,21 @@
     </row>
     <row r="2092">
       <c r="A2092" s="1" t="n">
-        <v>9000057</v>
+        <v>9000044</v>
       </c>
       <c r="B2092" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C2092" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D2092" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2092" s="1" t="n"/>
@@ -46543,21 +46543,21 @@
     </row>
     <row r="2093">
       <c r="A2093" s="1" t="n">
-        <v>9000058</v>
+        <v>9000045</v>
       </c>
       <c r="B2093" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C2093" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D2093" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2093" s="1" t="n"/>
@@ -46565,21 +46565,21 @@
     </row>
     <row r="2094">
       <c r="A2094" s="1" t="n">
-        <v>9000059</v>
+        <v>9000046</v>
       </c>
       <c r="B2094" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C2094" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D2094" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2094" s="1" t="n"/>
@@ -46587,21 +46587,21 @@
     </row>
     <row r="2095">
       <c r="A2095" s="1" t="n">
-        <v>9000060</v>
+        <v>9000047</v>
       </c>
       <c r="B2095" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C2095" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D2095" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2095" s="1" t="n"/>
@@ -46609,21 +46609,21 @@
     </row>
     <row r="2096">
       <c r="A2096" s="1" t="n">
-        <v>9000061</v>
+        <v>9000048</v>
       </c>
       <c r="B2096" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C2096" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D2096" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2096" s="1" t="n"/>
@@ -46631,21 +46631,21 @@
     </row>
     <row r="2097">
       <c r="A2097" s="1" t="n">
-        <v>9000062</v>
+        <v>9000049</v>
       </c>
       <c r="B2097" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C2097" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D2097" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E2097" s="1" t="n"/>
@@ -46653,21 +46653,21 @@
     </row>
     <row r="2098">
       <c r="A2098" s="1" t="n">
-        <v>9000063</v>
+        <v>9000050</v>
       </c>
       <c r="B2098" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C2098" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D2098" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E2098" s="1" t="n"/>
@@ -46675,21 +46675,21 @@
     </row>
     <row r="2099">
       <c r="A2099" s="1" t="n">
-        <v>9000064</v>
+        <v>9000051</v>
       </c>
       <c r="B2099" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C2099" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D2099" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2099" s="1" t="n"/>
@@ -46697,21 +46697,21 @@
     </row>
     <row r="2100">
       <c r="A2100" s="1" t="n">
-        <v>9000065</v>
+        <v>9000052</v>
       </c>
       <c r="B2100" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C2100" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D2100" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2100" s="1" t="n"/>
@@ -46719,21 +46719,21 @@
     </row>
     <row r="2101">
       <c r="A2101" s="1" t="n">
-        <v>9000066</v>
+        <v>9000053</v>
       </c>
       <c r="B2101" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C2101" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D2101" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E2101" s="1" t="n"/>
@@ -46741,21 +46741,21 @@
     </row>
     <row r="2102">
       <c r="A2102" s="1" t="n">
-        <v>9000067</v>
+        <v>9000054</v>
       </c>
       <c r="B2102" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C2102" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D2102" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2102" s="1" t="n"/>
@@ -46763,21 +46763,21 @@
     </row>
     <row r="2103">
       <c r="A2103" s="1" t="n">
-        <v>9000068</v>
+        <v>9000055</v>
       </c>
       <c r="B2103" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C2103" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D2103" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2103" s="1" t="n"/>
@@ -46785,21 +46785,21 @@
     </row>
     <row r="2104">
       <c r="A2104" s="1" t="n">
-        <v>9000069</v>
+        <v>9000056</v>
       </c>
       <c r="B2104" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C2104" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D2104" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2104" s="1" t="n"/>
@@ -46807,21 +46807,21 @@
     </row>
     <row r="2105">
       <c r="A2105" s="1" t="n">
-        <v>9000070</v>
+        <v>9000057</v>
       </c>
       <c r="B2105" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C2105" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D2105" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2105" s="1" t="n"/>
@@ -46829,21 +46829,21 @@
     </row>
     <row r="2106">
       <c r="A2106" s="1" t="n">
-        <v>9000071</v>
+        <v>9000058</v>
       </c>
       <c r="B2106" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C2106" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D2106" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2106" s="1" t="n"/>
@@ -46851,21 +46851,21 @@
     </row>
     <row r="2107">
       <c r="A2107" s="1" t="n">
-        <v>9000072</v>
+        <v>9000059</v>
       </c>
       <c r="B2107" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C2107" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D2107" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2107" s="1" t="n"/>
@@ -46873,21 +46873,21 @@
     </row>
     <row r="2108">
       <c r="A2108" s="1" t="n">
-        <v>9000073</v>
+        <v>9000060</v>
       </c>
       <c r="B2108" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C2108" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D2108" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2108" s="1" t="n"/>
@@ -46895,21 +46895,21 @@
     </row>
     <row r="2109">
       <c r="A2109" s="1" t="n">
-        <v>9000074</v>
+        <v>9000061</v>
       </c>
       <c r="B2109" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C2109" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D2109" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2109" s="1" t="n"/>
@@ -46917,21 +46917,21 @@
     </row>
     <row r="2110">
       <c r="A2110" s="1" t="n">
-        <v>9000075</v>
+        <v>9000062</v>
       </c>
       <c r="B2110" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C2110" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D2110" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2110" s="1" t="n"/>
@@ -46939,21 +46939,21 @@
     </row>
     <row r="2111">
       <c r="A2111" s="1" t="n">
-        <v>9000076</v>
+        <v>9000063</v>
       </c>
       <c r="B2111" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C2111" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D2111" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2111" s="1" t="n"/>
@@ -46961,21 +46961,21 @@
     </row>
     <row r="2112">
       <c r="A2112" s="1" t="n">
-        <v>9000077</v>
+        <v>9000064</v>
       </c>
       <c r="B2112" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C2112" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D2112" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2112" s="1" t="n"/>
@@ -46983,21 +46983,21 @@
     </row>
     <row r="2113">
       <c r="A2113" s="1" t="n">
-        <v>9000078</v>
+        <v>9000065</v>
       </c>
       <c r="B2113" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C2113" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D2113" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2113" s="1" t="n"/>
@@ -47005,21 +47005,21 @@
     </row>
     <row r="2114">
       <c r="A2114" s="1" t="n">
-        <v>9000079</v>
+        <v>9000066</v>
       </c>
       <c r="B2114" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C2114" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D2114" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2114" s="1" t="n"/>
@@ -47027,21 +47027,21 @@
     </row>
     <row r="2115">
       <c r="A2115" s="1" t="n">
-        <v>9000080</v>
+        <v>9000067</v>
       </c>
       <c r="B2115" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C2115" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D2115" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2115" s="1" t="n"/>
@@ -47049,21 +47049,21 @@
     </row>
     <row r="2116">
       <c r="A2116" s="1" t="n">
-        <v>9000081</v>
+        <v>9000068</v>
       </c>
       <c r="B2116" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C2116" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D2116" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2116" s="1" t="n"/>
@@ -47071,21 +47071,21 @@
     </row>
     <row r="2117">
       <c r="A2117" s="1" t="n">
-        <v>9000082</v>
+        <v>9000069</v>
       </c>
       <c r="B2117" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C2117" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D2117" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2117" s="1" t="n"/>
@@ -47093,21 +47093,21 @@
     </row>
     <row r="2118">
       <c r="A2118" s="1" t="n">
-        <v>9000083</v>
+        <v>9000070</v>
       </c>
       <c r="B2118" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C2118" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D2118" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2118" s="1" t="n"/>
@@ -47115,21 +47115,21 @@
     </row>
     <row r="2119">
       <c r="A2119" s="1" t="n">
-        <v>9000084</v>
+        <v>9000071</v>
       </c>
       <c r="B2119" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C2119" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D2119" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2119" s="1" t="n"/>
@@ -47137,21 +47137,21 @@
     </row>
     <row r="2120">
       <c r="A2120" s="1" t="n">
-        <v>9000085</v>
+        <v>9000072</v>
       </c>
       <c r="B2120" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C2120" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D2120" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2120" s="1" t="n"/>
@@ -47159,21 +47159,21 @@
     </row>
     <row r="2121">
       <c r="A2121" s="1" t="n">
-        <v>9000086</v>
+        <v>9000073</v>
       </c>
       <c r="B2121" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C2121" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D2121" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2121" s="1" t="n"/>
@@ -47181,21 +47181,21 @@
     </row>
     <row r="2122">
       <c r="A2122" s="1" t="n">
-        <v>9000087</v>
+        <v>9000074</v>
       </c>
       <c r="B2122" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C2122" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D2122" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2122" s="1" t="n"/>
@@ -47203,21 +47203,21 @@
     </row>
     <row r="2123">
       <c r="A2123" s="1" t="n">
-        <v>9000088</v>
+        <v>9000075</v>
       </c>
       <c r="B2123" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C2123" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D2123" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2123" s="1" t="n"/>
@@ -47225,21 +47225,21 @@
     </row>
     <row r="2124">
       <c r="A2124" s="1" t="n">
-        <v>9000089</v>
+        <v>9000076</v>
       </c>
       <c r="B2124" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C2124" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D2124" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2124" s="1" t="n"/>
@@ -47247,21 +47247,21 @@
     </row>
     <row r="2125">
       <c r="A2125" s="1" t="n">
-        <v>9000090</v>
+        <v>9000077</v>
       </c>
       <c r="B2125" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C2125" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D2125" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2125" s="1" t="n"/>
@@ -47269,21 +47269,21 @@
     </row>
     <row r="2126">
       <c r="A2126" s="1" t="n">
-        <v>9000091</v>
+        <v>9000078</v>
       </c>
       <c r="B2126" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C2126" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D2126" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2126" s="1" t="n"/>
@@ -47291,21 +47291,21 @@
     </row>
     <row r="2127">
       <c r="A2127" s="1" t="n">
-        <v>9000092</v>
+        <v>9000079</v>
       </c>
       <c r="B2127" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C2127" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D2127" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2127" s="1" t="n"/>
@@ -47313,21 +47313,21 @@
     </row>
     <row r="2128">
       <c r="A2128" s="1" t="n">
-        <v>9000093</v>
+        <v>9000080</v>
       </c>
       <c r="B2128" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C2128" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D2128" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2128" s="1" t="n"/>
@@ -47335,21 +47335,21 @@
     </row>
     <row r="2129">
       <c r="A2129" s="1" t="n">
-        <v>9000094</v>
+        <v>9000081</v>
       </c>
       <c r="B2129" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C2129" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D2129" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2129" s="1" t="n"/>
@@ -47357,21 +47357,21 @@
     </row>
     <row r="2130">
       <c r="A2130" s="1" t="n">
-        <v>9000095</v>
+        <v>9000082</v>
       </c>
       <c r="B2130" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C2130" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D2130" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2130" s="1" t="n"/>
@@ -47379,21 +47379,21 @@
     </row>
     <row r="2131">
       <c r="A2131" s="1" t="n">
-        <v>9000096</v>
+        <v>9000083</v>
       </c>
       <c r="B2131" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>헉헉</t>
         </is>
       </c>
       <c r="C2131" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>Huff puff</t>
         </is>
       </c>
       <c r="D2131" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2131" s="1" t="n"/>
@@ -47401,21 +47401,21 @@
     </row>
     <row r="2132">
       <c r="A2132" s="1" t="n">
-        <v>9000097</v>
+        <v>9000084</v>
       </c>
       <c r="B2132" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>더 빨리!</t>
         </is>
       </c>
       <c r="C2132" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>Faster!</t>
         </is>
       </c>
       <c r="D2132" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2132" s="1" t="n"/>
@@ -47423,21 +47423,21 @@
     </row>
     <row r="2133">
       <c r="A2133" s="1" t="n">
-        <v>9000098</v>
+        <v>9000085</v>
       </c>
       <c r="B2133" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>근육 붙는 중</t>
         </is>
       </c>
       <c r="C2133" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>Gains incoming</t>
         </is>
       </c>
       <c r="D2133" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2133" s="1" t="n"/>
@@ -47445,21 +47445,21 @@
     </row>
     <row r="2134">
       <c r="A2134" s="1" t="n">
-        <v>9000099</v>
+        <v>9000086</v>
       </c>
       <c r="B2134" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>찍찍찍찍</t>
         </is>
       </c>
       <c r="C2134" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>Squeak squeak squeak squeak</t>
         </is>
       </c>
       <c r="D2134" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2134" s="1" t="n"/>
@@ -47467,21 +47467,21 @@
     </row>
     <row r="2135">
       <c r="A2135" s="1" t="n">
-        <v>9000100</v>
+        <v>9000087</v>
       </c>
       <c r="B2135" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>으아아아~!</t>
         </is>
       </c>
       <c r="C2135" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>Waaaaah~!</t>
         </is>
       </c>
       <c r="D2135" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2135" s="1" t="n"/>
@@ -47489,21 +47489,21 @@
     </row>
     <row r="2136">
       <c r="A2136" s="1" t="n">
-        <v>9000101</v>
+        <v>9000088</v>
       </c>
       <c r="B2136" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>하암~ 잘 잤다</t>
         </is>
       </c>
       <c r="C2136" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>Yawn~ what a nap</t>
         </is>
       </c>
       <c r="D2136" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2136" s="1" t="n"/>
@@ -47511,21 +47511,21 @@
     </row>
     <row r="2137">
       <c r="A2137" s="1" t="n">
-        <v>9000102</v>
+        <v>9000089</v>
       </c>
       <c r="B2137" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>냠, 배부르다</t>
         </is>
       </c>
       <c r="C2137" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>Nom, so full</t>
         </is>
       </c>
       <c r="D2137" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2137" s="1" t="n"/>
@@ -47533,21 +47533,21 @@
     </row>
     <row r="2138">
       <c r="A2138" s="1" t="n">
-        <v>9000103</v>
+        <v>9000090</v>
       </c>
       <c r="B2138" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>휴…</t>
         </is>
       </c>
       <c r="C2138" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Phew...</t>
         </is>
       </c>
       <c r="D2138" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2138" s="1" t="n"/>
@@ -47555,21 +47555,21 @@
     </row>
     <row r="2139">
       <c r="A2139" s="1" t="n">
-        <v>9000104</v>
+        <v>9000091</v>
       </c>
       <c r="B2139" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>찍</t>
         </is>
       </c>
       <c r="C2139" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Squeak</t>
         </is>
       </c>
       <c r="D2139" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
         </is>
       </c>
       <c r="E2139" s="1" t="n"/>
@@ -47577,21 +47577,21 @@
     </row>
     <row r="2140">
       <c r="A2140" s="1" t="n">
-        <v>9000105</v>
+        <v>9000092</v>
       </c>
       <c r="B2140" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C2140" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D2140" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Lobby/RunPage.cs:99</t>
         </is>
       </c>
       <c r="E2140" s="1" t="n"/>
@@ -47599,21 +47599,21 @@
     </row>
     <row r="2141">
       <c r="A2141" s="1" t="n">
-        <v>9000106</v>
+        <v>9000093</v>
       </c>
       <c r="B2141" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="C2141" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D2141" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
         </is>
       </c>
       <c r="E2141" s="1" t="n"/>
@@ -47621,21 +47621,21 @@
     </row>
     <row r="2142">
       <c r="A2142" s="1" t="n">
-        <v>9000107</v>
+        <v>9000094</v>
       </c>
       <c r="B2142" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>찌릿!!</t>
         </is>
       </c>
       <c r="C2142" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>ZAP!!</t>
         </is>
       </c>
       <c r="D2142" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2142" s="1" t="n"/>
@@ -47643,21 +47643,21 @@
     </row>
     <row r="2143">
       <c r="A2143" s="1" t="n">
-        <v>9000108</v>
+        <v>9000095</v>
       </c>
       <c r="B2143" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>콰릉!</t>
         </is>
       </c>
       <c r="C2143" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>Ka-boom!</t>
         </is>
       </c>
       <c r="D2143" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2143" s="1" t="n"/>
@@ -47665,21 +47665,21 @@
     </row>
     <row r="2144">
       <c r="A2144" s="1" t="n">
-        <v>9000109</v>
+        <v>9000096</v>
       </c>
       <c r="B2144" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>냠!</t>
         </is>
       </c>
       <c r="C2144" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>Nom!</t>
         </is>
       </c>
       <c r="D2144" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2144" s="1" t="n"/>
@@ -47687,21 +47687,21 @@
     </row>
     <row r="2145">
       <c r="A2145" s="1" t="n">
-        <v>9000110</v>
+        <v>9000097</v>
       </c>
       <c r="B2145" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>다닥!</t>
         </is>
       </c>
       <c r="C2145" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>Scurry!</t>
         </is>
       </c>
       <c r="D2145" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2145" s="1" t="n"/>
@@ -47709,21 +47709,21 @@
     </row>
     <row r="2146">
       <c r="A2146" s="1" t="n">
-        <v>9000111</v>
+        <v>9000098</v>
       </c>
       <c r="B2146" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>메리 쥐스마스!</t>
         </is>
       </c>
       <c r="C2146" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>Merry Ratmas!</t>
         </is>
       </c>
       <c r="D2146" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2146" s="1" t="n"/>
@@ -47731,21 +47731,21 @@
     </row>
     <row r="2147">
       <c r="A2147" s="1" t="n">
-        <v>9000112</v>
+        <v>9000099</v>
       </c>
       <c r="B2147" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>흐에~ 후원 감사합니다~!</t>
         </is>
       </c>
       <c r="C2147" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>Heheh~ thanks for the dono~!</t>
         </is>
       </c>
       <c r="D2147" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2147" s="1" t="n"/>
@@ -47753,21 +47753,21 @@
     </row>
     <row r="2148">
       <c r="A2148" s="1" t="n">
-        <v>9000113</v>
+        <v>9000100</v>
       </c>
       <c r="B2148" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>배달 왔습니다~</t>
         </is>
       </c>
       <c r="C2148" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>Delivery~!</t>
         </is>
       </c>
       <c r="D2148" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2148" s="1" t="n"/>
@@ -47775,21 +47775,21 @@
     </row>
     <row r="2149">
       <c r="A2149" s="1" t="n">
-        <v>9000114</v>
+        <v>9000101</v>
       </c>
       <c r="B2149" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>백덤블링!</t>
         </is>
       </c>
       <c r="C2149" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>Backflip!</t>
         </is>
       </c>
       <c r="D2149" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2149" s="1" t="n"/>
@@ -47797,21 +47797,21 @@
     </row>
     <row r="2150">
       <c r="A2150" s="1" t="n">
-        <v>9000115</v>
+        <v>9000102</v>
       </c>
       <c r="B2150" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>공중제비!</t>
         </is>
       </c>
       <c r="C2150" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>Somersault!</t>
         </is>
       </c>
       <c r="D2150" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2150" s="1" t="n"/>
@@ -47819,21 +47819,21 @@
     </row>
     <row r="2151">
       <c r="A2151" s="1" t="n">
-        <v>9000116</v>
+        <v>9000103</v>
       </c>
       <c r="B2151" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>찍-공중회전!</t>
         </is>
       </c>
       <c r="C2151" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>Squeak-flip!</t>
         </is>
       </c>
       <c r="D2151" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2151" s="1" t="n"/>
@@ -47841,21 +47841,21 @@
     </row>
     <row r="2152">
       <c r="A2152" s="1" t="n">
-        <v>9000117</v>
+        <v>9000104</v>
       </c>
       <c r="B2152" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>트리플 악셀!!</t>
         </is>
       </c>
       <c r="C2152" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>TRIPLE AXEL!!</t>
         </is>
       </c>
       <c r="D2152" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2152" s="1" t="n"/>
@@ -47863,21 +47863,21 @@
     </row>
     <row r="2153">
       <c r="A2153" s="1" t="n">
-        <v>9000118</v>
+        <v>9000105</v>
       </c>
       <c r="B2153" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>3회전 성공!</t>
         </is>
       </c>
       <c r="C2153" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>Triple spin landed!</t>
         </is>
       </c>
       <c r="D2153" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2153" s="1" t="n"/>
@@ -47885,21 +47885,21 @@
     </row>
     <row r="2154">
       <c r="A2154" s="1" t="n">
-        <v>9000119</v>
+        <v>9000106</v>
       </c>
       <c r="B2154" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>심사위원 전원 10점!</t>
         </is>
       </c>
       <c r="C2154" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>Perfect 10s from every judge!</t>
         </is>
       </c>
       <c r="D2154" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2154" s="1" t="n"/>
@@ -47907,21 +47907,21 @@
     </row>
     <row r="2155">
       <c r="A2155" s="1" t="n">
-        <v>9000120</v>
+        <v>9000107</v>
       </c>
       <c r="B2155" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>윈드밀!!</t>
         </is>
       </c>
       <c r="C2155" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>WINDMILL!!</t>
         </is>
       </c>
       <c r="D2155" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2155" s="1" t="n"/>
@@ -47929,21 +47929,21 @@
     </row>
     <row r="2156">
       <c r="A2156" s="1" t="n">
-        <v>9000121</v>
+        <v>9000108</v>
       </c>
       <c r="B2156" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>브레이크 댄스!</t>
         </is>
       </c>
       <c r="C2156" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>Breakdance!</t>
         </is>
       </c>
       <c r="D2156" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2156" s="1" t="n"/>
@@ -47951,21 +47951,21 @@
     </row>
     <row r="2157">
       <c r="A2157" s="1" t="n">
-        <v>9000122</v>
+        <v>9000109</v>
       </c>
       <c r="B2157" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>빙글빙글 파괴!</t>
         </is>
       </c>
       <c r="C2157" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>Spin-to-win destruction!</t>
         </is>
       </c>
       <c r="D2157" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2157" s="1" t="n"/>
@@ -47973,21 +47973,21 @@
     </row>
     <row r="2158">
       <c r="A2158" s="1" t="n">
-        <v>9000123</v>
+        <v>9000110</v>
       </c>
       <c r="B2158" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>쥐 대포알!</t>
         </is>
       </c>
       <c r="C2158" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>Rat Cannonball!</t>
         </is>
       </c>
       <c r="D2158" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2158" s="1" t="n"/>
@@ -47995,21 +47995,21 @@
     </row>
     <row r="2159">
       <c r="A2159" s="1" t="n">
-        <v>9000124</v>
+        <v>9000111</v>
       </c>
       <c r="B2159" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>데굴데굴!</t>
         </is>
       </c>
       <c r="C2159" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>Roll roll!</t>
         </is>
       </c>
       <c r="D2159" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2159" s="1" t="n"/>
@@ -48017,21 +48017,21 @@
     </row>
     <row r="2160">
       <c r="A2160" s="1" t="n">
-        <v>9000125</v>
+        <v>9000112</v>
       </c>
       <c r="B2160" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>핀볼 모드!</t>
         </is>
       </c>
       <c r="C2160" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>Pinball mode!</t>
         </is>
       </c>
       <c r="D2160" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2160" s="1" t="n"/>
@@ -48039,21 +48039,21 @@
     </row>
     <row r="2161">
       <c r="A2161" s="1" t="n">
-        <v>9000126</v>
+        <v>9000113</v>
       </c>
       <c r="B2161" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>쳇바퀴 돌기!!</t>
         </is>
       </c>
       <c r="C2161" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>WHEEL SPIN!!</t>
         </is>
       </c>
       <c r="D2161" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2161" s="1" t="n"/>
@@ -48061,21 +48061,21 @@
     </row>
     <row r="2162">
       <c r="A2162" s="1" t="n">
-        <v>9000127</v>
+        <v>9000114</v>
       </c>
       <c r="B2162" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>빙글빙글~</t>
         </is>
       </c>
       <c r="C2162" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>Round and round~</t>
         </is>
       </c>
       <c r="D2162" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2162" s="1" t="n"/>
@@ -48083,21 +48083,21 @@
     </row>
     <row r="2163">
       <c r="A2163" s="1" t="n">
-        <v>9000128</v>
+        <v>9000115</v>
       </c>
       <c r="B2163" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>어지러워!!</t>
         </is>
       </c>
       <c r="C2163" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>So DIZZY!!</t>
         </is>
       </c>
       <c r="D2163" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2163" s="1" t="n"/>
@@ -48105,21 +48105,21 @@
     </row>
     <row r="2164">
       <c r="A2164" s="1" t="n">
-        <v>9000129</v>
+        <v>9000116</v>
       </c>
       <c r="B2164" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="C2164" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="D2164" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
         </is>
       </c>
       <c r="E2164" s="1" t="n"/>
@@ -48127,21 +48127,21 @@
     </row>
     <row r="2165">
       <c r="A2165" s="1" t="n">
-        <v>9000130</v>
+        <v>9000117</v>
       </c>
       <c r="B2165" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>기절!!</t>
         </is>
       </c>
       <c r="C2165" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Stunned!!</t>
         </is>
       </c>
       <c r="D2165" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Rats/RatManager.cs:38</t>
         </is>
       </c>
       <c r="E2165" s="1" t="n"/>
@@ -48149,25 +48149,311 @@
     </row>
     <row r="2166">
       <c r="A2166" s="1" t="n">
-        <v>9000131</v>
+        <v>9000118</v>
       </c>
       <c r="B2166" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>소품이 떨어졌다!</t>
         </is>
       </c>
       <c r="C2166" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>A prop dropped!</t>
         </is>
       </c>
       <c r="D2166" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Rats/RatManager.cs:397</t>
         </is>
       </c>
       <c r="E2166" s="1" t="n"/>
       <c r="F2166" s="1" t="n"/>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="1" t="n">
+        <v>9000119</v>
+      </c>
+      <c r="B2167" s="2" t="inlineStr">
+        <is>
+          <t>조각 +1</t>
+        </is>
+      </c>
+      <c r="C2167" s="2" t="inlineStr">
+        <is>
+          <t>Shard +1</t>
+        </is>
+      </c>
+      <c r="D2167" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:460</t>
+        </is>
+      </c>
+      <c r="E2167" s="1" t="n"/>
+      <c r="F2167" s="1" t="n"/>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="1" t="n">
+        <v>9000120</v>
+      </c>
+      <c r="B2168" s="2" t="inlineStr">
+        <is>
+          <t>{name} 강화! Lv {lv}</t>
+        </is>
+      </c>
+      <c r="C2168" s="2" t="inlineStr">
+        <is>
+          <t>{name} powered up! Lv {lv}</t>
+        </is>
+      </c>
+      <c r="D2168" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:461</t>
+        </is>
+      </c>
+      <c r="E2168" s="1" t="n"/>
+      <c r="F2168" s="1" t="n"/>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="1" t="n">
+        <v>9000121</v>
+      </c>
+      <c r="B2169" s="2" t="inlineStr">
+        <is>
+          <t>{grade} 탄생!</t>
+        </is>
+      </c>
+      <c r="C2169" s="2" t="inlineStr">
+        <is>
+          <t>{grade} born!</t>
+        </is>
+      </c>
+      <c r="D2169" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:561</t>
+        </is>
+      </c>
+      <c r="E2169" s="1" t="n"/>
+      <c r="F2169" s="1" t="n"/>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="1" t="n">
+        <v>9000122</v>
+      </c>
+      <c r="B2170" s="2" t="inlineStr">
+        <is>
+          <t>쌍둥이!</t>
+        </is>
+      </c>
+      <c r="C2170" s="2" t="inlineStr">
+        <is>
+          <t>Twins!</t>
+        </is>
+      </c>
+      <c r="D2170" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:566</t>
+        </is>
+      </c>
+      <c r="E2170" s="1" t="n"/>
+      <c r="F2170" s="1" t="n"/>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="1" t="n">
+        <v>9000123</v>
+      </c>
+      <c r="B2171" s="2" t="inlineStr">
+        <is>
+          <t>치즈 운석!</t>
+        </is>
+      </c>
+      <c r="C2171" s="2" t="inlineStr">
+        <is>
+          <t>Cheese Meteor!</t>
+        </is>
+      </c>
+      <c r="D2171" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:627</t>
+        </is>
+      </c>
+      <c r="E2171" s="1" t="n"/>
+      <c r="F2171" s="1" t="n"/>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="1" t="n">
+        <v>9000124</v>
+      </c>
+      <c r="B2172" s="2" t="inlineStr">
+        <is>
+          <t>{floor}층 · {zone}</t>
+        </is>
+      </c>
+      <c r="C2172" s="2" t="inlineStr">
+        <is>
+          <t>Floor {floor} · {zone}</t>
+        </is>
+      </c>
+      <c r="D2172" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+        </is>
+      </c>
+      <c r="E2172" s="1" t="n"/>
+      <c r="F2172" s="1" t="n"/>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="1" t="n">
+        <v>9000125</v>
+      </c>
+      <c r="B2173" s="2" t="inlineStr">
+        <is>
+          <t>계단 방 벽을 부숴라!</t>
+        </is>
+      </c>
+      <c r="C2173" s="2" t="inlineStr">
+        <is>
+          <t>Smash the wall to the stairs room!</t>
+        </is>
+      </c>
+      <c r="D2173" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:187</t>
+        </is>
+      </c>
+      <c r="E2173" s="1" t="n"/>
+      <c r="F2173" s="1" t="n"/>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="1" t="n">
+        <v>9000126</v>
+      </c>
+      <c r="B2174" s="2" t="inlineStr">
+        <is>
+          <t>벽 붕괴! 방 확장</t>
+        </is>
+      </c>
+      <c r="C2174" s="2" t="inlineStr">
+        <is>
+          <t>Wall down! Room expanded</t>
+        </is>
+      </c>
+      <c r="D2174" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:332</t>
+        </is>
+      </c>
+      <c r="E2174" s="1" t="n"/>
+      <c r="F2174" s="1" t="n"/>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="1" t="n">
+        <v>9000127</v>
+      </c>
+      <c r="B2175" s="2" t="inlineStr">
+        <is>
+          <t>계단 발견!</t>
+        </is>
+      </c>
+      <c r="C2175" s="2" t="inlineStr">
+        <is>
+          <t>Stairs found!</t>
+        </is>
+      </c>
+      <c r="D2175" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:338</t>
+        </is>
+      </c>
+      <c r="E2175" s="1" t="n"/>
+      <c r="F2175" s="1" t="n"/>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="1" t="n">
+        <v>9000128</v>
+      </c>
+      <c r="B2176" s="2" t="inlineStr">
+        <is>
+          <t>계단에 닿으면 {next}층으로</t>
+        </is>
+      </c>
+      <c r="C2176" s="2" t="inlineStr">
+        <is>
+          <t>Touch the stairs to go to Floor {next}</t>
+        </is>
+      </c>
+      <c r="D2176" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:338</t>
+        </is>
+      </c>
+      <c r="E2176" s="1" t="n"/>
+      <c r="F2176" s="1" t="n"/>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="1" t="n">
+        <v>9000129</v>
+      </c>
+      <c r="B2177" s="2" t="inlineStr">
+        <is>
+          <t>와르르!!</t>
+        </is>
+      </c>
+      <c r="C2177" s="2" t="inlineStr">
+        <is>
+          <t>Crumble!!</t>
+        </is>
+      </c>
+      <c r="D2177" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E2177" s="1" t="n"/>
+      <c r="F2177" s="1" t="n"/>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="1" t="n">
+        <v>9000130</v>
+      </c>
+      <c r="B2178" s="2" t="inlineStr">
+        <is>
+          <t>콰광!!</t>
+        </is>
+      </c>
+      <c r="C2178" s="2" t="inlineStr">
+        <is>
+          <t>KA-BOOM!!</t>
+        </is>
+      </c>
+      <c r="D2178" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E2178" s="1" t="n"/>
+      <c r="F2178" s="1" t="n"/>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B2179" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C2179" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D2179" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E2179" s="1" t="n"/>
+      <c r="F2179" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -51915,12 +51915,12 @@
       </c>
       <c r="B2229" s="2" t="inlineStr">
         <is>
-          <t>산산조각!!</t>
+          <t>전부 꽁꽁!!</t>
         </is>
       </c>
       <c r="C2229" s="2" t="inlineStr">
         <is>
-          <t>Shatter!!</t>
+          <t>Freeze, everyone!!</t>
         </is>
       </c>
       <c r="D2229" s="1" t="inlineStr">

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2999"/>
+  <dimension ref="A1:F3002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -64766,7 +64766,11 @@
           <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/StreamRat/Intro/Counter/Text</t>
         </is>
       </c>
-      <c r="E2800" s="1" t="n"/>
+      <c r="E2800" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F2800" s="1" t="n"/>
     </row>
     <row r="2801">
@@ -64829,7 +64833,7 @@
       </c>
       <c r="D2803" s="1" t="inlineStr">
         <is>
-          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/IceQueen/Finish/MemeText/Text</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/IceQueen/Top/MemeText/Text</t>
         </is>
       </c>
       <c r="E2803" s="1" t="n"/>
@@ -64895,7 +64899,7 @@
       </c>
       <c r="D2806" s="1" t="inlineStr">
         <is>
-          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/StreamRat/Finish/MemeText/Text</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/StreamRat/Top/MemeText/Text</t>
         </is>
       </c>
       <c r="E2806" s="1" t="n"/>
@@ -64917,7 +64921,7 @@
       </c>
       <c r="D2807" s="1" t="inlineStr">
         <is>
-          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Pharaoh/Finish/MemeText/Text</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Pharaoh/Top/MemeText/Text</t>
         </is>
       </c>
       <c r="E2807" s="1" t="n"/>
@@ -64983,7 +64987,7 @@
       </c>
       <c r="D2810" s="1" t="inlineStr">
         <is>
-          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Bomber/Finish/MemeText/Text</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Bomber/Top/MemeText/Text</t>
         </is>
       </c>
       <c r="E2810" s="1" t="n"/>
@@ -65008,7 +65012,11 @@
           <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Knight/Finish/MemeText/Text</t>
         </is>
       </c>
-      <c r="E2811" s="1" t="n"/>
+      <c r="E2811" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F2811" s="1" t="n"/>
     </row>
     <row r="2812">
@@ -66343,21 +66351,21 @@
     </row>
     <row r="2869">
       <c r="A2869" s="1" t="n">
-        <v>9000001</v>
+        <v>8000510</v>
       </c>
       <c r="B2869" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power} / 적정 {need}</t>
+          <t>보관함이 비었어요. 층을 깨면 증강을 얻어요!</t>
         </is>
       </c>
       <c r="C2869" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power} / Rec. {need}</t>
+          <t>Storage is empty. Clear floors to get augments!</t>
         </is>
       </c>
       <c r="D2869" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
+          <t>씬 · Game · HUD/Augment/Manage/Card/Storage/EmptyNote</t>
         </is>
       </c>
       <c r="E2869" s="1" t="n"/>
@@ -66365,21 +66373,23 @@
     </row>
     <row r="2870">
       <c r="A2870" s="1" t="n">
-        <v>9000002</v>
+        <v>8000511</v>
       </c>
       <c r="B2870" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>증강을 누르면
+여기에 자세히 보여요</t>
         </is>
       </c>
       <c r="C2870" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>Tap an augment
+to see its details here</t>
         </is>
       </c>
       <c r="D2870" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
+          <t>씬 · Game · HUD/Augment/Manage/Card/DetailHint/Text</t>
         </is>
       </c>
       <c r="E2870" s="1" t="n"/>
@@ -66387,21 +66397,21 @@
     </row>
     <row r="2871">
       <c r="A2871" s="1" t="n">
-        <v>9000003</v>
+        <v>8000512</v>
       </c>
       <c r="B2871" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>총 피해 {n}</t>
         </is>
       </c>
       <c r="C2871" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>Total {n}</t>
         </is>
       </c>
       <c r="D2871" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
+          <t>씬 · Game · HUD/SuperUlt/Cut/TotalDamage</t>
         </is>
       </c>
       <c r="E2871" s="1" t="n"/>
@@ -66409,21 +66419,21 @@
     </row>
     <row r="2872">
       <c r="A2872" s="1" t="n">
-        <v>9000004</v>
+        <v>9000001</v>
       </c>
       <c r="B2872" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>찍찍!! {power} / 적정 {need}</t>
         </is>
       </c>
       <c r="C2872" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>SQUEAK!! {power} / Rec. {need}</t>
         </is>
       </c>
       <c r="D2872" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E2872" s="1" t="n"/>
@@ -66431,21 +66441,21 @@
     </row>
     <row r="2873">
       <c r="A2873" s="1" t="n">
-        <v>9000005</v>
+        <v>9000002</v>
       </c>
       <c r="B2873" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C2873" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D2873" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2873" s="1" t="n"/>
@@ -66453,21 +66463,21 @@
     </row>
     <row r="2874">
       <c r="A2874" s="1" t="n">
-        <v>9000006</v>
+        <v>9000003</v>
       </c>
       <c r="B2874" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C2874" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D2874" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E2874" s="1" t="n"/>
@@ -66475,21 +66485,21 @@
     </row>
     <row r="2875">
       <c r="A2875" s="1" t="n">
-        <v>9000007</v>
+        <v>9000004</v>
       </c>
       <c r="B2875" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C2875" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D2875" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E2875" s="1" t="n"/>
@@ -66497,21 +66507,21 @@
     </row>
     <row r="2876">
       <c r="A2876" s="1" t="n">
-        <v>9000008</v>
+        <v>9000005</v>
       </c>
       <c r="B2876" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C2876" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D2876" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E2876" s="1" t="n"/>
@@ -66519,21 +66529,21 @@
     </row>
     <row r="2877">
       <c r="A2877" s="1" t="n">
-        <v>9000009</v>
+        <v>9000006</v>
       </c>
       <c r="B2877" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C2877" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D2877" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E2877" s="1" t="n"/>
@@ -66541,21 +66551,21 @@
     </row>
     <row r="2878">
       <c r="A2878" s="1" t="n">
-        <v>9000010</v>
+        <v>9000007</v>
       </c>
       <c r="B2878" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C2878" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D2878" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E2878" s="1" t="n"/>
@@ -66563,16 +66573,16 @@
     </row>
     <row r="2879">
       <c r="A2879" s="1" t="n">
-        <v>9000011</v>
+        <v>9000008</v>
       </c>
       <c r="B2879" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C2879" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D2879" s="1" t="inlineStr">
@@ -66585,21 +66595,21 @@
     </row>
     <row r="2880">
       <c r="A2880" s="1" t="n">
-        <v>9000012</v>
+        <v>9000009</v>
       </c>
       <c r="B2880" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C2880" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D2880" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2880" s="1" t="n"/>
@@ -66607,21 +66617,21 @@
     </row>
     <row r="2881">
       <c r="A2881" s="1" t="n">
-        <v>9000013</v>
+        <v>9000010</v>
       </c>
       <c r="B2881" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C2881" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D2881" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2881" s="1" t="n"/>
@@ -66629,21 +66639,21 @@
     </row>
     <row r="2882">
       <c r="A2882" s="1" t="n">
-        <v>9000014</v>
+        <v>9000011</v>
       </c>
       <c r="B2882" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C2882" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D2882" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2882" s="1" t="n"/>
@@ -66651,21 +66661,21 @@
     </row>
     <row r="2883">
       <c r="A2883" s="1" t="n">
-        <v>9000015</v>
+        <v>9000012</v>
       </c>
       <c r="B2883" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C2883" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D2883" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2883" s="1" t="n"/>
@@ -66673,21 +66683,21 @@
     </row>
     <row r="2884">
       <c r="A2884" s="1" t="n">
-        <v>9000016</v>
+        <v>9000013</v>
       </c>
       <c r="B2884" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C2884" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D2884" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2884" s="1" t="n"/>
@@ -66695,21 +66705,21 @@
     </row>
     <row r="2885">
       <c r="A2885" s="1" t="n">
-        <v>9000017</v>
+        <v>9000014</v>
       </c>
       <c r="B2885" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C2885" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D2885" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E2885" s="1" t="n"/>
@@ -66717,21 +66727,21 @@
     </row>
     <row r="2886">
       <c r="A2886" s="1" t="n">
-        <v>9000018</v>
+        <v>9000015</v>
       </c>
       <c r="B2886" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C2886" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D2886" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2886" s="1" t="n"/>
@@ -66739,21 +66749,21 @@
     </row>
     <row r="2887">
       <c r="A2887" s="1" t="n">
-        <v>9000019</v>
+        <v>9000016</v>
       </c>
       <c r="B2887" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C2887" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D2887" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2887" s="1" t="n"/>
@@ -66761,21 +66771,21 @@
     </row>
     <row r="2888">
       <c r="A2888" s="1" t="n">
-        <v>9000020</v>
+        <v>9000017</v>
       </c>
       <c r="B2888" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C2888" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D2888" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E2888" s="1" t="n"/>
@@ -66783,21 +66793,21 @@
     </row>
     <row r="2889">
       <c r="A2889" s="1" t="n">
-        <v>9000021</v>
+        <v>9000018</v>
       </c>
       <c r="B2889" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C2889" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D2889" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2889" s="1" t="n"/>
@@ -66805,21 +66815,21 @@
     </row>
     <row r="2890">
       <c r="A2890" s="1" t="n">
-        <v>9000022</v>
+        <v>9000019</v>
       </c>
       <c r="B2890" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C2890" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D2890" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2890" s="1" t="n"/>
@@ -66827,21 +66837,21 @@
     </row>
     <row r="2891">
       <c r="A2891" s="1" t="n">
-        <v>9000023</v>
+        <v>9000020</v>
       </c>
       <c r="B2891" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C2891" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D2891" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2891" s="1" t="n"/>
@@ -66849,21 +66859,21 @@
     </row>
     <row r="2892">
       <c r="A2892" s="1" t="n">
-        <v>9000024</v>
+        <v>9000021</v>
       </c>
       <c r="B2892" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C2892" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D2892" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E2892" s="1" t="n"/>
@@ -66871,16 +66881,16 @@
     </row>
     <row r="2893">
       <c r="A2893" s="1" t="n">
-        <v>9000025</v>
+        <v>9000022</v>
       </c>
       <c r="B2893" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C2893" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D2893" s="1" t="inlineStr">
@@ -66893,21 +66903,21 @@
     </row>
     <row r="2894">
       <c r="A2894" s="1" t="n">
-        <v>9000026</v>
+        <v>9000023</v>
       </c>
       <c r="B2894" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C2894" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D2894" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2894" s="1" t="n"/>
@@ -66915,21 +66925,21 @@
     </row>
     <row r="2895">
       <c r="A2895" s="1" t="n">
-        <v>9000027</v>
+        <v>9000024</v>
       </c>
       <c r="B2895" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C2895" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D2895" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2895" s="1" t="n"/>
@@ -66937,21 +66947,21 @@
     </row>
     <row r="2896">
       <c r="A2896" s="1" t="n">
-        <v>9000028</v>
+        <v>9000025</v>
       </c>
       <c r="B2896" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C2896" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D2896" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2896" s="1" t="n"/>
@@ -66959,21 +66969,21 @@
     </row>
     <row r="2897">
       <c r="A2897" s="1" t="n">
-        <v>9000029</v>
+        <v>9000026</v>
       </c>
       <c r="B2897" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C2897" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D2897" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E2897" s="1" t="n"/>
@@ -66981,21 +66991,21 @@
     </row>
     <row r="2898">
       <c r="A2898" s="1" t="n">
-        <v>9000030</v>
+        <v>9000027</v>
       </c>
       <c r="B2898" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C2898" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D2898" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2898" s="1" t="n"/>
@@ -67003,21 +67013,21 @@
     </row>
     <row r="2899">
       <c r="A2899" s="1" t="n">
-        <v>9000031</v>
+        <v>9000028</v>
       </c>
       <c r="B2899" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C2899" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D2899" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2899" s="1" t="n"/>
@@ -67025,21 +67035,21 @@
     </row>
     <row r="2900">
       <c r="A2900" s="1" t="n">
-        <v>9000032</v>
+        <v>9000029</v>
       </c>
       <c r="B2900" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C2900" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D2900" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2900" s="1" t="n"/>
@@ -67047,21 +67057,21 @@
     </row>
     <row r="2901">
       <c r="A2901" s="1" t="n">
-        <v>9000033</v>
+        <v>9000030</v>
       </c>
       <c r="B2901" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C2901" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D2901" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E2901" s="1" t="n"/>
@@ -67069,21 +67079,21 @@
     </row>
     <row r="2902">
       <c r="A2902" s="1" t="n">
-        <v>9000034</v>
+        <v>9000031</v>
       </c>
       <c r="B2902" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C2902" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D2902" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E2902" s="1" t="n"/>
@@ -67091,21 +67101,21 @@
     </row>
     <row r="2903">
       <c r="A2903" s="1" t="n">
-        <v>9000035</v>
+        <v>9000032</v>
       </c>
       <c r="B2903" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C2903" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D2903" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2903" s="1" t="n"/>
@@ -67113,21 +67123,21 @@
     </row>
     <row r="2904">
       <c r="A2904" s="1" t="n">
-        <v>9000036</v>
+        <v>9000033</v>
       </c>
       <c r="B2904" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C2904" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D2904" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2904" s="1" t="n"/>
@@ -67135,21 +67145,21 @@
     </row>
     <row r="2905">
       <c r="A2905" s="1" t="n">
-        <v>9000037</v>
+        <v>9000034</v>
       </c>
       <c r="B2905" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C2905" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D2905" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2905" s="1" t="n"/>
@@ -67157,21 +67167,21 @@
     </row>
     <row r="2906">
       <c r="A2906" s="1" t="n">
-        <v>9000038</v>
+        <v>9000035</v>
       </c>
       <c r="B2906" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C2906" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D2906" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E2906" s="1" t="n"/>
@@ -67179,21 +67189,21 @@
     </row>
     <row r="2907">
       <c r="A2907" s="1" t="n">
-        <v>9000039</v>
+        <v>9000036</v>
       </c>
       <c r="B2907" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C2907" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D2907" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E2907" s="1" t="n"/>
@@ -67201,21 +67211,21 @@
     </row>
     <row r="2908">
       <c r="A2908" s="1" t="n">
-        <v>9000040</v>
+        <v>9000037</v>
       </c>
       <c r="B2908" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C2908" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D2908" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E2908" s="1" t="n"/>
@@ -67223,21 +67233,21 @@
     </row>
     <row r="2909">
       <c r="A2909" s="1" t="n">
-        <v>9000041</v>
+        <v>9000038</v>
       </c>
       <c r="B2909" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C2909" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D2909" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E2909" s="1" t="n"/>
@@ -67245,21 +67255,21 @@
     </row>
     <row r="2910">
       <c r="A2910" s="1" t="n">
-        <v>9000042</v>
+        <v>9000039</v>
       </c>
       <c r="B2910" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C2910" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D2910" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E2910" s="1" t="n"/>
@@ -67267,21 +67277,21 @@
     </row>
     <row r="2911">
       <c r="A2911" s="1" t="n">
-        <v>9000043</v>
+        <v>9000040</v>
       </c>
       <c r="B2911" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C2911" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D2911" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E2911" s="1" t="n"/>
@@ -67289,21 +67299,21 @@
     </row>
     <row r="2912">
       <c r="A2912" s="1" t="n">
-        <v>9000044</v>
+        <v>9000041</v>
       </c>
       <c r="B2912" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C2912" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D2912" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2912" s="1" t="n"/>
@@ -67311,16 +67321,16 @@
     </row>
     <row r="2913">
       <c r="A2913" s="1" t="n">
-        <v>9000045</v>
+        <v>9000042</v>
       </c>
       <c r="B2913" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C2913" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D2913" s="1" t="inlineStr">
@@ -67333,21 +67343,21 @@
     </row>
     <row r="2914">
       <c r="A2914" s="1" t="n">
-        <v>9000046</v>
+        <v>9000043</v>
       </c>
       <c r="B2914" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C2914" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D2914" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2914" s="1" t="n"/>
@@ -67355,21 +67365,21 @@
     </row>
     <row r="2915">
       <c r="A2915" s="1" t="n">
-        <v>9000047</v>
+        <v>9000044</v>
       </c>
       <c r="B2915" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C2915" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D2915" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2915" s="1" t="n"/>
@@ -67377,21 +67387,21 @@
     </row>
     <row r="2916">
       <c r="A2916" s="1" t="n">
-        <v>9000048</v>
+        <v>9000045</v>
       </c>
       <c r="B2916" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C2916" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D2916" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2916" s="1" t="n"/>
@@ -67399,21 +67409,21 @@
     </row>
     <row r="2917">
       <c r="A2917" s="1" t="n">
-        <v>9000049</v>
+        <v>9000046</v>
       </c>
       <c r="B2917" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C2917" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D2917" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2917" s="1" t="n"/>
@@ -67421,21 +67431,21 @@
     </row>
     <row r="2918">
       <c r="A2918" s="1" t="n">
-        <v>9000050</v>
+        <v>9000047</v>
       </c>
       <c r="B2918" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C2918" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D2918" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2918" s="1" t="n"/>
@@ -67443,21 +67453,21 @@
     </row>
     <row r="2919">
       <c r="A2919" s="1" t="n">
-        <v>9000051</v>
+        <v>9000048</v>
       </c>
       <c r="B2919" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C2919" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D2919" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2919" s="1" t="n"/>
@@ -67465,21 +67475,21 @@
     </row>
     <row r="2920">
       <c r="A2920" s="1" t="n">
-        <v>9000052</v>
+        <v>9000049</v>
       </c>
       <c r="B2920" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C2920" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D2920" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E2920" s="1" t="n"/>
@@ -67487,21 +67497,21 @@
     </row>
     <row r="2921">
       <c r="A2921" s="1" t="n">
-        <v>9000053</v>
+        <v>9000050</v>
       </c>
       <c r="B2921" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C2921" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D2921" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E2921" s="1" t="n"/>
@@ -67509,21 +67519,21 @@
     </row>
     <row r="2922">
       <c r="A2922" s="1" t="n">
-        <v>9000054</v>
+        <v>9000051</v>
       </c>
       <c r="B2922" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C2922" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D2922" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2922" s="1" t="n"/>
@@ -67531,21 +67541,21 @@
     </row>
     <row r="2923">
       <c r="A2923" s="1" t="n">
-        <v>9000055</v>
+        <v>9000052</v>
       </c>
       <c r="B2923" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C2923" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D2923" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2923" s="1" t="n"/>
@@ -67553,21 +67563,21 @@
     </row>
     <row r="2924">
       <c r="A2924" s="1" t="n">
-        <v>9000056</v>
+        <v>9000053</v>
       </c>
       <c r="B2924" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C2924" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D2924" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E2924" s="1" t="n"/>
@@ -67575,21 +67585,21 @@
     </row>
     <row r="2925">
       <c r="A2925" s="1" t="n">
-        <v>9000057</v>
+        <v>9000054</v>
       </c>
       <c r="B2925" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C2925" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D2925" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2925" s="1" t="n"/>
@@ -67597,21 +67607,21 @@
     </row>
     <row r="2926">
       <c r="A2926" s="1" t="n">
-        <v>9000058</v>
+        <v>9000055</v>
       </c>
       <c r="B2926" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C2926" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D2926" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2926" s="1" t="n"/>
@@ -67619,16 +67629,16 @@
     </row>
     <row r="2927">
       <c r="A2927" s="1" t="n">
-        <v>9000059</v>
+        <v>9000056</v>
       </c>
       <c r="B2927" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C2927" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D2927" s="1" t="inlineStr">
@@ -67641,21 +67651,21 @@
     </row>
     <row r="2928">
       <c r="A2928" s="1" t="n">
-        <v>9000060</v>
+        <v>9000057</v>
       </c>
       <c r="B2928" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C2928" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D2928" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2928" s="1" t="n"/>
@@ -67663,21 +67673,21 @@
     </row>
     <row r="2929">
       <c r="A2929" s="1" t="n">
-        <v>9000061</v>
+        <v>9000058</v>
       </c>
       <c r="B2929" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C2929" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D2929" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2929" s="1" t="n"/>
@@ -67685,21 +67695,21 @@
     </row>
     <row r="2930">
       <c r="A2930" s="1" t="n">
-        <v>9000062</v>
+        <v>9000059</v>
       </c>
       <c r="B2930" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C2930" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D2930" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2930" s="1" t="n"/>
@@ -67707,16 +67717,16 @@
     </row>
     <row r="2931">
       <c r="A2931" s="1" t="n">
-        <v>9000063</v>
+        <v>9000060</v>
       </c>
       <c r="B2931" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C2931" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D2931" s="1" t="inlineStr">
@@ -67729,16 +67739,16 @@
     </row>
     <row r="2932">
       <c r="A2932" s="1" t="n">
-        <v>9000064</v>
+        <v>9000061</v>
       </c>
       <c r="B2932" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C2932" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D2932" s="1" t="inlineStr">
@@ -67751,21 +67761,21 @@
     </row>
     <row r="2933">
       <c r="A2933" s="1" t="n">
-        <v>9000065</v>
+        <v>9000062</v>
       </c>
       <c r="B2933" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C2933" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D2933" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2933" s="1" t="n"/>
@@ -67773,21 +67783,21 @@
     </row>
     <row r="2934">
       <c r="A2934" s="1" t="n">
-        <v>9000066</v>
+        <v>9000063</v>
       </c>
       <c r="B2934" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C2934" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D2934" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2934" s="1" t="n"/>
@@ -67795,21 +67805,21 @@
     </row>
     <row r="2935">
       <c r="A2935" s="1" t="n">
-        <v>9000067</v>
+        <v>9000064</v>
       </c>
       <c r="B2935" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C2935" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D2935" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2935" s="1" t="n"/>
@@ -67817,16 +67827,16 @@
     </row>
     <row r="2936">
       <c r="A2936" s="1" t="n">
-        <v>9000068</v>
+        <v>9000065</v>
       </c>
       <c r="B2936" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C2936" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D2936" s="1" t="inlineStr">
@@ -67839,16 +67849,16 @@
     </row>
     <row r="2937">
       <c r="A2937" s="1" t="n">
-        <v>9000069</v>
+        <v>9000066</v>
       </c>
       <c r="B2937" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C2937" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D2937" s="1" t="inlineStr">
@@ -67861,16 +67871,16 @@
     </row>
     <row r="2938">
       <c r="A2938" s="1" t="n">
-        <v>9000070</v>
+        <v>9000067</v>
       </c>
       <c r="B2938" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C2938" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D2938" s="1" t="inlineStr">
@@ -67883,16 +67893,16 @@
     </row>
     <row r="2939">
       <c r="A2939" s="1" t="n">
-        <v>9000071</v>
+        <v>9000068</v>
       </c>
       <c r="B2939" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C2939" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D2939" s="1" t="inlineStr">
@@ -67905,21 +67915,21 @@
     </row>
     <row r="2940">
       <c r="A2940" s="1" t="n">
-        <v>9000072</v>
+        <v>9000069</v>
       </c>
       <c r="B2940" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C2940" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D2940" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2940" s="1" t="n"/>
@@ -67927,21 +67937,21 @@
     </row>
     <row r="2941">
       <c r="A2941" s="1" t="n">
-        <v>9000073</v>
+        <v>9000070</v>
       </c>
       <c r="B2941" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C2941" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D2941" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2941" s="1" t="n"/>
@@ -67949,21 +67959,21 @@
     </row>
     <row r="2942">
       <c r="A2942" s="1" t="n">
-        <v>9000074</v>
+        <v>9000071</v>
       </c>
       <c r="B2942" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C2942" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D2942" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2942" s="1" t="n"/>
@@ -67971,16 +67981,16 @@
     </row>
     <row r="2943">
       <c r="A2943" s="1" t="n">
-        <v>9000075</v>
+        <v>9000072</v>
       </c>
       <c r="B2943" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C2943" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D2943" s="1" t="inlineStr">
@@ -67993,16 +68003,16 @@
     </row>
     <row r="2944">
       <c r="A2944" s="1" t="n">
-        <v>9000076</v>
+        <v>9000073</v>
       </c>
       <c r="B2944" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C2944" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D2944" s="1" t="inlineStr">
@@ -68015,21 +68025,21 @@
     </row>
     <row r="2945">
       <c r="A2945" s="1" t="n">
-        <v>9000077</v>
+        <v>9000074</v>
       </c>
       <c r="B2945" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C2945" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D2945" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2945" s="1" t="n"/>
@@ -68037,21 +68047,21 @@
     </row>
     <row r="2946">
       <c r="A2946" s="1" t="n">
-        <v>9000078</v>
+        <v>9000075</v>
       </c>
       <c r="B2946" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C2946" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D2946" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2946" s="1" t="n"/>
@@ -68059,21 +68069,21 @@
     </row>
     <row r="2947">
       <c r="A2947" s="1" t="n">
-        <v>9000079</v>
+        <v>9000076</v>
       </c>
       <c r="B2947" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C2947" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D2947" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2947" s="1" t="n"/>
@@ -68081,16 +68091,16 @@
     </row>
     <row r="2948">
       <c r="A2948" s="1" t="n">
-        <v>9000080</v>
+        <v>9000077</v>
       </c>
       <c r="B2948" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C2948" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D2948" s="1" t="inlineStr">
@@ -68103,21 +68113,21 @@
     </row>
     <row r="2949">
       <c r="A2949" s="1" t="n">
-        <v>9000081</v>
+        <v>9000078</v>
       </c>
       <c r="B2949" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C2949" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D2949" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2949" s="1" t="n"/>
@@ -68125,21 +68135,21 @@
     </row>
     <row r="2950">
       <c r="A2950" s="1" t="n">
-        <v>9000082</v>
+        <v>9000079</v>
       </c>
       <c r="B2950" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C2950" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D2950" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2950" s="1" t="n"/>
@@ -68147,21 +68157,21 @@
     </row>
     <row r="2951">
       <c r="A2951" s="1" t="n">
-        <v>9000083</v>
+        <v>9000080</v>
       </c>
       <c r="B2951" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C2951" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D2951" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2951" s="1" t="n"/>
@@ -68169,21 +68179,21 @@
     </row>
     <row r="2952">
       <c r="A2952" s="1" t="n">
-        <v>9000084</v>
+        <v>9000081</v>
       </c>
       <c r="B2952" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C2952" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D2952" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2952" s="1" t="n"/>
@@ -68191,21 +68201,21 @@
     </row>
     <row r="2953">
       <c r="A2953" s="1" t="n">
-        <v>9000085</v>
+        <v>9000082</v>
       </c>
       <c r="B2953" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C2953" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D2953" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2953" s="1" t="n"/>
@@ -68213,16 +68223,16 @@
     </row>
     <row r="2954">
       <c r="A2954" s="1" t="n">
-        <v>9000086</v>
+        <v>9000083</v>
       </c>
       <c r="B2954" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>헉헉</t>
         </is>
       </c>
       <c r="C2954" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>Huff puff</t>
         </is>
       </c>
       <c r="D2954" s="1" t="inlineStr">
@@ -68235,21 +68245,21 @@
     </row>
     <row r="2955">
       <c r="A2955" s="1" t="n">
-        <v>9000087</v>
+        <v>9000084</v>
       </c>
       <c r="B2955" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>더 빨리!</t>
         </is>
       </c>
       <c r="C2955" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>Faster!</t>
         </is>
       </c>
       <c r="D2955" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2955" s="1" t="n"/>
@@ -68257,21 +68267,21 @@
     </row>
     <row r="2956">
       <c r="A2956" s="1" t="n">
-        <v>9000088</v>
+        <v>9000085</v>
       </c>
       <c r="B2956" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>근육 붙는 중</t>
         </is>
       </c>
       <c r="C2956" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>Gains incoming</t>
         </is>
       </c>
       <c r="D2956" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2956" s="1" t="n"/>
@@ -68279,21 +68289,21 @@
     </row>
     <row r="2957">
       <c r="A2957" s="1" t="n">
-        <v>9000089</v>
+        <v>9000086</v>
       </c>
       <c r="B2957" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>찍찍찍찍</t>
         </is>
       </c>
       <c r="C2957" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>Squeak squeak squeak squeak</t>
         </is>
       </c>
       <c r="D2957" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2957" s="1" t="n"/>
@@ -68301,16 +68311,16 @@
     </row>
     <row r="2958">
       <c r="A2958" s="1" t="n">
-        <v>9000090</v>
+        <v>9000087</v>
       </c>
       <c r="B2958" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>으아아아~!</t>
         </is>
       </c>
       <c r="C2958" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>Waaaaah~!</t>
         </is>
       </c>
       <c r="D2958" s="1" t="inlineStr">
@@ -68323,21 +68333,21 @@
     </row>
     <row r="2959">
       <c r="A2959" s="1" t="n">
-        <v>9000091</v>
+        <v>9000088</v>
       </c>
       <c r="B2959" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>하암~ 잘 잤다</t>
         </is>
       </c>
       <c r="C2959" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Yawn~ what a nap</t>
         </is>
       </c>
       <c r="D2959" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2959" s="1" t="n"/>
@@ -68345,21 +68355,21 @@
     </row>
     <row r="2960">
       <c r="A2960" s="1" t="n">
-        <v>9000092</v>
+        <v>9000089</v>
       </c>
       <c r="B2960" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>냠, 배부르다</t>
         </is>
       </c>
       <c r="C2960" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Nom, so full</t>
         </is>
       </c>
       <c r="D2960" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2960" s="1" t="n"/>
@@ -68367,21 +68377,21 @@
     </row>
     <row r="2961">
       <c r="A2961" s="1" t="n">
-        <v>9000093</v>
+        <v>9000090</v>
       </c>
       <c r="B2961" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>휴…</t>
         </is>
       </c>
       <c r="C2961" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Phew...</t>
         </is>
       </c>
       <c r="D2961" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2961" s="1" t="n"/>
@@ -68389,21 +68399,21 @@
     </row>
     <row r="2962">
       <c r="A2962" s="1" t="n">
-        <v>9000094</v>
+        <v>9000091</v>
       </c>
       <c r="B2962" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>찍</t>
         </is>
       </c>
       <c r="C2962" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>Squeak</t>
         </is>
       </c>
       <c r="D2962" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
         </is>
       </c>
       <c r="E2962" s="1" t="n"/>
@@ -68411,21 +68421,21 @@
     </row>
     <row r="2963">
       <c r="A2963" s="1" t="n">
-        <v>9000095</v>
+        <v>9000092</v>
       </c>
       <c r="B2963" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C2963" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D2963" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/RunPage.cs:99</t>
         </is>
       </c>
       <c r="E2963" s="1" t="n"/>
@@ -68433,21 +68443,21 @@
     </row>
     <row r="2964">
       <c r="A2964" s="1" t="n">
-        <v>9000096</v>
+        <v>9000093</v>
       </c>
       <c r="B2964" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="C2964" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D2964" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
         </is>
       </c>
       <c r="E2964" s="1" t="n"/>
@@ -68455,21 +68465,21 @@
     </row>
     <row r="2965">
       <c r="A2965" s="1" t="n">
-        <v>9000097</v>
+        <v>9000094</v>
       </c>
       <c r="B2965" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>찌릿!!</t>
         </is>
       </c>
       <c r="C2965" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>ZAP!!</t>
         </is>
       </c>
       <c r="D2965" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2965" s="1" t="n"/>
@@ -68477,21 +68487,21 @@
     </row>
     <row r="2966">
       <c r="A2966" s="1" t="n">
-        <v>9000098</v>
+        <v>9000095</v>
       </c>
       <c r="B2966" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>콰릉!</t>
         </is>
       </c>
       <c r="C2966" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>Ka-boom!</t>
         </is>
       </c>
       <c r="D2966" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2966" s="1" t="n"/>
@@ -68499,21 +68509,21 @@
     </row>
     <row r="2967">
       <c r="A2967" s="1" t="n">
-        <v>9000099</v>
+        <v>9000096</v>
       </c>
       <c r="B2967" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>냠!</t>
         </is>
       </c>
       <c r="C2967" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>Nom!</t>
         </is>
       </c>
       <c r="D2967" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2967" s="1" t="n"/>
@@ -68521,21 +68531,21 @@
     </row>
     <row r="2968">
       <c r="A2968" s="1" t="n">
-        <v>9000100</v>
+        <v>9000097</v>
       </c>
       <c r="B2968" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>다닥!</t>
         </is>
       </c>
       <c r="C2968" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>Scurry!</t>
         </is>
       </c>
       <c r="D2968" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2968" s="1" t="n"/>
@@ -68543,21 +68553,21 @@
     </row>
     <row r="2969">
       <c r="A2969" s="1" t="n">
-        <v>9000101</v>
+        <v>9000098</v>
       </c>
       <c r="B2969" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>메리 쥐스마스!</t>
         </is>
       </c>
       <c r="C2969" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>Merry Ratmas!</t>
         </is>
       </c>
       <c r="D2969" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2969" s="1" t="n"/>
@@ -68565,21 +68575,21 @@
     </row>
     <row r="2970">
       <c r="A2970" s="1" t="n">
-        <v>9000102</v>
+        <v>9000099</v>
       </c>
       <c r="B2970" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>흐에~ 후원 감사합니다~!</t>
         </is>
       </c>
       <c r="C2970" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>Heheh~ thanks for the dono~!</t>
         </is>
       </c>
       <c r="D2970" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2970" s="1" t="n"/>
@@ -68587,21 +68597,21 @@
     </row>
     <row r="2971">
       <c r="A2971" s="1" t="n">
-        <v>9000103</v>
+        <v>9000100</v>
       </c>
       <c r="B2971" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>배달 왔습니다~</t>
         </is>
       </c>
       <c r="C2971" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Delivery~!</t>
         </is>
       </c>
       <c r="D2971" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2971" s="1" t="n"/>
@@ -68609,21 +68619,21 @@
     </row>
     <row r="2972">
       <c r="A2972" s="1" t="n">
-        <v>9000104</v>
+        <v>9000101</v>
       </c>
       <c r="B2972" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>백덤블링!</t>
         </is>
       </c>
       <c r="C2972" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Backflip!</t>
         </is>
       </c>
       <c r="D2972" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2972" s="1" t="n"/>
@@ -68631,21 +68641,21 @@
     </row>
     <row r="2973">
       <c r="A2973" s="1" t="n">
-        <v>9000105</v>
+        <v>9000102</v>
       </c>
       <c r="B2973" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>공중제비!</t>
         </is>
       </c>
       <c r="C2973" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>Somersault!</t>
         </is>
       </c>
       <c r="D2973" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2973" s="1" t="n"/>
@@ -68653,21 +68663,21 @@
     </row>
     <row r="2974">
       <c r="A2974" s="1" t="n">
-        <v>9000106</v>
+        <v>9000103</v>
       </c>
       <c r="B2974" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>찍-공중회전!</t>
         </is>
       </c>
       <c r="C2974" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>Squeak-flip!</t>
         </is>
       </c>
       <c r="D2974" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2974" s="1" t="n"/>
@@ -68675,21 +68685,21 @@
     </row>
     <row r="2975">
       <c r="A2975" s="1" t="n">
-        <v>9000107</v>
+        <v>9000104</v>
       </c>
       <c r="B2975" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>트리플 악셀!!</t>
         </is>
       </c>
       <c r="C2975" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>TRIPLE AXEL!!</t>
         </is>
       </c>
       <c r="D2975" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2975" s="1" t="n"/>
@@ -68697,21 +68707,21 @@
     </row>
     <row r="2976">
       <c r="A2976" s="1" t="n">
-        <v>9000108</v>
+        <v>9000105</v>
       </c>
       <c r="B2976" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>3회전 성공!</t>
         </is>
       </c>
       <c r="C2976" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>Triple spin landed!</t>
         </is>
       </c>
       <c r="D2976" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2976" s="1" t="n"/>
@@ -68719,21 +68729,21 @@
     </row>
     <row r="2977">
       <c r="A2977" s="1" t="n">
-        <v>9000109</v>
+        <v>9000106</v>
       </c>
       <c r="B2977" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>심사위원 전원 10점!</t>
         </is>
       </c>
       <c r="C2977" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>Perfect 10s from every judge!</t>
         </is>
       </c>
       <c r="D2977" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2977" s="1" t="n"/>
@@ -68741,21 +68751,21 @@
     </row>
     <row r="2978">
       <c r="A2978" s="1" t="n">
-        <v>9000110</v>
+        <v>9000107</v>
       </c>
       <c r="B2978" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>윈드밀!!</t>
         </is>
       </c>
       <c r="C2978" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>WINDMILL!!</t>
         </is>
       </c>
       <c r="D2978" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2978" s="1" t="n"/>
@@ -68763,21 +68773,21 @@
     </row>
     <row r="2979">
       <c r="A2979" s="1" t="n">
-        <v>9000111</v>
+        <v>9000108</v>
       </c>
       <c r="B2979" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>브레이크 댄스!</t>
         </is>
       </c>
       <c r="C2979" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>Breakdance!</t>
         </is>
       </c>
       <c r="D2979" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2979" s="1" t="n"/>
@@ -68785,21 +68795,21 @@
     </row>
     <row r="2980">
       <c r="A2980" s="1" t="n">
-        <v>9000112</v>
+        <v>9000109</v>
       </c>
       <c r="B2980" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>빙글빙글 파괴!</t>
         </is>
       </c>
       <c r="C2980" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>Spin-to-win destruction!</t>
         </is>
       </c>
       <c r="D2980" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2980" s="1" t="n"/>
@@ -68807,21 +68817,21 @@
     </row>
     <row r="2981">
       <c r="A2981" s="1" t="n">
-        <v>9000113</v>
+        <v>9000110</v>
       </c>
       <c r="B2981" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>쥐 대포알!</t>
         </is>
       </c>
       <c r="C2981" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>Rat Cannonball!</t>
         </is>
       </c>
       <c r="D2981" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2981" s="1" t="n"/>
@@ -68829,21 +68839,21 @@
     </row>
     <row r="2982">
       <c r="A2982" s="1" t="n">
-        <v>9000114</v>
+        <v>9000111</v>
       </c>
       <c r="B2982" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>데굴데굴!</t>
         </is>
       </c>
       <c r="C2982" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>Roll roll!</t>
         </is>
       </c>
       <c r="D2982" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2982" s="1" t="n"/>
@@ -68851,21 +68861,21 @@
     </row>
     <row r="2983">
       <c r="A2983" s="1" t="n">
-        <v>9000115</v>
+        <v>9000112</v>
       </c>
       <c r="B2983" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>핀볼 모드!</t>
         </is>
       </c>
       <c r="C2983" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>Pinball mode!</t>
         </is>
       </c>
       <c r="D2983" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2983" s="1" t="n"/>
@@ -68873,21 +68883,21 @@
     </row>
     <row r="2984">
       <c r="A2984" s="1" t="n">
-        <v>9000116</v>
+        <v>9000113</v>
       </c>
       <c r="B2984" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>쳇바퀴 돌기!!</t>
         </is>
       </c>
       <c r="C2984" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>WHEEL SPIN!!</t>
         </is>
       </c>
       <c r="D2984" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2984" s="1" t="n"/>
@@ -68895,21 +68905,21 @@
     </row>
     <row r="2985">
       <c r="A2985" s="1" t="n">
-        <v>9000117</v>
+        <v>9000114</v>
       </c>
       <c r="B2985" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>빙글빙글~</t>
         </is>
       </c>
       <c r="C2985" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>Round and round~</t>
         </is>
       </c>
       <c r="D2985" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2985" s="1" t="n"/>
@@ -68917,21 +68927,21 @@
     </row>
     <row r="2986">
       <c r="A2986" s="1" t="n">
-        <v>9000118</v>
+        <v>9000115</v>
       </c>
       <c r="B2986" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>어지러워!!</t>
         </is>
       </c>
       <c r="C2986" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>So DIZZY!!</t>
         </is>
       </c>
       <c r="D2986" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2986" s="1" t="n"/>
@@ -68939,21 +68949,21 @@
     </row>
     <row r="2987">
       <c r="A2987" s="1" t="n">
-        <v>9000119</v>
+        <v>9000116</v>
       </c>
       <c r="B2987" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="C2987" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="D2987" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
         </is>
       </c>
       <c r="E2987" s="1" t="n"/>
@@ -68961,21 +68971,21 @@
     </row>
     <row r="2988">
       <c r="A2988" s="1" t="n">
-        <v>9000120</v>
+        <v>9000117</v>
       </c>
       <c r="B2988" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>기절!!</t>
         </is>
       </c>
       <c r="C2988" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>Stunned!!</t>
         </is>
       </c>
       <c r="D2988" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Rats/RatManager.cs:38</t>
         </is>
       </c>
       <c r="E2988" s="1" t="n"/>
@@ -68983,21 +68993,21 @@
     </row>
     <row r="2989">
       <c r="A2989" s="1" t="n">
-        <v>9000121</v>
+        <v>9000118</v>
       </c>
       <c r="B2989" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>소품이 떨어졌다!</t>
         </is>
       </c>
       <c r="C2989" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>A prop dropped!</t>
         </is>
       </c>
       <c r="D2989" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Rats/RatManager.cs:397</t>
         </is>
       </c>
       <c r="E2989" s="1" t="n"/>
@@ -69005,21 +69015,21 @@
     </row>
     <row r="2990">
       <c r="A2990" s="1" t="n">
-        <v>9000122</v>
+        <v>9000119</v>
       </c>
       <c r="B2990" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>조각 +1</t>
         </is>
       </c>
       <c r="C2990" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>Shard +1</t>
         </is>
       </c>
       <c r="D2990" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Rats/RatManager.cs:460</t>
         </is>
       </c>
       <c r="E2990" s="1" t="n"/>
@@ -69027,21 +69037,21 @@
     </row>
     <row r="2991">
       <c r="A2991" s="1" t="n">
-        <v>9000123</v>
+        <v>9000120</v>
       </c>
       <c r="B2991" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>{name} 강화! Lv {lv}</t>
         </is>
       </c>
       <c r="C2991" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>{name} powered up! Lv {lv}</t>
         </is>
       </c>
       <c r="D2991" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Rats/RatManager.cs:461</t>
         </is>
       </c>
       <c r="E2991" s="1" t="n"/>
@@ -69049,21 +69059,21 @@
     </row>
     <row r="2992">
       <c r="A2992" s="1" t="n">
-        <v>9000124</v>
+        <v>9000121</v>
       </c>
       <c r="B2992" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>{grade} 탄생!</t>
         </is>
       </c>
       <c r="C2992" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>{grade} born!</t>
         </is>
       </c>
       <c r="D2992" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:561</t>
         </is>
       </c>
       <c r="E2992" s="1" t="n"/>
@@ -69071,21 +69081,21 @@
     </row>
     <row r="2993">
       <c r="A2993" s="1" t="n">
-        <v>9000125</v>
+        <v>9000122</v>
       </c>
       <c r="B2993" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>쌍둥이!</t>
         </is>
       </c>
       <c r="C2993" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>Twins!</t>
         </is>
       </c>
       <c r="D2993" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:566</t>
         </is>
       </c>
       <c r="E2993" s="1" t="n"/>
@@ -69093,21 +69103,21 @@
     </row>
     <row r="2994">
       <c r="A2994" s="1" t="n">
-        <v>9000126</v>
+        <v>9000123</v>
       </c>
       <c r="B2994" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>치즈 운석!</t>
         </is>
       </c>
       <c r="C2994" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>Cheese Meteor!</t>
         </is>
       </c>
       <c r="D2994" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Rats/RatManager.cs:627</t>
         </is>
       </c>
       <c r="E2994" s="1" t="n"/>
@@ -69115,21 +69125,21 @@
     </row>
     <row r="2995">
       <c r="A2995" s="1" t="n">
-        <v>9000127</v>
+        <v>9000124</v>
       </c>
       <c r="B2995" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>{floor}층 · {zone}</t>
         </is>
       </c>
       <c r="C2995" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>Floor {floor} · {zone}</t>
         </is>
       </c>
       <c r="D2995" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E2995" s="1" t="n"/>
@@ -69137,21 +69147,21 @@
     </row>
     <row r="2996">
       <c r="A2996" s="1" t="n">
-        <v>9000128</v>
+        <v>9000125</v>
       </c>
       <c r="B2996" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>계단 방 벽을 부숴라!</t>
         </is>
       </c>
       <c r="C2996" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>Smash the wall to the stairs room!</t>
         </is>
       </c>
       <c r="D2996" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E2996" s="1" t="n"/>
@@ -69159,21 +69169,21 @@
     </row>
     <row r="2997">
       <c r="A2997" s="1" t="n">
-        <v>9000129</v>
+        <v>9000126</v>
       </c>
       <c r="B2997" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>벽 붕괴! 방 확장</t>
         </is>
       </c>
       <c r="C2997" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>Wall down! Room expanded</t>
         </is>
       </c>
       <c r="D2997" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2997" s="1" t="n"/>
@@ -69181,21 +69191,21 @@
     </row>
     <row r="2998">
       <c r="A2998" s="1" t="n">
-        <v>9000130</v>
+        <v>9000127</v>
       </c>
       <c r="B2998" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>계단 발견!</t>
         </is>
       </c>
       <c r="C2998" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Stairs found!</t>
         </is>
       </c>
       <c r="D2998" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:338</t>
         </is>
       </c>
       <c r="E2998" s="1" t="n"/>
@@ -69203,25 +69213,91 @@
     </row>
     <row r="2999">
       <c r="A2999" s="1" t="n">
-        <v>9000131</v>
+        <v>9000128</v>
       </c>
       <c r="B2999" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>계단에 닿으면 {next}층으로</t>
         </is>
       </c>
       <c r="C2999" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>Touch the stairs to go to Floor {next}</t>
         </is>
       </c>
       <c r="D2999" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:338</t>
         </is>
       </c>
       <c r="E2999" s="1" t="n"/>
       <c r="F2999" s="1" t="n"/>
+    </row>
+    <row r="3000">
+      <c r="A3000" s="1" t="n">
+        <v>9000129</v>
+      </c>
+      <c r="B3000" s="2" t="inlineStr">
+        <is>
+          <t>와르르!!</t>
+        </is>
+      </c>
+      <c r="C3000" s="2" t="inlineStr">
+        <is>
+          <t>Crumble!!</t>
+        </is>
+      </c>
+      <c r="D3000" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3000" s="1" t="n"/>
+      <c r="F3000" s="1" t="n"/>
+    </row>
+    <row r="3001">
+      <c r="A3001" s="1" t="n">
+        <v>9000130</v>
+      </c>
+      <c r="B3001" s="2" t="inlineStr">
+        <is>
+          <t>콰광!!</t>
+        </is>
+      </c>
+      <c r="C3001" s="2" t="inlineStr">
+        <is>
+          <t>KA-BOOM!!</t>
+        </is>
+      </c>
+      <c r="D3001" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3001" s="1" t="n"/>
+      <c r="F3001" s="1" t="n"/>
+    </row>
+    <row r="3002">
+      <c r="A3002" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B3002" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C3002" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D3002" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3002" s="1" t="n"/>
+      <c r="F3002" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3002"/>
+  <dimension ref="A1:F3004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -56374,7 +56374,11 @@
           <t>씬 · Lobby · UI/Prep/TopBar/HomeButton/Label</t>
         </is>
       </c>
-      <c r="E2421" s="1" t="n"/>
+      <c r="E2421" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F2421" s="1" t="n"/>
     </row>
     <row r="2422">
@@ -66302,7 +66306,11 @@
           <t>씬 · Game · HUD/Augment/Bar/ManageButton/Label</t>
         </is>
       </c>
-      <c r="E2866" s="1" t="n"/>
+      <c r="E2866" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F2866" s="1" t="n"/>
     </row>
     <row r="2867">
@@ -66419,21 +66427,21 @@
     </row>
     <row r="2872">
       <c r="A2872" s="1" t="n">
-        <v>9000001</v>
+        <v>8000513</v>
       </c>
       <c r="B2872" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power} / 적정 {need}</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="C2872" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power} / Rec. {need}</t>
+          <t>Augments</t>
         </is>
       </c>
       <c r="D2872" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
+          <t>씬 · Game · HUD/Augment/Bar/ManageButton/Label</t>
         </is>
       </c>
       <c r="E2872" s="1" t="n"/>
@@ -66441,21 +66449,21 @@
     </row>
     <row r="2873">
       <c r="A2873" s="1" t="n">
-        <v>9000002</v>
+        <v>8000514</v>
       </c>
       <c r="B2873" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>아지트로</t>
         </is>
       </c>
       <c r="C2873" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>To Hideout</t>
         </is>
       </c>
       <c r="D2873" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
+          <t>씬 · Lobby · UI/Prep/TopBar/HomeButton/Label</t>
         </is>
       </c>
       <c r="E2873" s="1" t="n"/>
@@ -66463,21 +66471,21 @@
     </row>
     <row r="2874">
       <c r="A2874" s="1" t="n">
-        <v>9000003</v>
+        <v>9000001</v>
       </c>
       <c r="B2874" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>찍찍!! {power} / 적정 {need}</t>
         </is>
       </c>
       <c r="C2874" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>SQUEAK!! {power} / Rec. {need}</t>
         </is>
       </c>
       <c r="D2874" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E2874" s="1" t="n"/>
@@ -66485,21 +66493,21 @@
     </row>
     <row r="2875">
       <c r="A2875" s="1" t="n">
-        <v>9000004</v>
+        <v>9000002</v>
       </c>
       <c r="B2875" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C2875" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D2875" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2875" s="1" t="n"/>
@@ -66507,21 +66515,21 @@
     </row>
     <row r="2876">
       <c r="A2876" s="1" t="n">
-        <v>9000005</v>
+        <v>9000003</v>
       </c>
       <c r="B2876" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C2876" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D2876" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E2876" s="1" t="n"/>
@@ -66529,21 +66537,21 @@
     </row>
     <row r="2877">
       <c r="A2877" s="1" t="n">
-        <v>9000006</v>
+        <v>9000004</v>
       </c>
       <c r="B2877" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C2877" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D2877" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E2877" s="1" t="n"/>
@@ -66551,21 +66559,21 @@
     </row>
     <row r="2878">
       <c r="A2878" s="1" t="n">
-        <v>9000007</v>
+        <v>9000005</v>
       </c>
       <c r="B2878" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C2878" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D2878" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E2878" s="1" t="n"/>
@@ -66573,21 +66581,21 @@
     </row>
     <row r="2879">
       <c r="A2879" s="1" t="n">
-        <v>9000008</v>
+        <v>9000006</v>
       </c>
       <c r="B2879" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C2879" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D2879" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E2879" s="1" t="n"/>
@@ -66595,21 +66603,21 @@
     </row>
     <row r="2880">
       <c r="A2880" s="1" t="n">
-        <v>9000009</v>
+        <v>9000007</v>
       </c>
       <c r="B2880" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C2880" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D2880" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E2880" s="1" t="n"/>
@@ -66617,16 +66625,16 @@
     </row>
     <row r="2881">
       <c r="A2881" s="1" t="n">
-        <v>9000010</v>
+        <v>9000008</v>
       </c>
       <c r="B2881" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C2881" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D2881" s="1" t="inlineStr">
@@ -66639,16 +66647,16 @@
     </row>
     <row r="2882">
       <c r="A2882" s="1" t="n">
-        <v>9000011</v>
+        <v>9000009</v>
       </c>
       <c r="B2882" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C2882" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D2882" s="1" t="inlineStr">
@@ -66661,21 +66669,21 @@
     </row>
     <row r="2883">
       <c r="A2883" s="1" t="n">
-        <v>9000012</v>
+        <v>9000010</v>
       </c>
       <c r="B2883" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C2883" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D2883" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2883" s="1" t="n"/>
@@ -66683,21 +66691,21 @@
     </row>
     <row r="2884">
       <c r="A2884" s="1" t="n">
-        <v>9000013</v>
+        <v>9000011</v>
       </c>
       <c r="B2884" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C2884" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D2884" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2884" s="1" t="n"/>
@@ -66705,21 +66713,21 @@
     </row>
     <row r="2885">
       <c r="A2885" s="1" t="n">
-        <v>9000014</v>
+        <v>9000012</v>
       </c>
       <c r="B2885" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C2885" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D2885" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2885" s="1" t="n"/>
@@ -66727,21 +66735,21 @@
     </row>
     <row r="2886">
       <c r="A2886" s="1" t="n">
-        <v>9000015</v>
+        <v>9000013</v>
       </c>
       <c r="B2886" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C2886" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D2886" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2886" s="1" t="n"/>
@@ -66749,21 +66757,21 @@
     </row>
     <row r="2887">
       <c r="A2887" s="1" t="n">
-        <v>9000016</v>
+        <v>9000014</v>
       </c>
       <c r="B2887" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C2887" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D2887" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E2887" s="1" t="n"/>
@@ -66771,21 +66779,21 @@
     </row>
     <row r="2888">
       <c r="A2888" s="1" t="n">
-        <v>9000017</v>
+        <v>9000015</v>
       </c>
       <c r="B2888" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C2888" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D2888" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2888" s="1" t="n"/>
@@ -66793,21 +66801,21 @@
     </row>
     <row r="2889">
       <c r="A2889" s="1" t="n">
-        <v>9000018</v>
+        <v>9000016</v>
       </c>
       <c r="B2889" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C2889" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D2889" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2889" s="1" t="n"/>
@@ -66815,21 +66823,21 @@
     </row>
     <row r="2890">
       <c r="A2890" s="1" t="n">
-        <v>9000019</v>
+        <v>9000017</v>
       </c>
       <c r="B2890" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C2890" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D2890" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E2890" s="1" t="n"/>
@@ -66837,16 +66845,16 @@
     </row>
     <row r="2891">
       <c r="A2891" s="1" t="n">
-        <v>9000020</v>
+        <v>9000018</v>
       </c>
       <c r="B2891" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C2891" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D2891" s="1" t="inlineStr">
@@ -66859,21 +66867,21 @@
     </row>
     <row r="2892">
       <c r="A2892" s="1" t="n">
-        <v>9000021</v>
+        <v>9000019</v>
       </c>
       <c r="B2892" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C2892" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D2892" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2892" s="1" t="n"/>
@@ -66881,21 +66889,21 @@
     </row>
     <row r="2893">
       <c r="A2893" s="1" t="n">
-        <v>9000022</v>
+        <v>9000020</v>
       </c>
       <c r="B2893" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C2893" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D2893" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2893" s="1" t="n"/>
@@ -66903,21 +66911,21 @@
     </row>
     <row r="2894">
       <c r="A2894" s="1" t="n">
-        <v>9000023</v>
+        <v>9000021</v>
       </c>
       <c r="B2894" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C2894" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D2894" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E2894" s="1" t="n"/>
@@ -66925,16 +66933,16 @@
     </row>
     <row r="2895">
       <c r="A2895" s="1" t="n">
-        <v>9000024</v>
+        <v>9000022</v>
       </c>
       <c r="B2895" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C2895" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D2895" s="1" t="inlineStr">
@@ -66947,16 +66955,16 @@
     </row>
     <row r="2896">
       <c r="A2896" s="1" t="n">
-        <v>9000025</v>
+        <v>9000023</v>
       </c>
       <c r="B2896" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C2896" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D2896" s="1" t="inlineStr">
@@ -66969,21 +66977,21 @@
     </row>
     <row r="2897">
       <c r="A2897" s="1" t="n">
-        <v>9000026</v>
+        <v>9000024</v>
       </c>
       <c r="B2897" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C2897" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D2897" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2897" s="1" t="n"/>
@@ -66991,21 +66999,21 @@
     </row>
     <row r="2898">
       <c r="A2898" s="1" t="n">
-        <v>9000027</v>
+        <v>9000025</v>
       </c>
       <c r="B2898" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C2898" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D2898" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2898" s="1" t="n"/>
@@ -67013,21 +67021,21 @@
     </row>
     <row r="2899">
       <c r="A2899" s="1" t="n">
-        <v>9000028</v>
+        <v>9000026</v>
       </c>
       <c r="B2899" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C2899" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D2899" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E2899" s="1" t="n"/>
@@ -67035,21 +67043,21 @@
     </row>
     <row r="2900">
       <c r="A2900" s="1" t="n">
-        <v>9000029</v>
+        <v>9000027</v>
       </c>
       <c r="B2900" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C2900" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D2900" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2900" s="1" t="n"/>
@@ -67057,21 +67065,21 @@
     </row>
     <row r="2901">
       <c r="A2901" s="1" t="n">
-        <v>9000030</v>
+        <v>9000028</v>
       </c>
       <c r="B2901" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C2901" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D2901" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2901" s="1" t="n"/>
@@ -67079,21 +67087,21 @@
     </row>
     <row r="2902">
       <c r="A2902" s="1" t="n">
-        <v>9000031</v>
+        <v>9000029</v>
       </c>
       <c r="B2902" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C2902" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D2902" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2902" s="1" t="n"/>
@@ -67101,21 +67109,21 @@
     </row>
     <row r="2903">
       <c r="A2903" s="1" t="n">
-        <v>9000032</v>
+        <v>9000030</v>
       </c>
       <c r="B2903" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C2903" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D2903" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E2903" s="1" t="n"/>
@@ -67123,21 +67131,21 @@
     </row>
     <row r="2904">
       <c r="A2904" s="1" t="n">
-        <v>9000033</v>
+        <v>9000031</v>
       </c>
       <c r="B2904" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C2904" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D2904" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E2904" s="1" t="n"/>
@@ -67145,16 +67153,16 @@
     </row>
     <row r="2905">
       <c r="A2905" s="1" t="n">
-        <v>9000034</v>
+        <v>9000032</v>
       </c>
       <c r="B2905" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C2905" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D2905" s="1" t="inlineStr">
@@ -67167,21 +67175,21 @@
     </row>
     <row r="2906">
       <c r="A2906" s="1" t="n">
-        <v>9000035</v>
+        <v>9000033</v>
       </c>
       <c r="B2906" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C2906" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D2906" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2906" s="1" t="n"/>
@@ -67189,21 +67197,21 @@
     </row>
     <row r="2907">
       <c r="A2907" s="1" t="n">
-        <v>9000036</v>
+        <v>9000034</v>
       </c>
       <c r="B2907" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C2907" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D2907" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2907" s="1" t="n"/>
@@ -67211,21 +67219,21 @@
     </row>
     <row r="2908">
       <c r="A2908" s="1" t="n">
-        <v>9000037</v>
+        <v>9000035</v>
       </c>
       <c r="B2908" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C2908" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D2908" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E2908" s="1" t="n"/>
@@ -67233,21 +67241,21 @@
     </row>
     <row r="2909">
       <c r="A2909" s="1" t="n">
-        <v>9000038</v>
+        <v>9000036</v>
       </c>
       <c r="B2909" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C2909" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D2909" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E2909" s="1" t="n"/>
@@ -67255,21 +67263,21 @@
     </row>
     <row r="2910">
       <c r="A2910" s="1" t="n">
-        <v>9000039</v>
+        <v>9000037</v>
       </c>
       <c r="B2910" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C2910" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D2910" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E2910" s="1" t="n"/>
@@ -67277,21 +67285,21 @@
     </row>
     <row r="2911">
       <c r="A2911" s="1" t="n">
-        <v>9000040</v>
+        <v>9000038</v>
       </c>
       <c r="B2911" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C2911" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D2911" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E2911" s="1" t="n"/>
@@ -67299,21 +67307,21 @@
     </row>
     <row r="2912">
       <c r="A2912" s="1" t="n">
-        <v>9000041</v>
+        <v>9000039</v>
       </c>
       <c r="B2912" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C2912" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D2912" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E2912" s="1" t="n"/>
@@ -67321,21 +67329,21 @@
     </row>
     <row r="2913">
       <c r="A2913" s="1" t="n">
-        <v>9000042</v>
+        <v>9000040</v>
       </c>
       <c r="B2913" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C2913" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D2913" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E2913" s="1" t="n"/>
@@ -67343,21 +67351,21 @@
     </row>
     <row r="2914">
       <c r="A2914" s="1" t="n">
-        <v>9000043</v>
+        <v>9000041</v>
       </c>
       <c r="B2914" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C2914" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D2914" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2914" s="1" t="n"/>
@@ -67365,16 +67373,16 @@
     </row>
     <row r="2915">
       <c r="A2915" s="1" t="n">
-        <v>9000044</v>
+        <v>9000042</v>
       </c>
       <c r="B2915" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C2915" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D2915" s="1" t="inlineStr">
@@ -67387,16 +67395,16 @@
     </row>
     <row r="2916">
       <c r="A2916" s="1" t="n">
-        <v>9000045</v>
+        <v>9000043</v>
       </c>
       <c r="B2916" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C2916" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D2916" s="1" t="inlineStr">
@@ -67409,21 +67417,21 @@
     </row>
     <row r="2917">
       <c r="A2917" s="1" t="n">
-        <v>9000046</v>
+        <v>9000044</v>
       </c>
       <c r="B2917" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C2917" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D2917" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2917" s="1" t="n"/>
@@ -67431,21 +67439,21 @@
     </row>
     <row r="2918">
       <c r="A2918" s="1" t="n">
-        <v>9000047</v>
+        <v>9000045</v>
       </c>
       <c r="B2918" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C2918" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D2918" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2918" s="1" t="n"/>
@@ -67453,16 +67461,16 @@
     </row>
     <row r="2919">
       <c r="A2919" s="1" t="n">
-        <v>9000048</v>
+        <v>9000046</v>
       </c>
       <c r="B2919" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C2919" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D2919" s="1" t="inlineStr">
@@ -67475,21 +67483,21 @@
     </row>
     <row r="2920">
       <c r="A2920" s="1" t="n">
-        <v>9000049</v>
+        <v>9000047</v>
       </c>
       <c r="B2920" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C2920" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D2920" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2920" s="1" t="n"/>
@@ -67497,21 +67505,21 @@
     </row>
     <row r="2921">
       <c r="A2921" s="1" t="n">
-        <v>9000050</v>
+        <v>9000048</v>
       </c>
       <c r="B2921" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C2921" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D2921" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2921" s="1" t="n"/>
@@ -67519,21 +67527,21 @@
     </row>
     <row r="2922">
       <c r="A2922" s="1" t="n">
-        <v>9000051</v>
+        <v>9000049</v>
       </c>
       <c r="B2922" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C2922" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D2922" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E2922" s="1" t="n"/>
@@ -67541,21 +67549,21 @@
     </row>
     <row r="2923">
       <c r="A2923" s="1" t="n">
-        <v>9000052</v>
+        <v>9000050</v>
       </c>
       <c r="B2923" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C2923" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D2923" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E2923" s="1" t="n"/>
@@ -67563,21 +67571,21 @@
     </row>
     <row r="2924">
       <c r="A2924" s="1" t="n">
-        <v>9000053</v>
+        <v>9000051</v>
       </c>
       <c r="B2924" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C2924" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D2924" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2924" s="1" t="n"/>
@@ -67585,21 +67593,21 @@
     </row>
     <row r="2925">
       <c r="A2925" s="1" t="n">
-        <v>9000054</v>
+        <v>9000052</v>
       </c>
       <c r="B2925" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C2925" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D2925" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2925" s="1" t="n"/>
@@ -67607,21 +67615,21 @@
     </row>
     <row r="2926">
       <c r="A2926" s="1" t="n">
-        <v>9000055</v>
+        <v>9000053</v>
       </c>
       <c r="B2926" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C2926" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D2926" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E2926" s="1" t="n"/>
@@ -67629,21 +67637,21 @@
     </row>
     <row r="2927">
       <c r="A2927" s="1" t="n">
-        <v>9000056</v>
+        <v>9000054</v>
       </c>
       <c r="B2927" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C2927" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D2927" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2927" s="1" t="n"/>
@@ -67651,21 +67659,21 @@
     </row>
     <row r="2928">
       <c r="A2928" s="1" t="n">
-        <v>9000057</v>
+        <v>9000055</v>
       </c>
       <c r="B2928" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C2928" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D2928" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2928" s="1" t="n"/>
@@ -67673,16 +67681,16 @@
     </row>
     <row r="2929">
       <c r="A2929" s="1" t="n">
-        <v>9000058</v>
+        <v>9000056</v>
       </c>
       <c r="B2929" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C2929" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D2929" s="1" t="inlineStr">
@@ -67695,16 +67703,16 @@
     </row>
     <row r="2930">
       <c r="A2930" s="1" t="n">
-        <v>9000059</v>
+        <v>9000057</v>
       </c>
       <c r="B2930" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C2930" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D2930" s="1" t="inlineStr">
@@ -67717,21 +67725,21 @@
     </row>
     <row r="2931">
       <c r="A2931" s="1" t="n">
-        <v>9000060</v>
+        <v>9000058</v>
       </c>
       <c r="B2931" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C2931" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D2931" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2931" s="1" t="n"/>
@@ -67739,21 +67747,21 @@
     </row>
     <row r="2932">
       <c r="A2932" s="1" t="n">
-        <v>9000061</v>
+        <v>9000059</v>
       </c>
       <c r="B2932" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C2932" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D2932" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2932" s="1" t="n"/>
@@ -67761,16 +67769,16 @@
     </row>
     <row r="2933">
       <c r="A2933" s="1" t="n">
-        <v>9000062</v>
+        <v>9000060</v>
       </c>
       <c r="B2933" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C2933" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D2933" s="1" t="inlineStr">
@@ -67783,16 +67791,16 @@
     </row>
     <row r="2934">
       <c r="A2934" s="1" t="n">
-        <v>9000063</v>
+        <v>9000061</v>
       </c>
       <c r="B2934" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C2934" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D2934" s="1" t="inlineStr">
@@ -67805,16 +67813,16 @@
     </row>
     <row r="2935">
       <c r="A2935" s="1" t="n">
-        <v>9000064</v>
+        <v>9000062</v>
       </c>
       <c r="B2935" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C2935" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D2935" s="1" t="inlineStr">
@@ -67827,21 +67835,21 @@
     </row>
     <row r="2936">
       <c r="A2936" s="1" t="n">
-        <v>9000065</v>
+        <v>9000063</v>
       </c>
       <c r="B2936" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C2936" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D2936" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2936" s="1" t="n"/>
@@ -67849,21 +67857,21 @@
     </row>
     <row r="2937">
       <c r="A2937" s="1" t="n">
-        <v>9000066</v>
+        <v>9000064</v>
       </c>
       <c r="B2937" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C2937" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D2937" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2937" s="1" t="n"/>
@@ -67871,16 +67879,16 @@
     </row>
     <row r="2938">
       <c r="A2938" s="1" t="n">
-        <v>9000067</v>
+        <v>9000065</v>
       </c>
       <c r="B2938" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C2938" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D2938" s="1" t="inlineStr">
@@ -67893,16 +67901,16 @@
     </row>
     <row r="2939">
       <c r="A2939" s="1" t="n">
-        <v>9000068</v>
+        <v>9000066</v>
       </c>
       <c r="B2939" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C2939" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D2939" s="1" t="inlineStr">
@@ -67915,16 +67923,16 @@
     </row>
     <row r="2940">
       <c r="A2940" s="1" t="n">
-        <v>9000069</v>
+        <v>9000067</v>
       </c>
       <c r="B2940" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C2940" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D2940" s="1" t="inlineStr">
@@ -67937,16 +67945,16 @@
     </row>
     <row r="2941">
       <c r="A2941" s="1" t="n">
-        <v>9000070</v>
+        <v>9000068</v>
       </c>
       <c r="B2941" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C2941" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D2941" s="1" t="inlineStr">
@@ -67959,16 +67967,16 @@
     </row>
     <row r="2942">
       <c r="A2942" s="1" t="n">
-        <v>9000071</v>
+        <v>9000069</v>
       </c>
       <c r="B2942" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C2942" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D2942" s="1" t="inlineStr">
@@ -67981,21 +67989,21 @@
     </row>
     <row r="2943">
       <c r="A2943" s="1" t="n">
-        <v>9000072</v>
+        <v>9000070</v>
       </c>
       <c r="B2943" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C2943" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D2943" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2943" s="1" t="n"/>
@@ -68003,21 +68011,21 @@
     </row>
     <row r="2944">
       <c r="A2944" s="1" t="n">
-        <v>9000073</v>
+        <v>9000071</v>
       </c>
       <c r="B2944" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C2944" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D2944" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2944" s="1" t="n"/>
@@ -68025,16 +68033,16 @@
     </row>
     <row r="2945">
       <c r="A2945" s="1" t="n">
-        <v>9000074</v>
+        <v>9000072</v>
       </c>
       <c r="B2945" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C2945" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D2945" s="1" t="inlineStr">
@@ -68047,16 +68055,16 @@
     </row>
     <row r="2946">
       <c r="A2946" s="1" t="n">
-        <v>9000075</v>
+        <v>9000073</v>
       </c>
       <c r="B2946" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C2946" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D2946" s="1" t="inlineStr">
@@ -68069,16 +68077,16 @@
     </row>
     <row r="2947">
       <c r="A2947" s="1" t="n">
-        <v>9000076</v>
+        <v>9000074</v>
       </c>
       <c r="B2947" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C2947" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D2947" s="1" t="inlineStr">
@@ -68091,21 +68099,21 @@
     </row>
     <row r="2948">
       <c r="A2948" s="1" t="n">
-        <v>9000077</v>
+        <v>9000075</v>
       </c>
       <c r="B2948" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C2948" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D2948" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2948" s="1" t="n"/>
@@ -68113,21 +68121,21 @@
     </row>
     <row r="2949">
       <c r="A2949" s="1" t="n">
-        <v>9000078</v>
+        <v>9000076</v>
       </c>
       <c r="B2949" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C2949" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D2949" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2949" s="1" t="n"/>
@@ -68135,16 +68143,16 @@
     </row>
     <row r="2950">
       <c r="A2950" s="1" t="n">
-        <v>9000079</v>
+        <v>9000077</v>
       </c>
       <c r="B2950" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C2950" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D2950" s="1" t="inlineStr">
@@ -68157,16 +68165,16 @@
     </row>
     <row r="2951">
       <c r="A2951" s="1" t="n">
-        <v>9000080</v>
+        <v>9000078</v>
       </c>
       <c r="B2951" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C2951" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D2951" s="1" t="inlineStr">
@@ -68179,21 +68187,21 @@
     </row>
     <row r="2952">
       <c r="A2952" s="1" t="n">
-        <v>9000081</v>
+        <v>9000079</v>
       </c>
       <c r="B2952" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C2952" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D2952" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2952" s="1" t="n"/>
@@ -68201,21 +68209,21 @@
     </row>
     <row r="2953">
       <c r="A2953" s="1" t="n">
-        <v>9000082</v>
+        <v>9000080</v>
       </c>
       <c r="B2953" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C2953" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D2953" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2953" s="1" t="n"/>
@@ -68223,21 +68231,21 @@
     </row>
     <row r="2954">
       <c r="A2954" s="1" t="n">
-        <v>9000083</v>
+        <v>9000081</v>
       </c>
       <c r="B2954" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C2954" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D2954" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2954" s="1" t="n"/>
@@ -68245,21 +68253,21 @@
     </row>
     <row r="2955">
       <c r="A2955" s="1" t="n">
-        <v>9000084</v>
+        <v>9000082</v>
       </c>
       <c r="B2955" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C2955" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D2955" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2955" s="1" t="n"/>
@@ -68267,16 +68275,16 @@
     </row>
     <row r="2956">
       <c r="A2956" s="1" t="n">
-        <v>9000085</v>
+        <v>9000083</v>
       </c>
       <c r="B2956" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>헉헉</t>
         </is>
       </c>
       <c r="C2956" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>Huff puff</t>
         </is>
       </c>
       <c r="D2956" s="1" t="inlineStr">
@@ -68289,16 +68297,16 @@
     </row>
     <row r="2957">
       <c r="A2957" s="1" t="n">
-        <v>9000086</v>
+        <v>9000084</v>
       </c>
       <c r="B2957" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>더 빨리!</t>
         </is>
       </c>
       <c r="C2957" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>Faster!</t>
         </is>
       </c>
       <c r="D2957" s="1" t="inlineStr">
@@ -68311,21 +68319,21 @@
     </row>
     <row r="2958">
       <c r="A2958" s="1" t="n">
-        <v>9000087</v>
+        <v>9000085</v>
       </c>
       <c r="B2958" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>근육 붙는 중</t>
         </is>
       </c>
       <c r="C2958" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>Gains incoming</t>
         </is>
       </c>
       <c r="D2958" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2958" s="1" t="n"/>
@@ -68333,21 +68341,21 @@
     </row>
     <row r="2959">
       <c r="A2959" s="1" t="n">
-        <v>9000088</v>
+        <v>9000086</v>
       </c>
       <c r="B2959" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>찍찍찍찍</t>
         </is>
       </c>
       <c r="C2959" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>Squeak squeak squeak squeak</t>
         </is>
       </c>
       <c r="D2959" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E2959" s="1" t="n"/>
@@ -68355,16 +68363,16 @@
     </row>
     <row r="2960">
       <c r="A2960" s="1" t="n">
-        <v>9000089</v>
+        <v>9000087</v>
       </c>
       <c r="B2960" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>으아아아~!</t>
         </is>
       </c>
       <c r="C2960" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>Waaaaah~!</t>
         </is>
       </c>
       <c r="D2960" s="1" t="inlineStr">
@@ -68377,16 +68385,16 @@
     </row>
     <row r="2961">
       <c r="A2961" s="1" t="n">
-        <v>9000090</v>
+        <v>9000088</v>
       </c>
       <c r="B2961" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>하암~ 잘 잤다</t>
         </is>
       </c>
       <c r="C2961" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>Yawn~ what a nap</t>
         </is>
       </c>
       <c r="D2961" s="1" t="inlineStr">
@@ -68399,21 +68407,21 @@
     </row>
     <row r="2962">
       <c r="A2962" s="1" t="n">
-        <v>9000091</v>
+        <v>9000089</v>
       </c>
       <c r="B2962" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>냠, 배부르다</t>
         </is>
       </c>
       <c r="C2962" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Nom, so full</t>
         </is>
       </c>
       <c r="D2962" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2962" s="1" t="n"/>
@@ -68421,21 +68429,21 @@
     </row>
     <row r="2963">
       <c r="A2963" s="1" t="n">
-        <v>9000092</v>
+        <v>9000090</v>
       </c>
       <c r="B2963" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>휴…</t>
         </is>
       </c>
       <c r="C2963" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Phew...</t>
         </is>
       </c>
       <c r="D2963" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E2963" s="1" t="n"/>
@@ -68443,21 +68451,21 @@
     </row>
     <row r="2964">
       <c r="A2964" s="1" t="n">
-        <v>9000093</v>
+        <v>9000091</v>
       </c>
       <c r="B2964" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>찍</t>
         </is>
       </c>
       <c r="C2964" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Squeak</t>
         </is>
       </c>
       <c r="D2964" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
         </is>
       </c>
       <c r="E2964" s="1" t="n"/>
@@ -68465,21 +68473,21 @@
     </row>
     <row r="2965">
       <c r="A2965" s="1" t="n">
-        <v>9000094</v>
+        <v>9000092</v>
       </c>
       <c r="B2965" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C2965" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D2965" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/RunPage.cs:99</t>
         </is>
       </c>
       <c r="E2965" s="1" t="n"/>
@@ -68487,21 +68495,21 @@
     </row>
     <row r="2966">
       <c r="A2966" s="1" t="n">
-        <v>9000095</v>
+        <v>9000093</v>
       </c>
       <c r="B2966" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="C2966" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D2966" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
         </is>
       </c>
       <c r="E2966" s="1" t="n"/>
@@ -68509,21 +68517,21 @@
     </row>
     <row r="2967">
       <c r="A2967" s="1" t="n">
-        <v>9000096</v>
+        <v>9000094</v>
       </c>
       <c r="B2967" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>찌릿!!</t>
         </is>
       </c>
       <c r="C2967" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>ZAP!!</t>
         </is>
       </c>
       <c r="D2967" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2967" s="1" t="n"/>
@@ -68531,21 +68539,21 @@
     </row>
     <row r="2968">
       <c r="A2968" s="1" t="n">
-        <v>9000097</v>
+        <v>9000095</v>
       </c>
       <c r="B2968" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>콰릉!</t>
         </is>
       </c>
       <c r="C2968" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>Ka-boom!</t>
         </is>
       </c>
       <c r="D2968" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E2968" s="1" t="n"/>
@@ -68553,21 +68561,21 @@
     </row>
     <row r="2969">
       <c r="A2969" s="1" t="n">
-        <v>9000098</v>
+        <v>9000096</v>
       </c>
       <c r="B2969" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>냠!</t>
         </is>
       </c>
       <c r="C2969" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>Nom!</t>
         </is>
       </c>
       <c r="D2969" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2969" s="1" t="n"/>
@@ -68575,21 +68583,21 @@
     </row>
     <row r="2970">
       <c r="A2970" s="1" t="n">
-        <v>9000099</v>
+        <v>9000097</v>
       </c>
       <c r="B2970" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>다닥!</t>
         </is>
       </c>
       <c r="C2970" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>Scurry!</t>
         </is>
       </c>
       <c r="D2970" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E2970" s="1" t="n"/>
@@ -68597,16 +68605,16 @@
     </row>
     <row r="2971">
       <c r="A2971" s="1" t="n">
-        <v>9000100</v>
+        <v>9000098</v>
       </c>
       <c r="B2971" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>메리 쥐스마스!</t>
         </is>
       </c>
       <c r="C2971" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>Merry Ratmas!</t>
         </is>
       </c>
       <c r="D2971" s="1" t="inlineStr">
@@ -68619,21 +68627,21 @@
     </row>
     <row r="2972">
       <c r="A2972" s="1" t="n">
-        <v>9000101</v>
+        <v>9000099</v>
       </c>
       <c r="B2972" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>흐에~ 후원 감사합니다~!</t>
         </is>
       </c>
       <c r="C2972" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>Heheh~ thanks for the dono~!</t>
         </is>
       </c>
       <c r="D2972" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2972" s="1" t="n"/>
@@ -68641,21 +68649,21 @@
     </row>
     <row r="2973">
       <c r="A2973" s="1" t="n">
-        <v>9000102</v>
+        <v>9000100</v>
       </c>
       <c r="B2973" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>배달 왔습니다~</t>
         </is>
       </c>
       <c r="C2973" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>Delivery~!</t>
         </is>
       </c>
       <c r="D2973" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E2973" s="1" t="n"/>
@@ -68663,16 +68671,16 @@
     </row>
     <row r="2974">
       <c r="A2974" s="1" t="n">
-        <v>9000103</v>
+        <v>9000101</v>
       </c>
       <c r="B2974" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>백덤블링!</t>
         </is>
       </c>
       <c r="C2974" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Backflip!</t>
         </is>
       </c>
       <c r="D2974" s="1" t="inlineStr">
@@ -68685,21 +68693,21 @@
     </row>
     <row r="2975">
       <c r="A2975" s="1" t="n">
-        <v>9000104</v>
+        <v>9000102</v>
       </c>
       <c r="B2975" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>공중제비!</t>
         </is>
       </c>
       <c r="C2975" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Somersault!</t>
         </is>
       </c>
       <c r="D2975" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2975" s="1" t="n"/>
@@ -68707,21 +68715,21 @@
     </row>
     <row r="2976">
       <c r="A2976" s="1" t="n">
-        <v>9000105</v>
+        <v>9000103</v>
       </c>
       <c r="B2976" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>찍-공중회전!</t>
         </is>
       </c>
       <c r="C2976" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>Squeak-flip!</t>
         </is>
       </c>
       <c r="D2976" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E2976" s="1" t="n"/>
@@ -68729,16 +68737,16 @@
     </row>
     <row r="2977">
       <c r="A2977" s="1" t="n">
-        <v>9000106</v>
+        <v>9000104</v>
       </c>
       <c r="B2977" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>트리플 악셀!!</t>
         </is>
       </c>
       <c r="C2977" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>TRIPLE AXEL!!</t>
         </is>
       </c>
       <c r="D2977" s="1" t="inlineStr">
@@ -68751,21 +68759,21 @@
     </row>
     <row r="2978">
       <c r="A2978" s="1" t="n">
-        <v>9000107</v>
+        <v>9000105</v>
       </c>
       <c r="B2978" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>3회전 성공!</t>
         </is>
       </c>
       <c r="C2978" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>Triple spin landed!</t>
         </is>
       </c>
       <c r="D2978" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2978" s="1" t="n"/>
@@ -68773,21 +68781,21 @@
     </row>
     <row r="2979">
       <c r="A2979" s="1" t="n">
-        <v>9000108</v>
+        <v>9000106</v>
       </c>
       <c r="B2979" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>심사위원 전원 10점!</t>
         </is>
       </c>
       <c r="C2979" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>Perfect 10s from every judge!</t>
         </is>
       </c>
       <c r="D2979" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E2979" s="1" t="n"/>
@@ -68795,16 +68803,16 @@
     </row>
     <row r="2980">
       <c r="A2980" s="1" t="n">
-        <v>9000109</v>
+        <v>9000107</v>
       </c>
       <c r="B2980" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>윈드밀!!</t>
         </is>
       </c>
       <c r="C2980" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>WINDMILL!!</t>
         </is>
       </c>
       <c r="D2980" s="1" t="inlineStr">
@@ -68817,21 +68825,21 @@
     </row>
     <row r="2981">
       <c r="A2981" s="1" t="n">
-        <v>9000110</v>
+        <v>9000108</v>
       </c>
       <c r="B2981" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>브레이크 댄스!</t>
         </is>
       </c>
       <c r="C2981" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>Breakdance!</t>
         </is>
       </c>
       <c r="D2981" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2981" s="1" t="n"/>
@@ -68839,21 +68847,21 @@
     </row>
     <row r="2982">
       <c r="A2982" s="1" t="n">
-        <v>9000111</v>
+        <v>9000109</v>
       </c>
       <c r="B2982" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>빙글빙글 파괴!</t>
         </is>
       </c>
       <c r="C2982" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>Spin-to-win destruction!</t>
         </is>
       </c>
       <c r="D2982" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E2982" s="1" t="n"/>
@@ -68861,16 +68869,16 @@
     </row>
     <row r="2983">
       <c r="A2983" s="1" t="n">
-        <v>9000112</v>
+        <v>9000110</v>
       </c>
       <c r="B2983" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>쥐 대포알!</t>
         </is>
       </c>
       <c r="C2983" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>Rat Cannonball!</t>
         </is>
       </c>
       <c r="D2983" s="1" t="inlineStr">
@@ -68883,21 +68891,21 @@
     </row>
     <row r="2984">
       <c r="A2984" s="1" t="n">
-        <v>9000113</v>
+        <v>9000111</v>
       </c>
       <c r="B2984" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>데굴데굴!</t>
         </is>
       </c>
       <c r="C2984" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>Roll roll!</t>
         </is>
       </c>
       <c r="D2984" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2984" s="1" t="n"/>
@@ -68905,21 +68913,21 @@
     </row>
     <row r="2985">
       <c r="A2985" s="1" t="n">
-        <v>9000114</v>
+        <v>9000112</v>
       </c>
       <c r="B2985" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>핀볼 모드!</t>
         </is>
       </c>
       <c r="C2985" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>Pinball mode!</t>
         </is>
       </c>
       <c r="D2985" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E2985" s="1" t="n"/>
@@ -68927,16 +68935,16 @@
     </row>
     <row r="2986">
       <c r="A2986" s="1" t="n">
-        <v>9000115</v>
+        <v>9000113</v>
       </c>
       <c r="B2986" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>쳇바퀴 돌기!!</t>
         </is>
       </c>
       <c r="C2986" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>WHEEL SPIN!!</t>
         </is>
       </c>
       <c r="D2986" s="1" t="inlineStr">
@@ -68949,21 +68957,21 @@
     </row>
     <row r="2987">
       <c r="A2987" s="1" t="n">
-        <v>9000116</v>
+        <v>9000114</v>
       </c>
       <c r="B2987" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>빙글빙글~</t>
         </is>
       </c>
       <c r="C2987" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>Round and round~</t>
         </is>
       </c>
       <c r="D2987" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2987" s="1" t="n"/>
@@ -68971,21 +68979,21 @@
     </row>
     <row r="2988">
       <c r="A2988" s="1" t="n">
-        <v>9000117</v>
+        <v>9000115</v>
       </c>
       <c r="B2988" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>어지러워!!</t>
         </is>
       </c>
       <c r="C2988" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>So DIZZY!!</t>
         </is>
       </c>
       <c r="D2988" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E2988" s="1" t="n"/>
@@ -68993,21 +69001,21 @@
     </row>
     <row r="2989">
       <c r="A2989" s="1" t="n">
-        <v>9000118</v>
+        <v>9000116</v>
       </c>
       <c r="B2989" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="C2989" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="D2989" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
         </is>
       </c>
       <c r="E2989" s="1" t="n"/>
@@ -69015,21 +69023,21 @@
     </row>
     <row r="2990">
       <c r="A2990" s="1" t="n">
-        <v>9000119</v>
+        <v>9000117</v>
       </c>
       <c r="B2990" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>기절!!</t>
         </is>
       </c>
       <c r="C2990" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>Stunned!!</t>
         </is>
       </c>
       <c r="D2990" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Rats/RatManager.cs:38</t>
         </is>
       </c>
       <c r="E2990" s="1" t="n"/>
@@ -69037,21 +69045,21 @@
     </row>
     <row r="2991">
       <c r="A2991" s="1" t="n">
-        <v>9000120</v>
+        <v>9000118</v>
       </c>
       <c r="B2991" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>소품이 떨어졌다!</t>
         </is>
       </c>
       <c r="C2991" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>A prop dropped!</t>
         </is>
       </c>
       <c r="D2991" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Rats/RatManager.cs:397</t>
         </is>
       </c>
       <c r="E2991" s="1" t="n"/>
@@ -69059,21 +69067,21 @@
     </row>
     <row r="2992">
       <c r="A2992" s="1" t="n">
-        <v>9000121</v>
+        <v>9000119</v>
       </c>
       <c r="B2992" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>조각 +1</t>
         </is>
       </c>
       <c r="C2992" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>Shard +1</t>
         </is>
       </c>
       <c r="D2992" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Rats/RatManager.cs:460</t>
         </is>
       </c>
       <c r="E2992" s="1" t="n"/>
@@ -69081,21 +69089,21 @@
     </row>
     <row r="2993">
       <c r="A2993" s="1" t="n">
-        <v>9000122</v>
+        <v>9000120</v>
       </c>
       <c r="B2993" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>{name} 강화! Lv {lv}</t>
         </is>
       </c>
       <c r="C2993" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>{name} powered up! Lv {lv}</t>
         </is>
       </c>
       <c r="D2993" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Rats/RatManager.cs:461</t>
         </is>
       </c>
       <c r="E2993" s="1" t="n"/>
@@ -69103,21 +69111,21 @@
     </row>
     <row r="2994">
       <c r="A2994" s="1" t="n">
-        <v>9000123</v>
+        <v>9000121</v>
       </c>
       <c r="B2994" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>{grade} 탄생!</t>
         </is>
       </c>
       <c r="C2994" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>{grade} born!</t>
         </is>
       </c>
       <c r="D2994" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Rats/RatManager.cs:561</t>
         </is>
       </c>
       <c r="E2994" s="1" t="n"/>
@@ -69125,21 +69133,21 @@
     </row>
     <row r="2995">
       <c r="A2995" s="1" t="n">
-        <v>9000124</v>
+        <v>9000122</v>
       </c>
       <c r="B2995" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>쌍둥이!</t>
         </is>
       </c>
       <c r="C2995" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>Twins!</t>
         </is>
       </c>
       <c r="D2995" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:566</t>
         </is>
       </c>
       <c r="E2995" s="1" t="n"/>
@@ -69147,21 +69155,21 @@
     </row>
     <row r="2996">
       <c r="A2996" s="1" t="n">
-        <v>9000125</v>
+        <v>9000123</v>
       </c>
       <c r="B2996" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>치즈 운석!</t>
         </is>
       </c>
       <c r="C2996" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>Cheese Meteor!</t>
         </is>
       </c>
       <c r="D2996" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:627</t>
         </is>
       </c>
       <c r="E2996" s="1" t="n"/>
@@ -69169,21 +69177,21 @@
     </row>
     <row r="2997">
       <c r="A2997" s="1" t="n">
-        <v>9000126</v>
+        <v>9000124</v>
       </c>
       <c r="B2997" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>{floor}층 · {zone}</t>
         </is>
       </c>
       <c r="C2997" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>Floor {floor} · {zone}</t>
         </is>
       </c>
       <c r="D2997" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E2997" s="1" t="n"/>
@@ -69191,21 +69199,21 @@
     </row>
     <row r="2998">
       <c r="A2998" s="1" t="n">
-        <v>9000127</v>
+        <v>9000125</v>
       </c>
       <c r="B2998" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>계단 방 벽을 부숴라!</t>
         </is>
       </c>
       <c r="C2998" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>Smash the wall to the stairs room!</t>
         </is>
       </c>
       <c r="D2998" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E2998" s="1" t="n"/>
@@ -69213,21 +69221,21 @@
     </row>
     <row r="2999">
       <c r="A2999" s="1" t="n">
-        <v>9000128</v>
+        <v>9000126</v>
       </c>
       <c r="B2999" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>벽 붕괴! 방 확장</t>
         </is>
       </c>
       <c r="C2999" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>Wall down! Room expanded</t>
         </is>
       </c>
       <c r="D2999" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2999" s="1" t="n"/>
@@ -69235,21 +69243,21 @@
     </row>
     <row r="3000">
       <c r="A3000" s="1" t="n">
-        <v>9000129</v>
+        <v>9000127</v>
       </c>
       <c r="B3000" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>계단 발견!</t>
         </is>
       </c>
       <c r="C3000" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>Stairs found!</t>
         </is>
       </c>
       <c r="D3000" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:338</t>
         </is>
       </c>
       <c r="E3000" s="1" t="n"/>
@@ -69257,21 +69265,21 @@
     </row>
     <row r="3001">
       <c r="A3001" s="1" t="n">
-        <v>9000130</v>
+        <v>9000128</v>
       </c>
       <c r="B3001" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>계단에 닿으면 {next}층으로</t>
         </is>
       </c>
       <c r="C3001" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Touch the stairs to go to Floor {next}</t>
         </is>
       </c>
       <c r="D3001" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:338</t>
         </is>
       </c>
       <c r="E3001" s="1" t="n"/>
@@ -69279,16 +69287,16 @@
     </row>
     <row r="3002">
       <c r="A3002" s="1" t="n">
-        <v>9000131</v>
+        <v>9000129</v>
       </c>
       <c r="B3002" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>와르르!!</t>
         </is>
       </c>
       <c r="C3002" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>Crumble!!</t>
         </is>
       </c>
       <c r="D3002" s="1" t="inlineStr">
@@ -69298,6 +69306,50 @@
       </c>
       <c r="E3002" s="1" t="n"/>
       <c r="F3002" s="1" t="n"/>
+    </row>
+    <row r="3003">
+      <c r="A3003" s="1" t="n">
+        <v>9000130</v>
+      </c>
+      <c r="B3003" s="2" t="inlineStr">
+        <is>
+          <t>콰광!!</t>
+        </is>
+      </c>
+      <c r="C3003" s="2" t="inlineStr">
+        <is>
+          <t>KA-BOOM!!</t>
+        </is>
+      </c>
+      <c r="D3003" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3003" s="1" t="n"/>
+      <c r="F3003" s="1" t="n"/>
+    </row>
+    <row r="3004">
+      <c r="A3004" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B3004" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C3004" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D3004" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3004" s="1" t="n"/>
+      <c r="F3004" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -23127,7 +23127,7 @@
       </c>
       <c r="D1028" s="1" t="inlineStr">
         <is>
-          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92132, 92432, 92632, 92634</t>
+          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92232, 92234, 92434</t>
         </is>
       </c>
       <c r="E1028" s="1" t="n"/>
@@ -23592,7 +23592,11 @@
           <t>공용 스킬 테이블 · Common_Skill · skill_name · 92232, 92234, 92434</t>
         </is>
       </c>
-      <c r="E1049" s="1" t="n"/>
+      <c r="E1049" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F1049" s="1" t="n"/>
     </row>
     <row r="1050">
@@ -24161,7 +24165,7 @@
       </c>
       <c r="D1075" s="1" t="inlineStr">
         <is>
-          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92332, 92532, 92832, 92834</t>
+          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92432, 92632, 92634, 92832, 92834, 92932 외 10</t>
         </is>
       </c>
       <c r="E1075" s="1" t="n"/>
@@ -26183,7 +26187,7 @@
       </c>
       <c r="D1166" s="1" t="inlineStr">
         <is>
-          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92732</t>
+          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92332, 93432, 93632, 93634</t>
         </is>
       </c>
       <c r="E1166" s="1" t="n"/>
@@ -27257,7 +27261,7 @@
       </c>
       <c r="D1211" s="1" t="inlineStr">
         <is>
-          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92934</t>
+          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92732, 93532</t>
         </is>
       </c>
       <c r="E1211" s="1" t="inlineStr">
@@ -29749,7 +29753,7 @@
       </c>
       <c r="D1307" s="1" t="inlineStr">
         <is>
-          <t>공용 스킬 테이블 · Common_Skill · skill_name · 93032, 93034, 93132, 93134, 93232, 93234 외 8</t>
+          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92532, 93534</t>
         </is>
       </c>
       <c r="E1307" s="1" t="inlineStr">
@@ -31153,7 +31157,7 @@
       </c>
       <c r="D1361" s="1" t="inlineStr">
         <is>
-          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92932</t>
+          <t>공용 스킬 테이블 · Common_Skill · skill_name · 92132</t>
         </is>
       </c>
       <c r="E1361" s="1" t="inlineStr">

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -48995,12 +48995,12 @@
       </c>
       <c r="B2095" s="2" t="inlineStr">
         <is>
-          <t>지난번엔 아깝게 잡혀 버렸지... 이번엔 '적정 찍찍'을 알려 줄게!</t>
+          <t>지난번엔 아깝게 잡혀 버렸지... 이번엔 우리 힘을 보는 법을 알려 줄게!</t>
         </is>
       </c>
       <c r="C2095" s="2" t="inlineStr">
         <is>
-          <t>We got caught last time, so close... This time I'll teach you about 'Rec. SQUEAK!!'</t>
+          <t>We got caught last time... This time I'll show you how to read our strength!</t>
         </is>
       </c>
       <c r="D2095" s="1" t="inlineStr">
@@ -49017,12 +49017,12 @@
       </c>
       <c r="B2096" s="2" t="inlineStr">
         <is>
-          <t>왼쪽 위 '찍찍!!' 숫자는 지금 우리 무리의 힘이고, 옆의 '적정'은 이 층을 넉넉히 깨려면 필요한 힘이야.</t>
+          <t>왼쪽 위 '찍찍!!' 숫자가 지금 우리 무리의 힘이야. 쥐가 많아지고 세질수록 쑥쑥 올라가!</t>
         </is>
       </c>
       <c r="C2096" s="2" t="inlineStr">
         <is>
-          <t>The 'SQUEAK!!' number at the top left is our swarm's power right now, and 'Rec.' next to it is the power you need to clear this floor comfortably.</t>
+          <t>The 'SQUEAK!!' number at the top left is our crew's power. It shoots up as we get more and stronger rats!</t>
         </is>
       </c>
       <c r="D2096" s="1" t="inlineStr">
@@ -49039,12 +49039,12 @@
       </c>
       <c r="B2097" s="2" t="inlineStr">
         <is>
-          <t>우리 힘이 적정보다 낮으면 시간 안에 계단까지 가기 힘들어!</t>
+          <t>위층일수록 벽도 단단해져. 막히면 찍찍!!을 더 키워서 다시 도전하자!</t>
         </is>
       </c>
       <c r="C2097" s="2" t="inlineStr">
         <is>
-          <t>If our power is below Rec., it's tough to reach the stairs in time!</t>
+          <t>Walls get tougher the higher we go. If we get stuck, let's grow our SQUEAK!! and try again!</t>
         </is>
       </c>
       <c r="D2097" s="1" t="inlineStr">
@@ -49127,12 +49127,12 @@
       </c>
       <c r="B2101" s="2" t="inlineStr">
         <is>
-          <t>적정 찍찍이 모자랄 땐 쥐를 최대 마릿수까지 꽉 채워 봐!</t>
+          <t>더 강해지고 싶을 땐 쥐를 최대 마릿수까지 꽉 채워 봐!</t>
         </is>
       </c>
       <c r="C2101" s="2" t="inlineStr">
         <is>
-          <t>When SQUEAK!! is below Rec., try filling up to the max rat count!</t>
+          <t>Want to get stronger? Fill the crew all the way up to the max rat count!</t>
         </is>
       </c>
       <c r="D2101" s="1" t="inlineStr">
@@ -63437,12 +63437,12 @@
       </c>
       <c r="B2737" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! 0 / 적정 0</t>
+          <t>찍찍!! 0</t>
         </is>
       </c>
       <c r="C2737" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! 0 / Rec. 0</t>
+          <t>SQUEAK!! 0</t>
         </is>
       </c>
       <c r="D2737" s="1" t="inlineStr">
@@ -67487,12 +67487,12 @@
       </c>
       <c r="B2914" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power} / 적정 {need}</t>
+          <t>찍찍!! {power}</t>
         </is>
       </c>
       <c r="C2914" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power} / Rec. {need}</t>
+          <t>SQUEAK!! {power}</t>
         </is>
       </c>
       <c r="D2914" s="1" t="inlineStr">

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3044"/>
+  <dimension ref="A1:F3050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -66338,7 +66338,11 @@
           <t>씬 · Lobby · UI/Prep/Body/Page_aug/Card/StorageView/Upgrade/Label</t>
         </is>
       </c>
-      <c r="E2862" s="1" t="n"/>
+      <c r="E2862" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F2862" s="1" t="n"/>
     </row>
     <row r="2863">
@@ -66536,7 +66540,11 @@
           <t>씬 · Lobby · UI/Prep/Body/Page_aug/Card/StorageView/Detail/Card/Points | Game · HUD/Augment/Pick/Card2/Points | Game · HUD/Augment/Pick/Card3/Points | Game · HUD/Augment/Manage/Card/Detail/Points 외 1곳</t>
         </is>
       </c>
-      <c r="E2871" s="1" t="n"/>
+      <c r="E2871" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F2871" s="1" t="n"/>
     </row>
     <row r="2872">
@@ -67483,21 +67491,21 @@
     </row>
     <row r="2914">
       <c r="A2914" s="1" t="n">
-        <v>9000001</v>
+        <v>8000532</v>
       </c>
       <c r="B2914" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power}</t>
+          <t>강화 (같은 증강 {have}/{need} · 치즈 {cheese})</t>
         </is>
       </c>
       <c r="C2914" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power}</t>
+          <t>Upgrade (Duplicates {have}/{need} · Cheese {cheese})</t>
         </is>
       </c>
       <c r="D2914" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_aug/Card/StorageView/Upgrade/Label</t>
         </is>
       </c>
       <c r="E2914" s="1" t="n"/>
@@ -67505,21 +67513,21 @@
     </row>
     <row r="2915">
       <c r="A2915" s="1" t="n">
-        <v>9000002</v>
+        <v>8000533</v>
       </c>
       <c r="B2915" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>같은 증강 {pts}개 보유</t>
         </is>
       </c>
       <c r="C2915" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>{pts} duplicate(s) owned</t>
         </is>
       </c>
       <c r="D2915" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
+          <t>씬 · Lobby · UI/Prep/Body/Page_aug/Card/StorageView/Detail/Card/Points | Game · HUD/Augment/Pick/Card2/Points | Game · HUD/Augment/Pick/Card3/Points | Game · HUD/Augment/Manage/Card/Detail/Points 외 1곳</t>
         </is>
       </c>
       <c r="E2915" s="1" t="n"/>
@@ -67527,21 +67535,21 @@
     </row>
     <row r="2916">
       <c r="A2916" s="1" t="n">
-        <v>9000003</v>
+        <v>8000534</v>
       </c>
       <c r="B2916" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>같은 증강 장착 중</t>
         </is>
       </c>
       <c r="C2916" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>Same Augment equipped</t>
         </is>
       </c>
       <c r="D2916" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
+          <t>씬 · Game · AugmentManager · AugmentManager.sameLabel</t>
         </is>
       </c>
       <c r="E2916" s="1" t="n"/>
@@ -67549,21 +67557,21 @@
     </row>
     <row r="2917">
       <c r="A2917" s="1" t="n">
-        <v>9000004</v>
+        <v>8000535</v>
       </c>
       <c r="B2917" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>필살기 카메라 고정 켬</t>
         </is>
       </c>
       <c r="C2917" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>Ultimate camera lock ON</t>
         </is>
       </c>
       <c r="D2917" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
+          <t>씬 · Game · UltimateManager · UltimateManager.camLockOn</t>
         </is>
       </c>
       <c r="E2917" s="1" t="n"/>
@@ -67571,21 +67579,21 @@
     </row>
     <row r="2918">
       <c r="A2918" s="1" t="n">
-        <v>9000005</v>
+        <v>8000536</v>
       </c>
       <c r="B2918" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>필살기 카메라 고정 끔</t>
         </is>
       </c>
       <c r="C2918" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>Ultimate camera lock OFF</t>
         </is>
       </c>
       <c r="D2918" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
+          <t>씬 · Game · UltimateManager · UltimateManager.camLockOff</t>
         </is>
       </c>
       <c r="E2918" s="1" t="n"/>
@@ -67593,21 +67601,21 @@
     </row>
     <row r="2919">
       <c r="A2919" s="1" t="n">
-        <v>9000006</v>
+        <v>8000537</v>
       </c>
       <c r="B2919" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>{n}초 뒤에 가장 좋은 증강을 자동으로 골라요</t>
         </is>
       </c>
       <c r="C2919" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>Auto-picking the best Augment in {n}s</t>
         </is>
       </c>
       <c r="D2919" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
+          <t>씬 · Game · HUD/Augment/Pick/Timer</t>
         </is>
       </c>
       <c r="E2919" s="1" t="n"/>
@@ -67615,21 +67623,21 @@
     </row>
     <row r="2920">
       <c r="A2920" s="1" t="n">
-        <v>9000007</v>
+        <v>9000001</v>
       </c>
       <c r="B2920" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>찍찍!! {power}</t>
         </is>
       </c>
       <c r="C2920" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>SQUEAK!! {power}</t>
         </is>
       </c>
       <c r="D2920" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E2920" s="1" t="n"/>
@@ -67637,21 +67645,21 @@
     </row>
     <row r="2921">
       <c r="A2921" s="1" t="n">
-        <v>9000008</v>
+        <v>9000002</v>
       </c>
       <c r="B2921" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C2921" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D2921" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2921" s="1" t="n"/>
@@ -67659,21 +67667,21 @@
     </row>
     <row r="2922">
       <c r="A2922" s="1" t="n">
-        <v>9000009</v>
+        <v>9000003</v>
       </c>
       <c r="B2922" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C2922" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D2922" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E2922" s="1" t="n"/>
@@ -67681,21 +67689,21 @@
     </row>
     <row r="2923">
       <c r="A2923" s="1" t="n">
-        <v>9000010</v>
+        <v>9000004</v>
       </c>
       <c r="B2923" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C2923" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D2923" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E2923" s="1" t="n"/>
@@ -67703,21 +67711,21 @@
     </row>
     <row r="2924">
       <c r="A2924" s="1" t="n">
-        <v>9000011</v>
+        <v>9000005</v>
       </c>
       <c r="B2924" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C2924" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D2924" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E2924" s="1" t="n"/>
@@ -67725,21 +67733,21 @@
     </row>
     <row r="2925">
       <c r="A2925" s="1" t="n">
-        <v>9000012</v>
+        <v>9000006</v>
       </c>
       <c r="B2925" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C2925" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D2925" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E2925" s="1" t="n"/>
@@ -67747,21 +67755,21 @@
     </row>
     <row r="2926">
       <c r="A2926" s="1" t="n">
-        <v>9000013</v>
+        <v>9000007</v>
       </c>
       <c r="B2926" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C2926" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D2926" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E2926" s="1" t="n"/>
@@ -67769,21 +67777,21 @@
     </row>
     <row r="2927">
       <c r="A2927" s="1" t="n">
-        <v>9000014</v>
+        <v>9000008</v>
       </c>
       <c r="B2927" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C2927" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D2927" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2927" s="1" t="n"/>
@@ -67791,21 +67799,21 @@
     </row>
     <row r="2928">
       <c r="A2928" s="1" t="n">
-        <v>9000015</v>
+        <v>9000009</v>
       </c>
       <c r="B2928" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C2928" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D2928" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2928" s="1" t="n"/>
@@ -67813,21 +67821,21 @@
     </row>
     <row r="2929">
       <c r="A2929" s="1" t="n">
-        <v>9000016</v>
+        <v>9000010</v>
       </c>
       <c r="B2929" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C2929" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D2929" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2929" s="1" t="n"/>
@@ -67835,21 +67843,21 @@
     </row>
     <row r="2930">
       <c r="A2930" s="1" t="n">
-        <v>9000017</v>
+        <v>9000011</v>
       </c>
       <c r="B2930" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C2930" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D2930" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2930" s="1" t="n"/>
@@ -67857,21 +67865,21 @@
     </row>
     <row r="2931">
       <c r="A2931" s="1" t="n">
-        <v>9000018</v>
+        <v>9000012</v>
       </c>
       <c r="B2931" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C2931" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D2931" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2931" s="1" t="n"/>
@@ -67879,21 +67887,21 @@
     </row>
     <row r="2932">
       <c r="A2932" s="1" t="n">
-        <v>9000019</v>
+        <v>9000013</v>
       </c>
       <c r="B2932" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C2932" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D2932" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2932" s="1" t="n"/>
@@ -67901,21 +67909,21 @@
     </row>
     <row r="2933">
       <c r="A2933" s="1" t="n">
-        <v>9000020</v>
+        <v>9000014</v>
       </c>
       <c r="B2933" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C2933" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D2933" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E2933" s="1" t="n"/>
@@ -67923,21 +67931,21 @@
     </row>
     <row r="2934">
       <c r="A2934" s="1" t="n">
-        <v>9000021</v>
+        <v>9000015</v>
       </c>
       <c r="B2934" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C2934" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D2934" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2934" s="1" t="n"/>
@@ -67945,21 +67953,21 @@
     </row>
     <row r="2935">
       <c r="A2935" s="1" t="n">
-        <v>9000022</v>
+        <v>9000016</v>
       </c>
       <c r="B2935" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C2935" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D2935" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2935" s="1" t="n"/>
@@ -67967,21 +67975,21 @@
     </row>
     <row r="2936">
       <c r="A2936" s="1" t="n">
-        <v>9000023</v>
+        <v>9000017</v>
       </c>
       <c r="B2936" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C2936" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D2936" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E2936" s="1" t="n"/>
@@ -67989,21 +67997,21 @@
     </row>
     <row r="2937">
       <c r="A2937" s="1" t="n">
-        <v>9000024</v>
+        <v>9000018</v>
       </c>
       <c r="B2937" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C2937" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D2937" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2937" s="1" t="n"/>
@@ -68011,21 +68019,21 @@
     </row>
     <row r="2938">
       <c r="A2938" s="1" t="n">
-        <v>9000025</v>
+        <v>9000019</v>
       </c>
       <c r="B2938" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C2938" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D2938" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2938" s="1" t="n"/>
@@ -68033,21 +68041,21 @@
     </row>
     <row r="2939">
       <c r="A2939" s="1" t="n">
-        <v>9000026</v>
+        <v>9000020</v>
       </c>
       <c r="B2939" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C2939" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D2939" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2939" s="1" t="n"/>
@@ -68055,21 +68063,21 @@
     </row>
     <row r="2940">
       <c r="A2940" s="1" t="n">
-        <v>9000027</v>
+        <v>9000021</v>
       </c>
       <c r="B2940" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C2940" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D2940" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E2940" s="1" t="n"/>
@@ -68077,21 +68085,21 @@
     </row>
     <row r="2941">
       <c r="A2941" s="1" t="n">
-        <v>9000028</v>
+        <v>9000022</v>
       </c>
       <c r="B2941" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C2941" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D2941" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2941" s="1" t="n"/>
@@ -68099,21 +68107,21 @@
     </row>
     <row r="2942">
       <c r="A2942" s="1" t="n">
-        <v>9000029</v>
+        <v>9000023</v>
       </c>
       <c r="B2942" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C2942" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D2942" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2942" s="1" t="n"/>
@@ -68121,21 +68129,21 @@
     </row>
     <row r="2943">
       <c r="A2943" s="1" t="n">
-        <v>9000030</v>
+        <v>9000024</v>
       </c>
       <c r="B2943" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C2943" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D2943" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2943" s="1" t="n"/>
@@ -68143,21 +68151,21 @@
     </row>
     <row r="2944">
       <c r="A2944" s="1" t="n">
-        <v>9000031</v>
+        <v>9000025</v>
       </c>
       <c r="B2944" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C2944" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D2944" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2944" s="1" t="n"/>
@@ -68165,21 +68173,21 @@
     </row>
     <row r="2945">
       <c r="A2945" s="1" t="n">
-        <v>9000032</v>
+        <v>9000026</v>
       </c>
       <c r="B2945" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C2945" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D2945" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E2945" s="1" t="n"/>
@@ -68187,21 +68195,21 @@
     </row>
     <row r="2946">
       <c r="A2946" s="1" t="n">
-        <v>9000033</v>
+        <v>9000027</v>
       </c>
       <c r="B2946" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C2946" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D2946" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2946" s="1" t="n"/>
@@ -68209,21 +68217,21 @@
     </row>
     <row r="2947">
       <c r="A2947" s="1" t="n">
-        <v>9000034</v>
+        <v>9000028</v>
       </c>
       <c r="B2947" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C2947" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D2947" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2947" s="1" t="n"/>
@@ -68231,21 +68239,21 @@
     </row>
     <row r="2948">
       <c r="A2948" s="1" t="n">
-        <v>9000035</v>
+        <v>9000029</v>
       </c>
       <c r="B2948" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C2948" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D2948" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2948" s="1" t="n"/>
@@ -68253,21 +68261,21 @@
     </row>
     <row r="2949">
       <c r="A2949" s="1" t="n">
-        <v>9000036</v>
+        <v>9000030</v>
       </c>
       <c r="B2949" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C2949" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D2949" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E2949" s="1" t="n"/>
@@ -68275,21 +68283,21 @@
     </row>
     <row r="2950">
       <c r="A2950" s="1" t="n">
-        <v>9000037</v>
+        <v>9000031</v>
       </c>
       <c r="B2950" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C2950" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D2950" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E2950" s="1" t="n"/>
@@ -68297,21 +68305,21 @@
     </row>
     <row r="2951">
       <c r="A2951" s="1" t="n">
-        <v>9000038</v>
+        <v>9000032</v>
       </c>
       <c r="B2951" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C2951" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D2951" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2951" s="1" t="n"/>
@@ -68319,21 +68327,21 @@
     </row>
     <row r="2952">
       <c r="A2952" s="1" t="n">
-        <v>9000039</v>
+        <v>9000033</v>
       </c>
       <c r="B2952" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C2952" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D2952" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2952" s="1" t="n"/>
@@ -68341,21 +68349,21 @@
     </row>
     <row r="2953">
       <c r="A2953" s="1" t="n">
-        <v>9000040</v>
+        <v>9000034</v>
       </c>
       <c r="B2953" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C2953" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D2953" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2953" s="1" t="n"/>
@@ -68363,21 +68371,21 @@
     </row>
     <row r="2954">
       <c r="A2954" s="1" t="n">
-        <v>9000041</v>
+        <v>9000035</v>
       </c>
       <c r="B2954" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C2954" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D2954" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E2954" s="1" t="n"/>
@@ -68385,21 +68393,21 @@
     </row>
     <row r="2955">
       <c r="A2955" s="1" t="n">
-        <v>9000042</v>
+        <v>9000036</v>
       </c>
       <c r="B2955" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C2955" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D2955" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E2955" s="1" t="n"/>
@@ -68407,21 +68415,21 @@
     </row>
     <row r="2956">
       <c r="A2956" s="1" t="n">
-        <v>9000043</v>
+        <v>9000037</v>
       </c>
       <c r="B2956" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C2956" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D2956" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E2956" s="1" t="n"/>
@@ -68429,21 +68437,21 @@
     </row>
     <row r="2957">
       <c r="A2957" s="1" t="n">
-        <v>9000044</v>
+        <v>9000038</v>
       </c>
       <c r="B2957" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C2957" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D2957" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E2957" s="1" t="n"/>
@@ -68451,21 +68459,21 @@
     </row>
     <row r="2958">
       <c r="A2958" s="1" t="n">
-        <v>9000045</v>
+        <v>9000039</v>
       </c>
       <c r="B2958" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C2958" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D2958" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E2958" s="1" t="n"/>
@@ -68473,21 +68481,21 @@
     </row>
     <row r="2959">
       <c r="A2959" s="1" t="n">
-        <v>9000046</v>
+        <v>9000040</v>
       </c>
       <c r="B2959" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C2959" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D2959" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E2959" s="1" t="n"/>
@@ -68495,21 +68503,21 @@
     </row>
     <row r="2960">
       <c r="A2960" s="1" t="n">
-        <v>9000047</v>
+        <v>9000041</v>
       </c>
       <c r="B2960" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C2960" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D2960" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2960" s="1" t="n"/>
@@ -68517,21 +68525,21 @@
     </row>
     <row r="2961">
       <c r="A2961" s="1" t="n">
-        <v>9000048</v>
+        <v>9000042</v>
       </c>
       <c r="B2961" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C2961" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D2961" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2961" s="1" t="n"/>
@@ -68539,21 +68547,21 @@
     </row>
     <row r="2962">
       <c r="A2962" s="1" t="n">
-        <v>9000049</v>
+        <v>9000043</v>
       </c>
       <c r="B2962" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C2962" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D2962" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2962" s="1" t="n"/>
@@ -68561,21 +68569,21 @@
     </row>
     <row r="2963">
       <c r="A2963" s="1" t="n">
-        <v>9000050</v>
+        <v>9000044</v>
       </c>
       <c r="B2963" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C2963" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D2963" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2963" s="1" t="n"/>
@@ -68583,21 +68591,21 @@
     </row>
     <row r="2964">
       <c r="A2964" s="1" t="n">
-        <v>9000051</v>
+        <v>9000045</v>
       </c>
       <c r="B2964" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C2964" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D2964" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2964" s="1" t="n"/>
@@ -68605,21 +68613,21 @@
     </row>
     <row r="2965">
       <c r="A2965" s="1" t="n">
-        <v>9000052</v>
+        <v>9000046</v>
       </c>
       <c r="B2965" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C2965" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D2965" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2965" s="1" t="n"/>
@@ -68627,21 +68635,21 @@
     </row>
     <row r="2966">
       <c r="A2966" s="1" t="n">
-        <v>9000053</v>
+        <v>9000047</v>
       </c>
       <c r="B2966" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C2966" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D2966" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2966" s="1" t="n"/>
@@ -68649,21 +68657,21 @@
     </row>
     <row r="2967">
       <c r="A2967" s="1" t="n">
-        <v>9000054</v>
+        <v>9000048</v>
       </c>
       <c r="B2967" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C2967" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D2967" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2967" s="1" t="n"/>
@@ -68671,21 +68679,21 @@
     </row>
     <row r="2968">
       <c r="A2968" s="1" t="n">
-        <v>9000055</v>
+        <v>9000049</v>
       </c>
       <c r="B2968" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C2968" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D2968" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E2968" s="1" t="n"/>
@@ -68693,21 +68701,21 @@
     </row>
     <row r="2969">
       <c r="A2969" s="1" t="n">
-        <v>9000056</v>
+        <v>9000050</v>
       </c>
       <c r="B2969" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C2969" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D2969" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E2969" s="1" t="n"/>
@@ -68715,21 +68723,21 @@
     </row>
     <row r="2970">
       <c r="A2970" s="1" t="n">
-        <v>9000057</v>
+        <v>9000051</v>
       </c>
       <c r="B2970" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C2970" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D2970" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2970" s="1" t="n"/>
@@ -68737,21 +68745,21 @@
     </row>
     <row r="2971">
       <c r="A2971" s="1" t="n">
-        <v>9000058</v>
+        <v>9000052</v>
       </c>
       <c r="B2971" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C2971" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D2971" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2971" s="1" t="n"/>
@@ -68759,21 +68767,21 @@
     </row>
     <row r="2972">
       <c r="A2972" s="1" t="n">
-        <v>9000059</v>
+        <v>9000053</v>
       </c>
       <c r="B2972" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C2972" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D2972" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E2972" s="1" t="n"/>
@@ -68781,21 +68789,21 @@
     </row>
     <row r="2973">
       <c r="A2973" s="1" t="n">
-        <v>9000060</v>
+        <v>9000054</v>
       </c>
       <c r="B2973" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C2973" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D2973" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2973" s="1" t="n"/>
@@ -68803,21 +68811,21 @@
     </row>
     <row r="2974">
       <c r="A2974" s="1" t="n">
-        <v>9000061</v>
+        <v>9000055</v>
       </c>
       <c r="B2974" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C2974" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D2974" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2974" s="1" t="n"/>
@@ -68825,21 +68833,21 @@
     </row>
     <row r="2975">
       <c r="A2975" s="1" t="n">
-        <v>9000062</v>
+        <v>9000056</v>
       </c>
       <c r="B2975" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C2975" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D2975" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2975" s="1" t="n"/>
@@ -68847,21 +68855,21 @@
     </row>
     <row r="2976">
       <c r="A2976" s="1" t="n">
-        <v>9000063</v>
+        <v>9000057</v>
       </c>
       <c r="B2976" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C2976" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D2976" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2976" s="1" t="n"/>
@@ -68869,21 +68877,21 @@
     </row>
     <row r="2977">
       <c r="A2977" s="1" t="n">
-        <v>9000064</v>
+        <v>9000058</v>
       </c>
       <c r="B2977" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C2977" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D2977" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2977" s="1" t="n"/>
@@ -68891,21 +68899,21 @@
     </row>
     <row r="2978">
       <c r="A2978" s="1" t="n">
-        <v>9000065</v>
+        <v>9000059</v>
       </c>
       <c r="B2978" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C2978" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D2978" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2978" s="1" t="n"/>
@@ -68913,21 +68921,21 @@
     </row>
     <row r="2979">
       <c r="A2979" s="1" t="n">
-        <v>9000066</v>
+        <v>9000060</v>
       </c>
       <c r="B2979" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C2979" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D2979" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2979" s="1" t="n"/>
@@ -68935,21 +68943,21 @@
     </row>
     <row r="2980">
       <c r="A2980" s="1" t="n">
-        <v>9000067</v>
+        <v>9000061</v>
       </c>
       <c r="B2980" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C2980" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D2980" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2980" s="1" t="n"/>
@@ -68957,21 +68965,21 @@
     </row>
     <row r="2981">
       <c r="A2981" s="1" t="n">
-        <v>9000068</v>
+        <v>9000062</v>
       </c>
       <c r="B2981" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C2981" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D2981" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2981" s="1" t="n"/>
@@ -68979,21 +68987,21 @@
     </row>
     <row r="2982">
       <c r="A2982" s="1" t="n">
-        <v>9000069</v>
+        <v>9000063</v>
       </c>
       <c r="B2982" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C2982" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D2982" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2982" s="1" t="n"/>
@@ -69001,21 +69009,21 @@
     </row>
     <row r="2983">
       <c r="A2983" s="1" t="n">
-        <v>9000070</v>
+        <v>9000064</v>
       </c>
       <c r="B2983" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C2983" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D2983" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2983" s="1" t="n"/>
@@ -69023,16 +69031,16 @@
     </row>
     <row r="2984">
       <c r="A2984" s="1" t="n">
-        <v>9000071</v>
+        <v>9000065</v>
       </c>
       <c r="B2984" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C2984" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D2984" s="1" t="inlineStr">
@@ -69045,21 +69053,21 @@
     </row>
     <row r="2985">
       <c r="A2985" s="1" t="n">
-        <v>9000072</v>
+        <v>9000066</v>
       </c>
       <c r="B2985" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C2985" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D2985" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2985" s="1" t="n"/>
@@ -69067,21 +69075,21 @@
     </row>
     <row r="2986">
       <c r="A2986" s="1" t="n">
-        <v>9000073</v>
+        <v>9000067</v>
       </c>
       <c r="B2986" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C2986" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D2986" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2986" s="1" t="n"/>
@@ -69089,21 +69097,21 @@
     </row>
     <row r="2987">
       <c r="A2987" s="1" t="n">
-        <v>9000074</v>
+        <v>9000068</v>
       </c>
       <c r="B2987" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C2987" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D2987" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2987" s="1" t="n"/>
@@ -69111,21 +69119,21 @@
     </row>
     <row r="2988">
       <c r="A2988" s="1" t="n">
-        <v>9000075</v>
+        <v>9000069</v>
       </c>
       <c r="B2988" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C2988" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D2988" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2988" s="1" t="n"/>
@@ -69133,21 +69141,21 @@
     </row>
     <row r="2989">
       <c r="A2989" s="1" t="n">
-        <v>9000076</v>
+        <v>9000070</v>
       </c>
       <c r="B2989" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C2989" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D2989" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2989" s="1" t="n"/>
@@ -69155,21 +69163,21 @@
     </row>
     <row r="2990">
       <c r="A2990" s="1" t="n">
-        <v>9000077</v>
+        <v>9000071</v>
       </c>
       <c r="B2990" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C2990" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D2990" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2990" s="1" t="n"/>
@@ -69177,21 +69185,21 @@
     </row>
     <row r="2991">
       <c r="A2991" s="1" t="n">
-        <v>9000078</v>
+        <v>9000072</v>
       </c>
       <c r="B2991" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C2991" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D2991" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2991" s="1" t="n"/>
@@ -69199,21 +69207,21 @@
     </row>
     <row r="2992">
       <c r="A2992" s="1" t="n">
-        <v>9000079</v>
+        <v>9000073</v>
       </c>
       <c r="B2992" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C2992" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D2992" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2992" s="1" t="n"/>
@@ -69221,21 +69229,21 @@
     </row>
     <row r="2993">
       <c r="A2993" s="1" t="n">
-        <v>9000080</v>
+        <v>9000074</v>
       </c>
       <c r="B2993" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C2993" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D2993" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2993" s="1" t="n"/>
@@ -69243,21 +69251,21 @@
     </row>
     <row r="2994">
       <c r="A2994" s="1" t="n">
-        <v>9000081</v>
+        <v>9000075</v>
       </c>
       <c r="B2994" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C2994" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D2994" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2994" s="1" t="n"/>
@@ -69265,21 +69273,21 @@
     </row>
     <row r="2995">
       <c r="A2995" s="1" t="n">
-        <v>9000082</v>
+        <v>9000076</v>
       </c>
       <c r="B2995" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C2995" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D2995" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E2995" s="1" t="n"/>
@@ -69287,21 +69295,21 @@
     </row>
     <row r="2996">
       <c r="A2996" s="1" t="n">
-        <v>9000083</v>
+        <v>9000077</v>
       </c>
       <c r="B2996" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C2996" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D2996" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2996" s="1" t="n"/>
@@ -69309,21 +69317,21 @@
     </row>
     <row r="2997">
       <c r="A2997" s="1" t="n">
-        <v>9000084</v>
+        <v>9000078</v>
       </c>
       <c r="B2997" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C2997" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D2997" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2997" s="1" t="n"/>
@@ -69331,21 +69339,21 @@
     </row>
     <row r="2998">
       <c r="A2998" s="1" t="n">
-        <v>9000085</v>
+        <v>9000079</v>
       </c>
       <c r="B2998" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C2998" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D2998" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2998" s="1" t="n"/>
@@ -69353,21 +69361,21 @@
     </row>
     <row r="2999">
       <c r="A2999" s="1" t="n">
-        <v>9000086</v>
+        <v>9000080</v>
       </c>
       <c r="B2999" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C2999" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D2999" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E2999" s="1" t="n"/>
@@ -69375,21 +69383,21 @@
     </row>
     <row r="3000">
       <c r="A3000" s="1" t="n">
-        <v>9000087</v>
+        <v>9000081</v>
       </c>
       <c r="B3000" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C3000" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D3000" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E3000" s="1" t="n"/>
@@ -69397,21 +69405,21 @@
     </row>
     <row r="3001">
       <c r="A3001" s="1" t="n">
-        <v>9000088</v>
+        <v>9000082</v>
       </c>
       <c r="B3001" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C3001" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D3001" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E3001" s="1" t="n"/>
@@ -69419,21 +69427,21 @@
     </row>
     <row r="3002">
       <c r="A3002" s="1" t="n">
-        <v>9000089</v>
+        <v>9000083</v>
       </c>
       <c r="B3002" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>헉헉</t>
         </is>
       </c>
       <c r="C3002" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>Huff puff</t>
         </is>
       </c>
       <c r="D3002" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E3002" s="1" t="n"/>
@@ -69441,21 +69449,21 @@
     </row>
     <row r="3003">
       <c r="A3003" s="1" t="n">
-        <v>9000090</v>
+        <v>9000084</v>
       </c>
       <c r="B3003" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>더 빨리!</t>
         </is>
       </c>
       <c r="C3003" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>Faster!</t>
         </is>
       </c>
       <c r="D3003" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E3003" s="1" t="n"/>
@@ -69463,21 +69471,21 @@
     </row>
     <row r="3004">
       <c r="A3004" s="1" t="n">
-        <v>9000091</v>
+        <v>9000085</v>
       </c>
       <c r="B3004" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>근육 붙는 중</t>
         </is>
       </c>
       <c r="C3004" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Gains incoming</t>
         </is>
       </c>
       <c r="D3004" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E3004" s="1" t="n"/>
@@ -69485,21 +69493,21 @@
     </row>
     <row r="3005">
       <c r="A3005" s="1" t="n">
-        <v>9000092</v>
+        <v>9000086</v>
       </c>
       <c r="B3005" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>찍찍찍찍</t>
         </is>
       </c>
       <c r="C3005" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Squeak squeak squeak squeak</t>
         </is>
       </c>
       <c r="D3005" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E3005" s="1" t="n"/>
@@ -69507,21 +69515,21 @@
     </row>
     <row r="3006">
       <c r="A3006" s="1" t="n">
-        <v>9000093</v>
+        <v>9000087</v>
       </c>
       <c r="B3006" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>으아아아~!</t>
         </is>
       </c>
       <c r="C3006" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Waaaaah~!</t>
         </is>
       </c>
       <c r="D3006" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E3006" s="1" t="n"/>
@@ -69529,21 +69537,21 @@
     </row>
     <row r="3007">
       <c r="A3007" s="1" t="n">
-        <v>9000094</v>
+        <v>9000088</v>
       </c>
       <c r="B3007" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>하암~ 잘 잤다</t>
         </is>
       </c>
       <c r="C3007" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>Yawn~ what a nap</t>
         </is>
       </c>
       <c r="D3007" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E3007" s="1" t="n"/>
@@ -69551,21 +69559,21 @@
     </row>
     <row r="3008">
       <c r="A3008" s="1" t="n">
-        <v>9000095</v>
+        <v>9000089</v>
       </c>
       <c r="B3008" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>냠, 배부르다</t>
         </is>
       </c>
       <c r="C3008" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>Nom, so full</t>
         </is>
       </c>
       <c r="D3008" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E3008" s="1" t="n"/>
@@ -69573,21 +69581,21 @@
     </row>
     <row r="3009">
       <c r="A3009" s="1" t="n">
-        <v>9000096</v>
+        <v>9000090</v>
       </c>
       <c r="B3009" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>휴…</t>
         </is>
       </c>
       <c r="C3009" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>Phew...</t>
         </is>
       </c>
       <c r="D3009" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E3009" s="1" t="n"/>
@@ -69595,21 +69603,21 @@
     </row>
     <row r="3010">
       <c r="A3010" s="1" t="n">
-        <v>9000097</v>
+        <v>9000091</v>
       </c>
       <c r="B3010" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>찍</t>
         </is>
       </c>
       <c r="C3010" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>Squeak</t>
         </is>
       </c>
       <c r="D3010" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
         </is>
       </c>
       <c r="E3010" s="1" t="n"/>
@@ -69617,21 +69625,21 @@
     </row>
     <row r="3011">
       <c r="A3011" s="1" t="n">
-        <v>9000098</v>
+        <v>9000092</v>
       </c>
       <c r="B3011" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C3011" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D3011" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Lobby/RunPage.cs:99</t>
         </is>
       </c>
       <c r="E3011" s="1" t="n"/>
@@ -69639,21 +69647,21 @@
     </row>
     <row r="3012">
       <c r="A3012" s="1" t="n">
-        <v>9000099</v>
+        <v>9000093</v>
       </c>
       <c r="B3012" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="C3012" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D3012" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
         </is>
       </c>
       <c r="E3012" s="1" t="n"/>
@@ -69661,21 +69669,21 @@
     </row>
     <row r="3013">
       <c r="A3013" s="1" t="n">
-        <v>9000100</v>
+        <v>9000094</v>
       </c>
       <c r="B3013" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>찌릿!!</t>
         </is>
       </c>
       <c r="C3013" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>ZAP!!</t>
         </is>
       </c>
       <c r="D3013" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E3013" s="1" t="n"/>
@@ -69683,21 +69691,21 @@
     </row>
     <row r="3014">
       <c r="A3014" s="1" t="n">
-        <v>9000101</v>
+        <v>9000095</v>
       </c>
       <c r="B3014" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>콰릉!</t>
         </is>
       </c>
       <c r="C3014" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>Ka-boom!</t>
         </is>
       </c>
       <c r="D3014" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E3014" s="1" t="n"/>
@@ -69705,21 +69713,21 @@
     </row>
     <row r="3015">
       <c r="A3015" s="1" t="n">
-        <v>9000102</v>
+        <v>9000096</v>
       </c>
       <c r="B3015" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>냠!</t>
         </is>
       </c>
       <c r="C3015" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>Nom!</t>
         </is>
       </c>
       <c r="D3015" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E3015" s="1" t="n"/>
@@ -69727,21 +69735,21 @@
     </row>
     <row r="3016">
       <c r="A3016" s="1" t="n">
-        <v>9000103</v>
+        <v>9000097</v>
       </c>
       <c r="B3016" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>다닥!</t>
         </is>
       </c>
       <c r="C3016" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Scurry!</t>
         </is>
       </c>
       <c r="D3016" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E3016" s="1" t="n"/>
@@ -69749,21 +69757,21 @@
     </row>
     <row r="3017">
       <c r="A3017" s="1" t="n">
-        <v>9000104</v>
+        <v>9000098</v>
       </c>
       <c r="B3017" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>메리 쥐스마스!</t>
         </is>
       </c>
       <c r="C3017" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Merry Ratmas!</t>
         </is>
       </c>
       <c r="D3017" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E3017" s="1" t="n"/>
@@ -69771,21 +69779,21 @@
     </row>
     <row r="3018">
       <c r="A3018" s="1" t="n">
-        <v>9000105</v>
+        <v>9000099</v>
       </c>
       <c r="B3018" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>흐에~ 후원 감사합니다~!</t>
         </is>
       </c>
       <c r="C3018" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>Heheh~ thanks for the dono~!</t>
         </is>
       </c>
       <c r="D3018" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E3018" s="1" t="n"/>
@@ -69793,21 +69801,21 @@
     </row>
     <row r="3019">
       <c r="A3019" s="1" t="n">
-        <v>9000106</v>
+        <v>9000100</v>
       </c>
       <c r="B3019" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>배달 왔습니다~</t>
         </is>
       </c>
       <c r="C3019" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>Delivery~!</t>
         </is>
       </c>
       <c r="D3019" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E3019" s="1" t="n"/>
@@ -69815,21 +69823,21 @@
     </row>
     <row r="3020">
       <c r="A3020" s="1" t="n">
-        <v>9000107</v>
+        <v>9000101</v>
       </c>
       <c r="B3020" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>백덤블링!</t>
         </is>
       </c>
       <c r="C3020" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>Backflip!</t>
         </is>
       </c>
       <c r="D3020" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E3020" s="1" t="n"/>
@@ -69837,21 +69845,21 @@
     </row>
     <row r="3021">
       <c r="A3021" s="1" t="n">
-        <v>9000108</v>
+        <v>9000102</v>
       </c>
       <c r="B3021" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>공중제비!</t>
         </is>
       </c>
       <c r="C3021" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>Somersault!</t>
         </is>
       </c>
       <c r="D3021" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E3021" s="1" t="n"/>
@@ -69859,21 +69867,21 @@
     </row>
     <row r="3022">
       <c r="A3022" s="1" t="n">
-        <v>9000109</v>
+        <v>9000103</v>
       </c>
       <c r="B3022" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>찍-공중회전!</t>
         </is>
       </c>
       <c r="C3022" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>Squeak-flip!</t>
         </is>
       </c>
       <c r="D3022" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E3022" s="1" t="n"/>
@@ -69881,21 +69889,21 @@
     </row>
     <row r="3023">
       <c r="A3023" s="1" t="n">
-        <v>9000110</v>
+        <v>9000104</v>
       </c>
       <c r="B3023" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>트리플 악셀!!</t>
         </is>
       </c>
       <c r="C3023" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>TRIPLE AXEL!!</t>
         </is>
       </c>
       <c r="D3023" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E3023" s="1" t="n"/>
@@ -69903,21 +69911,21 @@
     </row>
     <row r="3024">
       <c r="A3024" s="1" t="n">
-        <v>9000111</v>
+        <v>9000105</v>
       </c>
       <c r="B3024" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>3회전 성공!</t>
         </is>
       </c>
       <c r="C3024" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>Triple spin landed!</t>
         </is>
       </c>
       <c r="D3024" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E3024" s="1" t="n"/>
@@ -69925,21 +69933,21 @@
     </row>
     <row r="3025">
       <c r="A3025" s="1" t="n">
-        <v>9000112</v>
+        <v>9000106</v>
       </c>
       <c r="B3025" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>심사위원 전원 10점!</t>
         </is>
       </c>
       <c r="C3025" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>Perfect 10s from every judge!</t>
         </is>
       </c>
       <c r="D3025" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E3025" s="1" t="n"/>
@@ -69947,21 +69955,21 @@
     </row>
     <row r="3026">
       <c r="A3026" s="1" t="n">
-        <v>9000113</v>
+        <v>9000107</v>
       </c>
       <c r="B3026" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>윈드밀!!</t>
         </is>
       </c>
       <c r="C3026" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>WINDMILL!!</t>
         </is>
       </c>
       <c r="D3026" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E3026" s="1" t="n"/>
@@ -69969,21 +69977,21 @@
     </row>
     <row r="3027">
       <c r="A3027" s="1" t="n">
-        <v>9000114</v>
+        <v>9000108</v>
       </c>
       <c r="B3027" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>브레이크 댄스!</t>
         </is>
       </c>
       <c r="C3027" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>Breakdance!</t>
         </is>
       </c>
       <c r="D3027" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E3027" s="1" t="n"/>
@@ -69991,21 +69999,21 @@
     </row>
     <row r="3028">
       <c r="A3028" s="1" t="n">
-        <v>9000115</v>
+        <v>9000109</v>
       </c>
       <c r="B3028" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>빙글빙글 파괴!</t>
         </is>
       </c>
       <c r="C3028" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>Spin-to-win destruction!</t>
         </is>
       </c>
       <c r="D3028" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E3028" s="1" t="n"/>
@@ -70013,21 +70021,21 @@
     </row>
     <row r="3029">
       <c r="A3029" s="1" t="n">
-        <v>9000116</v>
+        <v>9000110</v>
       </c>
       <c r="B3029" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>쥐 대포알!</t>
         </is>
       </c>
       <c r="C3029" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>Rat Cannonball!</t>
         </is>
       </c>
       <c r="D3029" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E3029" s="1" t="n"/>
@@ -70035,21 +70043,21 @@
     </row>
     <row r="3030">
       <c r="A3030" s="1" t="n">
-        <v>9000117</v>
+        <v>9000111</v>
       </c>
       <c r="B3030" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>데굴데굴!</t>
         </is>
       </c>
       <c r="C3030" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>Roll roll!</t>
         </is>
       </c>
       <c r="D3030" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E3030" s="1" t="n"/>
@@ -70057,21 +70065,21 @@
     </row>
     <row r="3031">
       <c r="A3031" s="1" t="n">
-        <v>9000118</v>
+        <v>9000112</v>
       </c>
       <c r="B3031" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>핀볼 모드!</t>
         </is>
       </c>
       <c r="C3031" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>Pinball mode!</t>
         </is>
       </c>
       <c r="D3031" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E3031" s="1" t="n"/>
@@ -70079,21 +70087,21 @@
     </row>
     <row r="3032">
       <c r="A3032" s="1" t="n">
-        <v>9000119</v>
+        <v>9000113</v>
       </c>
       <c r="B3032" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>쳇바퀴 돌기!!</t>
         </is>
       </c>
       <c r="C3032" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>WHEEL SPIN!!</t>
         </is>
       </c>
       <c r="D3032" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E3032" s="1" t="n"/>
@@ -70101,21 +70109,21 @@
     </row>
     <row r="3033">
       <c r="A3033" s="1" t="n">
-        <v>9000120</v>
+        <v>9000114</v>
       </c>
       <c r="B3033" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>빙글빙글~</t>
         </is>
       </c>
       <c r="C3033" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>Round and round~</t>
         </is>
       </c>
       <c r="D3033" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E3033" s="1" t="n"/>
@@ -70123,21 +70131,21 @@
     </row>
     <row r="3034">
       <c r="A3034" s="1" t="n">
-        <v>9000121</v>
+        <v>9000115</v>
       </c>
       <c r="B3034" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>어지러워!!</t>
         </is>
       </c>
       <c r="C3034" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>So DIZZY!!</t>
         </is>
       </c>
       <c r="D3034" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E3034" s="1" t="n"/>
@@ -70145,21 +70153,21 @@
     </row>
     <row r="3035">
       <c r="A3035" s="1" t="n">
-        <v>9000122</v>
+        <v>9000116</v>
       </c>
       <c r="B3035" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="C3035" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="D3035" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
         </is>
       </c>
       <c r="E3035" s="1" t="n"/>
@@ -70167,21 +70175,21 @@
     </row>
     <row r="3036">
       <c r="A3036" s="1" t="n">
-        <v>9000123</v>
+        <v>9000117</v>
       </c>
       <c r="B3036" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>기절!!</t>
         </is>
       </c>
       <c r="C3036" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>Stunned!!</t>
         </is>
       </c>
       <c r="D3036" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Rats/RatManager.cs:38</t>
         </is>
       </c>
       <c r="E3036" s="1" t="n"/>
@@ -70189,21 +70197,21 @@
     </row>
     <row r="3037">
       <c r="A3037" s="1" t="n">
-        <v>9000124</v>
+        <v>9000118</v>
       </c>
       <c r="B3037" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>소품이 떨어졌다!</t>
         </is>
       </c>
       <c r="C3037" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>A prop dropped!</t>
         </is>
       </c>
       <c r="D3037" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:397</t>
         </is>
       </c>
       <c r="E3037" s="1" t="n"/>
@@ -70211,21 +70219,21 @@
     </row>
     <row r="3038">
       <c r="A3038" s="1" t="n">
-        <v>9000125</v>
+        <v>9000119</v>
       </c>
       <c r="B3038" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>조각 +1</t>
         </is>
       </c>
       <c r="C3038" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>Shard +1</t>
         </is>
       </c>
       <c r="D3038" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:460</t>
         </is>
       </c>
       <c r="E3038" s="1" t="n"/>
@@ -70233,21 +70241,21 @@
     </row>
     <row r="3039">
       <c r="A3039" s="1" t="n">
-        <v>9000126</v>
+        <v>9000120</v>
       </c>
       <c r="B3039" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>{name} 강화! Lv {lv}</t>
         </is>
       </c>
       <c r="C3039" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>{name} powered up! Lv {lv}</t>
         </is>
       </c>
       <c r="D3039" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Rats/RatManager.cs:461</t>
         </is>
       </c>
       <c r="E3039" s="1" t="n"/>
@@ -70255,21 +70263,21 @@
     </row>
     <row r="3040">
       <c r="A3040" s="1" t="n">
-        <v>9000127</v>
+        <v>9000121</v>
       </c>
       <c r="B3040" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>{grade} 탄생!</t>
         </is>
       </c>
       <c r="C3040" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>{grade} born!</t>
         </is>
       </c>
       <c r="D3040" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Rats/RatManager.cs:561</t>
         </is>
       </c>
       <c r="E3040" s="1" t="n"/>
@@ -70277,21 +70285,21 @@
     </row>
     <row r="3041">
       <c r="A3041" s="1" t="n">
-        <v>9000128</v>
+        <v>9000122</v>
       </c>
       <c r="B3041" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>쌍둥이!</t>
         </is>
       </c>
       <c r="C3041" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>Twins!</t>
         </is>
       </c>
       <c r="D3041" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Rats/RatManager.cs:566</t>
         </is>
       </c>
       <c r="E3041" s="1" t="n"/>
@@ -70299,21 +70307,21 @@
     </row>
     <row r="3042">
       <c r="A3042" s="1" t="n">
-        <v>9000129</v>
+        <v>9000123</v>
       </c>
       <c r="B3042" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>치즈 운석!</t>
         </is>
       </c>
       <c r="C3042" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>Cheese Meteor!</t>
         </is>
       </c>
       <c r="D3042" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Rats/RatManager.cs:627</t>
         </is>
       </c>
       <c r="E3042" s="1" t="n"/>
@@ -70321,21 +70329,21 @@
     </row>
     <row r="3043">
       <c r="A3043" s="1" t="n">
-        <v>9000130</v>
+        <v>9000124</v>
       </c>
       <c r="B3043" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>{floor}층 · {zone}</t>
         </is>
       </c>
       <c r="C3043" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Floor {floor} · {zone}</t>
         </is>
       </c>
       <c r="D3043" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E3043" s="1" t="n"/>
@@ -70343,25 +70351,157 @@
     </row>
     <row r="3044">
       <c r="A3044" s="1" t="n">
-        <v>9000131</v>
+        <v>9000125</v>
       </c>
       <c r="B3044" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>계단 방 벽을 부숴라!</t>
         </is>
       </c>
       <c r="C3044" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>Smash the wall to the stairs room!</t>
         </is>
       </c>
       <c r="D3044" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E3044" s="1" t="n"/>
       <c r="F3044" s="1" t="n"/>
+    </row>
+    <row r="3045">
+      <c r="A3045" s="1" t="n">
+        <v>9000126</v>
+      </c>
+      <c r="B3045" s="2" t="inlineStr">
+        <is>
+          <t>벽 붕괴! 방 확장</t>
+        </is>
+      </c>
+      <c r="C3045" s="2" t="inlineStr">
+        <is>
+          <t>Wall down! Room expanded</t>
+        </is>
+      </c>
+      <c r="D3045" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:332</t>
+        </is>
+      </c>
+      <c r="E3045" s="1" t="n"/>
+      <c r="F3045" s="1" t="n"/>
+    </row>
+    <row r="3046">
+      <c r="A3046" s="1" t="n">
+        <v>9000127</v>
+      </c>
+      <c r="B3046" s="2" t="inlineStr">
+        <is>
+          <t>계단 발견!</t>
+        </is>
+      </c>
+      <c r="C3046" s="2" t="inlineStr">
+        <is>
+          <t>Stairs found!</t>
+        </is>
+      </c>
+      <c r="D3046" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:338</t>
+        </is>
+      </c>
+      <c r="E3046" s="1" t="n"/>
+      <c r="F3046" s="1" t="n"/>
+    </row>
+    <row r="3047">
+      <c r="A3047" s="1" t="n">
+        <v>9000128</v>
+      </c>
+      <c r="B3047" s="2" t="inlineStr">
+        <is>
+          <t>계단에 닿으면 {next}층으로</t>
+        </is>
+      </c>
+      <c r="C3047" s="2" t="inlineStr">
+        <is>
+          <t>Touch the stairs to go to Floor {next}</t>
+        </is>
+      </c>
+      <c r="D3047" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:338</t>
+        </is>
+      </c>
+      <c r="E3047" s="1" t="n"/>
+      <c r="F3047" s="1" t="n"/>
+    </row>
+    <row r="3048">
+      <c r="A3048" s="1" t="n">
+        <v>9000129</v>
+      </c>
+      <c r="B3048" s="2" t="inlineStr">
+        <is>
+          <t>와르르!!</t>
+        </is>
+      </c>
+      <c r="C3048" s="2" t="inlineStr">
+        <is>
+          <t>Crumble!!</t>
+        </is>
+      </c>
+      <c r="D3048" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3048" s="1" t="n"/>
+      <c r="F3048" s="1" t="n"/>
+    </row>
+    <row r="3049">
+      <c r="A3049" s="1" t="n">
+        <v>9000130</v>
+      </c>
+      <c r="B3049" s="2" t="inlineStr">
+        <is>
+          <t>콰광!!</t>
+        </is>
+      </c>
+      <c r="C3049" s="2" t="inlineStr">
+        <is>
+          <t>KA-BOOM!!</t>
+        </is>
+      </c>
+      <c r="D3049" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3049" s="1" t="n"/>
+      <c r="F3049" s="1" t="n"/>
+    </row>
+    <row r="3050">
+      <c r="A3050" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B3050" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C3050" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D3050" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3050" s="1" t="n"/>
+      <c r="F3050" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3057"/>
+  <dimension ref="A1:F3058"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -67777,21 +67777,21 @@
     </row>
     <row r="2927">
       <c r="A2927" s="1" t="n">
-        <v>9000001</v>
+        <v>8000538</v>
       </c>
       <c r="B2927" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power}</t>
+          <t>{name}의 필살기! {ult}</t>
         </is>
       </c>
       <c r="C2927" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power}</t>
+          <t>{name}'s Ultimate! {ult}</t>
         </is>
       </c>
       <c r="D2927" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
+          <t>씬 · Game · HUD/UltLog/Row3/Text | Game · HUD/UltLog/Row0/Text | Game · HUD/UltLog/Row2/Text | Game · HUD/UltLog/Row1/Text</t>
         </is>
       </c>
       <c r="E2927" s="1" t="n"/>
@@ -67799,21 +67799,21 @@
     </row>
     <row r="2928">
       <c r="A2928" s="1" t="n">
-        <v>9000002</v>
+        <v>9000001</v>
       </c>
       <c r="B2928" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>찍찍!! {power}</t>
         </is>
       </c>
       <c r="C2928" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>SQUEAK!! {power}</t>
         </is>
       </c>
       <c r="D2928" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E2928" s="1" t="n"/>
@@ -67821,21 +67821,21 @@
     </row>
     <row r="2929">
       <c r="A2929" s="1" t="n">
-        <v>9000003</v>
+        <v>9000002</v>
       </c>
       <c r="B2929" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C2929" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D2929" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E2929" s="1" t="n"/>
@@ -67843,21 +67843,21 @@
     </row>
     <row r="2930">
       <c r="A2930" s="1" t="n">
-        <v>9000004</v>
+        <v>9000003</v>
       </c>
       <c r="B2930" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C2930" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D2930" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E2930" s="1" t="n"/>
@@ -67865,21 +67865,21 @@
     </row>
     <row r="2931">
       <c r="A2931" s="1" t="n">
-        <v>9000005</v>
+        <v>9000004</v>
       </c>
       <c r="B2931" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C2931" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D2931" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E2931" s="1" t="n"/>
@@ -67887,21 +67887,21 @@
     </row>
     <row r="2932">
       <c r="A2932" s="1" t="n">
-        <v>9000006</v>
+        <v>9000005</v>
       </c>
       <c r="B2932" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C2932" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D2932" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E2932" s="1" t="n"/>
@@ -67909,21 +67909,21 @@
     </row>
     <row r="2933">
       <c r="A2933" s="1" t="n">
-        <v>9000007</v>
+        <v>9000006</v>
       </c>
       <c r="B2933" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C2933" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D2933" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E2933" s="1" t="n"/>
@@ -67931,21 +67931,21 @@
     </row>
     <row r="2934">
       <c r="A2934" s="1" t="n">
-        <v>9000008</v>
+        <v>9000007</v>
       </c>
       <c r="B2934" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C2934" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D2934" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E2934" s="1" t="n"/>
@@ -67953,16 +67953,16 @@
     </row>
     <row r="2935">
       <c r="A2935" s="1" t="n">
-        <v>9000009</v>
+        <v>9000008</v>
       </c>
       <c r="B2935" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C2935" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D2935" s="1" t="inlineStr">
@@ -67975,16 +67975,16 @@
     </row>
     <row r="2936">
       <c r="A2936" s="1" t="n">
-        <v>9000010</v>
+        <v>9000009</v>
       </c>
       <c r="B2936" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C2936" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D2936" s="1" t="inlineStr">
@@ -67997,16 +67997,16 @@
     </row>
     <row r="2937">
       <c r="A2937" s="1" t="n">
-        <v>9000011</v>
+        <v>9000010</v>
       </c>
       <c r="B2937" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C2937" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D2937" s="1" t="inlineStr">
@@ -68019,21 +68019,21 @@
     </row>
     <row r="2938">
       <c r="A2938" s="1" t="n">
-        <v>9000012</v>
+        <v>9000011</v>
       </c>
       <c r="B2938" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C2938" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D2938" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E2938" s="1" t="n"/>
@@ -68041,16 +68041,16 @@
     </row>
     <row r="2939">
       <c r="A2939" s="1" t="n">
-        <v>9000013</v>
+        <v>9000012</v>
       </c>
       <c r="B2939" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C2939" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D2939" s="1" t="inlineStr">
@@ -68063,21 +68063,21 @@
     </row>
     <row r="2940">
       <c r="A2940" s="1" t="n">
-        <v>9000014</v>
+        <v>9000013</v>
       </c>
       <c r="B2940" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C2940" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D2940" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E2940" s="1" t="n"/>
@@ -68085,21 +68085,21 @@
     </row>
     <row r="2941">
       <c r="A2941" s="1" t="n">
-        <v>9000015</v>
+        <v>9000014</v>
       </c>
       <c r="B2941" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C2941" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D2941" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E2941" s="1" t="n"/>
@@ -68107,16 +68107,16 @@
     </row>
     <row r="2942">
       <c r="A2942" s="1" t="n">
-        <v>9000016</v>
+        <v>9000015</v>
       </c>
       <c r="B2942" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C2942" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D2942" s="1" t="inlineStr">
@@ -68129,21 +68129,21 @@
     </row>
     <row r="2943">
       <c r="A2943" s="1" t="n">
-        <v>9000017</v>
+        <v>9000016</v>
       </c>
       <c r="B2943" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C2943" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D2943" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E2943" s="1" t="n"/>
@@ -68151,21 +68151,21 @@
     </row>
     <row r="2944">
       <c r="A2944" s="1" t="n">
-        <v>9000018</v>
+        <v>9000017</v>
       </c>
       <c r="B2944" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C2944" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D2944" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E2944" s="1" t="n"/>
@@ -68173,16 +68173,16 @@
     </row>
     <row r="2945">
       <c r="A2945" s="1" t="n">
-        <v>9000019</v>
+        <v>9000018</v>
       </c>
       <c r="B2945" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C2945" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D2945" s="1" t="inlineStr">
@@ -68195,16 +68195,16 @@
     </row>
     <row r="2946">
       <c r="A2946" s="1" t="n">
-        <v>9000020</v>
+        <v>9000019</v>
       </c>
       <c r="B2946" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C2946" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D2946" s="1" t="inlineStr">
@@ -68217,21 +68217,21 @@
     </row>
     <row r="2947">
       <c r="A2947" s="1" t="n">
-        <v>9000021</v>
+        <v>9000020</v>
       </c>
       <c r="B2947" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C2947" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D2947" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E2947" s="1" t="n"/>
@@ -68239,21 +68239,21 @@
     </row>
     <row r="2948">
       <c r="A2948" s="1" t="n">
-        <v>9000022</v>
+        <v>9000021</v>
       </c>
       <c r="B2948" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C2948" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D2948" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E2948" s="1" t="n"/>
@@ -68261,16 +68261,16 @@
     </row>
     <row r="2949">
       <c r="A2949" s="1" t="n">
-        <v>9000023</v>
+        <v>9000022</v>
       </c>
       <c r="B2949" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C2949" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D2949" s="1" t="inlineStr">
@@ -68283,16 +68283,16 @@
     </row>
     <row r="2950">
       <c r="A2950" s="1" t="n">
-        <v>9000024</v>
+        <v>9000023</v>
       </c>
       <c r="B2950" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C2950" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D2950" s="1" t="inlineStr">
@@ -68305,16 +68305,16 @@
     </row>
     <row r="2951">
       <c r="A2951" s="1" t="n">
-        <v>9000025</v>
+        <v>9000024</v>
       </c>
       <c r="B2951" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C2951" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D2951" s="1" t="inlineStr">
@@ -68327,21 +68327,21 @@
     </row>
     <row r="2952">
       <c r="A2952" s="1" t="n">
-        <v>9000026</v>
+        <v>9000025</v>
       </c>
       <c r="B2952" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C2952" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D2952" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E2952" s="1" t="n"/>
@@ -68349,21 +68349,21 @@
     </row>
     <row r="2953">
       <c r="A2953" s="1" t="n">
-        <v>9000027</v>
+        <v>9000026</v>
       </c>
       <c r="B2953" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C2953" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D2953" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E2953" s="1" t="n"/>
@@ -68371,16 +68371,16 @@
     </row>
     <row r="2954">
       <c r="A2954" s="1" t="n">
-        <v>9000028</v>
+        <v>9000027</v>
       </c>
       <c r="B2954" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C2954" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D2954" s="1" t="inlineStr">
@@ -68393,21 +68393,21 @@
     </row>
     <row r="2955">
       <c r="A2955" s="1" t="n">
-        <v>9000029</v>
+        <v>9000028</v>
       </c>
       <c r="B2955" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C2955" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D2955" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E2955" s="1" t="n"/>
@@ -68415,21 +68415,21 @@
     </row>
     <row r="2956">
       <c r="A2956" s="1" t="n">
-        <v>9000030</v>
+        <v>9000029</v>
       </c>
       <c r="B2956" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C2956" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D2956" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2956" s="1" t="n"/>
@@ -68437,21 +68437,21 @@
     </row>
     <row r="2957">
       <c r="A2957" s="1" t="n">
-        <v>9000031</v>
+        <v>9000030</v>
       </c>
       <c r="B2957" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C2957" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D2957" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E2957" s="1" t="n"/>
@@ -68459,21 +68459,21 @@
     </row>
     <row r="2958">
       <c r="A2958" s="1" t="n">
-        <v>9000032</v>
+        <v>9000031</v>
       </c>
       <c r="B2958" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C2958" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D2958" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E2958" s="1" t="n"/>
@@ -68481,16 +68481,16 @@
     </row>
     <row r="2959">
       <c r="A2959" s="1" t="n">
-        <v>9000033</v>
+        <v>9000032</v>
       </c>
       <c r="B2959" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C2959" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D2959" s="1" t="inlineStr">
@@ -68503,16 +68503,16 @@
     </row>
     <row r="2960">
       <c r="A2960" s="1" t="n">
-        <v>9000034</v>
+        <v>9000033</v>
       </c>
       <c r="B2960" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C2960" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D2960" s="1" t="inlineStr">
@@ -68525,21 +68525,21 @@
     </row>
     <row r="2961">
       <c r="A2961" s="1" t="n">
-        <v>9000035</v>
+        <v>9000034</v>
       </c>
       <c r="B2961" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C2961" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D2961" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E2961" s="1" t="n"/>
@@ -68547,21 +68547,21 @@
     </row>
     <row r="2962">
       <c r="A2962" s="1" t="n">
-        <v>9000036</v>
+        <v>9000035</v>
       </c>
       <c r="B2962" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C2962" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D2962" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E2962" s="1" t="n"/>
@@ -68569,21 +68569,21 @@
     </row>
     <row r="2963">
       <c r="A2963" s="1" t="n">
-        <v>9000037</v>
+        <v>9000036</v>
       </c>
       <c r="B2963" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C2963" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D2963" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E2963" s="1" t="n"/>
@@ -68591,21 +68591,21 @@
     </row>
     <row r="2964">
       <c r="A2964" s="1" t="n">
-        <v>9000038</v>
+        <v>9000037</v>
       </c>
       <c r="B2964" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C2964" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D2964" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E2964" s="1" t="n"/>
@@ -68613,21 +68613,21 @@
     </row>
     <row r="2965">
       <c r="A2965" s="1" t="n">
-        <v>9000039</v>
+        <v>9000038</v>
       </c>
       <c r="B2965" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C2965" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D2965" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E2965" s="1" t="n"/>
@@ -68635,21 +68635,21 @@
     </row>
     <row r="2966">
       <c r="A2966" s="1" t="n">
-        <v>9000040</v>
+        <v>9000039</v>
       </c>
       <c r="B2966" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C2966" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D2966" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E2966" s="1" t="n"/>
@@ -68657,21 +68657,21 @@
     </row>
     <row r="2967">
       <c r="A2967" s="1" t="n">
-        <v>9000041</v>
+        <v>9000040</v>
       </c>
       <c r="B2967" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C2967" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D2967" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E2967" s="1" t="n"/>
@@ -68679,21 +68679,21 @@
     </row>
     <row r="2968">
       <c r="A2968" s="1" t="n">
-        <v>9000042</v>
+        <v>9000041</v>
       </c>
       <c r="B2968" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C2968" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D2968" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E2968" s="1" t="n"/>
@@ -68701,16 +68701,16 @@
     </row>
     <row r="2969">
       <c r="A2969" s="1" t="n">
-        <v>9000043</v>
+        <v>9000042</v>
       </c>
       <c r="B2969" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C2969" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D2969" s="1" t="inlineStr">
@@ -68723,16 +68723,16 @@
     </row>
     <row r="2970">
       <c r="A2970" s="1" t="n">
-        <v>9000044</v>
+        <v>9000043</v>
       </c>
       <c r="B2970" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C2970" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D2970" s="1" t="inlineStr">
@@ -68745,16 +68745,16 @@
     </row>
     <row r="2971">
       <c r="A2971" s="1" t="n">
-        <v>9000045</v>
+        <v>9000044</v>
       </c>
       <c r="B2971" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C2971" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D2971" s="1" t="inlineStr">
@@ -68767,21 +68767,21 @@
     </row>
     <row r="2972">
       <c r="A2972" s="1" t="n">
-        <v>9000046</v>
+        <v>9000045</v>
       </c>
       <c r="B2972" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C2972" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D2972" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E2972" s="1" t="n"/>
@@ -68789,16 +68789,16 @@
     </row>
     <row r="2973">
       <c r="A2973" s="1" t="n">
-        <v>9000047</v>
+        <v>9000046</v>
       </c>
       <c r="B2973" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C2973" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D2973" s="1" t="inlineStr">
@@ -68811,16 +68811,16 @@
     </row>
     <row r="2974">
       <c r="A2974" s="1" t="n">
-        <v>9000048</v>
+        <v>9000047</v>
       </c>
       <c r="B2974" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C2974" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D2974" s="1" t="inlineStr">
@@ -68833,21 +68833,21 @@
     </row>
     <row r="2975">
       <c r="A2975" s="1" t="n">
-        <v>9000049</v>
+        <v>9000048</v>
       </c>
       <c r="B2975" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C2975" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D2975" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E2975" s="1" t="n"/>
@@ -68855,21 +68855,21 @@
     </row>
     <row r="2976">
       <c r="A2976" s="1" t="n">
-        <v>9000050</v>
+        <v>9000049</v>
       </c>
       <c r="B2976" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C2976" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D2976" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E2976" s="1" t="n"/>
@@ -68877,21 +68877,21 @@
     </row>
     <row r="2977">
       <c r="A2977" s="1" t="n">
-        <v>9000051</v>
+        <v>9000050</v>
       </c>
       <c r="B2977" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C2977" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D2977" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E2977" s="1" t="n"/>
@@ -68899,16 +68899,16 @@
     </row>
     <row r="2978">
       <c r="A2978" s="1" t="n">
-        <v>9000052</v>
+        <v>9000051</v>
       </c>
       <c r="B2978" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C2978" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D2978" s="1" t="inlineStr">
@@ -68921,21 +68921,21 @@
     </row>
     <row r="2979">
       <c r="A2979" s="1" t="n">
-        <v>9000053</v>
+        <v>9000052</v>
       </c>
       <c r="B2979" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C2979" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D2979" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E2979" s="1" t="n"/>
@@ -68943,21 +68943,21 @@
     </row>
     <row r="2980">
       <c r="A2980" s="1" t="n">
-        <v>9000054</v>
+        <v>9000053</v>
       </c>
       <c r="B2980" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C2980" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D2980" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E2980" s="1" t="n"/>
@@ -68965,16 +68965,16 @@
     </row>
     <row r="2981">
       <c r="A2981" s="1" t="n">
-        <v>9000055</v>
+        <v>9000054</v>
       </c>
       <c r="B2981" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C2981" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D2981" s="1" t="inlineStr">
@@ -68987,21 +68987,21 @@
     </row>
     <row r="2982">
       <c r="A2982" s="1" t="n">
-        <v>9000056</v>
+        <v>9000055</v>
       </c>
       <c r="B2982" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C2982" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D2982" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E2982" s="1" t="n"/>
@@ -69009,16 +69009,16 @@
     </row>
     <row r="2983">
       <c r="A2983" s="1" t="n">
-        <v>9000057</v>
+        <v>9000056</v>
       </c>
       <c r="B2983" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C2983" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D2983" s="1" t="inlineStr">
@@ -69031,16 +69031,16 @@
     </row>
     <row r="2984">
       <c r="A2984" s="1" t="n">
-        <v>9000058</v>
+        <v>9000057</v>
       </c>
       <c r="B2984" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C2984" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D2984" s="1" t="inlineStr">
@@ -69053,16 +69053,16 @@
     </row>
     <row r="2985">
       <c r="A2985" s="1" t="n">
-        <v>9000059</v>
+        <v>9000058</v>
       </c>
       <c r="B2985" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C2985" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D2985" s="1" t="inlineStr">
@@ -69075,21 +69075,21 @@
     </row>
     <row r="2986">
       <c r="A2986" s="1" t="n">
-        <v>9000060</v>
+        <v>9000059</v>
       </c>
       <c r="B2986" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C2986" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D2986" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E2986" s="1" t="n"/>
@@ -69097,16 +69097,16 @@
     </row>
     <row r="2987">
       <c r="A2987" s="1" t="n">
-        <v>9000061</v>
+        <v>9000060</v>
       </c>
       <c r="B2987" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C2987" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D2987" s="1" t="inlineStr">
@@ -69119,16 +69119,16 @@
     </row>
     <row r="2988">
       <c r="A2988" s="1" t="n">
-        <v>9000062</v>
+        <v>9000061</v>
       </c>
       <c r="B2988" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C2988" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D2988" s="1" t="inlineStr">
@@ -69141,16 +69141,16 @@
     </row>
     <row r="2989">
       <c r="A2989" s="1" t="n">
-        <v>9000063</v>
+        <v>9000062</v>
       </c>
       <c r="B2989" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C2989" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D2989" s="1" t="inlineStr">
@@ -69163,16 +69163,16 @@
     </row>
     <row r="2990">
       <c r="A2990" s="1" t="n">
-        <v>9000064</v>
+        <v>9000063</v>
       </c>
       <c r="B2990" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C2990" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D2990" s="1" t="inlineStr">
@@ -69185,21 +69185,21 @@
     </row>
     <row r="2991">
       <c r="A2991" s="1" t="n">
-        <v>9000065</v>
+        <v>9000064</v>
       </c>
       <c r="B2991" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C2991" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D2991" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E2991" s="1" t="n"/>
@@ -69207,16 +69207,16 @@
     </row>
     <row r="2992">
       <c r="A2992" s="1" t="n">
-        <v>9000066</v>
+        <v>9000065</v>
       </c>
       <c r="B2992" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C2992" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D2992" s="1" t="inlineStr">
@@ -69229,16 +69229,16 @@
     </row>
     <row r="2993">
       <c r="A2993" s="1" t="n">
-        <v>9000067</v>
+        <v>9000066</v>
       </c>
       <c r="B2993" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C2993" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D2993" s="1" t="inlineStr">
@@ -69251,16 +69251,16 @@
     </row>
     <row r="2994">
       <c r="A2994" s="1" t="n">
-        <v>9000068</v>
+        <v>9000067</v>
       </c>
       <c r="B2994" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C2994" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D2994" s="1" t="inlineStr">
@@ -69273,16 +69273,16 @@
     </row>
     <row r="2995">
       <c r="A2995" s="1" t="n">
-        <v>9000069</v>
+        <v>9000068</v>
       </c>
       <c r="B2995" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C2995" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D2995" s="1" t="inlineStr">
@@ -69295,16 +69295,16 @@
     </row>
     <row r="2996">
       <c r="A2996" s="1" t="n">
-        <v>9000070</v>
+        <v>9000069</v>
       </c>
       <c r="B2996" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C2996" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D2996" s="1" t="inlineStr">
@@ -69317,16 +69317,16 @@
     </row>
     <row r="2997">
       <c r="A2997" s="1" t="n">
-        <v>9000071</v>
+        <v>9000070</v>
       </c>
       <c r="B2997" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C2997" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D2997" s="1" t="inlineStr">
@@ -69339,21 +69339,21 @@
     </row>
     <row r="2998">
       <c r="A2998" s="1" t="n">
-        <v>9000072</v>
+        <v>9000071</v>
       </c>
       <c r="B2998" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C2998" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D2998" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E2998" s="1" t="n"/>
@@ -69361,16 +69361,16 @@
     </row>
     <row r="2999">
       <c r="A2999" s="1" t="n">
-        <v>9000073</v>
+        <v>9000072</v>
       </c>
       <c r="B2999" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C2999" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D2999" s="1" t="inlineStr">
@@ -69383,16 +69383,16 @@
     </row>
     <row r="3000">
       <c r="A3000" s="1" t="n">
-        <v>9000074</v>
+        <v>9000073</v>
       </c>
       <c r="B3000" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C3000" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D3000" s="1" t="inlineStr">
@@ -69405,16 +69405,16 @@
     </row>
     <row r="3001">
       <c r="A3001" s="1" t="n">
-        <v>9000075</v>
+        <v>9000074</v>
       </c>
       <c r="B3001" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C3001" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D3001" s="1" t="inlineStr">
@@ -69427,16 +69427,16 @@
     </row>
     <row r="3002">
       <c r="A3002" s="1" t="n">
-        <v>9000076</v>
+        <v>9000075</v>
       </c>
       <c r="B3002" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C3002" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D3002" s="1" t="inlineStr">
@@ -69449,21 +69449,21 @@
     </row>
     <row r="3003">
       <c r="A3003" s="1" t="n">
-        <v>9000077</v>
+        <v>9000076</v>
       </c>
       <c r="B3003" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C3003" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D3003" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E3003" s="1" t="n"/>
@@ -69471,16 +69471,16 @@
     </row>
     <row r="3004">
       <c r="A3004" s="1" t="n">
-        <v>9000078</v>
+        <v>9000077</v>
       </c>
       <c r="B3004" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C3004" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D3004" s="1" t="inlineStr">
@@ -69493,16 +69493,16 @@
     </row>
     <row r="3005">
       <c r="A3005" s="1" t="n">
-        <v>9000079</v>
+        <v>9000078</v>
       </c>
       <c r="B3005" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C3005" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D3005" s="1" t="inlineStr">
@@ -69515,16 +69515,16 @@
     </row>
     <row r="3006">
       <c r="A3006" s="1" t="n">
-        <v>9000080</v>
+        <v>9000079</v>
       </c>
       <c r="B3006" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C3006" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D3006" s="1" t="inlineStr">
@@ -69537,21 +69537,21 @@
     </row>
     <row r="3007">
       <c r="A3007" s="1" t="n">
-        <v>9000081</v>
+        <v>9000080</v>
       </c>
       <c r="B3007" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C3007" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D3007" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E3007" s="1" t="n"/>
@@ -69559,16 +69559,16 @@
     </row>
     <row r="3008">
       <c r="A3008" s="1" t="n">
-        <v>9000082</v>
+        <v>9000081</v>
       </c>
       <c r="B3008" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C3008" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D3008" s="1" t="inlineStr">
@@ -69581,21 +69581,21 @@
     </row>
     <row r="3009">
       <c r="A3009" s="1" t="n">
-        <v>9000083</v>
+        <v>9000082</v>
       </c>
       <c r="B3009" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C3009" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D3009" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E3009" s="1" t="n"/>
@@ -69603,16 +69603,16 @@
     </row>
     <row r="3010">
       <c r="A3010" s="1" t="n">
-        <v>9000084</v>
+        <v>9000083</v>
       </c>
       <c r="B3010" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>헉헉</t>
         </is>
       </c>
       <c r="C3010" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>Huff puff</t>
         </is>
       </c>
       <c r="D3010" s="1" t="inlineStr">
@@ -69625,16 +69625,16 @@
     </row>
     <row r="3011">
       <c r="A3011" s="1" t="n">
-        <v>9000085</v>
+        <v>9000084</v>
       </c>
       <c r="B3011" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>더 빨리!</t>
         </is>
       </c>
       <c r="C3011" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>Faster!</t>
         </is>
       </c>
       <c r="D3011" s="1" t="inlineStr">
@@ -69647,16 +69647,16 @@
     </row>
     <row r="3012">
       <c r="A3012" s="1" t="n">
-        <v>9000086</v>
+        <v>9000085</v>
       </c>
       <c r="B3012" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>근육 붙는 중</t>
         </is>
       </c>
       <c r="C3012" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>Gains incoming</t>
         </is>
       </c>
       <c r="D3012" s="1" t="inlineStr">
@@ -69669,21 +69669,21 @@
     </row>
     <row r="3013">
       <c r="A3013" s="1" t="n">
-        <v>9000087</v>
+        <v>9000086</v>
       </c>
       <c r="B3013" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>찍찍찍찍</t>
         </is>
       </c>
       <c r="C3013" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>Squeak squeak squeak squeak</t>
         </is>
       </c>
       <c r="D3013" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E3013" s="1" t="n"/>
@@ -69691,16 +69691,16 @@
     </row>
     <row r="3014">
       <c r="A3014" s="1" t="n">
-        <v>9000088</v>
+        <v>9000087</v>
       </c>
       <c r="B3014" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>으아아아~!</t>
         </is>
       </c>
       <c r="C3014" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>Waaaaah~!</t>
         </is>
       </c>
       <c r="D3014" s="1" t="inlineStr">
@@ -69713,16 +69713,16 @@
     </row>
     <row r="3015">
       <c r="A3015" s="1" t="n">
-        <v>9000089</v>
+        <v>9000088</v>
       </c>
       <c r="B3015" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>하암~ 잘 잤다</t>
         </is>
       </c>
       <c r="C3015" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>Yawn~ what a nap</t>
         </is>
       </c>
       <c r="D3015" s="1" t="inlineStr">
@@ -69735,16 +69735,16 @@
     </row>
     <row r="3016">
       <c r="A3016" s="1" t="n">
-        <v>9000090</v>
+        <v>9000089</v>
       </c>
       <c r="B3016" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>냠, 배부르다</t>
         </is>
       </c>
       <c r="C3016" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>Nom, so full</t>
         </is>
       </c>
       <c r="D3016" s="1" t="inlineStr">
@@ -69757,21 +69757,21 @@
     </row>
     <row r="3017">
       <c r="A3017" s="1" t="n">
-        <v>9000091</v>
+        <v>9000090</v>
       </c>
       <c r="B3017" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>휴…</t>
         </is>
       </c>
       <c r="C3017" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Phew...</t>
         </is>
       </c>
       <c r="D3017" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E3017" s="1" t="n"/>
@@ -69779,21 +69779,21 @@
     </row>
     <row r="3018">
       <c r="A3018" s="1" t="n">
-        <v>9000092</v>
+        <v>9000091</v>
       </c>
       <c r="B3018" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>찍</t>
         </is>
       </c>
       <c r="C3018" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Squeak</t>
         </is>
       </c>
       <c r="D3018" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
         </is>
       </c>
       <c r="E3018" s="1" t="n"/>
@@ -69801,21 +69801,21 @@
     </row>
     <row r="3019">
       <c r="A3019" s="1" t="n">
-        <v>9000093</v>
+        <v>9000092</v>
       </c>
       <c r="B3019" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C3019" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D3019" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Lobby/RunPage.cs:99</t>
         </is>
       </c>
       <c r="E3019" s="1" t="n"/>
@@ -69823,21 +69823,21 @@
     </row>
     <row r="3020">
       <c r="A3020" s="1" t="n">
-        <v>9000094</v>
+        <v>9000093</v>
       </c>
       <c r="B3020" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="C3020" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D3020" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
         </is>
       </c>
       <c r="E3020" s="1" t="n"/>
@@ -69845,16 +69845,16 @@
     </row>
     <row r="3021">
       <c r="A3021" s="1" t="n">
-        <v>9000095</v>
+        <v>9000094</v>
       </c>
       <c r="B3021" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>찌릿!!</t>
         </is>
       </c>
       <c r="C3021" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>ZAP!!</t>
         </is>
       </c>
       <c r="D3021" s="1" t="inlineStr">
@@ -69867,21 +69867,21 @@
     </row>
     <row r="3022">
       <c r="A3022" s="1" t="n">
-        <v>9000096</v>
+        <v>9000095</v>
       </c>
       <c r="B3022" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>콰릉!</t>
         </is>
       </c>
       <c r="C3022" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>Ka-boom!</t>
         </is>
       </c>
       <c r="D3022" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E3022" s="1" t="n"/>
@@ -69889,16 +69889,16 @@
     </row>
     <row r="3023">
       <c r="A3023" s="1" t="n">
-        <v>9000097</v>
+        <v>9000096</v>
       </c>
       <c r="B3023" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>냠!</t>
         </is>
       </c>
       <c r="C3023" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>Nom!</t>
         </is>
       </c>
       <c r="D3023" s="1" t="inlineStr">
@@ -69911,21 +69911,21 @@
     </row>
     <row r="3024">
       <c r="A3024" s="1" t="n">
-        <v>9000098</v>
+        <v>9000097</v>
       </c>
       <c r="B3024" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>다닥!</t>
         </is>
       </c>
       <c r="C3024" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>Scurry!</t>
         </is>
       </c>
       <c r="D3024" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E3024" s="1" t="n"/>
@@ -69933,16 +69933,16 @@
     </row>
     <row r="3025">
       <c r="A3025" s="1" t="n">
-        <v>9000099</v>
+        <v>9000098</v>
       </c>
       <c r="B3025" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>메리 쥐스마스!</t>
         </is>
       </c>
       <c r="C3025" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>Merry Ratmas!</t>
         </is>
       </c>
       <c r="D3025" s="1" t="inlineStr">
@@ -69955,16 +69955,16 @@
     </row>
     <row r="3026">
       <c r="A3026" s="1" t="n">
-        <v>9000100</v>
+        <v>9000099</v>
       </c>
       <c r="B3026" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>흐에~ 후원 감사합니다~!</t>
         </is>
       </c>
       <c r="C3026" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>Heheh~ thanks for the dono~!</t>
         </is>
       </c>
       <c r="D3026" s="1" t="inlineStr">
@@ -69977,21 +69977,21 @@
     </row>
     <row r="3027">
       <c r="A3027" s="1" t="n">
-        <v>9000101</v>
+        <v>9000100</v>
       </c>
       <c r="B3027" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>배달 왔습니다~</t>
         </is>
       </c>
       <c r="C3027" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>Delivery~!</t>
         </is>
       </c>
       <c r="D3027" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E3027" s="1" t="n"/>
@@ -69999,16 +69999,16 @@
     </row>
     <row r="3028">
       <c r="A3028" s="1" t="n">
-        <v>9000102</v>
+        <v>9000101</v>
       </c>
       <c r="B3028" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>백덤블링!</t>
         </is>
       </c>
       <c r="C3028" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>Backflip!</t>
         </is>
       </c>
       <c r="D3028" s="1" t="inlineStr">
@@ -70021,16 +70021,16 @@
     </row>
     <row r="3029">
       <c r="A3029" s="1" t="n">
-        <v>9000103</v>
+        <v>9000102</v>
       </c>
       <c r="B3029" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>공중제비!</t>
         </is>
       </c>
       <c r="C3029" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Somersault!</t>
         </is>
       </c>
       <c r="D3029" s="1" t="inlineStr">
@@ -70043,21 +70043,21 @@
     </row>
     <row r="3030">
       <c r="A3030" s="1" t="n">
-        <v>9000104</v>
+        <v>9000103</v>
       </c>
       <c r="B3030" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>찍-공중회전!</t>
         </is>
       </c>
       <c r="C3030" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Squeak-flip!</t>
         </is>
       </c>
       <c r="D3030" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E3030" s="1" t="n"/>
@@ -70065,16 +70065,16 @@
     </row>
     <row r="3031">
       <c r="A3031" s="1" t="n">
-        <v>9000105</v>
+        <v>9000104</v>
       </c>
       <c r="B3031" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>트리플 악셀!!</t>
         </is>
       </c>
       <c r="C3031" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>TRIPLE AXEL!!</t>
         </is>
       </c>
       <c r="D3031" s="1" t="inlineStr">
@@ -70087,16 +70087,16 @@
     </row>
     <row r="3032">
       <c r="A3032" s="1" t="n">
-        <v>9000106</v>
+        <v>9000105</v>
       </c>
       <c r="B3032" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>3회전 성공!</t>
         </is>
       </c>
       <c r="C3032" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>Triple spin landed!</t>
         </is>
       </c>
       <c r="D3032" s="1" t="inlineStr">
@@ -70109,21 +70109,21 @@
     </row>
     <row r="3033">
       <c r="A3033" s="1" t="n">
-        <v>9000107</v>
+        <v>9000106</v>
       </c>
       <c r="B3033" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>심사위원 전원 10점!</t>
         </is>
       </c>
       <c r="C3033" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>Perfect 10s from every judge!</t>
         </is>
       </c>
       <c r="D3033" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E3033" s="1" t="n"/>
@@ -70131,16 +70131,16 @@
     </row>
     <row r="3034">
       <c r="A3034" s="1" t="n">
-        <v>9000108</v>
+        <v>9000107</v>
       </c>
       <c r="B3034" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>윈드밀!!</t>
         </is>
       </c>
       <c r="C3034" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>WINDMILL!!</t>
         </is>
       </c>
       <c r="D3034" s="1" t="inlineStr">
@@ -70153,16 +70153,16 @@
     </row>
     <row r="3035">
       <c r="A3035" s="1" t="n">
-        <v>9000109</v>
+        <v>9000108</v>
       </c>
       <c r="B3035" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>브레이크 댄스!</t>
         </is>
       </c>
       <c r="C3035" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>Breakdance!</t>
         </is>
       </c>
       <c r="D3035" s="1" t="inlineStr">
@@ -70175,21 +70175,21 @@
     </row>
     <row r="3036">
       <c r="A3036" s="1" t="n">
-        <v>9000110</v>
+        <v>9000109</v>
       </c>
       <c r="B3036" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>빙글빙글 파괴!</t>
         </is>
       </c>
       <c r="C3036" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>Spin-to-win destruction!</t>
         </is>
       </c>
       <c r="D3036" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E3036" s="1" t="n"/>
@@ -70197,16 +70197,16 @@
     </row>
     <row r="3037">
       <c r="A3037" s="1" t="n">
-        <v>9000111</v>
+        <v>9000110</v>
       </c>
       <c r="B3037" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>쥐 대포알!</t>
         </is>
       </c>
       <c r="C3037" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>Rat Cannonball!</t>
         </is>
       </c>
       <c r="D3037" s="1" t="inlineStr">
@@ -70219,16 +70219,16 @@
     </row>
     <row r="3038">
       <c r="A3038" s="1" t="n">
-        <v>9000112</v>
+        <v>9000111</v>
       </c>
       <c r="B3038" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>데굴데굴!</t>
         </is>
       </c>
       <c r="C3038" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>Roll roll!</t>
         </is>
       </c>
       <c r="D3038" s="1" t="inlineStr">
@@ -70241,21 +70241,21 @@
     </row>
     <row r="3039">
       <c r="A3039" s="1" t="n">
-        <v>9000113</v>
+        <v>9000112</v>
       </c>
       <c r="B3039" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>핀볼 모드!</t>
         </is>
       </c>
       <c r="C3039" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>Pinball mode!</t>
         </is>
       </c>
       <c r="D3039" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E3039" s="1" t="n"/>
@@ -70263,16 +70263,16 @@
     </row>
     <row r="3040">
       <c r="A3040" s="1" t="n">
-        <v>9000114</v>
+        <v>9000113</v>
       </c>
       <c r="B3040" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>쳇바퀴 돌기!!</t>
         </is>
       </c>
       <c r="C3040" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>WHEEL SPIN!!</t>
         </is>
       </c>
       <c r="D3040" s="1" t="inlineStr">
@@ -70285,16 +70285,16 @@
     </row>
     <row r="3041">
       <c r="A3041" s="1" t="n">
-        <v>9000115</v>
+        <v>9000114</v>
       </c>
       <c r="B3041" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>빙글빙글~</t>
         </is>
       </c>
       <c r="C3041" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>Round and round~</t>
         </is>
       </c>
       <c r="D3041" s="1" t="inlineStr">
@@ -70307,21 +70307,21 @@
     </row>
     <row r="3042">
       <c r="A3042" s="1" t="n">
-        <v>9000116</v>
+        <v>9000115</v>
       </c>
       <c r="B3042" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>어지러워!!</t>
         </is>
       </c>
       <c r="C3042" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>So DIZZY!!</t>
         </is>
       </c>
       <c r="D3042" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E3042" s="1" t="n"/>
@@ -70329,21 +70329,21 @@
     </row>
     <row r="3043">
       <c r="A3043" s="1" t="n">
-        <v>9000117</v>
+        <v>9000116</v>
       </c>
       <c r="B3043" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="C3043" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="D3043" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
         </is>
       </c>
       <c r="E3043" s="1" t="n"/>
@@ -70351,21 +70351,21 @@
     </row>
     <row r="3044">
       <c r="A3044" s="1" t="n">
-        <v>9000118</v>
+        <v>9000117</v>
       </c>
       <c r="B3044" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>기절!!</t>
         </is>
       </c>
       <c r="C3044" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>Stunned!!</t>
         </is>
       </c>
       <c r="D3044" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Rats/RatManager.cs:38</t>
         </is>
       </c>
       <c r="E3044" s="1" t="n"/>
@@ -70373,21 +70373,21 @@
     </row>
     <row r="3045">
       <c r="A3045" s="1" t="n">
-        <v>9000119</v>
+        <v>9000118</v>
       </c>
       <c r="B3045" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>소품이 떨어졌다!</t>
         </is>
       </c>
       <c r="C3045" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>A prop dropped!</t>
         </is>
       </c>
       <c r="D3045" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Rats/RatManager.cs:397</t>
         </is>
       </c>
       <c r="E3045" s="1" t="n"/>
@@ -70395,21 +70395,21 @@
     </row>
     <row r="3046">
       <c r="A3046" s="1" t="n">
-        <v>9000120</v>
+        <v>9000119</v>
       </c>
       <c r="B3046" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>조각 +1</t>
         </is>
       </c>
       <c r="C3046" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>Shard +1</t>
         </is>
       </c>
       <c r="D3046" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Rats/RatManager.cs:460</t>
         </is>
       </c>
       <c r="E3046" s="1" t="n"/>
@@ -70417,21 +70417,21 @@
     </row>
     <row r="3047">
       <c r="A3047" s="1" t="n">
-        <v>9000121</v>
+        <v>9000120</v>
       </c>
       <c r="B3047" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>{name} 강화! Lv {lv}</t>
         </is>
       </c>
       <c r="C3047" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>{name} powered up! Lv {lv}</t>
         </is>
       </c>
       <c r="D3047" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Rats/RatManager.cs:461</t>
         </is>
       </c>
       <c r="E3047" s="1" t="n"/>
@@ -70439,21 +70439,21 @@
     </row>
     <row r="3048">
       <c r="A3048" s="1" t="n">
-        <v>9000122</v>
+        <v>9000121</v>
       </c>
       <c r="B3048" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>{grade} 탄생!</t>
         </is>
       </c>
       <c r="C3048" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>{grade} born!</t>
         </is>
       </c>
       <c r="D3048" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Rats/RatManager.cs:561</t>
         </is>
       </c>
       <c r="E3048" s="1" t="n"/>
@@ -70461,21 +70461,21 @@
     </row>
     <row r="3049">
       <c r="A3049" s="1" t="n">
-        <v>9000123</v>
+        <v>9000122</v>
       </c>
       <c r="B3049" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>쌍둥이!</t>
         </is>
       </c>
       <c r="C3049" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>Twins!</t>
         </is>
       </c>
       <c r="D3049" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Rats/RatManager.cs:566</t>
         </is>
       </c>
       <c r="E3049" s="1" t="n"/>
@@ -70483,21 +70483,21 @@
     </row>
     <row r="3050">
       <c r="A3050" s="1" t="n">
-        <v>9000124</v>
+        <v>9000123</v>
       </c>
       <c r="B3050" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>치즈 운석!</t>
         </is>
       </c>
       <c r="C3050" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>Cheese Meteor!</t>
         </is>
       </c>
       <c r="D3050" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:627</t>
         </is>
       </c>
       <c r="E3050" s="1" t="n"/>
@@ -70505,21 +70505,21 @@
     </row>
     <row r="3051">
       <c r="A3051" s="1" t="n">
-        <v>9000125</v>
+        <v>9000124</v>
       </c>
       <c r="B3051" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>{floor}층 · {zone}</t>
         </is>
       </c>
       <c r="C3051" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>Floor {floor} · {zone}</t>
         </is>
       </c>
       <c r="D3051" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E3051" s="1" t="n"/>
@@ -70527,21 +70527,21 @@
     </row>
     <row r="3052">
       <c r="A3052" s="1" t="n">
-        <v>9000126</v>
+        <v>9000125</v>
       </c>
       <c r="B3052" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>계단 방 벽을 부숴라!</t>
         </is>
       </c>
       <c r="C3052" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>Smash the wall to the stairs room!</t>
         </is>
       </c>
       <c r="D3052" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E3052" s="1" t="n"/>
@@ -70549,21 +70549,21 @@
     </row>
     <row r="3053">
       <c r="A3053" s="1" t="n">
-        <v>9000127</v>
+        <v>9000126</v>
       </c>
       <c r="B3053" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>벽 붕괴! 방 확장</t>
         </is>
       </c>
       <c r="C3053" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>Wall down! Room expanded</t>
         </is>
       </c>
       <c r="D3053" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E3053" s="1" t="n"/>
@@ -70571,16 +70571,16 @@
     </row>
     <row r="3054">
       <c r="A3054" s="1" t="n">
-        <v>9000128</v>
+        <v>9000127</v>
       </c>
       <c r="B3054" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>계단 발견!</t>
         </is>
       </c>
       <c r="C3054" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>Stairs found!</t>
         </is>
       </c>
       <c r="D3054" s="1" t="inlineStr">
@@ -70593,21 +70593,21 @@
     </row>
     <row r="3055">
       <c r="A3055" s="1" t="n">
-        <v>9000129</v>
+        <v>9000128</v>
       </c>
       <c r="B3055" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>계단에 닿으면 {next}층으로</t>
         </is>
       </c>
       <c r="C3055" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>Touch the stairs to go to Floor {next}</t>
         </is>
       </c>
       <c r="D3055" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:338</t>
         </is>
       </c>
       <c r="E3055" s="1" t="n"/>
@@ -70615,16 +70615,16 @@
     </row>
     <row r="3056">
       <c r="A3056" s="1" t="n">
-        <v>9000130</v>
+        <v>9000129</v>
       </c>
       <c r="B3056" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>와르르!!</t>
         </is>
       </c>
       <c r="C3056" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Crumble!!</t>
         </is>
       </c>
       <c r="D3056" s="1" t="inlineStr">
@@ -70637,16 +70637,16 @@
     </row>
     <row r="3057">
       <c r="A3057" s="1" t="n">
-        <v>9000131</v>
+        <v>9000130</v>
       </c>
       <c r="B3057" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>콰광!!</t>
         </is>
       </c>
       <c r="C3057" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>KA-BOOM!!</t>
         </is>
       </c>
       <c r="D3057" s="1" t="inlineStr">
@@ -70656,6 +70656,28 @@
       </c>
       <c r="E3057" s="1" t="n"/>
       <c r="F3057" s="1" t="n"/>
+    </row>
+    <row r="3058">
+      <c r="A3058" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B3058" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C3058" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D3058" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3058" s="1" t="n"/>
+      <c r="F3058" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3205"/>
+  <dimension ref="A1:F3206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -74592,6 +74592,26 @@
       </c>
       <c r="E3205" s="1" t="n"/>
       <c r="F3205" s="1" t="n"/>
+    </row>
+    <row r="3206">
+      <c r="A3206" t="n">
+        <v>9000132</v>
+      </c>
+      <c r="B3206" t="inlineStr">
+        <is>
+          <t>※ 출발 층은 스킬만으로 다 열리지 않아요 · 층을 클리어해야 더 위에서 출발할 수 있어요 (출동 화면에 안내)</t>
+        </is>
+      </c>
+      <c r="C3206" t="inlineStr">
+        <is>
+          <t>※ Skip needs cleared floors too · clear floors to start higher (shown on the Run screen)</t>
+        </is>
+      </c>
+      <c r="D3206" t="inlineStr">
+        <is>
+          <t>코드 · SkillPage.DrawDetail (Stage_Skip 노드)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3190"/>
+  <dimension ref="A1:F3215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -74198,6 +74198,506 @@
       </c>
       <c r="E3190" s="1" t="n"/>
       <c r="F3190" s="1" t="n"/>
+    </row>
+    <row r="3191">
+      <c r="A3191" t="n">
+        <v>8000405</v>
+      </c>
+      <c r="B3191" t="inlineStr">
+        <is>
+          <t>최고 층</t>
+        </is>
+      </c>
+      <c r="C3191" t="inlineStr">
+        <is>
+          <t>Best Floor</t>
+        </is>
+      </c>
+      <c r="D3191" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Header/Floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3192">
+      <c r="A3192" t="n">
+        <v>8000406</v>
+      </c>
+      <c r="B3192" t="inlineStr">
+        <is>
+          <t>닉네임 바꾸기</t>
+        </is>
+      </c>
+      <c r="C3192" t="inlineStr">
+        <is>
+          <t>Change Nickname</t>
+        </is>
+      </c>
+      <c r="D3192" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/NickButton/Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" t="n">
+        <v>8000407</v>
+      </c>
+      <c r="B3193" t="inlineStr">
+        <is>
+          <t>바꾸기</t>
+        </is>
+      </c>
+      <c r="C3193" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D3193" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_rec/Card/ServerRows/Row_닉네임/NickButton/Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="3194">
+      <c r="A3194" t="n">
+        <v>8000408</v>
+      </c>
+      <c r="B3194" t="inlineStr">
+        <is>
+          <t>닉네임 입력</t>
+        </is>
+      </c>
+      <c r="C3194" t="inlineStr">
+        <is>
+          <t>Enter nickname</t>
+        </is>
+      </c>
+      <c r="D3194" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/Input/Text Area/Placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="3195">
+      <c r="A3195" t="n">
+        <v>8000409</v>
+      </c>
+      <c r="B3195" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C3195" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="D3195" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Header/Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="3196">
+      <c r="A3196" t="n">
+        <v>8000410</v>
+      </c>
+      <c r="B3196" t="inlineStr">
+        <is>
+          <t>닉네임 정하기</t>
+        </is>
+      </c>
+      <c r="C3196" t="inlineStr">
+        <is>
+          <t>Choose a Nickname</t>
+        </is>
+      </c>
+      <c r="D3196" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="3197">
+      <c r="A3197" t="n">
+        <v>8000411</v>
+      </c>
+      <c r="B3197" t="inlineStr">
+        <is>
+          <t>아직 랭킹에 오른 쥐가 없어요. 첫 번째가 되어 보세요!</t>
+        </is>
+      </c>
+      <c r="C3197" t="inlineStr">
+        <is>
+          <t>No rats on the board yet. Be the first!</t>
+        </is>
+      </c>
+      <c r="D3197" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Scroll/Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="3198">
+      <c r="A3198" t="n">
+        <v>8000412</v>
+      </c>
+      <c r="B3198" t="inlineStr">
+        <is>
+          <t>훈장</t>
+        </is>
+      </c>
+      <c r="C3198" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="D3198" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Header/Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="3199">
+      <c r="A3199" t="n">
+        <v>8000413</v>
+      </c>
+      <c r="B3199" t="inlineStr">
+        <is>
+          <t>아직 없음</t>
+        </is>
+      </c>
+      <c r="C3199" t="inlineStr">
+        <is>
+          <t>Not set</t>
+        </is>
+      </c>
+      <c r="D3199" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_rec/Card/ServerRows/Row_닉네임/NoNick</t>
+        </is>
+      </c>
+    </row>
+    <row r="3200">
+      <c r="A3200" t="n">
+        <v>8000414</v>
+      </c>
+      <c r="B3200" t="inlineStr">
+        <is>
+          <t>시도</t>
+        </is>
+      </c>
+      <c r="C3200" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="D3200" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Header/Runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3201">
+      <c r="A3201" t="n">
+        <v>8000415</v>
+      </c>
+      <c r="B3201" t="inlineStr">
+        <is>
+          <t>닉네임</t>
+        </is>
+      </c>
+      <c r="C3201" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
+      <c r="D3201" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_rec/Card/ServerRows/Row_닉네임/Label | Lobby · UI/Prep/Body/Page_lb/Card/Header/Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="3202">
+      <c r="A3202" t="n">
+        <v>8000416</v>
+      </c>
+      <c r="B3202" t="inlineStr">
+        <is>
+          <t>불러오는 중...</t>
+        </is>
+      </c>
+      <c r="C3202" t="inlineStr">
+        <is>
+          <t>Loading...</t>
+        </is>
+      </c>
+      <c r="D3202" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Scroll/Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="3203">
+      <c r="A3203" t="n">
+        <v>8000417</v>
+      </c>
+      <c r="B3203" t="inlineStr">
+        <is>
+          <t>랭킹에 보일 이름이에요 (2~12자)</t>
+        </is>
+      </c>
+      <c r="C3203" t="inlineStr">
+        <is>
+          <t>The name shown on the leaderboard (2-12 characters)</t>
+        </is>
+      </c>
+      <c r="D3203" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3204">
+      <c r="A3204" t="n">
+        <v>8000418</v>
+      </c>
+      <c r="B3204" t="inlineStr">
+        <is>
+          <t>지금은 서버에 연결할 수 없어요</t>
+        </is>
+      </c>
+      <c r="C3204" t="inlineStr">
+        <is>
+          <t>Can't reach the server right now</t>
+        </is>
+      </c>
+      <c r="D3204" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/ErrOffline</t>
+        </is>
+      </c>
+    </row>
+    <row r="3205">
+      <c r="A3205" t="n">
+        <v>8000419</v>
+      </c>
+      <c r="B3205" t="inlineStr">
+        <is>
+          <t>새로고침</t>
+        </is>
+      </c>
+      <c r="C3205" t="inlineStr">
+        <is>
+          <t>Refresh</t>
+        </is>
+      </c>
+      <c r="D3205" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/RefreshButton/Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="3206">
+      <c r="A3206" t="n">
+        <v>8000420</v>
+      </c>
+      <c r="B3206" t="inlineStr">
+        <is>
+          <t>랭킹</t>
+        </is>
+      </c>
+      <c r="C3206" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="D3206" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · LobbyManager · LobbyManager.pages[8].label | Lobby · UI/Prep/Body/Page_lb/Card/Title | Lobby · UI/Prep/TopBar/Tabs/Tab_lb/Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="3207">
+      <c r="A3207" t="n">
+        <v>8000421</v>
+      </c>
+      <c r="B3207" t="inlineStr">
+        <is>
+          <t>랭킹을 불러오지 못했어요. 인터넷 연결을 확인해 주세요.</t>
+        </is>
+      </c>
+      <c r="C3207" t="inlineStr">
+        <is>
+          <t>Couldn't load the leaderboard. Please check your connection.</t>
+        </is>
+      </c>
+      <c r="D3207" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Scroll/Offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="3208">
+      <c r="A3208" t="n">
+        <v>8000422</v>
+      </c>
+      <c r="B3208" t="inlineStr">
+        <is>
+          <t>{n}회</t>
+        </is>
+      </c>
+      <c r="C3208" t="inlineStr">
+        <is>
+          <t>{n}</t>
+        </is>
+      </c>
+      <c r="D3208" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/MyRow/Runs | Lobby · UI/Prep/Body/Page_lb/Card/Scroll/Viewport/Content/RowTemplate/Runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3209">
+      <c r="A3209" t="n">
+        <v>8000423</v>
+      </c>
+      <c r="B3209" t="inlineStr">
+        <is>
+          <t>최고 층이 높은 순 · 같은 층이면 더 적은 시도로 닿은 순</t>
+        </is>
+      </c>
+      <c r="C3209" t="inlineStr">
+        <is>
+          <t>Highest floor first · ties go to fewer runs</t>
+        </is>
+      </c>
+      <c r="D3209" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/Sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="3210">
+      <c r="A3210" t="n">
+        <v>8000424</v>
+      </c>
+      <c r="B3210" t="inlineStr">
+        <is>
+          <t>내 기록</t>
+        </is>
+      </c>
+      <c r="C3210" t="inlineStr">
+        <is>
+          <t>My Record</t>
+        </is>
+      </c>
+      <c r="D3210" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/MyLabel</t>
+        </is>
+      </c>
+    </row>
+    <row r="3211">
+      <c r="A3211" t="n">
+        <v>8000425</v>
+      </c>
+      <c r="B3211" t="inlineStr">
+        <is>
+          <t>익명 통계 보내기</t>
+        </is>
+      </c>
+      <c r="C3211" t="inlineStr">
+        <is>
+          <t>Send anonymous stats</t>
+        </is>
+      </c>
+      <c r="D3211" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_rec/Card/ServerRows/Row_통계/Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="3212">
+      <c r="A3212" t="n">
+        <v>8000426</v>
+      </c>
+      <c r="B3212" t="inlineStr">
+        <is>
+          <t>100위 밖</t>
+        </is>
+      </c>
+      <c r="C3212" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="D3212" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/OutWord</t>
+        </is>
+      </c>
+    </row>
+    <row r="3213">
+      <c r="A3213" t="n">
+        <v>8000427</v>
+      </c>
+      <c r="B3213" t="inlineStr">
+        <is>
+          <t>닉네임을 정하면 내 기록이 랭킹에 올라가요</t>
+        </is>
+      </c>
+      <c r="C3213" t="inlineStr">
+        <is>
+          <t>Set a nickname to put your record on the board</t>
+        </is>
+      </c>
+      <c r="D3213" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/Prep/Body/Page_lb/Card/NoNick</t>
+        </is>
+      </c>
+    </row>
+    <row r="3214">
+      <c r="A3214" t="n">
+        <v>8000428</v>
+      </c>
+      <c r="B3214" t="inlineStr">
+        <is>
+          <t>2~12자로 정해 주세요</t>
+        </is>
+      </c>
+      <c r="C3214" t="inlineStr">
+        <is>
+          <t>Use 2-12 characters</t>
+        </is>
+      </c>
+      <c r="D3214" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/ErrLength</t>
+        </is>
+      </c>
+    </row>
+    <row r="3215">
+      <c r="A3215" t="n">
+        <v>8000429</v>
+      </c>
+      <c r="B3215" t="inlineStr">
+        <is>
+          <t>쓸 수 없는 말이 들어 있어요</t>
+        </is>
+      </c>
+      <c r="C3215" t="inlineStr">
+        <is>
+          <t>That name contains a word we can't use</t>
+        </is>
+      </c>
+      <c r="D3215" t="inlineStr">
+        <is>
+          <t>씬 · Lobby · UI/NickPopup/Window/Card/ErrBanned</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3211"/>
+  <dimension ref="A1:F3261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -60213,7 +60213,7 @@
       </c>
       <c r="D2562" s="1" t="inlineStr">
         <is>
-          <t>씬 · Title · UI/Settings/Card/Close/Text | Lobby · UI/Prep/Body/Page_rats/TreePopup/Card/CloseButton/Label | Game · HUD/Promote/Panel/CloseButton/Label | Game · HUD/Roster/Panel/Card/CloseButton/Label 외 1곳</t>
+          <t>씬 · Title · UI/Settings/Card/Close/Text | Lobby · UI/Prep/Body/Page_rats/TreePopup/Card/CloseButton/Label | Lobby · UI/ArcadeWindow/Board/Close/Label | Game · HUD/Promote/Panel/CloseButton/Label 외 2곳</t>
         </is>
       </c>
       <c r="E2562" s="1" t="n"/>
@@ -60257,7 +60257,7 @@
       </c>
       <c r="D2564" s="1" t="inlineStr">
         <is>
-          <t>씬 · Title · UI/Menu/New/Text</t>
+          <t>씬 · Title · UI/Menu/New/Text | Lobby · UI/ArcadeWindow/Board/OvPause/Card/Retry/Label</t>
         </is>
       </c>
       <c r="E2564" s="1" t="n"/>
@@ -61015,7 +61015,7 @@
       </c>
       <c r="D2598" s="1" t="inlineStr">
         <is>
-          <t>씬 · Lobby · UI/Prep/Body/Page_rats/DetailCard/Grade/Text | Lobby · UI/Prep/Body/Page_rank/UnlockCard/Scroll/Viewport/Content/UnlockTemplate/Grade | Lobby · UI/Prep/Body/Page_run/CrewCard/Odds/OddsTemplate/Name | Lobby · UI/Prep/Body/Page_dex/DetailCard/Grade/Text</t>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Left/Row4/Name | Lobby · UI/Prep/Body/Page_rats/DetailCard/Grade/Text | Lobby · UI/ArcadeWindow/Board/Left/Row1/Name | Lobby · UI/ArcadeWindow/Board/Left/Row0/Name 외 6곳</t>
         </is>
       </c>
       <c r="E2598" s="1" t="n"/>
@@ -71327,7 +71327,7 @@
       </c>
       <c r="D3057" s="1" t="inlineStr">
         <is>
-          <t>씬 · Game · HUD/Roster/Panel/Card/Scroll/Viewport/Content/CardTemplate/Damage</t>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Left/Row0/Dmg | Lobby · UI/ArcadeWindow/Board/Left/Row2/Dmg | Lobby · UI/ArcadeWindow/Board/Left/Row4/Dmg | Lobby · UI/ArcadeWindow/Board/Left/Row1/Dmg 외 3곳</t>
         </is>
       </c>
       <c r="E3057" s="1" t="n"/>
@@ -71831,1121 +71831,1331 @@
     </row>
     <row r="3080">
       <c r="A3080" s="1" t="n">
-        <v>9000001</v>
+        <v>8000554</v>
       </c>
       <c r="B3080" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power}</t>
+          <t>유니크 이상 스킬: 발사마다 첫 타격 + 이후 {rates}</t>
         </is>
       </c>
       <c r="C3080" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power}</t>
+          <t>Unique+ skill: first hit each launch + then {rates}</t>
         </is>
       </c>
       <c r="D3080" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
-        </is>
-      </c>
-      <c r="E3080" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Left/SkillNote</t>
+        </is>
+      </c>
+      <c r="E3080" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3080" s="1" t="n"/>
     </row>
     <row r="3081">
       <c r="A3081" s="1" t="n">
-        <v>9000002</v>
+        <v>8000555</v>
       </c>
       <c r="B3081" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>쥐를 새총처럼 끌었다 놓으면 가진 쥐가 &lt;b&gt;전부 줄지어&lt;/b&gt; 날아가 연구소 벽돌을 튕기며 깎습니다. 벽돌 숫자 = 남은 체력.
+처음 바닥에 닿은 쥐 자리에서 다음 발사. 한 턴이 끝나면 벽돌이 한 줄씩 내려오고, &lt;b&gt;바닥에 닿으면 끝&lt;/b&gt;. 받침대는 없어요 — 첫 발사 각도가 전부!
+벽돌을 부수면 치즈 → &lt;b&gt;쥐 뽑기(10 치즈)&lt;/b&gt;로 쥐를 늘리고, 쥐를 재료로 &lt;b&gt;증강 뽑기&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C3081" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>Pull a rat like a slingshot and release — &lt;b&gt;all your rats fly in a line&lt;/b&gt;, bouncing off the lab bricks. Brick number = HP left.
+The next launch starts where the first rat landed. After each turn the bricks drop one row — &lt;b&gt;if they reach the floor, it's over&lt;/b&gt;. No paddle — the first angle is everything!
+Break bricks for cheese → &lt;b&gt;Rat Draw (10 cheese)&lt;/b&gt; for more rats, then spend rats on &lt;b&gt;Augment Draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="D3081" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
-        </is>
-      </c>
-      <c r="E3081" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvTitle/Card/Body</t>
+        </is>
+      </c>
+      <c r="E3081" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3081" s="1" t="n"/>
     </row>
     <row r="3082">
       <c r="A3082" s="1" t="n">
-        <v>9000003</v>
+        <v>8000556</v>
       </c>
       <c r="B3082" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>최고 {n}</t>
         </is>
       </c>
       <c r="C3082" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>Best {n}</t>
         </is>
       </c>
       <c r="D3082" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
-        </is>
-      </c>
-      <c r="E3082" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Right/Best</t>
+        </is>
+      </c>
+      <c r="E3082" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3082" s="1" t="n"/>
     </row>
     <row r="3083">
       <c r="A3083" s="1" t="n">
-        <v>9000004</v>
+        <v>8000557</v>
       </c>
       <c r="B3083" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>계속</t>
         </is>
       </c>
       <c r="C3083" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="D3083" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
-        </is>
-      </c>
-      <c r="E3083" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvPause/Card/Resume/Label</t>
+        </is>
+      </c>
+      <c r="E3083" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3083" s="1" t="n"/>
     </row>
     <row r="3084">
       <c r="A3084" s="1" t="n">
-        <v>9000005</v>
+        <v>8000558</v>
       </c>
       <c r="B3084" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>증강 {n}개</t>
         </is>
       </c>
       <c r="C3084" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>Augments {n}</t>
         </is>
       </c>
       <c r="D3084" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
-        </is>
-      </c>
-      <c r="E3084" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Right/AugCount</t>
+        </is>
+      </c>
+      <c r="E3084" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3084" s="1" t="n"/>
     </row>
     <row r="3085">
       <c r="A3085" s="1" t="n">
-        <v>9000006</v>
+        <v>8000559</v>
       </c>
       <c r="B3085" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>벽돌이 바닥에 닿았어요!</t>
         </is>
       </c>
       <c r="C3085" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>The bricks hit the floor!</t>
         </is>
       </c>
       <c r="D3085" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
-        </is>
-      </c>
-      <c r="E3085" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvOver/Card/Title</t>
+        </is>
+      </c>
+      <c r="E3085" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3085" s="1" t="n"/>
     </row>
     <row r="3086">
       <c r="A3086" s="1" t="n">
-        <v>9000007</v>
+        <v>8000560</v>
       </c>
       <c r="B3086" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>경기장 아무 곳이나 끌었다 놓아 발사</t>
         </is>
       </c>
       <c r="C3086" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>Drag anywhere on the field and release to launch</t>
         </is>
       </c>
       <c r="D3086" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
-        </is>
-      </c>
-      <c r="E3086" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Right/AimHint</t>
+        </is>
+      </c>
+      <c r="E3086" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3086" s="1" t="n"/>
     </row>
     <row r="3087">
       <c r="A3087" s="1" t="n">
-        <v>9000008</v>
+        <v>8000561</v>
       </c>
       <c r="B3087" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>· 스킬</t>
         </is>
       </c>
       <c r="C3087" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>· Skill</t>
         </is>
       </c>
       <c r="D3087" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
-        </is>
-      </c>
-      <c r="E3087" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Left/Row1/Skill | Lobby · UI/ArcadeWindow/Board/Left/Row5/Skill | Lobby · UI/ArcadeWindow/Board/Left/Row4/Skill | Lobby · UI/ArcadeWindow/Board/Left/Row2/Skill 외 2곳</t>
+        </is>
+      </c>
+      <c r="E3087" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3087" s="1" t="n"/>
     </row>
     <row r="3088">
       <c r="A3088" s="1" t="n">
-        <v>9000009</v>
+        <v>8000562</v>
       </c>
       <c r="B3088" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>일시정지</t>
         </is>
       </c>
       <c r="C3088" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>Paused</t>
         </is>
       </c>
       <c r="D3088" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
-        </is>
-      </c>
-      <c r="E3088" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvPause/Card/Title</t>
+        </is>
+      </c>
+      <c r="E3088" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3088" s="1" t="n"/>
     </row>
     <row r="3089">
       <c r="A3089" s="1" t="n">
-        <v>9000010</v>
+        <v>8000563</v>
       </c>
       <c r="B3089" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>도달한 턴 &lt;b&gt;{turn}&lt;/b&gt; (최고 {best})
+부순 벽돌 {broken} · 모은 치즈 {cheese} · 쥐 {rats}마리 · 가장 높은 등급 {grade} · 증강 {augs}개</t>
         </is>
       </c>
       <c r="C3089" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>Reached turn &lt;b&gt;{turn}&lt;/b&gt; (Best {best})
+Bricks broken {broken} · Cheese earned {cheese} · Rats {rats} · Top grade {grade} · Augments {augs}</t>
         </is>
       </c>
       <c r="D3089" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
-        </is>
-      </c>
-      <c r="E3089" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvOver/Card/Body</t>
+        </is>
+      </c>
+      <c r="E3089" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3089" s="1" t="n"/>
     </row>
     <row r="3090">
       <c r="A3090" s="1" t="n">
-        <v>9000011</v>
+        <v>8000564</v>
       </c>
       <c r="B3090" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>쥐가 {n}마리 이상 필요</t>
         </is>
       </c>
       <c r="C3090" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>Need {n}+ rats</t>
         </is>
       </c>
       <c r="D3090" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
-        </is>
-      </c>
-      <c r="E3090" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Right/Aug/SubNeed</t>
+        </is>
+      </c>
+      <c r="E3090" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3090" s="1" t="n"/>
     </row>
     <row r="3091">
       <c r="A3091" s="1" t="n">
-        <v>9000012</v>
+        <v>8000565</v>
       </c>
       <c r="B3091" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>보유 쥐 {n}마리</t>
         </is>
       </c>
       <c r="C3091" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>Rats {n}</t>
         </is>
       </c>
       <c r="D3091" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
-        </is>
-      </c>
-      <c r="E3091" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Left/Owned</t>
+        </is>
+      </c>
+      <c r="E3091" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3091" s="1" t="n"/>
     </row>
     <row r="3092">
       <c r="A3092" s="1" t="n">
-        <v>9000013</v>
+        <v>8000566</v>
       </c>
       <c r="B3092" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>{list} 사용</t>
         </is>
       </c>
       <c r="C3092" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>Uses {list}</t>
         </is>
       </c>
       <c r="D3092" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
-        </is>
-      </c>
-      <c r="E3092" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Right/Aug/SubUse</t>
+        </is>
+      </c>
+      <c r="E3092" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3092" s="1" t="n"/>
     </row>
     <row r="3093">
       <c r="A3093" s="1" t="n">
-        <v>9000014</v>
+        <v>8000567</v>
       </c>
       <c r="B3093" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>쥐돌깨기</t>
         </is>
       </c>
       <c r="C3093" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>Rat Breaker</t>
         </is>
       </c>
       <c r="D3093" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
-        </is>
-      </c>
-      <c r="E3093" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvTitle/Card/Title</t>
+        </is>
+      </c>
+      <c r="E3093" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3093" s="1" t="n"/>
     </row>
     <row r="3094">
       <c r="A3094" s="1" t="n">
-        <v>9000015</v>
+        <v>8000568</v>
       </c>
       <c r="B3094" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>최근 뽑은 쥐</t>
         </is>
       </c>
       <c r="C3094" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>Recent draws</t>
         </is>
       </c>
       <c r="D3094" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
-        </is>
-      </c>
-      <c r="E3094" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Left/RecentLabel</t>
+        </is>
+      </c>
+      <c r="E3094" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3094" s="1" t="n"/>
     </row>
     <row r="3095">
       <c r="A3095" s="1" t="n">
-        <v>9000016</v>
+        <v>8000569</v>
       </c>
       <c r="B3095" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>재료로 쓴 쥐: {list}</t>
         </is>
       </c>
       <c r="C3095" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>Rats used: {list}</t>
         </is>
       </c>
       <c r="D3095" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
-        </is>
-      </c>
-      <c r="E3095" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvAug/Card/Info</t>
+        </is>
+      </c>
+      <c r="E3095" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3095" s="1" t="n"/>
     </row>
     <row r="3096">
       <c r="A3096" s="1" t="n">
-        <v>9000017</v>
+        <v>8000570</v>
       </c>
       <c r="B3096" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>빠르게 ×{n}</t>
         </is>
       </c>
       <c r="C3096" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>Fast ×{n}</t>
         </is>
       </c>
       <c r="D3096" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
-        </is>
-      </c>
-      <c r="E3096" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Right/Fast/Label</t>
+        </is>
+      </c>
+      <c r="E3096" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3096" s="1" t="n"/>
     </row>
     <row r="3097">
       <c r="A3097" s="1" t="n">
-        <v>9000018</v>
+        <v>8000571</v>
       </c>
       <c r="B3097" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>시작</t>
         </is>
       </c>
       <c r="C3097" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="D3097" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
-        </is>
-      </c>
-      <c r="E3097" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvTitle/Card/Start/Label</t>
+        </is>
+      </c>
+      <c r="E3097" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3097" s="1" t="n"/>
     </row>
     <row r="3098">
       <c r="A3098" s="1" t="n">
-        <v>9000019</v>
+        <v>8000572</v>
       </c>
       <c r="B3098" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>턴 {n}</t>
         </is>
       </c>
       <c r="C3098" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>Turn {n}</t>
         </is>
       </c>
       <c r="D3098" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
-        </is>
-      </c>
-      <c r="E3098" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Right/Turn</t>
+        </is>
+      </c>
+      <c r="E3098" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3098" s="1" t="n"/>
     </row>
     <row r="3099">
       <c r="A3099" s="1" t="n">
-        <v>9000020</v>
+        <v>8000573</v>
       </c>
       <c r="B3099" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>피해  일반 1 · 희귀 2 · 에픽 3 · 유니크 4 · 전설 5 · 신화 6
+고유 스킬 유니크 이상: 발사마다 첫 타격 + 이후 확률로 범위 피해 (3×3 · 가로줄 · 세로줄 · 대각선 · 십자)
+증강 쥐 10마리부터 1.5배씩 · 낮은 등급·오래된 쥐부터 재료로 씀 · 3개 중 1개</t>
         </is>
       </c>
       <c r="C3099" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>Damage  Common 1 · Rare 2 · Epic 3 · Unique 4 · Legendary 5 · Mythic 6
+Unique skill  Unique+: first hit each launch + chance of area damage after (3×3 · row · column · diagonal · cross)
+Augment  from 10 rats, ×1.5 each · uses lowest-grade, oldest rats first · pick 1 of 3</t>
         </is>
       </c>
       <c r="D3099" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
-        </is>
-      </c>
-      <c r="E3099" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvTitle/Card/Rules</t>
+        </is>
+      </c>
+      <c r="E3099" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3099" s="1" t="n"/>
     </row>
     <row r="3100">
       <c r="A3100" s="1" t="n">
-        <v>9000021</v>
+        <v>8000574</v>
       </c>
       <c r="B3100" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>쥐 뽑기</t>
         </is>
       </c>
       <c r="C3100" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Rat Draw</t>
         </is>
       </c>
       <c r="D3100" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
-        </is>
-      </c>
-      <c r="E3100" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Left/Buy/Label</t>
+        </is>
+      </c>
+      <c r="E3100" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3100" s="1" t="n"/>
     </row>
     <row r="3101">
       <c r="A3101" s="1" t="n">
-        <v>9000022</v>
+        <v>8000575</v>
       </c>
       <c r="B3101" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>다시 하기</t>
         </is>
       </c>
       <c r="C3101" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>Play Again</t>
         </is>
       </c>
       <c r="D3101" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
-        </is>
-      </c>
-      <c r="E3101" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvOver/Card/Again/Label</t>
+        </is>
+      </c>
+      <c r="E3101" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3101" s="1" t="n"/>
     </row>
     <row r="3102">
       <c r="A3102" s="1" t="n">
-        <v>9000023</v>
+        <v>8000576</v>
       </c>
       <c r="B3102" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>회수</t>
         </is>
       </c>
       <c r="C3102" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D3102" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
-        </is>
-      </c>
-      <c r="E3102" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Right/Recall/Label</t>
+        </is>
+      </c>
+      <c r="E3102" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3102" s="1" t="n"/>
     </row>
     <row r="3103">
       <c r="A3103" s="1" t="n">
-        <v>9000024</v>
+        <v>8000577</v>
       </c>
       <c r="B3103" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>{price} 치즈 · Shift = 10마리 · 꾹 = 연속 · 천장 {pity}</t>
         </is>
       </c>
       <c r="C3103" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>{price} cheese · Shift = 10 · Hold = repeat · Pity {pity}</t>
         </is>
       </c>
       <c r="D3103" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
-        </is>
-      </c>
-      <c r="E3103" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Left/Buy/Sub</t>
+        </is>
+      </c>
+      <c r="E3103" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3103" s="1" t="n"/>
     </row>
     <row r="3104">
       <c r="A3104" s="1" t="n">
-        <v>9000025</v>
+        <v>8000578</v>
       </c>
       <c r="B3104" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>증강 뽑기 · 쥐 {n}마리</t>
         </is>
       </c>
       <c r="C3104" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>Augment Draw · {n} rats</t>
         </is>
       </c>
       <c r="D3104" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
-        </is>
-      </c>
-      <c r="E3104" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Right/Aug/Label</t>
+        </is>
+      </c>
+      <c r="E3104" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3104" s="1" t="n"/>
     </row>
     <row r="3105">
       <c r="A3105" s="1" t="n">
-        <v>9000026</v>
+        <v>8000579</v>
       </c>
       <c r="B3105" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>뽑기 확률(%) {rates} (일반→신화)</t>
         </is>
       </c>
       <c r="C3105" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>Draw rates (%) {rates} (Common→Mythic)</t>
         </is>
       </c>
       <c r="D3105" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
-        </is>
-      </c>
-      <c r="E3105" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/Left/Rate</t>
+        </is>
+      </c>
+      <c r="E3105" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3105" s="1" t="n"/>
     </row>
     <row r="3106">
       <c r="A3106" s="1" t="n">
-        <v>9000027</v>
+        <v>8000580</v>
       </c>
       <c r="B3106" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>끌었다 놓기 = 발사 · Q 쥐 뽑기 (Shift = 10마리, 꾹 = 연속) · E 증강 뽑기 · F 빠르게 · Space 회수 · R 다시 · Esc 일시정지 · M 음악</t>
         </is>
       </c>
       <c r="C3106" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>Drag &amp; release = launch · Q rat draw (Shift = 10, hold = repeat) · E augment draw · F fast · Space recall · R restart · Esc pause · M music</t>
         </is>
       </c>
       <c r="D3106" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
-        </is>
-      </c>
-      <c r="E3106" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvTitle/Card/Keys</t>
+        </is>
+      </c>
+      <c r="E3106" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3106" s="1" t="n"/>
     </row>
     <row r="3107">
       <c r="A3107" s="1" t="n">
-        <v>9000028</v>
+        <v>8000581</v>
       </c>
       <c r="B3107" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>모든 쥐 피해 +{v}</t>
         </is>
       </c>
       <c r="C3107" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>All rats damage +{v}</t>
         </is>
       </c>
       <c r="D3107" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
-        </is>
-      </c>
-      <c r="E3107" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[0].desc</t>
+        </is>
+      </c>
+      <c r="E3107" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3107" s="1" t="n"/>
     </row>
     <row r="3108">
       <c r="A3108" s="1" t="n">
-        <v>9000029</v>
+        <v>8000582</v>
       </c>
       <c r="B3108" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>부딪힐 때 {v}% 확률 피해 ×{v2}</t>
         </is>
       </c>
       <c r="C3108" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>{v}% chance on hit: damage ×{v2}</t>
         </is>
       </c>
       <c r="D3108" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
-        </is>
-      </c>
-      <c r="E3108" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[1].desc</t>
+        </is>
+      </c>
+      <c r="E3108" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3108" s="1" t="n"/>
     </row>
     <row r="3109">
       <c r="A3109" s="1" t="n">
-        <v>9000030</v>
+        <v>8000583</v>
       </c>
       <c r="B3109" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>벽돌 치즈 +{v}%</t>
         </is>
       </c>
       <c r="C3109" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>Brick cheese +{v}%</t>
         </is>
       </c>
       <c r="D3109" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
-        </is>
-      </c>
-      <c r="E3109" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[2].desc</t>
+        </is>
+      </c>
+      <c r="E3109" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3109" s="1" t="n"/>
     </row>
     <row r="3110">
       <c r="A3110" s="1" t="n">
-        <v>9000031</v>
+        <v>8000584</v>
       </c>
       <c r="B3110" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>벽돌을 부수면 {v}% 확률 치즈 ×{v2}</t>
         </is>
       </c>
       <c r="C3110" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>{v}% chance on break: cheese ×{v2}</t>
         </is>
       </c>
       <c r="D3110" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
-        </is>
-      </c>
-      <c r="E3110" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[3].desc</t>
+        </is>
+      </c>
+      <c r="E3110" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3110" s="1" t="n"/>
     </row>
     <row r="3111">
       <c r="A3111" s="1" t="n">
-        <v>9000032</v>
+        <v>8000585</v>
       </c>
       <c r="B3111" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>부딪힐 때 {v}% 확률 한 번 더 타격</t>
         </is>
       </c>
       <c r="C3111" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>{v}% chance on hit: strike again</t>
         </is>
       </c>
       <c r="D3111" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
-        </is>
-      </c>
-      <c r="E3111" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[4].desc</t>
+        </is>
+      </c>
+      <c r="E3111" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3111" s="1" t="n"/>
     </row>
     <row r="3112">
       <c r="A3112" s="1" t="n">
-        <v>9000033</v>
+        <v>8000586</v>
       </c>
       <c r="B3112" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>부딪힐 때 {v}% 확률 옆 벽돌 감전 (피해 {v2})</t>
         </is>
       </c>
       <c r="C3112" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>{v}% chance on hit: shock a neighbor brick ({v2} dmg)</t>
         </is>
       </c>
       <c r="D3112" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
-        </is>
-      </c>
-      <c r="E3112" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[5].desc</t>
+        </is>
+      </c>
+      <c r="E3112" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3112" s="1" t="n"/>
     </row>
     <row r="3113">
       <c r="A3113" s="1" t="n">
-        <v>9000034</v>
+        <v>8000587</v>
       </c>
       <c r="B3113" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>턴마다 치즈 + 턴 수 × {v}</t>
         </is>
       </c>
       <c r="C3113" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>Each turn: cheese + turn × {v}</t>
         </is>
       </c>
       <c r="D3113" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
-        </is>
-      </c>
-      <c r="E3113" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[6].desc</t>
+        </is>
+      </c>
+      <c r="E3113" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3113" s="1" t="n"/>
     </row>
     <row r="3114">
       <c r="A3114" s="1" t="n">
-        <v>9000035</v>
+        <v>8000588</v>
       </c>
       <c r="B3114" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>쥐를 뽑을 때 {v}% 확률 1마리 더</t>
         </is>
       </c>
       <c r="C3114" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>{v}% chance for 1 extra rat per draw</t>
         </is>
       </c>
       <c r="D3114" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
-        </is>
-      </c>
-      <c r="E3114" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[7].desc</t>
+        </is>
+      </c>
+      <c r="E3114" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3114" s="1" t="n"/>
     </row>
     <row r="3115">
       <c r="A3115" s="1" t="n">
-        <v>9000036</v>
+        <v>8000589</v>
       </c>
       <c r="B3115" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>벽돌이 부서지면 상하좌우 벽돌 피해 {v}</t>
         </is>
       </c>
       <c r="C3115" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>Broken bricks deal {v} damage to adjacent bricks</t>
         </is>
       </c>
       <c r="D3115" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
-        </is>
-      </c>
-      <c r="E3115" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[8].desc</t>
+        </is>
+      </c>
+      <c r="E3115" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3115" s="1" t="n"/>
     </row>
     <row r="3116">
       <c r="A3116" s="1" t="n">
-        <v>9000037</v>
+        <v>8000590</v>
       </c>
       <c r="B3116" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>턴 시작마다 무작위 벽돌 {v}개에 번개 (최고 등급 쥐 피해)</t>
         </is>
       </c>
       <c r="C3116" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>Each turn: lightning on {v} random bricks (top-grade rat damage)</t>
         </is>
       </c>
       <c r="D3116" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
-        </is>
-      </c>
-      <c r="E3116" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[9].desc</t>
+        </is>
+      </c>
+      <c r="E3116" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3116" s="1" t="n"/>
     </row>
     <row r="3117">
       <c r="A3117" s="1" t="n">
-        <v>9000038</v>
+        <v>8000591</v>
       </c>
       <c r="B3117" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>발사마다 첫 쥐 거대화 (크기 ×{v2}, 피해 +{v})</t>
         </is>
       </c>
       <c r="C3117" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>First rat each launch grows (size ×{v2}, damage +{v})</t>
         </is>
       </c>
       <c r="D3117" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
-        </is>
-      </c>
-      <c r="E3117" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[10].desc</t>
+        </is>
+      </c>
+      <c r="E3117" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3117" s="1" t="n"/>
     </row>
     <row r="3118">
       <c r="A3118" s="1" t="n">
-        <v>9000039</v>
+        <v>8000592</v>
       </c>
       <c r="B3118" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>턴마다 가장 아래 벽돌 줄에 기차 (피해 {v})</t>
         </is>
       </c>
       <c r="C3118" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>Each turn: a train hits the lowest brick row ({v} dmg)</t>
         </is>
       </c>
       <c r="D3118" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
-        </is>
-      </c>
-      <c r="E3118" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[11].desc</t>
+        </is>
+      </c>
+      <c r="E3118" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3118" s="1" t="n"/>
     </row>
     <row r="3119">
       <c r="A3119" s="1" t="n">
-        <v>9000040</v>
+        <v>8000593</v>
       </c>
       <c r="B3119" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>발사마다 가장 강한 쥐 분신 {v}마리가 같이 날아감</t>
         </is>
       </c>
       <c r="C3119" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>{v} clones of your strongest rat join each launch</t>
         </is>
       </c>
       <c r="D3119" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
-        </is>
-      </c>
-      <c r="E3119" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[12].desc</t>
+        </is>
+      </c>
+      <c r="E3119" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3119" s="1" t="n"/>
     </row>
     <row r="3120">
       <c r="A3120" s="1" t="n">
-        <v>9000041</v>
+        <v>8000594</v>
       </c>
       <c r="B3120" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>{v2}턴마다 체력이 많은 벽돌 {v}개에 운석 (체력 {v3}%)</t>
         </is>
       </c>
       <c r="C3120" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>Every {v2} turns: meteors on the {v} toughest bricks ({v3}% HP)</t>
         </is>
       </c>
       <c r="D3120" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
-        </is>
-      </c>
-      <c r="E3120" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[13].desc</t>
+        </is>
+      </c>
+      <c r="E3120" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3120" s="1" t="n"/>
     </row>
     <row r="3121">
       <c r="A3121" s="1" t="n">
-        <v>9000042</v>
+        <v>8000595</v>
       </c>
       <c r="B3121" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>첫 쥐 둘레에 치즈 칼날 {v}개 (스치면 피해 {v2})</t>
         </is>
       </c>
       <c r="C3121" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>{v} cheese blades circle the first rat ({v2} dmg on touch)</t>
         </is>
       </c>
       <c r="D3121" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
-        </is>
-      </c>
-      <c r="E3121" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[14].desc</t>
+        </is>
+      </c>
+      <c r="E3121" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3121" s="1" t="n"/>
     </row>
     <row r="3122">
       <c r="A3122" s="1" t="n">
-        <v>9000043</v>
+        <v>8000596</v>
       </c>
       <c r="B3122" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>모든 피해 +{v}%</t>
         </is>
       </c>
       <c r="C3122" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>All damage +{v}%</t>
         </is>
       </c>
       <c r="D3122" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
-        </is>
-      </c>
-      <c r="E3122" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augTexts[15].desc</t>
+        </is>
+      </c>
+      <c r="E3122" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3122" s="1" t="n"/>
     </row>
     <row r="3123">
       <c r="A3123" s="1" t="n">
-        <v>9000044</v>
+        <v>8000597</v>
       </c>
       <c r="B3123" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>치명!</t>
         </is>
       </c>
       <c r="C3123" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>Crit!</t>
         </is>
       </c>
       <c r="D3123" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
-        </is>
-      </c>
-      <c r="E3123" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.critText</t>
+        </is>
+      </c>
+      <c r="E3123" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3123" s="1" t="n"/>
     </row>
     <row r="3124">
       <c r="A3124" s="1" t="n">
-        <v>9000045</v>
+        <v>8000598</v>
       </c>
       <c r="B3124" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>잭팟!</t>
         </is>
       </c>
       <c r="C3124" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>Jackpot!</t>
         </is>
       </c>
       <c r="D3124" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
-        </is>
-      </c>
-      <c r="E3124" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.jackpotText</t>
+        </is>
+      </c>
+      <c r="E3124" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3124" s="1" t="n"/>
     </row>
     <row r="3125">
       <c r="A3125" s="1" t="n">
-        <v>9000046</v>
+        <v>8000599</v>
       </c>
       <c r="B3125" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>치즈 비 +{n}</t>
         </is>
       </c>
       <c r="C3125" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>Cheese rain +{n}</t>
         </is>
       </c>
       <c r="D3125" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
-        </is>
-      </c>
-      <c r="E3125" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.rainText</t>
+        </is>
+      </c>
+      <c r="E3125" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3125" s="1" t="n"/>
     </row>
     <row r="3126">
       <c r="A3126" s="1" t="n">
-        <v>9000047</v>
+        <v>8000600</v>
       </c>
       <c r="B3126" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>장난감 기차!</t>
         </is>
       </c>
       <c r="C3126" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>Toy train!</t>
         </is>
       </c>
       <c r="D3126" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
-        </is>
-      </c>
-      <c r="E3126" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.trainText</t>
+        </is>
+      </c>
+      <c r="E3126" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3126" s="1" t="n"/>
     </row>
     <row r="3127">
       <c r="A3127" s="1" t="n">
-        <v>9000048</v>
+        <v>8000601</v>
       </c>
       <c r="B3127" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>필살!</t>
         </is>
       </c>
       <c r="C3127" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>Special!</t>
         </is>
       </c>
       <c r="D3127" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
-        </is>
-      </c>
-      <c r="E3127" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.skillNoName</t>
+        </is>
+      </c>
+      <c r="E3127" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3127" s="1" t="n"/>
     </row>
     <row r="3128">
       <c r="A3128" s="1" t="n">
-        <v>9000049</v>
+        <v>8000602</v>
       </c>
       <c r="B3128" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t xml:space="preserve"> · {n}단계</t>
         </is>
       </c>
       <c r="C3128" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t xml:space="preserve"> · Lv {n}</t>
         </is>
       </c>
       <c r="D3128" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
-        </is>
-      </c>
-      <c r="E3128" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow · JudolGame.augStageText</t>
+        </is>
+      </c>
+      <c r="E3128" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3128" s="1" t="n"/>
     </row>
     <row r="3129">
       <c r="A3129" s="1" t="n">
-        <v>9000050</v>
+        <v>8000603</v>
       </c>
       <c r="B3129" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>증강 고르기</t>
         </is>
       </c>
       <c r="C3129" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>Choose an Augment</t>
         </is>
       </c>
       <c r="D3129" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
-        </is>
-      </c>
-      <c r="E3129" s="1" t="n"/>
+          <t>씬 · Lobby · UI/ArcadeWindow/Board/OvAug/Card/Title</t>
+        </is>
+      </c>
+      <c r="E3129" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
       <c r="F3129" s="1" t="n"/>
     </row>
     <row r="3130">
       <c r="A3130" s="1" t="n">
-        <v>9000051</v>
+        <v>9000001</v>
       </c>
       <c r="B3130" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>찍찍!! {power}</t>
         </is>
       </c>
       <c r="C3130" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>SQUEAK!! {power}</t>
         </is>
       </c>
       <c r="D3130" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E3130" s="1" t="n"/>
@@ -72953,21 +73163,21 @@
     </row>
     <row r="3131">
       <c r="A3131" s="1" t="n">
-        <v>9000052</v>
+        <v>9000002</v>
       </c>
       <c r="B3131" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C3131" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D3131" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E3131" s="1" t="n"/>
@@ -72975,21 +73185,21 @@
     </row>
     <row r="3132">
       <c r="A3132" s="1" t="n">
-        <v>9000053</v>
+        <v>9000003</v>
       </c>
       <c r="B3132" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C3132" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D3132" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E3132" s="1" t="n"/>
@@ -72997,21 +73207,21 @@
     </row>
     <row r="3133">
       <c r="A3133" s="1" t="n">
-        <v>9000054</v>
+        <v>9000004</v>
       </c>
       <c r="B3133" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C3133" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D3133" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E3133" s="1" t="n"/>
@@ -73019,21 +73229,21 @@
     </row>
     <row r="3134">
       <c r="A3134" s="1" t="n">
-        <v>9000055</v>
+        <v>9000005</v>
       </c>
       <c r="B3134" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C3134" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D3134" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E3134" s="1" t="n"/>
@@ -73041,21 +73251,21 @@
     </row>
     <row r="3135">
       <c r="A3135" s="1" t="n">
-        <v>9000056</v>
+        <v>9000006</v>
       </c>
       <c r="B3135" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C3135" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D3135" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E3135" s="1" t="n"/>
@@ -73063,21 +73273,21 @@
     </row>
     <row r="3136">
       <c r="A3136" s="1" t="n">
-        <v>9000057</v>
+        <v>9000007</v>
       </c>
       <c r="B3136" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C3136" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D3136" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E3136" s="1" t="n"/>
@@ -73085,21 +73295,21 @@
     </row>
     <row r="3137">
       <c r="A3137" s="1" t="n">
-        <v>9000058</v>
+        <v>9000008</v>
       </c>
       <c r="B3137" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C3137" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D3137" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E3137" s="1" t="n"/>
@@ -73107,21 +73317,21 @@
     </row>
     <row r="3138">
       <c r="A3138" s="1" t="n">
-        <v>9000059</v>
+        <v>9000009</v>
       </c>
       <c r="B3138" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C3138" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D3138" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E3138" s="1" t="n"/>
@@ -73129,21 +73339,21 @@
     </row>
     <row r="3139">
       <c r="A3139" s="1" t="n">
-        <v>9000060</v>
+        <v>9000010</v>
       </c>
       <c r="B3139" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C3139" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D3139" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E3139" s="1" t="n"/>
@@ -73151,21 +73361,21 @@
     </row>
     <row r="3140">
       <c r="A3140" s="1" t="n">
-        <v>9000061</v>
+        <v>9000011</v>
       </c>
       <c r="B3140" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C3140" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D3140" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E3140" s="1" t="n"/>
@@ -73173,21 +73383,21 @@
     </row>
     <row r="3141">
       <c r="A3141" s="1" t="n">
-        <v>9000062</v>
+        <v>9000012</v>
       </c>
       <c r="B3141" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C3141" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D3141" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E3141" s="1" t="n"/>
@@ -73195,21 +73405,21 @@
     </row>
     <row r="3142">
       <c r="A3142" s="1" t="n">
-        <v>9000063</v>
+        <v>9000013</v>
       </c>
       <c r="B3142" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C3142" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D3142" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E3142" s="1" t="n"/>
@@ -73217,21 +73427,21 @@
     </row>
     <row r="3143">
       <c r="A3143" s="1" t="n">
-        <v>9000064</v>
+        <v>9000014</v>
       </c>
       <c r="B3143" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C3143" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D3143" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E3143" s="1" t="n"/>
@@ -73239,21 +73449,21 @@
     </row>
     <row r="3144">
       <c r="A3144" s="1" t="n">
-        <v>9000065</v>
+        <v>9000015</v>
       </c>
       <c r="B3144" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C3144" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D3144" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E3144" s="1" t="n"/>
@@ -73261,21 +73471,21 @@
     </row>
     <row r="3145">
       <c r="A3145" s="1" t="n">
-        <v>9000066</v>
+        <v>9000016</v>
       </c>
       <c r="B3145" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C3145" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D3145" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E3145" s="1" t="n"/>
@@ -73283,21 +73493,21 @@
     </row>
     <row r="3146">
       <c r="A3146" s="1" t="n">
-        <v>9000067</v>
+        <v>9000017</v>
       </c>
       <c r="B3146" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C3146" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D3146" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E3146" s="1" t="n"/>
@@ -73305,21 +73515,21 @@
     </row>
     <row r="3147">
       <c r="A3147" s="1" t="n">
-        <v>9000068</v>
+        <v>9000018</v>
       </c>
       <c r="B3147" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C3147" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D3147" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E3147" s="1" t="n"/>
@@ -73327,21 +73537,21 @@
     </row>
     <row r="3148">
       <c r="A3148" s="1" t="n">
-        <v>9000069</v>
+        <v>9000019</v>
       </c>
       <c r="B3148" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C3148" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D3148" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E3148" s="1" t="n"/>
@@ -73349,21 +73559,21 @@
     </row>
     <row r="3149">
       <c r="A3149" s="1" t="n">
-        <v>9000070</v>
+        <v>9000020</v>
       </c>
       <c r="B3149" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C3149" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D3149" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E3149" s="1" t="n"/>
@@ -73371,21 +73581,21 @@
     </row>
     <row r="3150">
       <c r="A3150" s="1" t="n">
-        <v>9000071</v>
+        <v>9000021</v>
       </c>
       <c r="B3150" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C3150" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D3150" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E3150" s="1" t="n"/>
@@ -73393,21 +73603,21 @@
     </row>
     <row r="3151">
       <c r="A3151" s="1" t="n">
-        <v>9000072</v>
+        <v>9000022</v>
       </c>
       <c r="B3151" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C3151" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D3151" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E3151" s="1" t="n"/>
@@ -73415,21 +73625,21 @@
     </row>
     <row r="3152">
       <c r="A3152" s="1" t="n">
-        <v>9000073</v>
+        <v>9000023</v>
       </c>
       <c r="B3152" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C3152" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D3152" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E3152" s="1" t="n"/>
@@ -73437,21 +73647,21 @@
     </row>
     <row r="3153">
       <c r="A3153" s="1" t="n">
-        <v>9000074</v>
+        <v>9000024</v>
       </c>
       <c r="B3153" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C3153" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D3153" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E3153" s="1" t="n"/>
@@ -73459,21 +73669,21 @@
     </row>
     <row r="3154">
       <c r="A3154" s="1" t="n">
-        <v>9000075</v>
+        <v>9000025</v>
       </c>
       <c r="B3154" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C3154" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D3154" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E3154" s="1" t="n"/>
@@ -73481,21 +73691,21 @@
     </row>
     <row r="3155">
       <c r="A3155" s="1" t="n">
-        <v>9000076</v>
+        <v>9000026</v>
       </c>
       <c r="B3155" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C3155" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D3155" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E3155" s="1" t="n"/>
@@ -73503,21 +73713,21 @@
     </row>
     <row r="3156">
       <c r="A3156" s="1" t="n">
-        <v>9000077</v>
+        <v>9000027</v>
       </c>
       <c r="B3156" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C3156" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D3156" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E3156" s="1" t="n"/>
@@ -73525,21 +73735,21 @@
     </row>
     <row r="3157">
       <c r="A3157" s="1" t="n">
-        <v>9000078</v>
+        <v>9000028</v>
       </c>
       <c r="B3157" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C3157" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D3157" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E3157" s="1" t="n"/>
@@ -73547,21 +73757,21 @@
     </row>
     <row r="3158">
       <c r="A3158" s="1" t="n">
-        <v>9000079</v>
+        <v>9000029</v>
       </c>
       <c r="B3158" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C3158" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D3158" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E3158" s="1" t="n"/>
@@ -73569,21 +73779,21 @@
     </row>
     <row r="3159">
       <c r="A3159" s="1" t="n">
-        <v>9000080</v>
+        <v>9000030</v>
       </c>
       <c r="B3159" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C3159" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D3159" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E3159" s="1" t="n"/>
@@ -73591,21 +73801,21 @@
     </row>
     <row r="3160">
       <c r="A3160" s="1" t="n">
-        <v>9000081</v>
+        <v>9000031</v>
       </c>
       <c r="B3160" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C3160" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D3160" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E3160" s="1" t="n"/>
@@ -73613,21 +73823,21 @@
     </row>
     <row r="3161">
       <c r="A3161" s="1" t="n">
-        <v>9000082</v>
+        <v>9000032</v>
       </c>
       <c r="B3161" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C3161" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D3161" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E3161" s="1" t="n"/>
@@ -73635,21 +73845,21 @@
     </row>
     <row r="3162">
       <c r="A3162" s="1" t="n">
-        <v>9000083</v>
+        <v>9000033</v>
       </c>
       <c r="B3162" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C3162" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D3162" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E3162" s="1" t="n"/>
@@ -73657,21 +73867,21 @@
     </row>
     <row r="3163">
       <c r="A3163" s="1" t="n">
-        <v>9000084</v>
+        <v>9000034</v>
       </c>
       <c r="B3163" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C3163" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D3163" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E3163" s="1" t="n"/>
@@ -73679,21 +73889,21 @@
     </row>
     <row r="3164">
       <c r="A3164" s="1" t="n">
-        <v>9000085</v>
+        <v>9000035</v>
       </c>
       <c r="B3164" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C3164" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D3164" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E3164" s="1" t="n"/>
@@ -73701,21 +73911,21 @@
     </row>
     <row r="3165">
       <c r="A3165" s="1" t="n">
-        <v>9000086</v>
+        <v>9000036</v>
       </c>
       <c r="B3165" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C3165" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D3165" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E3165" s="1" t="n"/>
@@ -73723,21 +73933,21 @@
     </row>
     <row r="3166">
       <c r="A3166" s="1" t="n">
-        <v>9000087</v>
+        <v>9000037</v>
       </c>
       <c r="B3166" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C3166" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D3166" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E3166" s="1" t="n"/>
@@ -73745,21 +73955,21 @@
     </row>
     <row r="3167">
       <c r="A3167" s="1" t="n">
-        <v>9000088</v>
+        <v>9000038</v>
       </c>
       <c r="B3167" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C3167" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D3167" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E3167" s="1" t="n"/>
@@ -73767,21 +73977,21 @@
     </row>
     <row r="3168">
       <c r="A3168" s="1" t="n">
-        <v>9000089</v>
+        <v>9000039</v>
       </c>
       <c r="B3168" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C3168" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D3168" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E3168" s="1" t="n"/>
@@ -73789,21 +73999,21 @@
     </row>
     <row r="3169">
       <c r="A3169" s="1" t="n">
-        <v>9000090</v>
+        <v>9000040</v>
       </c>
       <c r="B3169" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C3169" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D3169" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E3169" s="1" t="n"/>
@@ -73811,21 +74021,21 @@
     </row>
     <row r="3170">
       <c r="A3170" s="1" t="n">
-        <v>9000091</v>
+        <v>9000041</v>
       </c>
       <c r="B3170" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C3170" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D3170" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E3170" s="1" t="n"/>
@@ -73833,21 +74043,21 @@
     </row>
     <row r="3171">
       <c r="A3171" s="1" t="n">
-        <v>9000092</v>
+        <v>9000042</v>
       </c>
       <c r="B3171" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C3171" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D3171" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E3171" s="1" t="n"/>
@@ -73855,21 +74065,21 @@
     </row>
     <row r="3172">
       <c r="A3172" s="1" t="n">
-        <v>9000093</v>
+        <v>9000043</v>
       </c>
       <c r="B3172" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C3172" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D3172" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E3172" s="1" t="n"/>
@@ -73877,21 +74087,21 @@
     </row>
     <row r="3173">
       <c r="A3173" s="1" t="n">
-        <v>9000094</v>
+        <v>9000044</v>
       </c>
       <c r="B3173" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C3173" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D3173" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E3173" s="1" t="n"/>
@@ -73899,21 +74109,21 @@
     </row>
     <row r="3174">
       <c r="A3174" s="1" t="n">
-        <v>9000095</v>
+        <v>9000045</v>
       </c>
       <c r="B3174" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C3174" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D3174" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E3174" s="1" t="n"/>
@@ -73921,21 +74131,21 @@
     </row>
     <row r="3175">
       <c r="A3175" s="1" t="n">
-        <v>9000096</v>
+        <v>9000046</v>
       </c>
       <c r="B3175" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C3175" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D3175" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E3175" s="1" t="n"/>
@@ -73943,21 +74153,21 @@
     </row>
     <row r="3176">
       <c r="A3176" s="1" t="n">
-        <v>9000097</v>
+        <v>9000047</v>
       </c>
       <c r="B3176" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C3176" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D3176" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E3176" s="1" t="n"/>
@@ -73965,21 +74175,21 @@
     </row>
     <row r="3177">
       <c r="A3177" s="1" t="n">
-        <v>9000098</v>
+        <v>9000048</v>
       </c>
       <c r="B3177" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C3177" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D3177" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E3177" s="1" t="n"/>
@@ -73987,21 +74197,21 @@
     </row>
     <row r="3178">
       <c r="A3178" s="1" t="n">
-        <v>9000099</v>
+        <v>9000049</v>
       </c>
       <c r="B3178" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C3178" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D3178" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E3178" s="1" t="n"/>
@@ -74009,21 +74219,21 @@
     </row>
     <row r="3179">
       <c r="A3179" s="1" t="n">
-        <v>9000100</v>
+        <v>9000050</v>
       </c>
       <c r="B3179" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C3179" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D3179" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E3179" s="1" t="n"/>
@@ -74031,21 +74241,21 @@
     </row>
     <row r="3180">
       <c r="A3180" s="1" t="n">
-        <v>9000101</v>
+        <v>9000051</v>
       </c>
       <c r="B3180" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C3180" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D3180" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E3180" s="1" t="n"/>
@@ -74053,21 +74263,21 @@
     </row>
     <row r="3181">
       <c r="A3181" s="1" t="n">
-        <v>9000102</v>
+        <v>9000052</v>
       </c>
       <c r="B3181" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C3181" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D3181" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E3181" s="1" t="n"/>
@@ -74075,21 +74285,21 @@
     </row>
     <row r="3182">
       <c r="A3182" s="1" t="n">
-        <v>9000103</v>
+        <v>9000053</v>
       </c>
       <c r="B3182" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C3182" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D3182" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E3182" s="1" t="n"/>
@@ -74097,21 +74307,21 @@
     </row>
     <row r="3183">
       <c r="A3183" s="1" t="n">
-        <v>9000104</v>
+        <v>9000054</v>
       </c>
       <c r="B3183" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C3183" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D3183" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E3183" s="1" t="n"/>
@@ -74119,21 +74329,21 @@
     </row>
     <row r="3184">
       <c r="A3184" s="1" t="n">
-        <v>9000105</v>
+        <v>9000055</v>
       </c>
       <c r="B3184" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C3184" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D3184" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E3184" s="1" t="n"/>
@@ -74141,21 +74351,21 @@
     </row>
     <row r="3185">
       <c r="A3185" s="1" t="n">
-        <v>9000106</v>
+        <v>9000056</v>
       </c>
       <c r="B3185" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C3185" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D3185" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E3185" s="1" t="n"/>
@@ -74163,21 +74373,21 @@
     </row>
     <row r="3186">
       <c r="A3186" s="1" t="n">
-        <v>9000107</v>
+        <v>9000057</v>
       </c>
       <c r="B3186" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C3186" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D3186" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E3186" s="1" t="n"/>
@@ -74185,21 +74395,21 @@
     </row>
     <row r="3187">
       <c r="A3187" s="1" t="n">
-        <v>9000108</v>
+        <v>9000058</v>
       </c>
       <c r="B3187" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C3187" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D3187" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E3187" s="1" t="n"/>
@@ -74207,21 +74417,21 @@
     </row>
     <row r="3188">
       <c r="A3188" s="1" t="n">
-        <v>9000109</v>
+        <v>9000059</v>
       </c>
       <c r="B3188" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C3188" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D3188" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E3188" s="1" t="n"/>
@@ -74229,21 +74439,21 @@
     </row>
     <row r="3189">
       <c r="A3189" s="1" t="n">
-        <v>9000110</v>
+        <v>9000060</v>
       </c>
       <c r="B3189" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C3189" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D3189" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E3189" s="1" t="n"/>
@@ -74251,21 +74461,21 @@
     </row>
     <row r="3190">
       <c r="A3190" s="1" t="n">
-        <v>9000111</v>
+        <v>9000061</v>
       </c>
       <c r="B3190" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C3190" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D3190" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E3190" s="1" t="n"/>
@@ -74273,21 +74483,21 @@
     </row>
     <row r="3191">
       <c r="A3191" s="1" t="n">
-        <v>9000112</v>
+        <v>9000062</v>
       </c>
       <c r="B3191" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C3191" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D3191" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E3191" s="1" t="n"/>
@@ -74295,21 +74505,21 @@
     </row>
     <row r="3192">
       <c r="A3192" s="1" t="n">
-        <v>9000113</v>
+        <v>9000063</v>
       </c>
       <c r="B3192" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C3192" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D3192" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E3192" s="1" t="n"/>
@@ -74317,21 +74527,21 @@
     </row>
     <row r="3193">
       <c r="A3193" s="1" t="n">
-        <v>9000114</v>
+        <v>9000064</v>
       </c>
       <c r="B3193" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C3193" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D3193" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E3193" s="1" t="n"/>
@@ -74339,21 +74549,21 @@
     </row>
     <row r="3194">
       <c r="A3194" s="1" t="n">
-        <v>9000115</v>
+        <v>9000065</v>
       </c>
       <c r="B3194" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C3194" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D3194" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3194" s="1" t="n"/>
@@ -74361,21 +74571,21 @@
     </row>
     <row r="3195">
       <c r="A3195" s="1" t="n">
-        <v>9000116</v>
+        <v>9000066</v>
       </c>
       <c r="B3195" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C3195" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D3195" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3195" s="1" t="n"/>
@@ -74383,21 +74593,21 @@
     </row>
     <row r="3196">
       <c r="A3196" s="1" t="n">
-        <v>9000117</v>
+        <v>9000067</v>
       </c>
       <c r="B3196" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C3196" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D3196" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3196" s="1" t="n"/>
@@ -74405,21 +74615,21 @@
     </row>
     <row r="3197">
       <c r="A3197" s="1" t="n">
-        <v>9000118</v>
+        <v>9000068</v>
       </c>
       <c r="B3197" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C3197" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D3197" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3197" s="1" t="n"/>
@@ -74427,21 +74637,21 @@
     </row>
     <row r="3198">
       <c r="A3198" s="1" t="n">
-        <v>9000119</v>
+        <v>9000069</v>
       </c>
       <c r="B3198" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C3198" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D3198" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3198" s="1" t="n"/>
@@ -74449,21 +74659,21 @@
     </row>
     <row r="3199">
       <c r="A3199" s="1" t="n">
-        <v>9000120</v>
+        <v>9000070</v>
       </c>
       <c r="B3199" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C3199" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D3199" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3199" s="1" t="n"/>
@@ -74471,21 +74681,21 @@
     </row>
     <row r="3200">
       <c r="A3200" s="1" t="n">
-        <v>9000121</v>
+        <v>9000071</v>
       </c>
       <c r="B3200" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C3200" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D3200" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3200" s="1" t="n"/>
@@ -74493,21 +74703,21 @@
     </row>
     <row r="3201">
       <c r="A3201" s="1" t="n">
-        <v>9000122</v>
+        <v>9000072</v>
       </c>
       <c r="B3201" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C3201" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D3201" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E3201" s="1" t="n"/>
@@ -74515,21 +74725,21 @@
     </row>
     <row r="3202">
       <c r="A3202" s="1" t="n">
-        <v>9000123</v>
+        <v>9000073</v>
       </c>
       <c r="B3202" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C3202" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D3202" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E3202" s="1" t="n"/>
@@ -74537,21 +74747,21 @@
     </row>
     <row r="3203">
       <c r="A3203" s="1" t="n">
-        <v>9000124</v>
+        <v>9000074</v>
       </c>
       <c r="B3203" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C3203" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D3203" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E3203" s="1" t="n"/>
@@ -74559,21 +74769,21 @@
     </row>
     <row r="3204">
       <c r="A3204" s="1" t="n">
-        <v>9000125</v>
+        <v>9000075</v>
       </c>
       <c r="B3204" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C3204" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D3204" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E3204" s="1" t="n"/>
@@ -74581,21 +74791,21 @@
     </row>
     <row r="3205">
       <c r="A3205" s="1" t="n">
-        <v>9000126</v>
+        <v>9000076</v>
       </c>
       <c r="B3205" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C3205" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D3205" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E3205" s="1" t="n"/>
@@ -74603,21 +74813,21 @@
     </row>
     <row r="3206">
       <c r="A3206" s="1" t="n">
-        <v>9000127</v>
+        <v>9000077</v>
       </c>
       <c r="B3206" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C3206" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D3206" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E3206" s="1" t="n"/>
@@ -74625,21 +74835,21 @@
     </row>
     <row r="3207">
       <c r="A3207" s="1" t="n">
-        <v>9000128</v>
+        <v>9000078</v>
       </c>
       <c r="B3207" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C3207" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D3207" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E3207" s="1" t="n"/>
@@ -74647,21 +74857,21 @@
     </row>
     <row r="3208">
       <c r="A3208" s="1" t="n">
-        <v>9000129</v>
+        <v>9000079</v>
       </c>
       <c r="B3208" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C3208" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D3208" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E3208" s="1" t="n"/>
@@ -74669,21 +74879,21 @@
     </row>
     <row r="3209">
       <c r="A3209" s="1" t="n">
-        <v>9000130</v>
+        <v>9000080</v>
       </c>
       <c r="B3209" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C3209" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D3209" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E3209" s="1" t="n"/>
@@ -74691,21 +74901,21 @@
     </row>
     <row r="3210">
       <c r="A3210" s="1" t="n">
-        <v>9000131</v>
+        <v>9000081</v>
       </c>
       <c r="B3210" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C3210" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D3210" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E3210" s="1" t="n"/>
@@ -74713,25 +74923,1125 @@
     </row>
     <row r="3211">
       <c r="A3211" s="1" t="n">
-        <v>9000132</v>
+        <v>9000082</v>
       </c>
       <c r="B3211" s="2" t="inlineStr">
         <is>
-          <t>※ 출발 층은 스킬만으로 다 열리지 않아요 · 층을 클리어해야 더 위에서 출발할 수 있어요 (출동 화면에 안내)</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C3211" s="2" t="inlineStr">
         <is>
-          <t>※ Skip needs cleared floors too · clear floors to start higher (shown on the Run screen)</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D3211" s="1" t="inlineStr">
         <is>
-          <t>코드 · SkillPage.DrawDetail (Stage_Skip 노드)</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E3211" s="1" t="n"/>
       <c r="F3211" s="1" t="n"/>
+    </row>
+    <row r="3212">
+      <c r="A3212" s="1" t="n">
+        <v>9000083</v>
+      </c>
+      <c r="B3212" s="2" t="inlineStr">
+        <is>
+          <t>헉헉</t>
+        </is>
+      </c>
+      <c r="C3212" s="2" t="inlineStr">
+        <is>
+          <t>Huff puff</t>
+        </is>
+      </c>
+      <c r="D3212" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
+        </is>
+      </c>
+      <c r="E3212" s="1" t="n"/>
+      <c r="F3212" s="1" t="n"/>
+    </row>
+    <row r="3213">
+      <c r="A3213" s="1" t="n">
+        <v>9000084</v>
+      </c>
+      <c r="B3213" s="2" t="inlineStr">
+        <is>
+          <t>더 빨리!</t>
+        </is>
+      </c>
+      <c r="C3213" s="2" t="inlineStr">
+        <is>
+          <t>Faster!</t>
+        </is>
+      </c>
+      <c r="D3213" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
+        </is>
+      </c>
+      <c r="E3213" s="1" t="n"/>
+      <c r="F3213" s="1" t="n"/>
+    </row>
+    <row r="3214">
+      <c r="A3214" s="1" t="n">
+        <v>9000085</v>
+      </c>
+      <c r="B3214" s="2" t="inlineStr">
+        <is>
+          <t>근육 붙는 중</t>
+        </is>
+      </c>
+      <c r="C3214" s="2" t="inlineStr">
+        <is>
+          <t>Gains incoming</t>
+        </is>
+      </c>
+      <c r="D3214" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
+        </is>
+      </c>
+      <c r="E3214" s="1" t="n"/>
+      <c r="F3214" s="1" t="n"/>
+    </row>
+    <row r="3215">
+      <c r="A3215" s="1" t="n">
+        <v>9000086</v>
+      </c>
+      <c r="B3215" s="2" t="inlineStr">
+        <is>
+          <t>찍찍찍찍</t>
+        </is>
+      </c>
+      <c r="C3215" s="2" t="inlineStr">
+        <is>
+          <t>Squeak squeak squeak squeak</t>
+        </is>
+      </c>
+      <c r="D3215" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
+        </is>
+      </c>
+      <c r="E3215" s="1" t="n"/>
+      <c r="F3215" s="1" t="n"/>
+    </row>
+    <row r="3216">
+      <c r="A3216" s="1" t="n">
+        <v>9000087</v>
+      </c>
+      <c r="B3216" s="2" t="inlineStr">
+        <is>
+          <t>으아아아~!</t>
+        </is>
+      </c>
+      <c r="C3216" s="2" t="inlineStr">
+        <is>
+          <t>Waaaaah~!</t>
+        </is>
+      </c>
+      <c r="D3216" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
+        </is>
+      </c>
+      <c r="E3216" s="1" t="n"/>
+      <c r="F3216" s="1" t="n"/>
+    </row>
+    <row r="3217">
+      <c r="A3217" s="1" t="n">
+        <v>9000088</v>
+      </c>
+      <c r="B3217" s="2" t="inlineStr">
+        <is>
+          <t>하암~ 잘 잤다</t>
+        </is>
+      </c>
+      <c r="C3217" s="2" t="inlineStr">
+        <is>
+          <t>Yawn~ what a nap</t>
+        </is>
+      </c>
+      <c r="D3217" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
+        </is>
+      </c>
+      <c r="E3217" s="1" t="n"/>
+      <c r="F3217" s="1" t="n"/>
+    </row>
+    <row r="3218">
+      <c r="A3218" s="1" t="n">
+        <v>9000089</v>
+      </c>
+      <c r="B3218" s="2" t="inlineStr">
+        <is>
+          <t>냠, 배부르다</t>
+        </is>
+      </c>
+      <c r="C3218" s="2" t="inlineStr">
+        <is>
+          <t>Nom, so full</t>
+        </is>
+      </c>
+      <c r="D3218" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
+        </is>
+      </c>
+      <c r="E3218" s="1" t="n"/>
+      <c r="F3218" s="1" t="n"/>
+    </row>
+    <row r="3219">
+      <c r="A3219" s="1" t="n">
+        <v>9000090</v>
+      </c>
+      <c r="B3219" s="2" t="inlineStr">
+        <is>
+          <t>휴…</t>
+        </is>
+      </c>
+      <c r="C3219" s="2" t="inlineStr">
+        <is>
+          <t>Phew...</t>
+        </is>
+      </c>
+      <c r="D3219" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
+        </is>
+      </c>
+      <c r="E3219" s="1" t="n"/>
+      <c r="F3219" s="1" t="n"/>
+    </row>
+    <row r="3220">
+      <c r="A3220" s="1" t="n">
+        <v>9000091</v>
+      </c>
+      <c r="B3220" s="2" t="inlineStr">
+        <is>
+          <t>찍</t>
+        </is>
+      </c>
+      <c r="C3220" s="2" t="inlineStr">
+        <is>
+          <t>Squeak</t>
+        </is>
+      </c>
+      <c r="D3220" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
+        </is>
+      </c>
+      <c r="E3220" s="1" t="n"/>
+      <c r="F3220" s="1" t="n"/>
+    </row>
+    <row r="3221">
+      <c r="A3221" s="1" t="n">
+        <v>9000092</v>
+      </c>
+      <c r="B3221" s="2" t="inlineStr">
+        <is>
+          <t>보스</t>
+        </is>
+      </c>
+      <c r="C3221" s="2" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D3221" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/RunPage.cs:99</t>
+        </is>
+      </c>
+      <c r="E3221" s="1" t="n"/>
+      <c r="F3221" s="1" t="n"/>
+    </row>
+    <row r="3222">
+      <c r="A3222" s="1" t="n">
+        <v>9000093</v>
+      </c>
+      <c r="B3222" s="2" t="inlineStr">
+        <is>
+          <t>잠김</t>
+        </is>
+      </c>
+      <c r="C3222" s="2" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D3222" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+        </is>
+      </c>
+      <c r="E3222" s="1" t="n"/>
+      <c r="F3222" s="1" t="n"/>
+    </row>
+    <row r="3223">
+      <c r="A3223" s="1" t="n">
+        <v>9000094</v>
+      </c>
+      <c r="B3223" s="2" t="inlineStr">
+        <is>
+          <t>찌릿!!</t>
+        </is>
+      </c>
+      <c r="C3223" s="2" t="inlineStr">
+        <is>
+          <t>ZAP!!</t>
+        </is>
+      </c>
+      <c r="D3223" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
+        </is>
+      </c>
+      <c r="E3223" s="1" t="n"/>
+      <c r="F3223" s="1" t="n"/>
+    </row>
+    <row r="3224">
+      <c r="A3224" s="1" t="n">
+        <v>9000095</v>
+      </c>
+      <c r="B3224" s="2" t="inlineStr">
+        <is>
+          <t>콰릉!</t>
+        </is>
+      </c>
+      <c r="C3224" s="2" t="inlineStr">
+        <is>
+          <t>Ka-boom!</t>
+        </is>
+      </c>
+      <c r="D3224" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
+        </is>
+      </c>
+      <c r="E3224" s="1" t="n"/>
+      <c r="F3224" s="1" t="n"/>
+    </row>
+    <row r="3225">
+      <c r="A3225" s="1" t="n">
+        <v>9000096</v>
+      </c>
+      <c r="B3225" s="2" t="inlineStr">
+        <is>
+          <t>냠!</t>
+        </is>
+      </c>
+      <c r="C3225" s="2" t="inlineStr">
+        <is>
+          <t>Nom!</t>
+        </is>
+      </c>
+      <c r="D3225" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
+        </is>
+      </c>
+      <c r="E3225" s="1" t="n"/>
+      <c r="F3225" s="1" t="n"/>
+    </row>
+    <row r="3226">
+      <c r="A3226" s="1" t="n">
+        <v>9000097</v>
+      </c>
+      <c r="B3226" s="2" t="inlineStr">
+        <is>
+          <t>다닥!</t>
+        </is>
+      </c>
+      <c r="C3226" s="2" t="inlineStr">
+        <is>
+          <t>Scurry!</t>
+        </is>
+      </c>
+      <c r="D3226" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
+        </is>
+      </c>
+      <c r="E3226" s="1" t="n"/>
+      <c r="F3226" s="1" t="n"/>
+    </row>
+    <row r="3227">
+      <c r="A3227" s="1" t="n">
+        <v>9000098</v>
+      </c>
+      <c r="B3227" s="2" t="inlineStr">
+        <is>
+          <t>메리 쥐스마스!</t>
+        </is>
+      </c>
+      <c r="C3227" s="2" t="inlineStr">
+        <is>
+          <t>Merry Ratmas!</t>
+        </is>
+      </c>
+      <c r="D3227" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
+        </is>
+      </c>
+      <c r="E3227" s="1" t="n"/>
+      <c r="F3227" s="1" t="n"/>
+    </row>
+    <row r="3228">
+      <c r="A3228" s="1" t="n">
+        <v>9000099</v>
+      </c>
+      <c r="B3228" s="2" t="inlineStr">
+        <is>
+          <t>흐에~ 후원 감사합니다~!</t>
+        </is>
+      </c>
+      <c r="C3228" s="2" t="inlineStr">
+        <is>
+          <t>Heheh~ thanks for the dono~!</t>
+        </is>
+      </c>
+      <c r="D3228" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
+        </is>
+      </c>
+      <c r="E3228" s="1" t="n"/>
+      <c r="F3228" s="1" t="n"/>
+    </row>
+    <row r="3229">
+      <c r="A3229" s="1" t="n">
+        <v>9000100</v>
+      </c>
+      <c r="B3229" s="2" t="inlineStr">
+        <is>
+          <t>배달 왔습니다~</t>
+        </is>
+      </c>
+      <c r="C3229" s="2" t="inlineStr">
+        <is>
+          <t>Delivery~!</t>
+        </is>
+      </c>
+      <c r="D3229" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
+        </is>
+      </c>
+      <c r="E3229" s="1" t="n"/>
+      <c r="F3229" s="1" t="n"/>
+    </row>
+    <row r="3230">
+      <c r="A3230" s="1" t="n">
+        <v>9000101</v>
+      </c>
+      <c r="B3230" s="2" t="inlineStr">
+        <is>
+          <t>백덤블링!</t>
+        </is>
+      </c>
+      <c r="C3230" s="2" t="inlineStr">
+        <is>
+          <t>Backflip!</t>
+        </is>
+      </c>
+      <c r="D3230" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
+        </is>
+      </c>
+      <c r="E3230" s="1" t="n"/>
+      <c r="F3230" s="1" t="n"/>
+    </row>
+    <row r="3231">
+      <c r="A3231" s="1" t="n">
+        <v>9000102</v>
+      </c>
+      <c r="B3231" s="2" t="inlineStr">
+        <is>
+          <t>공중제비!</t>
+        </is>
+      </c>
+      <c r="C3231" s="2" t="inlineStr">
+        <is>
+          <t>Somersault!</t>
+        </is>
+      </c>
+      <c r="D3231" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
+        </is>
+      </c>
+      <c r="E3231" s="1" t="n"/>
+      <c r="F3231" s="1" t="n"/>
+    </row>
+    <row r="3232">
+      <c r="A3232" s="1" t="n">
+        <v>9000103</v>
+      </c>
+      <c r="B3232" s="2" t="inlineStr">
+        <is>
+          <t>찍-공중회전!</t>
+        </is>
+      </c>
+      <c r="C3232" s="2" t="inlineStr">
+        <is>
+          <t>Squeak-flip!</t>
+        </is>
+      </c>
+      <c r="D3232" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
+        </is>
+      </c>
+      <c r="E3232" s="1" t="n"/>
+      <c r="F3232" s="1" t="n"/>
+    </row>
+    <row r="3233">
+      <c r="A3233" s="1" t="n">
+        <v>9000104</v>
+      </c>
+      <c r="B3233" s="2" t="inlineStr">
+        <is>
+          <t>트리플 악셀!!</t>
+        </is>
+      </c>
+      <c r="C3233" s="2" t="inlineStr">
+        <is>
+          <t>TRIPLE AXEL!!</t>
+        </is>
+      </c>
+      <c r="D3233" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
+        </is>
+      </c>
+      <c r="E3233" s="1" t="n"/>
+      <c r="F3233" s="1" t="n"/>
+    </row>
+    <row r="3234">
+      <c r="A3234" s="1" t="n">
+        <v>9000105</v>
+      </c>
+      <c r="B3234" s="2" t="inlineStr">
+        <is>
+          <t>3회전 성공!</t>
+        </is>
+      </c>
+      <c r="C3234" s="2" t="inlineStr">
+        <is>
+          <t>Triple spin landed!</t>
+        </is>
+      </c>
+      <c r="D3234" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
+        </is>
+      </c>
+      <c r="E3234" s="1" t="n"/>
+      <c r="F3234" s="1" t="n"/>
+    </row>
+    <row r="3235">
+      <c r="A3235" s="1" t="n">
+        <v>9000106</v>
+      </c>
+      <c r="B3235" s="2" t="inlineStr">
+        <is>
+          <t>심사위원 전원 10점!</t>
+        </is>
+      </c>
+      <c r="C3235" s="2" t="inlineStr">
+        <is>
+          <t>Perfect 10s from every judge!</t>
+        </is>
+      </c>
+      <c r="D3235" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
+        </is>
+      </c>
+      <c r="E3235" s="1" t="n"/>
+      <c r="F3235" s="1" t="n"/>
+    </row>
+    <row r="3236">
+      <c r="A3236" s="1" t="n">
+        <v>9000107</v>
+      </c>
+      <c r="B3236" s="2" t="inlineStr">
+        <is>
+          <t>윈드밀!!</t>
+        </is>
+      </c>
+      <c r="C3236" s="2" t="inlineStr">
+        <is>
+          <t>WINDMILL!!</t>
+        </is>
+      </c>
+      <c r="D3236" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
+        </is>
+      </c>
+      <c r="E3236" s="1" t="n"/>
+      <c r="F3236" s="1" t="n"/>
+    </row>
+    <row r="3237">
+      <c r="A3237" s="1" t="n">
+        <v>9000108</v>
+      </c>
+      <c r="B3237" s="2" t="inlineStr">
+        <is>
+          <t>브레이크 댄스!</t>
+        </is>
+      </c>
+      <c r="C3237" s="2" t="inlineStr">
+        <is>
+          <t>Breakdance!</t>
+        </is>
+      </c>
+      <c r="D3237" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
+        </is>
+      </c>
+      <c r="E3237" s="1" t="n"/>
+      <c r="F3237" s="1" t="n"/>
+    </row>
+    <row r="3238">
+      <c r="A3238" s="1" t="n">
+        <v>9000109</v>
+      </c>
+      <c r="B3238" s="2" t="inlineStr">
+        <is>
+          <t>빙글빙글 파괴!</t>
+        </is>
+      </c>
+      <c r="C3238" s="2" t="inlineStr">
+        <is>
+          <t>Spin-to-win destruction!</t>
+        </is>
+      </c>
+      <c r="D3238" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
+        </is>
+      </c>
+      <c r="E3238" s="1" t="n"/>
+      <c r="F3238" s="1" t="n"/>
+    </row>
+    <row r="3239">
+      <c r="A3239" s="1" t="n">
+        <v>9000110</v>
+      </c>
+      <c r="B3239" s="2" t="inlineStr">
+        <is>
+          <t>쥐 대포알!</t>
+        </is>
+      </c>
+      <c r="C3239" s="2" t="inlineStr">
+        <is>
+          <t>Rat Cannonball!</t>
+        </is>
+      </c>
+      <c r="D3239" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
+        </is>
+      </c>
+      <c r="E3239" s="1" t="n"/>
+      <c r="F3239" s="1" t="n"/>
+    </row>
+    <row r="3240">
+      <c r="A3240" s="1" t="n">
+        <v>9000111</v>
+      </c>
+      <c r="B3240" s="2" t="inlineStr">
+        <is>
+          <t>데굴데굴!</t>
+        </is>
+      </c>
+      <c r="C3240" s="2" t="inlineStr">
+        <is>
+          <t>Roll roll!</t>
+        </is>
+      </c>
+      <c r="D3240" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
+        </is>
+      </c>
+      <c r="E3240" s="1" t="n"/>
+      <c r="F3240" s="1" t="n"/>
+    </row>
+    <row r="3241">
+      <c r="A3241" s="1" t="n">
+        <v>9000112</v>
+      </c>
+      <c r="B3241" s="2" t="inlineStr">
+        <is>
+          <t>핀볼 모드!</t>
+        </is>
+      </c>
+      <c r="C3241" s="2" t="inlineStr">
+        <is>
+          <t>Pinball mode!</t>
+        </is>
+      </c>
+      <c r="D3241" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
+        </is>
+      </c>
+      <c r="E3241" s="1" t="n"/>
+      <c r="F3241" s="1" t="n"/>
+    </row>
+    <row r="3242">
+      <c r="A3242" s="1" t="n">
+        <v>9000113</v>
+      </c>
+      <c r="B3242" s="2" t="inlineStr">
+        <is>
+          <t>쳇바퀴 돌기!!</t>
+        </is>
+      </c>
+      <c r="C3242" s="2" t="inlineStr">
+        <is>
+          <t>WHEEL SPIN!!</t>
+        </is>
+      </c>
+      <c r="D3242" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
+        </is>
+      </c>
+      <c r="E3242" s="1" t="n"/>
+      <c r="F3242" s="1" t="n"/>
+    </row>
+    <row r="3243">
+      <c r="A3243" s="1" t="n">
+        <v>9000114</v>
+      </c>
+      <c r="B3243" s="2" t="inlineStr">
+        <is>
+          <t>빙글빙글~</t>
+        </is>
+      </c>
+      <c r="C3243" s="2" t="inlineStr">
+        <is>
+          <t>Round and round~</t>
+        </is>
+      </c>
+      <c r="D3243" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
+        </is>
+      </c>
+      <c r="E3243" s="1" t="n"/>
+      <c r="F3243" s="1" t="n"/>
+    </row>
+    <row r="3244">
+      <c r="A3244" s="1" t="n">
+        <v>9000115</v>
+      </c>
+      <c r="B3244" s="2" t="inlineStr">
+        <is>
+          <t>어지러워!!</t>
+        </is>
+      </c>
+      <c r="C3244" s="2" t="inlineStr">
+        <is>
+          <t>So DIZZY!!</t>
+        </is>
+      </c>
+      <c r="D3244" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
+        </is>
+      </c>
+      <c r="E3244" s="1" t="n"/>
+      <c r="F3244" s="1" t="n"/>
+    </row>
+    <row r="3245">
+      <c r="A3245" s="1" t="n">
+        <v>9000116</v>
+      </c>
+      <c r="B3245" s="2" t="inlineStr">
+        <is>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
+        </is>
+      </c>
+      <c r="C3245" s="2" t="inlineStr">
+        <is>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+        </is>
+      </c>
+      <c r="D3245" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
+        </is>
+      </c>
+      <c r="E3245" s="1" t="n"/>
+      <c r="F3245" s="1" t="n"/>
+    </row>
+    <row r="3246">
+      <c r="A3246" s="1" t="n">
+        <v>9000117</v>
+      </c>
+      <c r="B3246" s="2" t="inlineStr">
+        <is>
+          <t>기절!!</t>
+        </is>
+      </c>
+      <c r="C3246" s="2" t="inlineStr">
+        <is>
+          <t>Stunned!!</t>
+        </is>
+      </c>
+      <c r="D3246" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:38</t>
+        </is>
+      </c>
+      <c r="E3246" s="1" t="n"/>
+      <c r="F3246" s="1" t="n"/>
+    </row>
+    <row r="3247">
+      <c r="A3247" s="1" t="n">
+        <v>9000118</v>
+      </c>
+      <c r="B3247" s="2" t="inlineStr">
+        <is>
+          <t>소품이 떨어졌다!</t>
+        </is>
+      </c>
+      <c r="C3247" s="2" t="inlineStr">
+        <is>
+          <t>A prop dropped!</t>
+        </is>
+      </c>
+      <c r="D3247" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:397</t>
+        </is>
+      </c>
+      <c r="E3247" s="1" t="n"/>
+      <c r="F3247" s="1" t="n"/>
+    </row>
+    <row r="3248">
+      <c r="A3248" s="1" t="n">
+        <v>9000119</v>
+      </c>
+      <c r="B3248" s="2" t="inlineStr">
+        <is>
+          <t>조각 +1</t>
+        </is>
+      </c>
+      <c r="C3248" s="2" t="inlineStr">
+        <is>
+          <t>Shard +1</t>
+        </is>
+      </c>
+      <c r="D3248" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:460</t>
+        </is>
+      </c>
+      <c r="E3248" s="1" t="n"/>
+      <c r="F3248" s="1" t="n"/>
+    </row>
+    <row r="3249">
+      <c r="A3249" s="1" t="n">
+        <v>9000120</v>
+      </c>
+      <c r="B3249" s="2" t="inlineStr">
+        <is>
+          <t>{name} 강화! Lv {lv}</t>
+        </is>
+      </c>
+      <c r="C3249" s="2" t="inlineStr">
+        <is>
+          <t>{name} powered up! Lv {lv}</t>
+        </is>
+      </c>
+      <c r="D3249" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:461</t>
+        </is>
+      </c>
+      <c r="E3249" s="1" t="n"/>
+      <c r="F3249" s="1" t="n"/>
+    </row>
+    <row r="3250">
+      <c r="A3250" s="1" t="n">
+        <v>9000121</v>
+      </c>
+      <c r="B3250" s="2" t="inlineStr">
+        <is>
+          <t>{grade} 탄생!</t>
+        </is>
+      </c>
+      <c r="C3250" s="2" t="inlineStr">
+        <is>
+          <t>{grade} born!</t>
+        </is>
+      </c>
+      <c r="D3250" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:561</t>
+        </is>
+      </c>
+      <c r="E3250" s="1" t="n"/>
+      <c r="F3250" s="1" t="n"/>
+    </row>
+    <row r="3251">
+      <c r="A3251" s="1" t="n">
+        <v>9000122</v>
+      </c>
+      <c r="B3251" s="2" t="inlineStr">
+        <is>
+          <t>쌍둥이!</t>
+        </is>
+      </c>
+      <c r="C3251" s="2" t="inlineStr">
+        <is>
+          <t>Twins!</t>
+        </is>
+      </c>
+      <c r="D3251" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:566</t>
+        </is>
+      </c>
+      <c r="E3251" s="1" t="n"/>
+      <c r="F3251" s="1" t="n"/>
+    </row>
+    <row r="3252">
+      <c r="A3252" s="1" t="n">
+        <v>9000123</v>
+      </c>
+      <c r="B3252" s="2" t="inlineStr">
+        <is>
+          <t>치즈 운석!</t>
+        </is>
+      </c>
+      <c r="C3252" s="2" t="inlineStr">
+        <is>
+          <t>Cheese Meteor!</t>
+        </is>
+      </c>
+      <c r="D3252" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Rats/RatManager.cs:627</t>
+        </is>
+      </c>
+      <c r="E3252" s="1" t="n"/>
+      <c r="F3252" s="1" t="n"/>
+    </row>
+    <row r="3253">
+      <c r="A3253" s="1" t="n">
+        <v>9000124</v>
+      </c>
+      <c r="B3253" s="2" t="inlineStr">
+        <is>
+          <t>{floor}층 · {zone}</t>
+        </is>
+      </c>
+      <c r="C3253" s="2" t="inlineStr">
+        <is>
+          <t>Floor {floor} · {zone}</t>
+        </is>
+      </c>
+      <c r="D3253" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+        </is>
+      </c>
+      <c r="E3253" s="1" t="n"/>
+      <c r="F3253" s="1" t="n"/>
+    </row>
+    <row r="3254">
+      <c r="A3254" s="1" t="n">
+        <v>9000125</v>
+      </c>
+      <c r="B3254" s="2" t="inlineStr">
+        <is>
+          <t>계단 방 벽을 부숴라!</t>
+        </is>
+      </c>
+      <c r="C3254" s="2" t="inlineStr">
+        <is>
+          <t>Smash the wall to the stairs room!</t>
+        </is>
+      </c>
+      <c r="D3254" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:187</t>
+        </is>
+      </c>
+      <c r="E3254" s="1" t="n"/>
+      <c r="F3254" s="1" t="n"/>
+    </row>
+    <row r="3255">
+      <c r="A3255" s="1" t="n">
+        <v>9000126</v>
+      </c>
+      <c r="B3255" s="2" t="inlineStr">
+        <is>
+          <t>벽 붕괴! 방 확장</t>
+        </is>
+      </c>
+      <c r="C3255" s="2" t="inlineStr">
+        <is>
+          <t>Wall down! Room expanded</t>
+        </is>
+      </c>
+      <c r="D3255" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:332</t>
+        </is>
+      </c>
+      <c r="E3255" s="1" t="n"/>
+      <c r="F3255" s="1" t="n"/>
+    </row>
+    <row r="3256">
+      <c r="A3256" s="1" t="n">
+        <v>9000127</v>
+      </c>
+      <c r="B3256" s="2" t="inlineStr">
+        <is>
+          <t>계단 발견!</t>
+        </is>
+      </c>
+      <c r="C3256" s="2" t="inlineStr">
+        <is>
+          <t>Stairs found!</t>
+        </is>
+      </c>
+      <c r="D3256" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:338</t>
+        </is>
+      </c>
+      <c r="E3256" s="1" t="n"/>
+      <c r="F3256" s="1" t="n"/>
+    </row>
+    <row r="3257">
+      <c r="A3257" s="1" t="n">
+        <v>9000128</v>
+      </c>
+      <c r="B3257" s="2" t="inlineStr">
+        <is>
+          <t>계단에 닿으면 {next}층으로</t>
+        </is>
+      </c>
+      <c r="C3257" s="2" t="inlineStr">
+        <is>
+          <t>Touch the stairs to go to Floor {next}</t>
+        </is>
+      </c>
+      <c r="D3257" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/StageManager.cs:338</t>
+        </is>
+      </c>
+      <c r="E3257" s="1" t="n"/>
+      <c r="F3257" s="1" t="n"/>
+    </row>
+    <row r="3258">
+      <c r="A3258" s="1" t="n">
+        <v>9000129</v>
+      </c>
+      <c r="B3258" s="2" t="inlineStr">
+        <is>
+          <t>와르르!!</t>
+        </is>
+      </c>
+      <c r="C3258" s="2" t="inlineStr">
+        <is>
+          <t>Crumble!!</t>
+        </is>
+      </c>
+      <c r="D3258" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3258" s="1" t="n"/>
+      <c r="F3258" s="1" t="n"/>
+    </row>
+    <row r="3259">
+      <c r="A3259" s="1" t="n">
+        <v>9000130</v>
+      </c>
+      <c r="B3259" s="2" t="inlineStr">
+        <is>
+          <t>콰광!!</t>
+        </is>
+      </c>
+      <c r="C3259" s="2" t="inlineStr">
+        <is>
+          <t>KA-BOOM!!</t>
+        </is>
+      </c>
+      <c r="D3259" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3259" s="1" t="n"/>
+      <c r="F3259" s="1" t="n"/>
+    </row>
+    <row r="3260">
+      <c r="A3260" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B3260" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C3260" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D3260" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3260" s="1" t="n"/>
+      <c r="F3260" s="1" t="n"/>
+    </row>
+    <row r="3261">
+      <c r="A3261" s="1" t="n">
+        <v>9000132</v>
+      </c>
+      <c r="B3261" s="2" t="inlineStr">
+        <is>
+          <t>※ 출발 층은 스킬만으로 다 열리지 않아요 · 층을 클리어해야 더 위에서 출발할 수 있어요 (출동 화면에 안내)</t>
+        </is>
+      </c>
+      <c r="C3261" s="2" t="inlineStr">
+        <is>
+          <t>※ Skip needs cleared floors too · clear floors to start higher (shown on the Run screen)</t>
+        </is>
+      </c>
+      <c r="D3261" s="1" t="inlineStr">
+        <is>
+          <t>코드 · SkillPage.DrawDetail (Stage_Skip 노드)</t>
+        </is>
+      </c>
+      <c r="E3261" s="1" t="n"/>
+      <c r="F3261" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3261"/>
+  <dimension ref="A1:F3264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -73141,87 +73141,99 @@
     </row>
     <row r="3130">
       <c r="A3130" s="1" t="n">
-        <v>9000001</v>
+        <v>8000604</v>
       </c>
       <c r="B3130" s="2" t="inlineStr">
         <is>
-          <t>찍찍!! {power}</t>
+          <t>끝</t>
         </is>
       </c>
       <c r="C3130" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK!! {power}</t>
+          <t>The End</t>
         </is>
       </c>
       <c r="D3130" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:89</t>
-        </is>
-      </c>
-      <c r="E3130" s="1" t="n"/>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Jwerry/Card3/Text/Text</t>
+        </is>
+      </c>
+      <c r="E3130" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F3130" s="1" t="n"/>
     </row>
     <row r="3131">
       <c r="A3131" s="1" t="n">
-        <v>9000002</v>
+        <v>8000605</v>
       </c>
       <c r="B3131" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · 방 {open}/{total}</t>
+          <t>웨이터는 단단히 화가 났다!</t>
         </is>
       </c>
       <c r="C3131" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · Room {open}/{total}</t>
+          <t>The waiter is NOT amused!</t>
         </is>
       </c>
       <c r="D3131" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
-        </is>
-      </c>
-      <c r="E3131" s="1" t="n"/>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Jwerry/Card2/Text/Text</t>
+        </is>
+      </c>
+      <c r="E3131" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F3131" s="1" t="n"/>
     </row>
     <row r="3132">
       <c r="A3132" s="1" t="n">
-        <v>9000003</v>
+        <v>8000606</v>
       </c>
       <c r="B3132" s="2" t="inlineStr">
         <is>
-          <t>치즈 {cheese}</t>
+          <t>오늘의 앵콜 공연</t>
         </is>
       </c>
       <c r="C3132" s="2" t="inlineStr">
         <is>
-          <t>Cheese {cheese}</t>
+          <t>Tonight's Encore</t>
         </is>
       </c>
       <c r="D3132" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:110</t>
-        </is>
-      </c>
-      <c r="E3132" s="1" t="n"/>
+          <t>씬 · Game · HUD/SuperUlt/Cut/Frame/Scenes/Jwerry/Card1/Text/Text</t>
+        </is>
+      </c>
+      <c r="E3132" s="1" t="inlineStr">
+        <is>
+          <t>안 쓰임</t>
+        </is>
+      </c>
       <c r="F3132" s="1" t="n"/>
     </row>
     <row r="3133">
       <c r="A3133" s="1" t="n">
-        <v>9000004</v>
+        <v>9000001</v>
       </c>
       <c r="B3133" s="2" t="inlineStr">
         <is>
-          <t>{combo} 콤보!</t>
+          <t>찍찍!! {power}</t>
         </is>
       </c>
       <c r="C3133" s="2" t="inlineStr">
         <is>
-          <t>{combo} Combo!</t>
+          <t>SQUEAK!! {power}</t>
         </is>
       </c>
       <c r="D3133" s="1" t="inlineStr">
         <is>
-          <t>코드 · Core/GameManager.cs:111</t>
+          <t>코드 · Core/GameManager.cs:89</t>
         </is>
       </c>
       <c r="E3133" s="1" t="n"/>
@@ -73229,21 +73241,21 @@
     </row>
     <row r="3134">
       <c r="A3134" s="1" t="n">
-        <v>9000005</v>
+        <v>9000002</v>
       </c>
       <c r="B3134" s="2" t="inlineStr">
         <is>
-          <t>{name}의 필살 패턴!!</t>
+          <t>{floor}층 · 방 {open}/{total}</t>
         </is>
       </c>
       <c r="C3134" s="2" t="inlineStr">
         <is>
-          <t>{name}'s Special Pattern!!</t>
+          <t>Floor {floor} · Room {open}/{total}</t>
         </is>
       </c>
       <c r="D3134" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:88</t>
+          <t>코드 · Core/GameManager.cs:90, Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E3134" s="1" t="n"/>
@@ -73251,21 +73263,21 @@
     </row>
     <row r="3135">
       <c r="A3135" s="1" t="n">
-        <v>9000006</v>
+        <v>9000003</v>
       </c>
       <c r="B3135" s="2" t="inlineStr">
         <is>
-          <t>개굴!</t>
+          <t>치즈 {cheese}</t>
         </is>
       </c>
       <c r="C3135" s="2" t="inlineStr">
         <is>
-          <t>Ribbit!</t>
+          <t>Cheese {cheese}</t>
         </is>
       </c>
       <c r="D3135" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:89</t>
+          <t>코드 · Core/GameManager.cs:110</t>
         </is>
       </c>
       <c r="E3135" s="1" t="n"/>
@@ -73273,21 +73285,21 @@
     </row>
     <row r="3136">
       <c r="A3136" s="1" t="n">
-        <v>9000007</v>
+        <v>9000004</v>
       </c>
       <c r="B3136" s="2" t="inlineStr">
         <is>
-          <t>짜잔!!</t>
+          <t>{combo} 콤보!</t>
         </is>
       </c>
       <c r="C3136" s="2" t="inlineStr">
         <is>
-          <t>Ta-da!!</t>
+          <t>{combo} Combo!</t>
         </is>
       </c>
       <c r="D3136" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Boss.cs:90</t>
+          <t>코드 · Core/GameManager.cs:111</t>
         </is>
       </c>
       <c r="E3136" s="1" t="n"/>
@@ -73295,21 +73307,21 @@
     </row>
     <row r="3137">
       <c r="A3137" s="1" t="n">
-        <v>9000008</v>
+        <v>9000005</v>
       </c>
       <c r="B3137" s="2" t="inlineStr">
         <is>
-          <t>냥!</t>
+          <t>{name}의 필살 패턴!!</t>
         </is>
       </c>
       <c r="C3137" s="2" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>{name}'s Special Pattern!!</t>
         </is>
       </c>
       <c r="D3137" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:88</t>
         </is>
       </c>
       <c r="E3137" s="1" t="n"/>
@@ -73317,21 +73329,21 @@
     </row>
     <row r="3138">
       <c r="A3138" s="1" t="n">
-        <v>9000009</v>
+        <v>9000006</v>
       </c>
       <c r="B3138" s="2" t="inlineStr">
         <is>
-          <t>캬악!</t>
+          <t>개굴!</t>
         </is>
       </c>
       <c r="C3138" s="2" t="inlineStr">
         <is>
-          <t>Hsssk!</t>
+          <t>Ribbit!</t>
         </is>
       </c>
       <c r="D3138" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:89</t>
         </is>
       </c>
       <c r="E3138" s="1" t="n"/>
@@ -73339,21 +73351,21 @@
     </row>
     <row r="3139">
       <c r="A3139" s="1" t="n">
-        <v>9000010</v>
+        <v>9000007</v>
       </c>
       <c r="B3139" s="2" t="inlineStr">
         <is>
-          <t>냐?!</t>
+          <t>짜잔!!</t>
         </is>
       </c>
       <c r="C3139" s="2" t="inlineStr">
         <is>
-          <t>Mrow?!</t>
+          <t>Ta-da!!</t>
         </is>
       </c>
       <c r="D3139" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:86</t>
+          <t>코드 · Hazards/Boss.cs:90</t>
         </is>
       </c>
       <c r="E3139" s="1" t="n"/>
@@ -73361,16 +73373,16 @@
     </row>
     <row r="3140">
       <c r="A3140" s="1" t="n">
-        <v>9000011</v>
+        <v>9000008</v>
       </c>
       <c r="B3140" s="2" t="inlineStr">
         <is>
-          <t>하악!</t>
+          <t>냥!</t>
         </is>
       </c>
       <c r="C3140" s="2" t="inlineStr">
         <is>
-          <t>HISS!</t>
+          <t>Meow!</t>
         </is>
       </c>
       <c r="D3140" s="1" t="inlineStr">
@@ -73383,21 +73395,21 @@
     </row>
     <row r="3141">
       <c r="A3141" s="1" t="n">
-        <v>9000012</v>
+        <v>9000009</v>
       </c>
       <c r="B3141" s="2" t="inlineStr">
         <is>
-          <t>고양이 날려버림!</t>
+          <t>캬악!</t>
         </is>
       </c>
       <c r="C3141" s="2" t="inlineStr">
         <is>
-          <t>Cat sent flying!</t>
+          <t>Hsssk!</t>
         </is>
       </c>
       <c r="D3141" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E3141" s="1" t="n"/>
@@ -73405,21 +73417,21 @@
     </row>
     <row r="3142">
       <c r="A3142" s="1" t="n">
-        <v>9000013</v>
+        <v>9000010</v>
       </c>
       <c r="B3142" s="2" t="inlineStr">
         <is>
-          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
+          <t>냐?!</t>
         </is>
       </c>
       <c r="C3142" s="2" t="inlineStr">
         <is>
-          <t>{name} defeated · Behold the power of rats</t>
+          <t>Mrow?!</t>
         </is>
       </c>
       <c r="D3142" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:99</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E3142" s="1" t="n"/>
@@ -73427,21 +73439,21 @@
     </row>
     <row r="3143">
       <c r="A3143" s="1" t="n">
-        <v>9000014</v>
+        <v>9000011</v>
       </c>
       <c r="B3143" s="2" t="inlineStr">
         <is>
-          <t>(삐짐)</t>
+          <t>하악!</t>
         </is>
       </c>
       <c r="C3143" s="2" t="inlineStr">
         <is>
-          <t>(sulking)</t>
+          <t>HISS!</t>
         </is>
       </c>
       <c r="D3143" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:123</t>
+          <t>코드 · Hazards/Cat.cs:86</t>
         </is>
       </c>
       <c r="E3143" s="1" t="n"/>
@@ -73449,21 +73461,21 @@
     </row>
     <row r="3144">
       <c r="A3144" s="1" t="n">
-        <v>9000015</v>
+        <v>9000012</v>
       </c>
       <c r="B3144" s="2" t="inlineStr">
         <is>
-          <t>신사의 일격!! 크리티컬!</t>
+          <t>고양이 날려버림!</t>
         </is>
       </c>
       <c r="C3144" s="2" t="inlineStr">
         <is>
-          <t>Gentleman's Strike!! CRITICAL!</t>
+          <t>Cat sent flying!</t>
         </is>
       </c>
       <c r="D3144" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E3144" s="1" t="n"/>
@@ -73471,21 +73483,21 @@
     </row>
     <row r="3145">
       <c r="A3145" s="1" t="n">
-        <v>9000016</v>
+        <v>9000013</v>
       </c>
       <c r="B3145" s="2" t="inlineStr">
         <is>
-          <t>냥냥펀치!!</t>
+          <t>{name} 퇴치 · 쥐의 힘을 보여줬다</t>
         </is>
       </c>
       <c r="C3145" s="2" t="inlineStr">
         <is>
-          <t>Paw-paw punch!!</t>
+          <t>{name} defeated · Behold the power of rats</t>
         </is>
       </c>
       <c r="D3145" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:202</t>
+          <t>코드 · Hazards/Cat.cs:99</t>
         </is>
       </c>
       <c r="E3145" s="1" t="n"/>
@@ -73493,21 +73505,21 @@
     </row>
     <row r="3146">
       <c r="A3146" s="1" t="n">
-        <v>9000017</v>
+        <v>9000014</v>
       </c>
       <c r="B3146" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>(삐짐)</t>
         </is>
       </c>
       <c r="C3146" s="2" t="inlineStr">
         <is>
-          <t>One more!!</t>
+          <t>(sulking)</t>
         </is>
       </c>
       <c r="D3146" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:203</t>
+          <t>코드 · Hazards/Cat.cs:123</t>
         </is>
       </c>
       <c r="E3146" s="1" t="n"/>
@@ -73515,21 +73527,21 @@
     </row>
     <row r="3147">
       <c r="A3147" s="1" t="n">
-        <v>9000018</v>
+        <v>9000015</v>
       </c>
       <c r="B3147" s="2" t="inlineStr">
         <is>
-          <t>냐옹~</t>
+          <t>신사의 일격!! 크리티컬!</t>
         </is>
       </c>
       <c r="C3147" s="2" t="inlineStr">
         <is>
-          <t>Meow~</t>
+          <t>Gentleman's Strike!! CRITICAL!</t>
         </is>
       </c>
       <c r="D3147" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E3147" s="1" t="n"/>
@@ -73537,21 +73549,21 @@
     </row>
     <row r="3148">
       <c r="A3148" s="1" t="n">
-        <v>9000019</v>
+        <v>9000016</v>
       </c>
       <c r="B3148" s="2" t="inlineStr">
         <is>
-          <t>냥?</t>
+          <t>냥냥펀치!!</t>
         </is>
       </c>
       <c r="C3148" s="2" t="inlineStr">
         <is>
-          <t>Mrow?</t>
+          <t>Paw-paw punch!!</t>
         </is>
       </c>
       <c r="D3148" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:202</t>
         </is>
       </c>
       <c r="E3148" s="1" t="n"/>
@@ -73559,21 +73571,21 @@
     </row>
     <row r="3149">
       <c r="A3149" s="1" t="n">
-        <v>9000020</v>
+        <v>9000017</v>
       </c>
       <c r="B3149" s="2" t="inlineStr">
         <is>
-          <t>크르릉…</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="C3149" s="2" t="inlineStr">
         <is>
-          <t>Grrr...</t>
+          <t>One more!!</t>
         </is>
       </c>
       <c r="D3149" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:220</t>
+          <t>코드 · Hazards/Cat.cs:203</t>
         </is>
       </c>
       <c r="E3149" s="1" t="n"/>
@@ -73581,21 +73593,21 @@
     </row>
     <row r="3150">
       <c r="A3150" s="1" t="n">
-        <v>9000021</v>
+        <v>9000018</v>
       </c>
       <c r="B3150" s="2" t="inlineStr">
         <is>
-          <t>크아아앙!!</t>
+          <t>냐옹~</t>
         </is>
       </c>
       <c r="C3150" s="2" t="inlineStr">
         <is>
-          <t>RAAAWR!!</t>
+          <t>Meow~</t>
         </is>
       </c>
       <c r="D3150" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Cat.cs:413</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E3150" s="1" t="n"/>
@@ -73603,21 +73615,21 @@
     </row>
     <row r="3151">
       <c r="A3151" s="1" t="n">
-        <v>9000022</v>
+        <v>9000019</v>
       </c>
       <c r="B3151" s="2" t="inlineStr">
         <is>
-          <t>거기 모였냥?!</t>
+          <t>냥?</t>
         </is>
       </c>
       <c r="C3151" s="2" t="inlineStr">
         <is>
-          <t>All bunched up, meow?!</t>
+          <t>Mrow?</t>
         </is>
       </c>
       <c r="D3151" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E3151" s="1" t="n"/>
@@ -73625,21 +73637,21 @@
     </row>
     <row r="3152">
       <c r="A3152" s="1" t="n">
-        <v>9000023</v>
+        <v>9000020</v>
       </c>
       <c r="B3152" s="2" t="inlineStr">
         <is>
-          <t>딱 걸렸냥!</t>
+          <t>크르릉…</t>
         </is>
       </c>
       <c r="C3152" s="2" t="inlineStr">
         <is>
-          <t>Gotcha, meow!</t>
+          <t>Grrr...</t>
         </is>
       </c>
       <c r="D3152" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:220</t>
         </is>
       </c>
       <c r="E3152" s="1" t="n"/>
@@ -73647,21 +73659,21 @@
     </row>
     <row r="3153">
       <c r="A3153" s="1" t="n">
-        <v>9000024</v>
+        <v>9000021</v>
       </c>
       <c r="B3153" s="2" t="inlineStr">
         <is>
-          <t>냥냥냥!!</t>
+          <t>크아아앙!!</t>
         </is>
       </c>
       <c r="C3153" s="2" t="inlineStr">
         <is>
-          <t>Meow meow meow!!</t>
+          <t>RAAAWR!!</t>
         </is>
       </c>
       <c r="D3153" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:46</t>
+          <t>코드 · Hazards/Cat.cs:413</t>
         </is>
       </c>
       <c r="E3153" s="1" t="n"/>
@@ -73669,16 +73681,16 @@
     </row>
     <row r="3154">
       <c r="A3154" s="1" t="n">
-        <v>9000025</v>
+        <v>9000022</v>
       </c>
       <c r="B3154" s="2" t="inlineStr">
         <is>
-          <t>다 잡았다옹!</t>
+          <t>거기 모였냥?!</t>
         </is>
       </c>
       <c r="C3154" s="2" t="inlineStr">
         <is>
-          <t>Caught 'em all, meow!</t>
+          <t>All bunched up, meow?!</t>
         </is>
       </c>
       <c r="D3154" s="1" t="inlineStr">
@@ -73691,21 +73703,21 @@
     </row>
     <row r="3155">
       <c r="A3155" s="1" t="n">
-        <v>9000026</v>
+        <v>9000023</v>
       </c>
       <c r="B3155" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
+          <t>딱 걸렸냥!</t>
         </is>
       </c>
       <c r="C3155" s="2" t="inlineStr">
         <is>
-          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
+          <t>Gotcha, meow!</t>
         </is>
       </c>
       <c r="D3155" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:47</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E3155" s="1" t="n"/>
@@ -73713,21 +73725,21 @@
     </row>
     <row r="3156">
       <c r="A3156" s="1" t="n">
-        <v>9000027</v>
+        <v>9000024</v>
       </c>
       <c r="B3156" s="2" t="inlineStr">
         <is>
-          <t>특별 고양이: {name}!</t>
+          <t>냥냥냥!!</t>
         </is>
       </c>
       <c r="C3156" s="2" t="inlineStr">
         <is>
-          <t>Special cat: {name}!</t>
+          <t>Meow meow meow!!</t>
         </is>
       </c>
       <c r="D3156" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E3156" s="1" t="n"/>
@@ -73735,21 +73747,21 @@
     </row>
     <row r="3157">
       <c r="A3157" s="1" t="n">
-        <v>9000028</v>
+        <v>9000025</v>
       </c>
       <c r="B3157" s="2" t="inlineStr">
         <is>
-          <t>{name} 출현!</t>
+          <t>다 잡았다옹!</t>
         </is>
       </c>
       <c r="C3157" s="2" t="inlineStr">
         <is>
-          <t>{name} appears!</t>
+          <t>Caught 'em all, meow!</t>
         </is>
       </c>
       <c r="D3157" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:117</t>
+          <t>코드 · Hazards/CatManager.cs:46</t>
         </is>
       </c>
       <c r="E3157" s="1" t="n"/>
@@ -73757,21 +73769,21 @@
     </row>
     <row r="3158">
       <c r="A3158" s="1" t="n">
-        <v>9000029</v>
+        <v>9000026</v>
       </c>
       <c r="B3158" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>{crowd} · 쥐가 몰린 곳에 빨간 원이 뜨면 피하기 · 들이받아서 날려버려요!</t>
         </is>
       </c>
       <c r="C3158" s="2" t="inlineStr">
         <is>
-          <t>WHAM!</t>
+          <t>{crowd} · Dodge when a red circle appears where rats are bunched up · Headbutt it to send it flying!</t>
         </is>
       </c>
       <c r="D3158" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:47</t>
         </is>
       </c>
       <c r="E3158" s="1" t="n"/>
@@ -73779,21 +73791,21 @@
     </row>
     <row r="3159">
       <c r="A3159" s="1" t="n">
-        <v>9000030</v>
+        <v>9000027</v>
       </c>
       <c r="B3159" s="2" t="inlineStr">
         <is>
-          <t>치즈만 쏙!</t>
+          <t>특별 고양이: {name}!</t>
         </is>
       </c>
       <c r="C3159" s="2" t="inlineStr">
         <is>
-          <t>Snatched the cheese!</t>
+          <t>Special cat: {name}!</t>
         </is>
       </c>
       <c r="D3159" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:48</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E3159" s="1" t="n"/>
@@ -73801,21 +73813,21 @@
     </row>
     <row r="3160">
       <c r="A3160" s="1" t="n">
-        <v>9000031</v>
+        <v>9000028</v>
       </c>
       <c r="B3160" s="2" t="inlineStr">
         <is>
-          <t>딸깍!!</t>
+          <t>{name} 출현!</t>
         </is>
       </c>
       <c r="C3160" s="2" t="inlineStr">
         <is>
-          <t>SNAP!!</t>
+          <t>{name} appears!</t>
         </is>
       </c>
       <c r="D3160" s="1" t="inlineStr">
         <is>
-          <t>코드 · Hazards/Trap.cs:52</t>
+          <t>코드 · Hazards/CatManager.cs:117</t>
         </is>
       </c>
       <c r="E3160" s="1" t="n"/>
@@ -73823,21 +73835,21 @@
     </row>
     <row r="3161">
       <c r="A3161" s="1" t="n">
-        <v>9000032</v>
+        <v>9000029</v>
       </c>
       <c r="B3161" s="2" t="inlineStr">
         <is>
-          <t>아야!!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="C3161" s="2" t="inlineStr">
         <is>
-          <t>OUCH!!</t>
+          <t>WHAM!</t>
         </is>
       </c>
       <c r="D3161" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/CatManager.cs:143, Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E3161" s="1" t="n"/>
@@ -73845,21 +73857,21 @@
     </row>
     <row r="3162">
       <c r="A3162" s="1" t="n">
-        <v>9000033</v>
+        <v>9000030</v>
       </c>
       <c r="B3162" s="2" t="inlineStr">
         <is>
-          <t>뿅!</t>
+          <t>치즈만 쏙!</t>
         </is>
       </c>
       <c r="C3162" s="2" t="inlineStr">
         <is>
-          <t>Pop!</t>
+          <t>Snatched the cheese!</t>
         </is>
       </c>
       <c r="D3162" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Trap.cs:48</t>
         </is>
       </c>
       <c r="E3162" s="1" t="n"/>
@@ -73867,21 +73879,21 @@
     </row>
     <row r="3163">
       <c r="A3163" s="1" t="n">
-        <v>9000034</v>
+        <v>9000031</v>
       </c>
       <c r="B3163" s="2" t="inlineStr">
         <is>
-          <t>(맞음)</t>
+          <t>딸깍!!</t>
         </is>
       </c>
       <c r="C3163" s="2" t="inlineStr">
         <is>
-          <t>(hit)</t>
+          <t>SNAP!!</t>
         </is>
       </c>
       <c r="D3163" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:92</t>
+          <t>코드 · Hazards/Trap.cs:52</t>
         </is>
       </c>
       <c r="E3163" s="1" t="n"/>
@@ -73889,21 +73901,21 @@
     </row>
     <row r="3164">
       <c r="A3164" s="1" t="n">
-        <v>9000035</v>
+        <v>9000032</v>
       </c>
       <c r="B3164" s="2" t="inlineStr">
         <is>
-          <t>스트라이크!!</t>
+          <t>아야!!</t>
         </is>
       </c>
       <c r="C3164" s="2" t="inlineStr">
         <is>
-          <t>STRIKE!!</t>
+          <t>OUCH!!</t>
         </is>
       </c>
       <c r="D3164" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:212</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E3164" s="1" t="n"/>
@@ -73911,21 +73923,21 @@
     </row>
     <row r="3165">
       <c r="A3165" s="1" t="n">
-        <v>9000036</v>
+        <v>9000033</v>
       </c>
       <c r="B3165" s="2" t="inlineStr">
         <is>
-          <t>펑!!</t>
+          <t>뿅!</t>
         </is>
       </c>
       <c r="C3165" s="2" t="inlineStr">
         <is>
-          <t>BOOM!!</t>
+          <t>Pop!</t>
         </is>
       </c>
       <c r="D3165" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:253</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E3165" s="1" t="n"/>
@@ -73933,21 +73945,21 @@
     </row>
     <row r="3166">
       <c r="A3166" s="1" t="n">
-        <v>9000037</v>
+        <v>9000034</v>
       </c>
       <c r="B3166" s="2" t="inlineStr">
         <is>
-          <t>치즈+</t>
+          <t>(맞음)</t>
         </is>
       </c>
       <c r="C3166" s="2" t="inlineStr">
         <is>
-          <t>Cheese+</t>
+          <t>(hit)</t>
         </is>
       </c>
       <c r="D3166" s="1" t="inlineStr">
         <is>
-          <t>코드 · Humans/Human.cs:254</t>
+          <t>코드 · Humans/Human.cs:92</t>
         </is>
       </c>
       <c r="E3166" s="1" t="n"/>
@@ -73955,21 +73967,21 @@
     </row>
     <row r="3167">
       <c r="A3167" s="1" t="n">
-        <v>9000038</v>
+        <v>9000035</v>
       </c>
       <c r="B3167" s="2" t="inlineStr">
         <is>
-          <t>크리티컬!</t>
+          <t>스트라이크!!</t>
         </is>
       </c>
       <c r="C3167" s="2" t="inlineStr">
         <is>
-          <t>Critical!</t>
+          <t>STRIKE!!</t>
         </is>
       </c>
       <c r="D3167" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:85</t>
+          <t>코드 · Humans/Human.cs:212</t>
         </is>
       </c>
       <c r="E3167" s="1" t="n"/>
@@ -73977,21 +73989,21 @@
     </row>
     <row r="3168">
       <c r="A3168" s="1" t="n">
-        <v>9000039</v>
+        <v>9000036</v>
       </c>
       <c r="B3168" s="2" t="inlineStr">
         <is>
-          <t>황금!</t>
+          <t>펑!!</t>
         </is>
       </c>
       <c r="C3168" s="2" t="inlineStr">
         <is>
-          <t>Gold!</t>
+          <t>BOOM!!</t>
         </is>
       </c>
       <c r="D3168" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:115</t>
+          <t>코드 · Humans/Human.cs:253</t>
         </is>
       </c>
       <c r="E3168" s="1" t="n"/>
@@ -73999,21 +74011,21 @@
     </row>
     <row r="3169">
       <c r="A3169" s="1" t="n">
-        <v>9000040</v>
+        <v>9000037</v>
       </c>
       <c r="B3169" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>치즈+</t>
         </is>
       </c>
       <c r="C3169" s="2" t="inlineStr">
         <is>
-          <t>BANG!</t>
+          <t>Cheese+</t>
         </is>
       </c>
       <c r="D3169" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/Item.cs:229</t>
+          <t>코드 · Humans/Human.cs:254</t>
         </is>
       </c>
       <c r="E3169" s="1" t="n"/>
@@ -74021,21 +74033,21 @@
     </row>
     <row r="3170">
       <c r="A3170" s="1" t="n">
-        <v>9000041</v>
+        <v>9000038</v>
       </c>
       <c r="B3170" s="2" t="inlineStr">
         <is>
-          <t>찍!</t>
+          <t>크리티컬!</t>
         </is>
       </c>
       <c r="C3170" s="2" t="inlineStr">
         <is>
-          <t>Squeak!</t>
+          <t>Critical!</t>
         </is>
       </c>
       <c r="D3170" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Items/Item.cs:85</t>
         </is>
       </c>
       <c r="E3170" s="1" t="n"/>
@@ -74043,21 +74055,21 @@
     </row>
     <row r="3171">
       <c r="A3171" s="1" t="n">
-        <v>9000042</v>
+        <v>9000039</v>
       </c>
       <c r="B3171" s="2" t="inlineStr">
         <is>
-          <t>와장창!</t>
+          <t>황금!</t>
         </is>
       </c>
       <c r="C3171" s="2" t="inlineStr">
         <is>
-          <t>CRASH!</t>
+          <t>Gold!</t>
         </is>
       </c>
       <c r="D3171" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/Item.cs:115</t>
         </is>
       </c>
       <c r="E3171" s="1" t="n"/>
@@ -74065,21 +74077,21 @@
     </row>
     <row r="3172">
       <c r="A3172" s="1" t="n">
-        <v>9000043</v>
+        <v>9000040</v>
       </c>
       <c r="B3172" s="2" t="inlineStr">
         <is>
-          <t>갉갉!</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="C3172" s="2" t="inlineStr">
         <is>
-          <t>Gnaw gnaw!</t>
+          <t>BANG!</t>
         </is>
       </c>
       <c r="D3172" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/Item.cs:229</t>
         </is>
       </c>
       <c r="E3172" s="1" t="n"/>
@@ -74087,21 +74099,21 @@
     </row>
     <row r="3173">
       <c r="A3173" s="1" t="n">
-        <v>9000044</v>
+        <v>9000041</v>
       </c>
       <c r="B3173" s="2" t="inlineStr">
         <is>
-          <t>챙그랑!</t>
+          <t>찍!</t>
         </is>
       </c>
       <c r="C3173" s="2" t="inlineStr">
         <is>
-          <t>Clang!</t>
+          <t>Squeak!</t>
         </is>
       </c>
       <c r="D3173" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:57</t>
+          <t>코드 · Items/ItemManager.cs:57, Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E3173" s="1" t="n"/>
@@ -74109,16 +74121,16 @@
     </row>
     <row r="3174">
       <c r="A3174" s="1" t="n">
-        <v>9000045</v>
+        <v>9000042</v>
       </c>
       <c r="B3174" s="2" t="inlineStr">
         <is>
-          <t>와르르!</t>
+          <t>와장창!</t>
         </is>
       </c>
       <c r="C3174" s="2" t="inlineStr">
         <is>
-          <t>Crumble!</t>
+          <t>CRASH!</t>
         </is>
       </c>
       <c r="D3174" s="1" t="inlineStr">
@@ -74131,21 +74143,21 @@
     </row>
     <row r="3175">
       <c r="A3175" s="1" t="n">
-        <v>9000046</v>
+        <v>9000043</v>
       </c>
       <c r="B3175" s="2" t="inlineStr">
         <is>
-          <t>와장창!!</t>
+          <t>갉갉!</t>
         </is>
       </c>
       <c r="C3175" s="2" t="inlineStr">
         <is>
-          <t>CRASH!!</t>
+          <t>Gnaw gnaw!</t>
         </is>
       </c>
       <c r="D3175" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E3175" s="1" t="n"/>
@@ -74153,21 +74165,21 @@
     </row>
     <row r="3176">
       <c r="A3176" s="1" t="n">
-        <v>9000047</v>
+        <v>9000044</v>
       </c>
       <c r="B3176" s="2" t="inlineStr">
         <is>
-          <t>쿠당탕!!</t>
+          <t>챙그랑!</t>
         </is>
       </c>
       <c r="C3176" s="2" t="inlineStr">
         <is>
-          <t>Ka-THUNK!!</t>
+          <t>Clang!</t>
         </is>
       </c>
       <c r="D3176" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E3176" s="1" t="n"/>
@@ -74175,21 +74187,21 @@
     </row>
     <row r="3177">
       <c r="A3177" s="1" t="n">
-        <v>9000048</v>
+        <v>9000045</v>
       </c>
       <c r="B3177" s="2" t="inlineStr">
         <is>
-          <t>콰직!!</t>
+          <t>와르르!</t>
         </is>
       </c>
       <c r="C3177" s="2" t="inlineStr">
         <is>
-          <t>CRUNCH!!</t>
+          <t>Crumble!</t>
         </is>
       </c>
       <c r="D3177" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:59</t>
+          <t>코드 · Items/ItemManager.cs:57</t>
         </is>
       </c>
       <c r="E3177" s="1" t="n"/>
@@ -74197,21 +74209,21 @@
     </row>
     <row r="3178">
       <c r="A3178" s="1" t="n">
-        <v>9000049</v>
+        <v>9000046</v>
       </c>
       <c r="B3178" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} 보너스!</t>
+          <t>와장창!!</t>
         </is>
       </c>
       <c r="C3178" s="2" t="inlineStr">
         <is>
-          <t>AIR x{n} Bonus!</t>
+          <t>CRASH!!</t>
         </is>
       </c>
       <c r="D3178" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:219</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E3178" s="1" t="n"/>
@@ -74219,21 +74231,21 @@
     </row>
     <row r="3179">
       <c r="A3179" s="1" t="n">
-        <v>9000050</v>
+        <v>9000047</v>
       </c>
       <c r="B3179" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>쿠당탕!!</t>
         </is>
       </c>
       <c r="C3179" s="2" t="inlineStr">
         <is>
-          <t>Zap!</t>
+          <t>Ka-THUNK!!</t>
         </is>
       </c>
       <c r="D3179" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:296</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E3179" s="1" t="n"/>
@@ -74241,21 +74253,21 @@
     </row>
     <row r="3180">
       <c r="A3180" s="1" t="n">
-        <v>9000051</v>
+        <v>9000048</v>
       </c>
       <c r="B3180" s="2" t="inlineStr">
         <is>
-          <t>로켓배송!</t>
+          <t>콰직!!</t>
         </is>
       </c>
       <c r="C3180" s="2" t="inlineStr">
         <is>
-          <t>Rocket Delivery!</t>
+          <t>CRUNCH!!</t>
         </is>
       </c>
       <c r="D3180" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:59</t>
         </is>
       </c>
       <c r="E3180" s="1" t="n"/>
@@ -74263,21 +74275,21 @@
     </row>
     <row r="3181">
       <c r="A3181" s="1" t="n">
-        <v>9000052</v>
+        <v>9000049</v>
       </c>
       <c r="B3181" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!! ×{n}</t>
+          <t>AIR x{n} 보너스!</t>
         </is>
       </c>
       <c r="C3181" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!! ×{n}</t>
+          <t>AIR x{n} Bonus!</t>
         </is>
       </c>
       <c r="D3181" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:441</t>
+          <t>코드 · Items/ItemManager.cs:219</t>
         </is>
       </c>
       <c r="E3181" s="1" t="n"/>
@@ -74285,21 +74297,21 @@
     </row>
     <row r="3182">
       <c r="A3182" s="1" t="n">
-        <v>9000053</v>
+        <v>9000050</v>
       </c>
       <c r="B3182" s="2" t="inlineStr">
         <is>
-          <t>택배 왔습니다!!</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="C3182" s="2" t="inlineStr">
         <is>
-          <t>Package delivered!!</t>
+          <t>Zap!</t>
         </is>
       </c>
       <c r="D3182" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:457</t>
+          <t>코드 · Items/ItemManager.cs:296</t>
         </is>
       </c>
       <c r="E3182" s="1" t="n"/>
@@ -74307,21 +74319,21 @@
     </row>
     <row r="3183">
       <c r="A3183" s="1" t="n">
-        <v>9000054</v>
+        <v>9000051</v>
       </c>
       <c r="B3183" s="2" t="inlineStr">
         <is>
-          <t>쿵!</t>
+          <t>로켓배송!</t>
         </is>
       </c>
       <c r="C3183" s="2" t="inlineStr">
         <is>
-          <t>Thud!</t>
+          <t>Rocket Delivery!</t>
         </is>
       </c>
       <c r="D3183" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E3183" s="1" t="n"/>
@@ -74329,21 +74341,21 @@
     </row>
     <row r="3184">
       <c r="A3184" s="1" t="n">
-        <v>9000055</v>
+        <v>9000052</v>
       </c>
       <c r="B3184" s="2" t="inlineStr">
         <is>
-          <t>문 앞 배송 완료</t>
+          <t>택배 왔습니다!! ×{n}</t>
         </is>
       </c>
       <c r="C3184" s="2" t="inlineStr">
         <is>
-          <t>Left at your door</t>
+          <t>Package delivered!! ×{n}</t>
         </is>
       </c>
       <c r="D3184" s="1" t="inlineStr">
         <is>
-          <t>코드 · Items/ItemManager.cs:458</t>
+          <t>코드 · Items/ItemManager.cs:441</t>
         </is>
       </c>
       <c r="E3184" s="1" t="n"/>
@@ -74351,21 +74363,21 @@
     </row>
     <row r="3185">
       <c r="A3185" s="1" t="n">
-        <v>9000056</v>
+        <v>9000053</v>
       </c>
       <c r="B3185" s="2" t="inlineStr">
         <is>
-          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
+          <t>택배 왔습니다!!</t>
         </is>
       </c>
       <c r="C3185" s="2" t="inlineStr">
         <is>
-          <t>Next time we go higher!|We just gotta find the stairs!</t>
+          <t>Package delivered!!</t>
         </is>
       </c>
       <c r="D3185" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:457</t>
         </is>
       </c>
       <c r="E3185" s="1" t="n"/>
@@ -74373,21 +74385,21 @@
     </row>
     <row r="3186">
       <c r="A3186" s="1" t="n">
-        <v>9000057</v>
+        <v>9000054</v>
       </c>
       <c r="B3186" s="2" t="inlineStr">
         <is>
-          <t>치즈 몰래 먹었지?|…아니?</t>
+          <t>쿵!</t>
         </is>
       </c>
       <c r="C3186" s="2" t="inlineStr">
         <is>
-          <t>You ate the Cheese, didn't you?|...Nope?</t>
+          <t>Thud!</t>
         </is>
       </c>
       <c r="D3186" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E3186" s="1" t="n"/>
@@ -74395,21 +74407,21 @@
     </row>
     <row r="3187">
       <c r="A3187" s="1" t="n">
-        <v>9000058</v>
+        <v>9000055</v>
       </c>
       <c r="B3187" s="2" t="inlineStr">
         <is>
-          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
+          <t>문 앞 배송 완료</t>
         </is>
       </c>
       <c r="C3187" s="2" t="inlineStr">
         <is>
-          <t>See the researcher's face?|LOL total panic</t>
+          <t>Left at your door</t>
         </is>
       </c>
       <c r="D3187" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:69</t>
+          <t>코드 · Items/ItemManager.cs:458</t>
         </is>
       </c>
       <c r="E3187" s="1" t="n"/>
@@ -74417,16 +74429,16 @@
     </row>
     <row r="3188">
       <c r="A3188" s="1" t="n">
-        <v>9000059</v>
+        <v>9000056</v>
       </c>
       <c r="B3188" s="2" t="inlineStr">
         <is>
-          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
+          <t>다음엔 더 높이 간다!|계단만 찾으면 돼!</t>
         </is>
       </c>
       <c r="C3188" s="2" t="inlineStr">
         <is>
-          <t>That cat was SO scary...|It stepped on my tail</t>
+          <t>Next time we go higher!|We just gotta find the stairs!</t>
         </is>
       </c>
       <c r="D3188" s="1" t="inlineStr">
@@ -74439,21 +74451,21 @@
     </row>
     <row r="3189">
       <c r="A3189" s="1" t="n">
-        <v>9000060</v>
+        <v>9000057</v>
       </c>
       <c r="B3189" s="2" t="inlineStr">
         <is>
-          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
+          <t>치즈 몰래 먹었지?|…아니?</t>
         </is>
       </c>
       <c r="C3189" s="2" t="inlineStr">
         <is>
-          <t>Rank up and new buddies come!|Wait, really?</t>
+          <t>You ate the Cheese, didn't you?|...Nope?</t>
         </is>
       </c>
       <c r="D3189" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E3189" s="1" t="n"/>
@@ -74461,21 +74473,21 @@
     </row>
     <row r="3190">
       <c r="A3190" s="1" t="n">
-        <v>9000061</v>
+        <v>9000058</v>
       </c>
       <c r="B3190" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 내 차례야|5분만…</t>
+          <t>연구원 표정 봤어?|ㅋㅋㅋ 완전 놀람</t>
         </is>
       </c>
       <c r="C3190" s="2" t="inlineStr">
         <is>
-          <t>My turn on the wheel|5 more minutes...</t>
+          <t>See the researcher's face?|LOL total panic</t>
         </is>
       </c>
       <c r="D3190" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E3190" s="1" t="n"/>
@@ -74483,21 +74495,21 @@
     </row>
     <row r="3191">
       <c r="A3191" s="1" t="n">
-        <v>9000062</v>
+        <v>9000059</v>
       </c>
       <c r="B3191" s="2" t="inlineStr">
         <is>
-          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
+          <t>고양이 진짜 무서웠어…|난 꼬리 밟혔어</t>
         </is>
       </c>
       <c r="C3191" s="2" t="inlineStr">
         <is>
-          <t>See the guard's flashlight?|Nearly blinded me</t>
+          <t>That cat was SO scary...|It stepped on my tail</t>
         </is>
       </c>
       <c r="D3191" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:70</t>
+          <t>코드 · Lobby/LobbyHome.cs:69</t>
         </is>
       </c>
       <c r="E3191" s="1" t="n"/>
@@ -74505,16 +74517,16 @@
     </row>
     <row r="3192">
       <c r="A3192" s="1" t="n">
-        <v>9000063</v>
+        <v>9000060</v>
       </c>
       <c r="B3192" s="2" t="inlineStr">
         <is>
-          <t>연구 자료 또 훔치자!|찍찍!</t>
+          <t>훈장 달면 새 친구 온대!|오 진짜?</t>
         </is>
       </c>
       <c r="C3192" s="2" t="inlineStr">
         <is>
-          <t>Let's steal more Research!|Squeak squeak!</t>
+          <t>Rank up and new buddies come!|Wait, really?</t>
         </is>
       </c>
       <c r="D3192" s="1" t="inlineStr">
@@ -74527,16 +74539,16 @@
     </row>
     <row r="3193">
       <c r="A3193" s="1" t="n">
-        <v>9000064</v>
+        <v>9000061</v>
       </c>
       <c r="B3193" s="2" t="inlineStr">
         <is>
-          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
+          <t>쳇바퀴 내 차례야|5분만…</t>
         </is>
       </c>
       <c r="C3193" s="2" t="inlineStr">
         <is>
-          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
+          <t>My turn on the wheel|5 more minutes...</t>
         </is>
       </c>
       <c r="D3193" s="1" t="inlineStr">
@@ -74549,21 +74561,21 @@
     </row>
     <row r="3194">
       <c r="A3194" s="1" t="n">
-        <v>9000065</v>
+        <v>9000062</v>
       </c>
       <c r="B3194" s="2" t="inlineStr">
         <is>
-          <t>찍?</t>
+          <t>경비원 손전등 봤어?|눈부셔 죽는 줄</t>
         </is>
       </c>
       <c r="C3194" s="2" t="inlineStr">
         <is>
-          <t>Squeak?</t>
+          <t>See the guard's flashlight?|Nearly blinded me</t>
         </is>
       </c>
       <c r="D3194" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E3194" s="1" t="n"/>
@@ -74571,21 +74583,21 @@
     </row>
     <row r="3195">
       <c r="A3195" s="1" t="n">
-        <v>9000066</v>
+        <v>9000063</v>
       </c>
       <c r="B3195" s="2" t="inlineStr">
         <is>
-          <t>찍찍!</t>
+          <t>연구 자료 또 훔치자!|찍찍!</t>
         </is>
       </c>
       <c r="C3195" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak!</t>
+          <t>Let's steal more Research!|Squeak squeak!</t>
         </is>
       </c>
       <c r="D3195" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E3195" s="1" t="n"/>
@@ -74593,21 +74605,21 @@
     </row>
     <row r="3196">
       <c r="A3196" s="1" t="n">
-        <v>9000067</v>
+        <v>9000064</v>
       </c>
       <c r="B3196" s="2" t="inlineStr">
         <is>
-          <t>킁킁…</t>
+          <t>오늘 저녁은 체다!|어제도 체다였잖아</t>
         </is>
       </c>
       <c r="C3196" s="2" t="inlineStr">
         <is>
-          <t>Sniff sniff...</t>
+          <t>Cheddar for dinner tonight!|We had cheddar yesterday too</t>
         </is>
       </c>
       <c r="D3196" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:72</t>
+          <t>코드 · Lobby/LobbyHome.cs:70</t>
         </is>
       </c>
       <c r="E3196" s="1" t="n"/>
@@ -74615,16 +74627,16 @@
     </row>
     <row r="3197">
       <c r="A3197" s="1" t="n">
-        <v>9000068</v>
+        <v>9000065</v>
       </c>
       <c r="B3197" s="2" t="inlineStr">
         <is>
-          <t>배고파…</t>
+          <t>찍?</t>
         </is>
       </c>
       <c r="C3197" s="2" t="inlineStr">
         <is>
-          <t>So hungry...</t>
+          <t>Squeak?</t>
         </is>
       </c>
       <c r="D3197" s="1" t="inlineStr">
@@ -74637,16 +74649,16 @@
     </row>
     <row r="3198">
       <c r="A3198" s="1" t="n">
-        <v>9000069</v>
+        <v>9000066</v>
       </c>
       <c r="B3198" s="2" t="inlineStr">
         <is>
-          <t>탈출하고 싶다</t>
+          <t>찍찍!</t>
         </is>
       </c>
       <c r="C3198" s="2" t="inlineStr">
         <is>
-          <t>I wanna escape</t>
+          <t>Squeak squeak!</t>
         </is>
       </c>
       <c r="D3198" s="1" t="inlineStr">
@@ -74659,16 +74671,16 @@
     </row>
     <row r="3199">
       <c r="A3199" s="1" t="n">
-        <v>9000070</v>
+        <v>9000067</v>
       </c>
       <c r="B3199" s="2" t="inlineStr">
         <is>
-          <t>치즈 냄새!</t>
+          <t>킁킁…</t>
         </is>
       </c>
       <c r="C3199" s="2" t="inlineStr">
         <is>
-          <t>I smell Cheese!</t>
+          <t>Sniff sniff...</t>
         </is>
       </c>
       <c r="D3199" s="1" t="inlineStr">
@@ -74681,16 +74693,16 @@
     </row>
     <row r="3200">
       <c r="A3200" s="1" t="n">
-        <v>9000071</v>
+        <v>9000068</v>
       </c>
       <c r="B3200" s="2" t="inlineStr">
         <is>
-          <t>여긴 안전해</t>
+          <t>배고파…</t>
         </is>
       </c>
       <c r="C3200" s="2" t="inlineStr">
         <is>
-          <t>It's safe here</t>
+          <t>So hungry...</t>
         </is>
       </c>
       <c r="D3200" s="1" t="inlineStr">
@@ -74703,21 +74715,21 @@
     </row>
     <row r="3201">
       <c r="A3201" s="1" t="n">
-        <v>9000072</v>
+        <v>9000069</v>
       </c>
       <c r="B3201" s="2" t="inlineStr">
         <is>
-          <t>찍?!</t>
+          <t>탈출하고 싶다</t>
         </is>
       </c>
       <c r="C3201" s="2" t="inlineStr">
         <is>
-          <t>Squeak?!</t>
+          <t>I wanna escape</t>
         </is>
       </c>
       <c r="D3201" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3201" s="1" t="n"/>
@@ -74725,21 +74737,21 @@
     </row>
     <row r="3202">
       <c r="A3202" s="1" t="n">
-        <v>9000073</v>
+        <v>9000070</v>
       </c>
       <c r="B3202" s="2" t="inlineStr">
         <is>
-          <t>놔줘~!</t>
+          <t>치즈 냄새!</t>
         </is>
       </c>
       <c r="C3202" s="2" t="inlineStr">
         <is>
-          <t>Lemme go~!</t>
+          <t>I smell Cheese!</t>
         </is>
       </c>
       <c r="D3202" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3202" s="1" t="n"/>
@@ -74747,21 +74759,21 @@
     </row>
     <row r="3203">
       <c r="A3203" s="1" t="n">
-        <v>9000074</v>
+        <v>9000071</v>
       </c>
       <c r="B3203" s="2" t="inlineStr">
         <is>
-          <t>으아아</t>
+          <t>여긴 안전해</t>
         </is>
       </c>
       <c r="C3203" s="2" t="inlineStr">
         <is>
-          <t>Waaah</t>
+          <t>It's safe here</t>
         </is>
       </c>
       <c r="D3203" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:73</t>
+          <t>코드 · Lobby/LobbyHome.cs:72</t>
         </is>
       </c>
       <c r="E3203" s="1" t="n"/>
@@ -74769,16 +74781,16 @@
     </row>
     <row r="3204">
       <c r="A3204" s="1" t="n">
-        <v>9000075</v>
+        <v>9000072</v>
       </c>
       <c r="B3204" s="2" t="inlineStr">
         <is>
-          <t>높아 높아!</t>
+          <t>찍?!</t>
         </is>
       </c>
       <c r="C3204" s="2" t="inlineStr">
         <is>
-          <t>So high, so high!</t>
+          <t>Squeak?!</t>
         </is>
       </c>
       <c r="D3204" s="1" t="inlineStr">
@@ -74791,16 +74803,16 @@
     </row>
     <row r="3205">
       <c r="A3205" s="1" t="n">
-        <v>9000076</v>
+        <v>9000073</v>
       </c>
       <c r="B3205" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍!!</t>
+          <t>놔줘~!</t>
         </is>
       </c>
       <c r="C3205" s="2" t="inlineStr">
         <is>
-          <t>SQUEAK SQUEAK SQUEAK!!</t>
+          <t>Lemme go~!</t>
         </is>
       </c>
       <c r="D3205" s="1" t="inlineStr">
@@ -74813,21 +74825,21 @@
     </row>
     <row r="3206">
       <c r="A3206" s="1" t="n">
-        <v>9000077</v>
+        <v>9000074</v>
       </c>
       <c r="B3206" s="2" t="inlineStr">
         <is>
-          <t>어질어질…</t>
+          <t>으아아</t>
         </is>
       </c>
       <c r="C3206" s="2" t="inlineStr">
         <is>
-          <t>So dizzy...</t>
+          <t>Waaah</t>
         </is>
       </c>
       <c r="D3206" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E3206" s="1" t="n"/>
@@ -74835,21 +74847,21 @@
     </row>
     <row r="3207">
       <c r="A3207" s="1" t="n">
-        <v>9000078</v>
+        <v>9000075</v>
       </c>
       <c r="B3207" s="2" t="inlineStr">
         <is>
-          <t>다시 해줘!</t>
+          <t>높아 높아!</t>
         </is>
       </c>
       <c r="C3207" s="2" t="inlineStr">
         <is>
-          <t>Again again!</t>
+          <t>So high, so high!</t>
         </is>
       </c>
       <c r="D3207" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E3207" s="1" t="n"/>
@@ -74857,21 +74869,21 @@
     </row>
     <row r="3208">
       <c r="A3208" s="1" t="n">
-        <v>9000079</v>
+        <v>9000076</v>
       </c>
       <c r="B3208" s="2" t="inlineStr">
         <is>
-          <t>별이 보여…</t>
+          <t>찍찍찍!!</t>
         </is>
       </c>
       <c r="C3208" s="2" t="inlineStr">
         <is>
-          <t>Seeing stars...</t>
+          <t>SQUEAK SQUEAK SQUEAK!!</t>
         </is>
       </c>
       <c r="D3208" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:74</t>
+          <t>코드 · Lobby/LobbyHome.cs:73</t>
         </is>
       </c>
       <c r="E3208" s="1" t="n"/>
@@ -74879,16 +74891,16 @@
     </row>
     <row r="3209">
       <c r="A3209" s="1" t="n">
-        <v>9000080</v>
+        <v>9000077</v>
       </c>
       <c r="B3209" s="2" t="inlineStr">
         <is>
-          <t>찍… 찍…</t>
+          <t>어질어질…</t>
         </is>
       </c>
       <c r="C3209" s="2" t="inlineStr">
         <is>
-          <t>Squeak... squeak...</t>
+          <t>So dizzy...</t>
         </is>
       </c>
       <c r="D3209" s="1" t="inlineStr">
@@ -74901,21 +74913,21 @@
     </row>
     <row r="3210">
       <c r="A3210" s="1" t="n">
-        <v>9000081</v>
+        <v>9000078</v>
       </c>
       <c r="B3210" s="2" t="inlineStr">
         <is>
-          <t>폴짝!</t>
+          <t>다시 해줘!</t>
         </is>
       </c>
       <c r="C3210" s="2" t="inlineStr">
         <is>
-          <t>Hop!</t>
+          <t>Again again!</t>
         </is>
       </c>
       <c r="D3210" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E3210" s="1" t="n"/>
@@ -74923,21 +74935,21 @@
     </row>
     <row r="3211">
       <c r="A3211" s="1" t="n">
-        <v>9000082</v>
+        <v>9000079</v>
       </c>
       <c r="B3211" s="2" t="inlineStr">
         <is>
-          <t>야호!</t>
+          <t>별이 보여…</t>
         </is>
       </c>
       <c r="C3211" s="2" t="inlineStr">
         <is>
-          <t>Wheee!</t>
+          <t>Seeing stars...</t>
         </is>
       </c>
       <c r="D3211" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:75</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E3211" s="1" t="n"/>
@@ -74945,21 +74957,21 @@
     </row>
     <row r="3212">
       <c r="A3212" s="1" t="n">
-        <v>9000083</v>
+        <v>9000080</v>
       </c>
       <c r="B3212" s="2" t="inlineStr">
         <is>
-          <t>헉헉</t>
+          <t>찍… 찍…</t>
         </is>
       </c>
       <c r="C3212" s="2" t="inlineStr">
         <is>
-          <t>Huff puff</t>
+          <t>Squeak... squeak...</t>
         </is>
       </c>
       <c r="D3212" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:74</t>
         </is>
       </c>
       <c r="E3212" s="1" t="n"/>
@@ -74967,21 +74979,21 @@
     </row>
     <row r="3213">
       <c r="A3213" s="1" t="n">
-        <v>9000084</v>
+        <v>9000081</v>
       </c>
       <c r="B3213" s="2" t="inlineStr">
         <is>
-          <t>더 빨리!</t>
+          <t>폴짝!</t>
         </is>
       </c>
       <c r="C3213" s="2" t="inlineStr">
         <is>
-          <t>Faster!</t>
+          <t>Hop!</t>
         </is>
       </c>
       <c r="D3213" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E3213" s="1" t="n"/>
@@ -74989,21 +75001,21 @@
     </row>
     <row r="3214">
       <c r="A3214" s="1" t="n">
-        <v>9000085</v>
+        <v>9000082</v>
       </c>
       <c r="B3214" s="2" t="inlineStr">
         <is>
-          <t>근육 붙는 중</t>
+          <t>야호!</t>
         </is>
       </c>
       <c r="C3214" s="2" t="inlineStr">
         <is>
-          <t>Gains incoming</t>
+          <t>Wheee!</t>
         </is>
       </c>
       <c r="D3214" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:76</t>
+          <t>코드 · Lobby/LobbyHome.cs:75</t>
         </is>
       </c>
       <c r="E3214" s="1" t="n"/>
@@ -75011,16 +75023,16 @@
     </row>
     <row r="3215">
       <c r="A3215" s="1" t="n">
-        <v>9000086</v>
+        <v>9000083</v>
       </c>
       <c r="B3215" s="2" t="inlineStr">
         <is>
-          <t>찍찍찍찍</t>
+          <t>헉헉</t>
         </is>
       </c>
       <c r="C3215" s="2" t="inlineStr">
         <is>
-          <t>Squeak squeak squeak squeak</t>
+          <t>Huff puff</t>
         </is>
       </c>
       <c r="D3215" s="1" t="inlineStr">
@@ -75033,21 +75045,21 @@
     </row>
     <row r="3216">
       <c r="A3216" s="1" t="n">
-        <v>9000087</v>
+        <v>9000084</v>
       </c>
       <c r="B3216" s="2" t="inlineStr">
         <is>
-          <t>으아아아~!</t>
+          <t>더 빨리!</t>
         </is>
       </c>
       <c r="C3216" s="2" t="inlineStr">
         <is>
-          <t>Waaaaah~!</t>
+          <t>Faster!</t>
         </is>
       </c>
       <c r="D3216" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E3216" s="1" t="n"/>
@@ -75055,21 +75067,21 @@
     </row>
     <row r="3217">
       <c r="A3217" s="1" t="n">
-        <v>9000088</v>
+        <v>9000085</v>
       </c>
       <c r="B3217" s="2" t="inlineStr">
         <is>
-          <t>하암~ 잘 잤다</t>
+          <t>근육 붙는 중</t>
         </is>
       </c>
       <c r="C3217" s="2" t="inlineStr">
         <is>
-          <t>Yawn~ what a nap</t>
+          <t>Gains incoming</t>
         </is>
       </c>
       <c r="D3217" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E3217" s="1" t="n"/>
@@ -75077,21 +75089,21 @@
     </row>
     <row r="3218">
       <c r="A3218" s="1" t="n">
-        <v>9000089</v>
+        <v>9000086</v>
       </c>
       <c r="B3218" s="2" t="inlineStr">
         <is>
-          <t>냠, 배부르다</t>
+          <t>찍찍찍찍</t>
         </is>
       </c>
       <c r="C3218" s="2" t="inlineStr">
         <is>
-          <t>Nom, so full</t>
+          <t>Squeak squeak squeak squeak</t>
         </is>
       </c>
       <c r="D3218" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:77</t>
+          <t>코드 · Lobby/LobbyHome.cs:76</t>
         </is>
       </c>
       <c r="E3218" s="1" t="n"/>
@@ -75099,16 +75111,16 @@
     </row>
     <row r="3219">
       <c r="A3219" s="1" t="n">
-        <v>9000090</v>
+        <v>9000087</v>
       </c>
       <c r="B3219" s="2" t="inlineStr">
         <is>
-          <t>휴…</t>
+          <t>으아아아~!</t>
         </is>
       </c>
       <c r="C3219" s="2" t="inlineStr">
         <is>
-          <t>Phew...</t>
+          <t>Waaaaah~!</t>
         </is>
       </c>
       <c r="D3219" s="1" t="inlineStr">
@@ -75121,21 +75133,21 @@
     </row>
     <row r="3220">
       <c r="A3220" s="1" t="n">
-        <v>9000091</v>
+        <v>9000088</v>
       </c>
       <c r="B3220" s="2" t="inlineStr">
         <is>
-          <t>찍</t>
+          <t>하암~ 잘 잤다</t>
         </is>
       </c>
       <c r="C3220" s="2" t="inlineStr">
         <is>
-          <t>Squeak</t>
+          <t>Yawn~ what a nap</t>
         </is>
       </c>
       <c r="D3220" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/LobbyHome.cs:161</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E3220" s="1" t="n"/>
@@ -75143,21 +75155,21 @@
     </row>
     <row r="3221">
       <c r="A3221" s="1" t="n">
-        <v>9000092</v>
+        <v>9000089</v>
       </c>
       <c r="B3221" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>냠, 배부르다</t>
         </is>
       </c>
       <c r="C3221" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Nom, so full</t>
         </is>
       </c>
       <c r="D3221" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E3221" s="1" t="n"/>
@@ -75165,21 +75177,21 @@
     </row>
     <row r="3222">
       <c r="A3222" s="1" t="n">
-        <v>9000093</v>
+        <v>9000090</v>
       </c>
       <c r="B3222" s="2" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>휴…</t>
         </is>
       </c>
       <c r="C3222" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Phew...</t>
         </is>
       </c>
       <c r="D3222" s="1" t="inlineStr">
         <is>
-          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
+          <t>코드 · Lobby/LobbyHome.cs:77</t>
         </is>
       </c>
       <c r="E3222" s="1" t="n"/>
@@ -75187,21 +75199,21 @@
     </row>
     <row r="3223">
       <c r="A3223" s="1" t="n">
-        <v>9000094</v>
+        <v>9000091</v>
       </c>
       <c r="B3223" s="2" t="inlineStr">
         <is>
-          <t>찌릿!!</t>
+          <t>찍</t>
         </is>
       </c>
       <c r="C3223" s="2" t="inlineStr">
         <is>
-          <t>ZAP!!</t>
+          <t>Squeak</t>
         </is>
       </c>
       <c r="D3223" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/LobbyHome.cs:161</t>
         </is>
       </c>
       <c r="E3223" s="1" t="n"/>
@@ -75209,21 +75221,21 @@
     </row>
     <row r="3224">
       <c r="A3224" s="1" t="n">
-        <v>9000095</v>
+        <v>9000092</v>
       </c>
       <c r="B3224" s="2" t="inlineStr">
         <is>
-          <t>콰릉!</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="C3224" s="2" t="inlineStr">
         <is>
-          <t>Ka-boom!</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D3224" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:237</t>
+          <t>코드 · Lobby/RunPage.cs:99</t>
         </is>
       </c>
       <c r="E3224" s="1" t="n"/>
@@ -75231,21 +75243,21 @@
     </row>
     <row r="3225">
       <c r="A3225" s="1" t="n">
-        <v>9000096</v>
+        <v>9000093</v>
       </c>
       <c r="B3225" s="2" t="inlineStr">
         <is>
-          <t>냠!</t>
+          <t>잠김</t>
         </is>
       </c>
       <c r="C3225" s="2" t="inlineStr">
         <is>
-          <t>Nom!</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="D3225" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Lobby/RunPage.cs:99, Lobby/RunPage.cs:124</t>
         </is>
       </c>
       <c r="E3225" s="1" t="n"/>
@@ -75253,21 +75265,21 @@
     </row>
     <row r="3226">
       <c r="A3226" s="1" t="n">
-        <v>9000097</v>
+        <v>9000094</v>
       </c>
       <c r="B3226" s="2" t="inlineStr">
         <is>
-          <t>다닥!</t>
+          <t>찌릿!!</t>
         </is>
       </c>
       <c r="C3226" s="2" t="inlineStr">
         <is>
-          <t>Scurry!</t>
+          <t>ZAP!!</t>
         </is>
       </c>
       <c r="D3226" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Action.cs:514</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E3226" s="1" t="n"/>
@@ -75275,21 +75287,21 @@
     </row>
     <row r="3227">
       <c r="A3227" s="1" t="n">
-        <v>9000098</v>
+        <v>9000095</v>
       </c>
       <c r="B3227" s="2" t="inlineStr">
         <is>
-          <t>메리 쥐스마스!</t>
+          <t>콰릉!</t>
         </is>
       </c>
       <c r="C3227" s="2" t="inlineStr">
         <is>
-          <t>Merry Ratmas!</t>
+          <t>Ka-boom!</t>
         </is>
       </c>
       <c r="D3227" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:237</t>
         </is>
       </c>
       <c r="E3227" s="1" t="n"/>
@@ -75297,21 +75309,21 @@
     </row>
     <row r="3228">
       <c r="A3228" s="1" t="n">
-        <v>9000099</v>
+        <v>9000096</v>
       </c>
       <c r="B3228" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~!</t>
+          <t>냠!</t>
         </is>
       </c>
       <c r="C3228" s="2" t="inlineStr">
         <is>
-          <t>Heheh~ thanks for the dono~!</t>
+          <t>Nom!</t>
         </is>
       </c>
       <c r="D3228" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E3228" s="1" t="n"/>
@@ -75319,21 +75331,21 @@
     </row>
     <row r="3229">
       <c r="A3229" s="1" t="n">
-        <v>9000100</v>
+        <v>9000097</v>
       </c>
       <c r="B3229" s="2" t="inlineStr">
         <is>
-          <t>배달 왔습니다~</t>
+          <t>다닥!</t>
         </is>
       </c>
       <c r="C3229" s="2" t="inlineStr">
         <is>
-          <t>Delivery~!</t>
+          <t>Scurry!</t>
         </is>
       </c>
       <c r="D3229" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Passive.cs:171</t>
+          <t>코드 · Rats/Rat.Action.cs:514</t>
         </is>
       </c>
       <c r="E3229" s="1" t="n"/>
@@ -75341,21 +75353,21 @@
     </row>
     <row r="3230">
       <c r="A3230" s="1" t="n">
-        <v>9000101</v>
+        <v>9000098</v>
       </c>
       <c r="B3230" s="2" t="inlineStr">
         <is>
-          <t>백덤블링!</t>
+          <t>메리 쥐스마스!</t>
         </is>
       </c>
       <c r="C3230" s="2" t="inlineStr">
         <is>
-          <t>Backflip!</t>
+          <t>Merry Ratmas!</t>
         </is>
       </c>
       <c r="D3230" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E3230" s="1" t="n"/>
@@ -75363,21 +75375,21 @@
     </row>
     <row r="3231">
       <c r="A3231" s="1" t="n">
-        <v>9000102</v>
+        <v>9000099</v>
       </c>
       <c r="B3231" s="2" t="inlineStr">
         <is>
-          <t>공중제비!</t>
+          <t>흐에~ 후원 감사합니다~!</t>
         </is>
       </c>
       <c r="C3231" s="2" t="inlineStr">
         <is>
-          <t>Somersault!</t>
+          <t>Heheh~ thanks for the dono~!</t>
         </is>
       </c>
       <c r="D3231" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E3231" s="1" t="n"/>
@@ -75385,21 +75397,21 @@
     </row>
     <row r="3232">
       <c r="A3232" s="1" t="n">
-        <v>9000103</v>
+        <v>9000100</v>
       </c>
       <c r="B3232" s="2" t="inlineStr">
         <is>
-          <t>찍-공중회전!</t>
+          <t>배달 왔습니다~</t>
         </is>
       </c>
       <c r="C3232" s="2" t="inlineStr">
         <is>
-          <t>Squeak-flip!</t>
+          <t>Delivery~!</t>
         </is>
       </c>
       <c r="D3232" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:15</t>
+          <t>코드 · Rats/Rat.Passive.cs:171</t>
         </is>
       </c>
       <c r="E3232" s="1" t="n"/>
@@ -75407,21 +75419,21 @@
     </row>
     <row r="3233">
       <c r="A3233" s="1" t="n">
-        <v>9000104</v>
+        <v>9000101</v>
       </c>
       <c r="B3233" s="2" t="inlineStr">
         <is>
-          <t>트리플 악셀!!</t>
+          <t>백덤블링!</t>
         </is>
       </c>
       <c r="C3233" s="2" t="inlineStr">
         <is>
-          <t>TRIPLE AXEL!!</t>
+          <t>Backflip!</t>
         </is>
       </c>
       <c r="D3233" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E3233" s="1" t="n"/>
@@ -75429,21 +75441,21 @@
     </row>
     <row r="3234">
       <c r="A3234" s="1" t="n">
-        <v>9000105</v>
+        <v>9000102</v>
       </c>
       <c r="B3234" s="2" t="inlineStr">
         <is>
-          <t>3회전 성공!</t>
+          <t>공중제비!</t>
         </is>
       </c>
       <c r="C3234" s="2" t="inlineStr">
         <is>
-          <t>Triple spin landed!</t>
+          <t>Somersault!</t>
         </is>
       </c>
       <c r="D3234" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E3234" s="1" t="n"/>
@@ -75451,21 +75463,21 @@
     </row>
     <row r="3235">
       <c r="A3235" s="1" t="n">
-        <v>9000106</v>
+        <v>9000103</v>
       </c>
       <c r="B3235" s="2" t="inlineStr">
         <is>
-          <t>심사위원 전원 10점!</t>
+          <t>찍-공중회전!</t>
         </is>
       </c>
       <c r="C3235" s="2" t="inlineStr">
         <is>
-          <t>Perfect 10s from every judge!</t>
+          <t>Squeak-flip!</t>
         </is>
       </c>
       <c r="D3235" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:16</t>
+          <t>코드 · Rats/Rat.Trick.cs:15</t>
         </is>
       </c>
       <c r="E3235" s="1" t="n"/>
@@ -75473,21 +75485,21 @@
     </row>
     <row r="3236">
       <c r="A3236" s="1" t="n">
-        <v>9000107</v>
+        <v>9000104</v>
       </c>
       <c r="B3236" s="2" t="inlineStr">
         <is>
-          <t>윈드밀!!</t>
+          <t>트리플 악셀!!</t>
         </is>
       </c>
       <c r="C3236" s="2" t="inlineStr">
         <is>
-          <t>WINDMILL!!</t>
+          <t>TRIPLE AXEL!!</t>
         </is>
       </c>
       <c r="D3236" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E3236" s="1" t="n"/>
@@ -75495,21 +75507,21 @@
     </row>
     <row r="3237">
       <c r="A3237" s="1" t="n">
-        <v>9000108</v>
+        <v>9000105</v>
       </c>
       <c r="B3237" s="2" t="inlineStr">
         <is>
-          <t>브레이크 댄스!</t>
+          <t>3회전 성공!</t>
         </is>
       </c>
       <c r="C3237" s="2" t="inlineStr">
         <is>
-          <t>Breakdance!</t>
+          <t>Triple spin landed!</t>
         </is>
       </c>
       <c r="D3237" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E3237" s="1" t="n"/>
@@ -75517,21 +75529,21 @@
     </row>
     <row r="3238">
       <c r="A3238" s="1" t="n">
-        <v>9000109</v>
+        <v>9000106</v>
       </c>
       <c r="B3238" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글 파괴!</t>
+          <t>심사위원 전원 10점!</t>
         </is>
       </c>
       <c r="C3238" s="2" t="inlineStr">
         <is>
-          <t>Spin-to-win destruction!</t>
+          <t>Perfect 10s from every judge!</t>
         </is>
       </c>
       <c r="D3238" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:17</t>
+          <t>코드 · Rats/Rat.Trick.cs:16</t>
         </is>
       </c>
       <c r="E3238" s="1" t="n"/>
@@ -75539,21 +75551,21 @@
     </row>
     <row r="3239">
       <c r="A3239" s="1" t="n">
-        <v>9000110</v>
+        <v>9000107</v>
       </c>
       <c r="B3239" s="2" t="inlineStr">
         <is>
-          <t>쥐 대포알!</t>
+          <t>윈드밀!!</t>
         </is>
       </c>
       <c r="C3239" s="2" t="inlineStr">
         <is>
-          <t>Rat Cannonball!</t>
+          <t>WINDMILL!!</t>
         </is>
       </c>
       <c r="D3239" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E3239" s="1" t="n"/>
@@ -75561,21 +75573,21 @@
     </row>
     <row r="3240">
       <c r="A3240" s="1" t="n">
-        <v>9000111</v>
+        <v>9000108</v>
       </c>
       <c r="B3240" s="2" t="inlineStr">
         <is>
-          <t>데굴데굴!</t>
+          <t>브레이크 댄스!</t>
         </is>
       </c>
       <c r="C3240" s="2" t="inlineStr">
         <is>
-          <t>Roll roll!</t>
+          <t>Breakdance!</t>
         </is>
       </c>
       <c r="D3240" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E3240" s="1" t="n"/>
@@ -75583,21 +75595,21 @@
     </row>
     <row r="3241">
       <c r="A3241" s="1" t="n">
-        <v>9000112</v>
+        <v>9000109</v>
       </c>
       <c r="B3241" s="2" t="inlineStr">
         <is>
-          <t>핀볼 모드!</t>
+          <t>빙글빙글 파괴!</t>
         </is>
       </c>
       <c r="C3241" s="2" t="inlineStr">
         <is>
-          <t>Pinball mode!</t>
+          <t>Spin-to-win destruction!</t>
         </is>
       </c>
       <c r="D3241" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:18</t>
+          <t>코드 · Rats/Rat.Trick.cs:17</t>
         </is>
       </c>
       <c r="E3241" s="1" t="n"/>
@@ -75605,21 +75617,21 @@
     </row>
     <row r="3242">
       <c r="A3242" s="1" t="n">
-        <v>9000113</v>
+        <v>9000110</v>
       </c>
       <c r="B3242" s="2" t="inlineStr">
         <is>
-          <t>쳇바퀴 돌기!!</t>
+          <t>쥐 대포알!</t>
         </is>
       </c>
       <c r="C3242" s="2" t="inlineStr">
         <is>
-          <t>WHEEL SPIN!!</t>
+          <t>Rat Cannonball!</t>
         </is>
       </c>
       <c r="D3242" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E3242" s="1" t="n"/>
@@ -75627,21 +75639,21 @@
     </row>
     <row r="3243">
       <c r="A3243" s="1" t="n">
-        <v>9000114</v>
+        <v>9000111</v>
       </c>
       <c r="B3243" s="2" t="inlineStr">
         <is>
-          <t>빙글빙글~</t>
+          <t>데굴데굴!</t>
         </is>
       </c>
       <c r="C3243" s="2" t="inlineStr">
         <is>
-          <t>Round and round~</t>
+          <t>Roll roll!</t>
         </is>
       </c>
       <c r="D3243" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E3243" s="1" t="n"/>
@@ -75649,21 +75661,21 @@
     </row>
     <row r="3244">
       <c r="A3244" s="1" t="n">
-        <v>9000115</v>
+        <v>9000112</v>
       </c>
       <c r="B3244" s="2" t="inlineStr">
         <is>
-          <t>어지러워!!</t>
+          <t>핀볼 모드!</t>
         </is>
       </c>
       <c r="C3244" s="2" t="inlineStr">
         <is>
-          <t>So DIZZY!!</t>
+          <t>Pinball mode!</t>
         </is>
       </c>
       <c r="D3244" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:19</t>
+          <t>코드 · Rats/Rat.Trick.cs:18</t>
         </is>
       </c>
       <c r="E3244" s="1" t="n"/>
@@ -75671,21 +75683,21 @@
     </row>
     <row r="3245">
       <c r="A3245" s="1" t="n">
-        <v>9000116</v>
+        <v>9000113</v>
       </c>
       <c r="B3245" s="2" t="inlineStr">
         <is>
-          <t>짠! 10.0 · 10.0 · 10.0</t>
+          <t>쳇바퀴 돌기!!</t>
         </is>
       </c>
       <c r="C3245" s="2" t="inlineStr">
         <is>
-          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
+          <t>WHEEL SPIN!!</t>
         </is>
       </c>
       <c r="D3245" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/Rat.Trick.cs:76</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E3245" s="1" t="n"/>
@@ -75693,21 +75705,21 @@
     </row>
     <row r="3246">
       <c r="A3246" s="1" t="n">
-        <v>9000117</v>
+        <v>9000114</v>
       </c>
       <c r="B3246" s="2" t="inlineStr">
         <is>
-          <t>기절!!</t>
+          <t>빙글빙글~</t>
         </is>
       </c>
       <c r="C3246" s="2" t="inlineStr">
         <is>
-          <t>Stunned!!</t>
+          <t>Round and round~</t>
         </is>
       </c>
       <c r="D3246" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:38</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E3246" s="1" t="n"/>
@@ -75715,21 +75727,21 @@
     </row>
     <row r="3247">
       <c r="A3247" s="1" t="n">
-        <v>9000118</v>
+        <v>9000115</v>
       </c>
       <c r="B3247" s="2" t="inlineStr">
         <is>
-          <t>소품이 떨어졌다!</t>
+          <t>어지러워!!</t>
         </is>
       </c>
       <c r="C3247" s="2" t="inlineStr">
         <is>
-          <t>A prop dropped!</t>
+          <t>So DIZZY!!</t>
         </is>
       </c>
       <c r="D3247" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:397</t>
+          <t>코드 · Rats/Rat.Trick.cs:19</t>
         </is>
       </c>
       <c r="E3247" s="1" t="n"/>
@@ -75737,21 +75749,21 @@
     </row>
     <row r="3248">
       <c r="A3248" s="1" t="n">
-        <v>9000119</v>
+        <v>9000116</v>
       </c>
       <c r="B3248" s="2" t="inlineStr">
         <is>
-          <t>조각 +1</t>
+          <t>짠! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="C3248" s="2" t="inlineStr">
         <is>
-          <t>Shard +1</t>
+          <t>Ta-da! 10.0 · 10.0 · 10.0</t>
         </is>
       </c>
       <c r="D3248" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:460</t>
+          <t>코드 · Rats/Rat.Trick.cs:76</t>
         </is>
       </c>
       <c r="E3248" s="1" t="n"/>
@@ -75759,21 +75771,21 @@
     </row>
     <row r="3249">
       <c r="A3249" s="1" t="n">
-        <v>9000120</v>
+        <v>9000117</v>
       </c>
       <c r="B3249" s="2" t="inlineStr">
         <is>
-          <t>{name} 강화! Lv {lv}</t>
+          <t>기절!!</t>
         </is>
       </c>
       <c r="C3249" s="2" t="inlineStr">
         <is>
-          <t>{name} powered up! Lv {lv}</t>
+          <t>Stunned!!</t>
         </is>
       </c>
       <c r="D3249" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:461</t>
+          <t>코드 · Rats/RatManager.cs:38</t>
         </is>
       </c>
       <c r="E3249" s="1" t="n"/>
@@ -75781,21 +75793,21 @@
     </row>
     <row r="3250">
       <c r="A3250" s="1" t="n">
-        <v>9000121</v>
+        <v>9000118</v>
       </c>
       <c r="B3250" s="2" t="inlineStr">
         <is>
-          <t>{grade} 탄생!</t>
+          <t>소품이 떨어졌다!</t>
         </is>
       </c>
       <c r="C3250" s="2" t="inlineStr">
         <is>
-          <t>{grade} born!</t>
+          <t>A prop dropped!</t>
         </is>
       </c>
       <c r="D3250" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:561</t>
+          <t>코드 · Rats/RatManager.cs:397</t>
         </is>
       </c>
       <c r="E3250" s="1" t="n"/>
@@ -75803,21 +75815,21 @@
     </row>
     <row r="3251">
       <c r="A3251" s="1" t="n">
-        <v>9000122</v>
+        <v>9000119</v>
       </c>
       <c r="B3251" s="2" t="inlineStr">
         <is>
-          <t>쌍둥이!</t>
+          <t>조각 +1</t>
         </is>
       </c>
       <c r="C3251" s="2" t="inlineStr">
         <is>
-          <t>Twins!</t>
+          <t>Shard +1</t>
         </is>
       </c>
       <c r="D3251" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:566</t>
+          <t>코드 · Rats/RatManager.cs:460</t>
         </is>
       </c>
       <c r="E3251" s="1" t="n"/>
@@ -75825,21 +75837,21 @@
     </row>
     <row r="3252">
       <c r="A3252" s="1" t="n">
-        <v>9000123</v>
+        <v>9000120</v>
       </c>
       <c r="B3252" s="2" t="inlineStr">
         <is>
-          <t>치즈 운석!</t>
+          <t>{name} 강화! Lv {lv}</t>
         </is>
       </c>
       <c r="C3252" s="2" t="inlineStr">
         <is>
-          <t>Cheese Meteor!</t>
+          <t>{name} powered up! Lv {lv}</t>
         </is>
       </c>
       <c r="D3252" s="1" t="inlineStr">
         <is>
-          <t>코드 · Rats/RatManager.cs:627</t>
+          <t>코드 · Rats/RatManager.cs:461</t>
         </is>
       </c>
       <c r="E3252" s="1" t="n"/>
@@ -75847,21 +75859,21 @@
     </row>
     <row r="3253">
       <c r="A3253" s="1" t="n">
-        <v>9000124</v>
+        <v>9000121</v>
       </c>
       <c r="B3253" s="2" t="inlineStr">
         <is>
-          <t>{floor}층 · {zone}</t>
+          <t>{grade} 탄생!</t>
         </is>
       </c>
       <c r="C3253" s="2" t="inlineStr">
         <is>
-          <t>Floor {floor} · {zone}</t>
+          <t>{grade} born!</t>
         </is>
       </c>
       <c r="D3253" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:561</t>
         </is>
       </c>
       <c r="E3253" s="1" t="n"/>
@@ -75869,21 +75881,21 @@
     </row>
     <row r="3254">
       <c r="A3254" s="1" t="n">
-        <v>9000125</v>
+        <v>9000122</v>
       </c>
       <c r="B3254" s="2" t="inlineStr">
         <is>
-          <t>계단 방 벽을 부숴라!</t>
+          <t>쌍둥이!</t>
         </is>
       </c>
       <c r="C3254" s="2" t="inlineStr">
         <is>
-          <t>Smash the wall to the stairs room!</t>
+          <t>Twins!</t>
         </is>
       </c>
       <c r="D3254" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:187</t>
+          <t>코드 · Rats/RatManager.cs:566</t>
         </is>
       </c>
       <c r="E3254" s="1" t="n"/>
@@ -75891,21 +75903,21 @@
     </row>
     <row r="3255">
       <c r="A3255" s="1" t="n">
-        <v>9000126</v>
+        <v>9000123</v>
       </c>
       <c r="B3255" s="2" t="inlineStr">
         <is>
-          <t>벽 붕괴! 방 확장</t>
+          <t>치즈 운석!</t>
         </is>
       </c>
       <c r="C3255" s="2" t="inlineStr">
         <is>
-          <t>Wall down! Room expanded</t>
+          <t>Cheese Meteor!</t>
         </is>
       </c>
       <c r="D3255" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:332</t>
+          <t>코드 · Rats/RatManager.cs:627</t>
         </is>
       </c>
       <c r="E3255" s="1" t="n"/>
@@ -75913,21 +75925,21 @@
     </row>
     <row r="3256">
       <c r="A3256" s="1" t="n">
-        <v>9000127</v>
+        <v>9000124</v>
       </c>
       <c r="B3256" s="2" t="inlineStr">
         <is>
-          <t>계단 발견!</t>
+          <t>{floor}층 · {zone}</t>
         </is>
       </c>
       <c r="C3256" s="2" t="inlineStr">
         <is>
-          <t>Stairs found!</t>
+          <t>Floor {floor} · {zone}</t>
         </is>
       </c>
       <c r="D3256" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Stage/Minimap.cs:95, Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E3256" s="1" t="n"/>
@@ -75935,21 +75947,21 @@
     </row>
     <row r="3257">
       <c r="A3257" s="1" t="n">
-        <v>9000128</v>
+        <v>9000125</v>
       </c>
       <c r="B3257" s="2" t="inlineStr">
         <is>
-          <t>계단에 닿으면 {next}층으로</t>
+          <t>계단 방 벽을 부숴라!</t>
         </is>
       </c>
       <c r="C3257" s="2" t="inlineStr">
         <is>
-          <t>Touch the stairs to go to Floor {next}</t>
+          <t>Smash the wall to the stairs room!</t>
         </is>
       </c>
       <c r="D3257" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/StageManager.cs:338</t>
+          <t>코드 · Stage/StageManager.cs:187</t>
         </is>
       </c>
       <c r="E3257" s="1" t="n"/>
@@ -75957,21 +75969,21 @@
     </row>
     <row r="3258">
       <c r="A3258" s="1" t="n">
-        <v>9000129</v>
+        <v>9000126</v>
       </c>
       <c r="B3258" s="2" t="inlineStr">
         <is>
-          <t>와르르!!</t>
+          <t>벽 붕괴! 방 확장</t>
         </is>
       </c>
       <c r="C3258" s="2" t="inlineStr">
         <is>
-          <t>Crumble!!</t>
+          <t>Wall down! Room expanded</t>
         </is>
       </c>
       <c r="D3258" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:332</t>
         </is>
       </c>
       <c r="E3258" s="1" t="n"/>
@@ -75979,21 +75991,21 @@
     </row>
     <row r="3259">
       <c r="A3259" s="1" t="n">
-        <v>9000130</v>
+        <v>9000127</v>
       </c>
       <c r="B3259" s="2" t="inlineStr">
         <is>
-          <t>콰광!!</t>
+          <t>계단 발견!</t>
         </is>
       </c>
       <c r="C3259" s="2" t="inlineStr">
         <is>
-          <t>KA-BOOM!!</t>
+          <t>Stairs found!</t>
         </is>
       </c>
       <c r="D3259" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:338</t>
         </is>
       </c>
       <c r="E3259" s="1" t="n"/>
@@ -76001,21 +76013,21 @@
     </row>
     <row r="3260">
       <c r="A3260" s="1" t="n">
-        <v>9000131</v>
+        <v>9000128</v>
       </c>
       <c r="B3260" s="2" t="inlineStr">
         <is>
-          <t>쿠르릉!!</t>
+          <t>계단에 닿으면 {next}층으로</t>
         </is>
       </c>
       <c r="C3260" s="2" t="inlineStr">
         <is>
-          <t>Rumble!!</t>
+          <t>Touch the stairs to go to Floor {next}</t>
         </is>
       </c>
       <c r="D3260" s="1" t="inlineStr">
         <is>
-          <t>코드 · Stage/WallFx.cs:42</t>
+          <t>코드 · Stage/StageManager.cs:338</t>
         </is>
       </c>
       <c r="E3260" s="1" t="n"/>
@@ -76023,25 +76035,91 @@
     </row>
     <row r="3261">
       <c r="A3261" s="1" t="n">
-        <v>9000132</v>
+        <v>9000129</v>
       </c>
       <c r="B3261" s="2" t="inlineStr">
         <is>
-          <t>※ 출발 층은 스킬만으로 다 열리지 않아요 · 층을 클리어해야 더 위에서 출발할 수 있어요 (출동 화면에 안내)</t>
+          <t>와르르!!</t>
         </is>
       </c>
       <c r="C3261" s="2" t="inlineStr">
         <is>
-          <t>※ Skip needs cleared floors too · clear floors to start higher (shown on the Run screen)</t>
+          <t>Crumble!!</t>
         </is>
       </c>
       <c r="D3261" s="1" t="inlineStr">
         <is>
-          <t>코드 · SkillPage.DrawDetail (Stage_Skip 노드)</t>
+          <t>코드 · Stage/WallFx.cs:42</t>
         </is>
       </c>
       <c r="E3261" s="1" t="n"/>
       <c r="F3261" s="1" t="n"/>
+    </row>
+    <row r="3262">
+      <c r="A3262" s="1" t="n">
+        <v>9000130</v>
+      </c>
+      <c r="B3262" s="2" t="inlineStr">
+        <is>
+          <t>콰광!!</t>
+        </is>
+      </c>
+      <c r="C3262" s="2" t="inlineStr">
+        <is>
+          <t>KA-BOOM!!</t>
+        </is>
+      </c>
+      <c r="D3262" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3262" s="1" t="n"/>
+      <c r="F3262" s="1" t="n"/>
+    </row>
+    <row r="3263">
+      <c r="A3263" s="1" t="n">
+        <v>9000131</v>
+      </c>
+      <c r="B3263" s="2" t="inlineStr">
+        <is>
+          <t>쿠르릉!!</t>
+        </is>
+      </c>
+      <c r="C3263" s="2" t="inlineStr">
+        <is>
+          <t>Rumble!!</t>
+        </is>
+      </c>
+      <c r="D3263" s="1" t="inlineStr">
+        <is>
+          <t>코드 · Stage/WallFx.cs:42</t>
+        </is>
+      </c>
+      <c r="E3263" s="1" t="n"/>
+      <c r="F3263" s="1" t="n"/>
+    </row>
+    <row r="3264">
+      <c r="A3264" s="1" t="n">
+        <v>9000132</v>
+      </c>
+      <c r="B3264" s="2" t="inlineStr">
+        <is>
+          <t>※ 출발 층은 스킬만으로 다 열리지 않아요 · 층을 클리어해야 더 위에서 출발할 수 있어요 (출동 화면에 안내)</t>
+        </is>
+      </c>
+      <c r="C3264" s="2" t="inlineStr">
+        <is>
+          <t>※ Skip needs cleared floors too · clear floors to start higher (shown on the Run screen)</t>
+        </is>
+      </c>
+      <c r="D3264" s="1" t="inlineStr">
+        <is>
+          <t>코드 · SkillPage.DrawDetail (Stage_Skip 노드)</t>
+        </is>
+      </c>
+      <c r="E3264" s="1" t="n"/>
+      <c r="F3264" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -2232,7 +2232,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Detective Squeakan</t>
+          <t>Detective Squeaks</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
@@ -2240,8 +2240,16 @@
           <t>쥐 캐릭터 테이블 · Character · character_name · 10078</t>
         </is>
       </c>
-      <c r="E81" s="1" t="n"/>
-      <c r="F81" s="1" t="n"/>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -2983,12 +2991,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>어디선가 본 것 같은 요리사. 치즈 요리만 18가지.</t>
+          <t>치즈 요리만 18가지를 아는 요리사 쥐.</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>A chef you swear you've seen somewhere before. Knows 18 cheese recipes.</t>
+          <t>A chef rat who knows 18 cheese recipes.</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
@@ -2996,8 +3004,16 @@
           <t>쥐 캐릭터 테이블 · Character · character_desc · 10023</t>
         </is>
       </c>
-      <c r="E115" s="1" t="n"/>
-      <c r="F115" s="1" t="n"/>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -3269,12 +3285,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>하수구에서 무술을 배웠다. 피자를 좋아한다.</t>
+          <t>하수구에서 무술을 배웠다. 수리검 대신 해바라기씨를 던진다.</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Learned martial arts in the sewers. Loves pizza.</t>
+          <t>Learned martial arts in the sewers. Throws sunflower seeds instead of shuriken.</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
@@ -3282,8 +3298,16 @@
           <t>쥐 캐릭터 테이블 · Character · character_desc · 10036</t>
         </is>
       </c>
-      <c r="E128" s="1" t="n"/>
-      <c r="F128" s="1" t="n"/>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -3951,12 +3975,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>전기 쥐 코스프레 중인 햄스터. 사실 전기는 등에 멘 건전지에서 나온다.</t>
+          <t>번개 머리띠를 쓰고 전기 흉내를 내는 햄스터. 사실 전기는 등에 멘 건전지에서 나온다.</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>A hamster cosplaying an electric mouse. The zap actually comes from the batteries strapped to its back.</t>
+          <t>A hamster in a lightning headband, pretending to be electric. The zap actually comes from the batteries strapped to its back.</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
@@ -3964,8 +3988,16 @@
           <t>쥐 캐릭터 테이블 · Character · character_desc · 10067</t>
         </is>
       </c>
-      <c r="E159" s="1" t="n"/>
-      <c r="F159" s="1" t="n"/>
+      <c r="E159" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -3973,12 +4005,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>놀이공원 기념품 가게에서 산 동그란 귀 머리띠를 절대 안 벗는다. 자기가 원조라고 우긴다.</t>
+          <t>놀이공원 기념품 가게에서 산 머리띠를 절대 안 벗는다. 퍼레이드만 보이면 맨 앞에 선다.</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Never takes off the round-ear headband from the theme park gift shop. Insists it's the original.</t>
+          <t>Never takes off the headband from the theme park gift shop. Always first in line for the parade.</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
@@ -3986,8 +4018,16 @@
           <t>쥐 캐릭터 테이블 · Character · character_desc · 10068</t>
         </is>
       </c>
-      <c r="E160" s="1" t="n"/>
-      <c r="F160" s="1" t="n"/>
+      <c r="E160" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -4237,12 +4277,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>폭발 마법(이라고 우기는 폭탄)만 배웠다. 하루에 딱 한 발 쏘고 그대로 뻗는다. 안대는 멋으로 찼다.</t>
+          <t>폭탄을 마법이라고 우기는 쥐. 한 번 크게 터뜨리고 나면 기운이 쭉 빠져 뻗는다.</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Only learned Explosion magic (a bomb it swears is magic). Fires exactly one shot a day, then faceplants. The eyepatch is for style.</t>
+          <t>A rat that insists its bomb is magic. After one big blast, it runs out of steam and collapses.</t>
         </is>
       </c>
       <c r="D172" s="1" t="inlineStr">
@@ -4250,8 +4290,16 @@
           <t>쥐 캐릭터 테이블 · Character · character_desc · 10080</t>
         </is>
       </c>
-      <c r="E172" s="1" t="n"/>
-      <c r="F172" s="1" t="n"/>
+      <c r="E172" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F172" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -4369,12 +4417,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>엘사가 연상되는 얼음 마법사 쥐. 때릴 때마다 생명체를 얼린다. 렛잇고를 부르면 동료 쥐들도 덜덜 떤다.</t>
+          <t>얼음 마법을 쓰는 쥐 여왕. 때릴 때마다 생명체를 얼린다. 노래를 부르면 동료 쥐들도 덜덜 떤다.</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>An ice-mage rat with a certain snow-queen vibe. Freezes every creature it hits. When it sings "Rat It Go", even its buddies shiver.</t>
+          <t>An ice-magic rat queen. Freezes every creature it hits. When it sings, even its buddies start shivering.</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
@@ -4382,8 +4430,16 @@
           <t>쥐 캐릭터 테이블 · Character · character_desc · 10086</t>
         </is>
       </c>
-      <c r="E178" s="1" t="n"/>
-      <c r="F178" s="1" t="n"/>
+      <c r="E178" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F178" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -6203,12 +6259,12 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>폭렬 외길</t>
+          <t>폭탄 외길</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Explosion or Bust</t>
+          <t>Bombs Only</t>
         </is>
       </c>
       <c r="D261" s="1" t="inlineStr">
@@ -6216,8 +6272,16 @@
           <t>쥐 캐릭터 테이블 · Skill · skill_name · 20080</t>
         </is>
       </c>
-      <c r="E261" s="1" t="n"/>
-      <c r="F261" s="1" t="n"/>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F261" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -7201,12 +7265,12 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>그림자 분신술</t>
+          <t>그림자 쥐떼</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Shadow Clone Jutsu</t>
+          <t>Shadow Swarm</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr">
@@ -7214,8 +7278,16 @@
           <t>쥐 캐릭터 테이블 · Skill · skill_name · 21036</t>
         </is>
       </c>
-      <c r="E306" s="1" t="n"/>
-      <c r="F306" s="1" t="n"/>
+      <c r="E306" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F306" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -7861,12 +7933,12 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>건전지 백만 볼트</t>
+          <t>건전지 대방전</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Million-Volt Battery</t>
+          <t>Battery Overload</t>
         </is>
       </c>
       <c r="D336" s="1" t="inlineStr">
@@ -7874,8 +7946,16 @@
           <t>쥐 캐릭터 테이블 · Skill · skill_name · 21067</t>
         </is>
       </c>
-      <c r="E336" s="1" t="n"/>
-      <c r="F336" s="1" t="n"/>
+      <c r="E336" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F336" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -10649,12 +10729,12 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>물건에 부딪힐 때 3% 확률로 → 그림자 분신술: 동료 3마리 소환 (6초 동안 함께 난동)</t>
+          <t>물건에 부딪힐 때 3% 확률로 → 그림자 쥐떼: 동료 3마리 소환 (6초 동안 함께 난동)</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>3% chance on object impact → Shadow Clone Jutsu: summons 3 buddies (they rampage together for 6s)</t>
+          <t>3% chance on object impact → Shadow Swarm: summons 3 buddies (they rampage together for 6s)</t>
         </is>
       </c>
       <c r="D462" s="1" t="inlineStr">
@@ -10662,8 +10742,16 @@
           <t>쥐 캐릭터 테이블 · Skill · skill_explain · 21036</t>
         </is>
       </c>
-      <c r="E462" s="1" t="n"/>
-      <c r="F462" s="1" t="n"/>
+      <c r="E462" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F462" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="n">
@@ -11331,12 +11419,12 @@
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>18초마다 → 건전지 백만 볼트: 360° 회전 레이저 (피해 ×8.0)</t>
+          <t>18초마다 → 건전지 대방전: 360° 회전 레이저 (피해 ×8.0)</t>
         </is>
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>Every 18s → Million-Volt Battery: spinning 360° laser (damage ×8.0)</t>
+          <t>Every 18s → Battery Overload: spinning 360° laser (damage ×8.0)</t>
         </is>
       </c>
       <c r="D493" s="1" t="inlineStr">
@@ -11344,8 +11432,16 @@
           <t>쥐 캐릭터 테이블 · Skill · skill_explain · 21067</t>
         </is>
       </c>
-      <c r="E493" s="1" t="n"/>
-      <c r="F493" s="1" t="n"/>
+      <c r="E493" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F493" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="1" t="n">
@@ -12043,12 +12139,12 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>천본앵 난무</t>
+          <t>벚꽃 일섬</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>Thousand Cherry Blossom Slash</t>
+          <t>Cherry Blossom Flash</t>
         </is>
       </c>
       <c r="D525" s="1" t="inlineStr">
@@ -12056,8 +12152,16 @@
           <t>쥐 캐릭터 테이블 · Ultimate · ultimate_name · 30011</t>
         </is>
       </c>
-      <c r="E525" s="1" t="n"/>
-      <c r="F525" s="1" t="n"/>
+      <c r="E525" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F525" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="1" t="n">
@@ -13803,12 +13907,12 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>백만 볼트…! (건전지는 1.5볼트)</t>
+          <t>충전 완료…! (건전지는 1.5볼트)</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
         <is>
-          <t>A million volts...! (Battery: 1.5V)</t>
+          <t>Fully charged...! (Battery: 1.5V)</t>
         </is>
       </c>
       <c r="D605" s="1" t="inlineStr">
@@ -13816,8 +13920,16 @@
           <t>쥐 캐릭터 테이블 · Ultimate · ult_line · 30021</t>
         </is>
       </c>
-      <c r="E605" s="1" t="n"/>
-      <c r="F605" s="1" t="n"/>
+      <c r="E605" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F605" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="1" t="n">
@@ -14089,12 +14201,12 @@
       </c>
       <c r="B618" s="2" t="inlineStr">
         <is>
-          <t>내 이름은 찍구밍! 최강의 폭렬 마법을 다루는 쥐!</t>
+          <t>이 한 방에 전부 건다! 폭탄 마법, 발사!</t>
         </is>
       </c>
       <c r="C618" s="2" t="inlineStr">
         <is>
-          <t>My name is Squeakumin! Wielder of the mightiest Explosion magic!</t>
+          <t>Everything on this one shot! Bomb magic, FIRE!</t>
         </is>
       </c>
       <c r="D618" s="1" t="inlineStr">
@@ -14102,8 +14214,16 @@
           <t>쥐 캐릭터 테이블 · Ultimate · ult_line · 30034</t>
         </is>
       </c>
-      <c r="E618" s="1" t="n"/>
-      <c r="F618" s="1" t="n"/>
+      <c r="E618" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F618" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="1" t="n">
@@ -14842,7 +14962,7 @@
       </c>
       <c r="C652" s="2" t="inlineStr">
         <is>
-          <t>Stairway to heaven~</t>
+          <t>Stairs to heaven~</t>
         </is>
       </c>
       <c r="D652" s="1" t="inlineStr">
@@ -14850,8 +14970,16 @@
           <t>쥐 캐릭터 테이블 · Ult_Caption · text · 30008</t>
         </is>
       </c>
-      <c r="E652" s="1" t="n"/>
-      <c r="F652" s="1" t="n"/>
+      <c r="E652" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F652" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="1" t="n">
@@ -15233,12 +15361,12 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>뇌의 호흡…</t>
+          <t>번개의 기운…</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>Thunder Breathing...</t>
+          <t>Lightning gathers...</t>
         </is>
       </c>
       <c r="D670" s="1" t="inlineStr">
@@ -15246,8 +15374,16 @@
           <t>쥐 캐릭터 테이블 · Ult_Caption · text · 30011</t>
         </is>
       </c>
-      <c r="E670" s="1" t="n"/>
-      <c r="F670" s="1" t="n"/>
+      <c r="E670" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F670" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="1" t="n">
@@ -15255,12 +15391,12 @@
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>제1형…</t>
+          <t>첫 번째 칼…</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>First Form...</t>
+          <t>First strike...</t>
         </is>
       </c>
       <c r="D671" s="1" t="inlineStr">
@@ -15268,8 +15404,16 @@
           <t>쥐 캐릭터 테이블 · Ult_Caption · text · 30011</t>
         </is>
       </c>
-      <c r="E671" s="1" t="n"/>
-      <c r="F671" s="1" t="n"/>
+      <c r="E671" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F671" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="1" t="n">
@@ -15277,12 +15421,12 @@
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>벽력일섬!!</t>
+          <t>번개 일섬!!</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>Thunderclap and Flash!!</t>
+          <t>Lightning Flash!!</t>
         </is>
       </c>
       <c r="D672" s="1" t="inlineStr">
@@ -15290,8 +15434,16 @@
           <t>쥐 캐릭터 테이블 · Ult_Caption · text · 30011</t>
         </is>
       </c>
-      <c r="E672" s="1" t="n"/>
-      <c r="F672" s="1" t="n"/>
+      <c r="E672" s="1" t="inlineStr">
+        <is>
+          <t>번역 완료</t>
+        </is>
+      </c>
+      <c r="F672" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-30 저작권 고침 (사용자 검토)</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="1" t="n">

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -72595,12 +72595,12 @@
       </c>
       <c r="B3103" s="2" t="inlineStr">
         <is>
-          <t>{price} 치즈 · Shift = 10마리 · 꾹 = 연속 · 천장 {pity}</t>
+          <t>{price} 치즈 · Shift 뽑기 · Ctrl 일괄 · 천장 {pity}</t>
         </is>
       </c>
       <c r="C3103" s="2" t="inlineStr">
         <is>
-          <t>{price} cheese · Shift = 10 · Hold = repeat · Pity {pity}</t>
+          <t>{price} cheese · Shift draw · Ctrl all · Pity {pity}</t>
         </is>
       </c>
       <c r="D3103" s="1" t="inlineStr">
@@ -72673,12 +72673,12 @@
       </c>
       <c r="B3106" s="2" t="inlineStr">
         <is>
-          <t>끌었다 놓기 = 발사 · Q 쥐 뽑기 (Shift = 10마리, 꾹 = 연속) · E 증강 뽑기 · F 빠르게 · Space 회수 · R 다시 · Esc 일시정지 · M 음악</t>
+          <t>끌었다 놓기 = 발사 · 왼쪽 Shift 쥐 뽑기 (꾹 = 연속) · 왼쪽 Ctrl 일괄 뽑기 · E 증강 뽑기 · F 빠르게 · Space 회수 · R 다시 · Esc 일시정지 · M 음악</t>
         </is>
       </c>
       <c r="C3106" s="2" t="inlineStr">
         <is>
-          <t>Drag &amp; release = launch · Q rat draw (Shift = 10, hold = repeat) · E augment draw · F fast · Space recall · R restart · Esc pause · M music</t>
+          <t>Drag &amp; release = launch · Left Shift rat draw (hold = repeat) · Left Ctrl draw all · E augment draw · F fast · Space recall · R restart · Esc pause · M music</t>
         </is>
       </c>
       <c r="D3106" s="1" t="inlineStr">

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -72424,7 +72424,7 @@
       </c>
       <c r="E3096" s="1" t="inlineStr">
         <is>
-          <t>번역 완료</t>
+          <t>안 쓰임</t>
         </is>
       </c>
       <c r="F3096" s="1" t="n"/>

--- a/Data_Table/스트링 테이블.xlsx
+++ b/Data_Table/스트링 테이블.xlsx
@@ -72013,14 +72013,14 @@
       </c>
       <c r="B3081" s="2" t="inlineStr">
         <is>
-          <t>쥐를 새총처럼 끌었다 놓으면 가진 쥐가 &lt;b&gt;전부 줄지어&lt;/b&gt; 날아가 연구소 벽돌을 튕기며 깎습니다. 벽돌 숫자 = 남은 체력.
+          <t>쥐를 날리고 싶은 방향으로 끌었다 놓으면 가진 쥐가 &lt;b&gt;전부 줄지어&lt;/b&gt; 날아가 연구소 벽돌을 튕기며 깎습니다. 벽돌 숫자 = 남은 체력.
 처음 바닥에 닿은 쥐 자리에서 다음 발사. 한 턴이 끝나면 벽돌이 한 줄씩 내려오고, &lt;b&gt;바닥에 닿으면 끝&lt;/b&gt;. 받침대는 없어요 — 첫 발사 각도가 전부!
 벽돌을 부수면 치즈 → &lt;b&gt;쥐 뽑기(10 치즈)&lt;/b&gt;로 쥐를 늘리고, 쥐를 재료로 &lt;b&gt;증강 뽑기&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C3081" s="2" t="inlineStr">
         <is>
-          <t>Pull a rat like a slingshot and release — &lt;b&gt;all your rats fly in a line&lt;/b&gt;, bouncing off the lab bricks. Brick number = HP left.
+          <t>Drag toward where you want to aim and release — &lt;b&gt;all your rats fly in a line&lt;/b&gt;, bouncing off the lab bricks. Brick number = HP left.
 The next launch starts where the first rat landed. After each turn the bricks drop one row — &lt;b&gt;if they reach the floor, it's over&lt;/b&gt;. No paddle — the first angle is everything!
 Break bricks for cheese → &lt;b&gt;Rat Draw (10 cheese)&lt;/b&gt; for more rats, then spend rats on &lt;b&gt;Augment Draw&lt;/b&gt;.</t>
         </is>
@@ -72147,12 +72147,12 @@
       </c>
       <c r="B3086" s="2" t="inlineStr">
         <is>
-          <t>경기장 아무 곳이나 끌었다 놓아 발사</t>
+          <t>날리고 싶은 방향으로 끌었다 놓아 발사</t>
         </is>
       </c>
       <c r="C3086" s="2" t="inlineStr">
         <is>
-          <t>Drag anywhere on the field and release to launch</t>
+          <t>Drag toward your target and release to launch</t>
         </is>
       </c>
       <c r="D3086" s="1" t="inlineStr">
@@ -72673,12 +72673,12 @@
       </c>
       <c r="B3106" s="2" t="inlineStr">
         <is>
-          <t>끌었다 놓기 = 발사 · 왼쪽 Shift 쥐 뽑기 (꾹 = 연속) · 왼쪽 Ctrl 일괄 뽑기 · E 증강 뽑기 · F 빠르게 · Space 회수 · R 다시 · Esc 일시정지 · M 음악</t>
+          <t>쏠 방향으로 끌었다 놓기 = 발사 · 왼쪽 Shift 쥐 뽑기 (꾹 = 연속) · 왼쪽 Ctrl 일괄 뽑기 · E 증강 뽑기 · F 빠르게 · Space 회수 · R 다시 · Esc 일시정지 · M 음악</t>
         </is>
       </c>
       <c r="C3106" s="2" t="inlineStr">
         <is>
-          <t>Drag &amp; release = launch · Left Shift rat draw (hold = repeat) · Left Ctrl draw all · E augment draw · F fast · Space recall · R restart · Esc pause · M music</t>
+          <t>Drag toward target &amp; release = launch · Left Shift rat draw (hold = repeat) · Left Ctrl draw all · E augment draw · F fast · Space recall · R restart · Esc pause · M music</t>
         </is>
       </c>
       <c r="D3106" s="1" t="inlineStr">
